--- a/C219B_L10_L11_TestPlan_PV_1A00_added.xlsx
+++ b/C219B_L10_L11_TestPlan_PV_1A00_added.xlsx
@@ -607,13 +607,13 @@
     <xf numFmtId="0" fontId="21" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="13" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="12" fillId="13" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1397,8 +1397,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表格1" displayName="表格1" ref="A1:L106" headerRowCount="1" totalsRowShown="0" headerRowDxfId="44" dataDxfId="43" tableBorderDxfId="42">
-  <autoFilter ref="A1:L106">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表格1" displayName="表格1" ref="A1:L102" headerRowCount="1" totalsRowShown="0" headerRowDxfId="44" dataDxfId="43" tableBorderDxfId="42">
+  <autoFilter ref="A1:L102">
     <filterColumn colId="0" hiddenButton="1" showButton="1"/>
     <filterColumn colId="1" hiddenButton="1" showButton="1"/>
     <filterColumn colId="2" hiddenButton="1" showButton="1"/>
@@ -1455,8 +1455,8 @@
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="表格3" displayName="表格3" ref="A1:G17" headerRowCount="1" totalsRowShown="0" headerRowDxfId="21" tableBorderDxfId="20">
-  <autoFilter ref="A1:G17">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="表格3" displayName="表格3" ref="A1:G16" headerRowCount="1" totalsRowShown="0" headerRowDxfId="21" tableBorderDxfId="20">
+  <autoFilter ref="A1:G16">
     <filterColumn colId="0" hiddenButton="1" showButton="1"/>
     <filterColumn colId="1" hiddenButton="1" showButton="1"/>
     <filterColumn colId="2" hiddenButton="1" showButton="1"/>
@@ -1479,8 +1479,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="表格4" displayName="表格4" ref="A1:L92" headerRowCount="1" totalsRowShown="0" dataDxfId="12">
-  <autoFilter ref="A1:L92">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="表格4" displayName="表格4" ref="A1:L89" headerRowCount="1" totalsRowShown="0" dataDxfId="12">
+  <autoFilter ref="A1:L89">
     <filterColumn colId="0" hiddenButton="1" showButton="1"/>
     <filterColumn colId="1" hiddenButton="1" showButton="1"/>
     <filterColumn colId="2" hiddenButton="1" showButton="1"/>
@@ -6312,7 +6312,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y108"/>
+  <dimension ref="A1:Y104"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
     <col width="5.7109375" customWidth="1" style="77" min="1" max="1"/>
@@ -6993,104 +6993,91 @@
       <c r="K18" s="39" t="n"/>
       <c r="L18" s="51" t="n"/>
     </row>
-    <row r="19" customFormat="1" s="33">
-      <c r="A19" s="81" t="n">
+    <row r="19" ht="15" customFormat="1" customHeight="1" s="33">
+      <c r="A19" s="76" t="n">
         <v>17</v>
       </c>
-      <c r="B19" s="82" t="inlineStr">
-        <is>
-          <t>nic_fw_chk</t>
-        </is>
-      </c>
-      <c r="C19" s="82" t="inlineStr">
-        <is>
-          <t>NIC CX8 FW check</t>
-        </is>
-      </c>
-      <c r="D19" s="83" t="inlineStr">
-        <is>
-          <t>Pass - match; Fail – mismatch</t>
-        </is>
-      </c>
-      <c r="E19" s="83" t="inlineStr">
-        <is>
-          <t>&gt;&gt;&gt; Enable this check only for CX8 SKU</t>
-        </is>
-      </c>
-      <c r="F19" s="84" t="inlineStr">
-        <is>
-          <t>[CMD] mlxfwmanager --query | egrep 'Device Type:|PCI Device Name:|FW|PXE|UEFI'</t>
-        </is>
-      </c>
-      <c r="G19" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="H19" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="I19" s="84" t="n"/>
-      <c r="J19" s="84" t="n"/>
-      <c r="K19" s="85" t="n"/>
-      <c r="L19" s="86" t="n"/>
-    </row>
-    <row r="20" customFormat="1" s="33">
-      <c r="A20" s="81" t="n">
+      <c r="B19" s="43" t="inlineStr">
+        <is>
+          <t>bmc_retimer_fw_chk</t>
+        </is>
+      </c>
+      <c r="C19" s="43" t="inlineStr">
+        <is>
+          <t>Check the HPM retimer version</t>
+        </is>
+      </c>
+      <c r="D19" s="40" t="inlineStr">
+        <is>
+          <t>PASS if decoded version matches exactly.</t>
+        </is>
+      </c>
+      <c r="E19" s="40" t="n"/>
+      <c r="F19" s="75" t="n"/>
+      <c r="G19" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="H19" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="I19" s="55" t="n"/>
+      <c r="J19" s="55" t="n"/>
+      <c r="K19" s="39" t="n"/>
+      <c r="L19" s="51" t="n"/>
+    </row>
+    <row r="20" ht="40.5" customFormat="1" customHeight="1" s="33">
+      <c r="A20" s="76" t="n">
         <v>18</v>
       </c>
-      <c r="B20" s="82" t="inlineStr">
-        <is>
-          <t>[NIC, CX8 IB mode settings]</t>
-        </is>
-      </c>
-      <c r="C20" s="82" t="inlineStr">
-        <is>
-          <t>Check CX8 IB mode settings
-This test item checks whether the CX8 NIC’s firmware is set to IB (InfiniBand) mode and whether the link configuration is correct. The flow is to start the MST tool, find the first NIC, then use mlxconfig to query each setting one by one and compare it against the expected value. If everything matches, the test passes.</t>
-        </is>
-      </c>
-      <c r="D20" s="83" t="n"/>
-      <c r="E20" s="83" t="inlineStr">
-        <is>
-          <t>&gt;&gt;&gt; Enable this check only for CX8 SKU</t>
-        </is>
-      </c>
-      <c r="F20" s="84" t="inlineStr">
-        <is>
-          <t>mst start
-mst status
-mst status | grep -i '/dev/mst/' | awk '{print $1}' | head -n1
-mlxconfig -d /dev/mst/mt4131_pciconf0 query LINK_TYPE_P1 | grep LINK_TYPE_P1
-mlxconfig -d /dev/mst/mt4131_pciconf0 query NUM_OF_PF | grep NUM_OF_PF</t>
-        </is>
-      </c>
-      <c r="G20" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="H20" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="I20" s="84" t="n"/>
-      <c r="J20" s="84" t="n"/>
-      <c r="K20" s="85" t="n"/>
-      <c r="L20" s="86" t="n"/>
-    </row>
-    <row r="21" ht="15" customFormat="1" customHeight="1" s="33">
+      <c r="B20" s="43" t="inlineStr">
+        <is>
+          <t>storage_hdd_info_chk</t>
+        </is>
+      </c>
+      <c r="C20" s="43" t="inlineStr">
+        <is>
+          <t>Enumerates all SATA+NVMe disks, maps each to its expected SF entry via PCIe mapping, and validates Model/Size/Firmware via tools/smartctl -i parsed with SmartCtlParser, with firmware auto-upgrade on mismatch.</t>
+        </is>
+      </c>
+      <c r="D20" s="40" t="inlineStr">
+        <is>
+          <t>PASS if every disk's model, size, and firmware version match its mapped SF expectation (after any allowed firmware upgrade).</t>
+        </is>
+      </c>
+      <c r="E20" s="40" t="inlineStr">
+        <is>
+          <t>On a firmware mismatch with upgrade allowed, if the post-upgrade re-check still doesn't match, reboot and rerun after reboot to re-validate.</t>
+        </is>
+      </c>
+      <c r="F20" s="75" t="n"/>
+      <c r="G20" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="H20" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="I20" s="55" t="n"/>
+      <c r="J20" s="55" t="n"/>
+      <c r="K20" s="39" t="n"/>
+      <c r="L20" s="51" t="n"/>
+    </row>
+    <row r="21" ht="27" customFormat="1" customHeight="1" s="33">
       <c r="A21" s="76" t="n">
         <v>19</v>
       </c>
       <c r="B21" s="43" t="inlineStr">
         <is>
-          <t>bmc_retimer_fw_chk</t>
+          <t>bmc_psu_fw_chk</t>
         </is>
       </c>
       <c r="C21" s="43" t="inlineStr">
         <is>
-          <t>Check the HPM retimer version</t>
+          <t>Check the PSU version</t>
         </is>
       </c>
       <c r="D21" s="40" t="inlineStr">
         <is>
-          <t>PASS if decoded version matches exactly.</t>
+          <t>PASS if current version equals expected. On mismatch, if upgrade is allowed, attempts psu upgrade.</t>
         </is>
       </c>
       <c r="E21" s="40" t="n"/>
@@ -7112,22 +7099,22 @@
       </c>
       <c r="B22" s="43" t="inlineStr">
         <is>
-          <t>storage_hdd_info_chk</t>
+          <t>fpga_gp_cerberus_reharvest_chk</t>
         </is>
       </c>
       <c r="C22" s="43" t="inlineStr">
         <is>
-          <t>Enumerates all SATA+NVMe disks, maps each to its expected SF entry via PCIe mapping, and validates Model/Size/Firmware via tools/smartctl -i parsed with SmartCtlParser, with firmware auto-upgrade on mismatch.</t>
+          <t>Same re-harvest check pattern as the PCIe reharvest checks, but for the GlacierPeak Cerberus controller (uses self.pcie_tool rather than PCIE's own methods, since this lives in the FPGA engine class).</t>
         </is>
       </c>
       <c r="D22" s="40" t="inlineStr">
         <is>
-          <t>PASS if every disk's model, size, and firmware version match its mapped SF expectation (after any allowed firmware upgrade).</t>
+          <t>PASS when the public key matches or re-harvest succeeds. FAIL on pre-work hard error or upload_reharvest() failure.</t>
         </is>
       </c>
       <c r="E22" s="40" t="inlineStr">
         <is>
-          <t>On a firmware mismatch with upgrade allowed, if the post-upgrade re-check still doesn't match, reboot and rerun after reboot to re-validate.</t>
+          <t>A mismatch is not itself a failure, only a trigger for re-harvest.</t>
         </is>
       </c>
       <c r="F22" s="75" t="n"/>
@@ -7142,26 +7129,30 @@
       <c r="K22" s="39" t="n"/>
       <c r="L22" s="51" t="n"/>
     </row>
-    <row r="23" ht="27" customFormat="1" customHeight="1" s="33">
+    <row r="23" ht="40.5" customFormat="1" customHeight="1" s="33">
       <c r="A23" s="76" t="n">
         <v>21</v>
       </c>
       <c r="B23" s="43" t="inlineStr">
         <is>
-          <t>bmc_psu_fw_chk</t>
+          <t>pcie_manticore_reharvest_chk</t>
         </is>
       </c>
       <c r="C23" s="43" t="inlineStr">
         <is>
-          <t>Check the PSU version</t>
+          <t>Checks whether the DC-SCM Manticore controller's provisioned public key still matches the one on file (SF/HKMS), and re-harvests the CSR/certificate if it has drifted.</t>
         </is>
       </c>
       <c r="D23" s="40" t="inlineStr">
         <is>
-          <t>PASS if current version equals expected. On mismatch, if upgrade is allowed, attempts psu upgrade.</t>
-        </is>
-      </c>
-      <c r="E23" s="40" t="n"/>
+          <t>PASS when the public key matches (no re-harvest needed) or re-harvest completes successfully. FAIL if the pre-work step errors out (ret==1) or upload_reharvest() fails.</t>
+        </is>
+      </c>
+      <c r="E23" s="40" t="inlineStr">
+        <is>
+          <t>A mismatch is not itself a failure, only a trigger for re-harvest.</t>
+        </is>
+      </c>
       <c r="F23" s="75" t="n"/>
       <c r="G23" s="55" t="b">
         <v>0</v>
@@ -7180,12 +7171,12 @@
       </c>
       <c r="B24" s="43" t="inlineStr">
         <is>
-          <t>fpga_gp_cerberus_reharvest_chk</t>
+          <t>pcie_tip_reharvest_chk</t>
         </is>
       </c>
       <c r="C24" s="43" t="inlineStr">
         <is>
-          <t>Same re-harvest check pattern as the PCIe reharvest checks, but for the GlacierPeak Cerberus controller (uses self.pcie_tool rather than PCIE's own methods, since this lives in the FPGA engine class).</t>
+          <t>Checks whether the DC-SCM Hydra/TIP controller's provisioned public key still matches the one on file (SF/HKMS), and re-harvests the CSR/certificate if it has drifted.</t>
         </is>
       </c>
       <c r="D24" s="40" t="inlineStr">
@@ -7216,24 +7207,20 @@
       </c>
       <c r="B25" s="43" t="inlineStr">
         <is>
-          <t>pcie_manticore_reharvest_chk</t>
+          <t>tpm_ekey_chk</t>
         </is>
       </c>
       <c r="C25" s="43" t="inlineStr">
         <is>
-          <t>Checks whether the DC-SCM Manticore controller's provisioned public key still matches the one on file (SF/HKMS), and re-harvests the CSR/certificate if it has drifted.</t>
+          <t>Harvests the TPM's Endorsement Key (EK) certificate via tpm2_nvread, computes its SHA-256 hash, and compares against the expected TPMEKHASH value fetched from SF (or a local backup file when run with -no_sf).</t>
         </is>
       </c>
       <c r="D25" s="40" t="inlineStr">
         <is>
-          <t>PASS when the public key matches (no re-harvest needed) or re-harvest completes successfully. FAIL if the pre-work step errors out (ret==1) or upload_reharvest() fails.</t>
-        </is>
-      </c>
-      <c r="E25" s="40" t="inlineStr">
-        <is>
-          <t>A mismatch is not itself a failure, only a trigger for re-harvest.</t>
-        </is>
-      </c>
+          <t>PASS if the locally computed SHA-256 (base64) of the EK cert CSR equals the TPMEKHASH value from SF/backup.</t>
+        </is>
+      </c>
+      <c r="E25" s="40" t="n"/>
       <c r="F25" s="75" t="n"/>
       <c r="G25" s="55" t="b">
         <v>0</v>
@@ -7246,89 +7233,21 @@
       <c r="K25" s="39" t="n"/>
       <c r="L25" s="51" t="n"/>
     </row>
-    <row r="26" ht="40.5" customFormat="1" customHeight="1" s="33">
-      <c r="A26" s="76" t="n">
+    <row r="26" customFormat="1" s="33">
+      <c r="A26" s="81" t="n">
         <v>24</v>
       </c>
-      <c r="B26" s="43" t="inlineStr">
-        <is>
-          <t>pcie_tip_reharvest_chk</t>
-        </is>
-      </c>
-      <c r="C26" s="43" t="inlineStr">
-        <is>
-          <t>Checks whether the DC-SCM Hydra/TIP controller's provisioned public key still matches the one on file (SF/HKMS), and re-harvests the CSR/certificate if it has drifted.</t>
-        </is>
-      </c>
-      <c r="D26" s="40" t="inlineStr">
-        <is>
-          <t>PASS when the public key matches or re-harvest succeeds. FAIL on pre-work hard error or upload_reharvest() failure.</t>
-        </is>
-      </c>
-      <c r="E26" s="40" t="inlineStr">
-        <is>
-          <t>A mismatch is not itself a failure, only a trigger for re-harvest.</t>
-        </is>
-      </c>
-      <c r="F26" s="75" t="n"/>
-      <c r="G26" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="H26" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="I26" s="55" t="n"/>
-      <c r="J26" s="55" t="n"/>
-      <c r="K26" s="39" t="n"/>
-      <c r="L26" s="51" t="n"/>
-    </row>
-    <row r="27" ht="40.5" customFormat="1" customHeight="1" s="33">
-      <c r="A27" s="76" t="n">
-        <v>25</v>
-      </c>
-      <c r="B27" s="43" t="inlineStr">
-        <is>
-          <t>tpm_ekey_chk</t>
-        </is>
-      </c>
-      <c r="C27" s="43" t="inlineStr">
-        <is>
-          <t>Harvests the TPM's Endorsement Key (EK) certificate via tpm2_nvread, computes its SHA-256 hash, and compares against the expected TPMEKHASH value fetched from SF (or a local backup file when run with -no_sf).</t>
-        </is>
-      </c>
-      <c r="D27" s="40" t="inlineStr">
-        <is>
-          <t>PASS if the locally computed SHA-256 (base64) of the EK cert CSR equals the TPMEKHASH value from SF/backup.</t>
-        </is>
-      </c>
-      <c r="E27" s="40" t="n"/>
-      <c r="F27" s="75" t="n"/>
-      <c r="G27" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="H27" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="I27" s="55" t="n"/>
-      <c r="J27" s="55" t="n"/>
-      <c r="K27" s="39" t="n"/>
-      <c r="L27" s="51" t="n"/>
-    </row>
-    <row r="28" customFormat="1" s="33">
-      <c r="A28" s="81" t="n">
-        <v>26</v>
-      </c>
-      <c r="B28" s="82" t="inlineStr">
+      <c r="B26" s="82" t="inlineStr">
         <is>
           <t>rm_powershelf_fw_chk</t>
         </is>
       </c>
-      <c r="C28" s="82" t="inlineStr">
+      <c r="C26" s="82" t="inlineStr">
         <is>
           <t>Check the PSU firmware version on the power shelf via R-SCM for the current UUT. This function only performs the check on master nodes.</t>
         </is>
       </c>
-      <c r="D28" s="83" t="inlineStr">
+      <c r="D26" s="83" t="inlineStr">
         <is>
           <t>- Pass:
 - UUT is a master node.
@@ -7340,7 +7259,7 @@
 - Firmware version mismatch and auto-upgrade fails.</t>
         </is>
       </c>
-      <c r="E28" s="83" t="inlineStr">
+      <c r="E26" s="83" t="inlineStr">
         <is>
           <t>- Only master nodes will perform the check.
 - Only master nodes in pretest station will perform the upgrade if mismatch
@@ -7348,7 +7267,7 @@
 (Master Only)</t>
         </is>
       </c>
-      <c r="F28" s="84" t="inlineStr">
+      <c r="F26" s="84" t="inlineStr">
         <is>
           <t>[Check powershelf firmware version]
 show powershelf psu info -s {INDEX}
@@ -7369,118 +7288,118 @@
 -       rscm_psu_upgrade = set powershelf psu update -s {INDEX} -f {FILE}</t>
         </is>
       </c>
-      <c r="G28" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="H28" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="I28" s="84" t="n"/>
-      <c r="J28" s="84" t="n"/>
-      <c r="K28" s="85" t="n"/>
-      <c r="L28" s="86" t="n"/>
-    </row>
-    <row r="29" ht="135" customFormat="1" customHeight="1" s="33">
-      <c r="A29" s="76" t="n">
-        <v>27</v>
-      </c>
-      <c r="B29" s="43" t="inlineStr">
+      <c r="G26" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="H26" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="I26" s="84" t="n"/>
+      <c r="J26" s="84" t="n"/>
+      <c r="K26" s="85" t="n"/>
+      <c r="L26" s="86" t="n"/>
+    </row>
+    <row r="27" ht="135" customFormat="1" customHeight="1" s="33">
+      <c r="A27" s="76" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" s="43" t="inlineStr">
         <is>
           <t>pcie_manticore_provision</t>
         </is>
       </c>
-      <c r="C29" s="43" t="inlineStr">
+      <c r="C27" s="43" t="inlineStr">
         <is>
           <t>One-time factory provisioning of the DC-SCM Manticore (Cerberus v2) security chip's certificate chain — Device ID, Root CA, and Intermediate CA certificates are fused into the chip via cerberus_utility importsignedcert.</t>
         </is>
       </c>
-      <c r="D29" s="40" t="inlineStr">
+      <c r="D27" s="40" t="inlineStr">
         <is>
           <t>PASS if the chip already shows a complete signed certificate chain, or if all three cerberus_fuse() calls succeed and a post-fuse is_provision check confirms completion.</t>
         </is>
       </c>
-      <c r="E29" s="40" t="inlineStr">
+      <c r="E27" s="40" t="inlineStr">
         <is>
           <t>- Security/identity-relevant, one-time step. Uses is_provision("Manticore") to skip entirely if already provisioned (idempotent). If the public key harvested from the chip (CSR) doesn't match what SF (the factory server / key-management system) has on file, it is treated as a "re-harvest" condition.
 - Certificate fusing order is Device ID (HWKey1, cert index 0/file index 1) → Root CA (HWKey3, cert index 1/file index 3) → Intermediate CA (HWKey2, cert index 2/file index 2). 
 - cerberus_fuse() treats IPMI return code 74 ("Certificate provisioning locked") as a soft-success, not a failure, since re-fusing an already-locked slot is expected on retries.</t>
         </is>
       </c>
-      <c r="F29" s="75" t="n"/>
-      <c r="G29" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="H29" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="I29" s="55" t="n"/>
-      <c r="J29" s="55" t="n"/>
-      <c r="K29" s="39" t="n"/>
-      <c r="L29" s="51" t="n"/>
-    </row>
-    <row r="30" ht="40.5" customFormat="1" customHeight="1" s="33">
-      <c r="A30" s="76" t="n">
-        <v>28</v>
-      </c>
-      <c r="B30" s="43" t="inlineStr">
+      <c r="F27" s="75" t="n"/>
+      <c r="G27" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="H27" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="I27" s="55" t="n"/>
+      <c r="J27" s="55" t="n"/>
+      <c r="K27" s="39" t="n"/>
+      <c r="L27" s="51" t="n"/>
+    </row>
+    <row r="28" ht="40.5" customFormat="1" customHeight="1" s="33">
+      <c r="A28" s="76" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" s="43" t="inlineStr">
         <is>
           <t>pcie_tip_provision</t>
         </is>
       </c>
-      <c r="C30" s="43" t="inlineStr">
+      <c r="C28" s="43" t="inlineStr">
         <is>
           <t>Same one-time provisioning flow as pcie_manticore_provision, but for the DC-SCM Hydra/TIP security chip (BMC-side security control introduced with M1120).</t>
         </is>
       </c>
-      <c r="D30" s="40" t="inlineStr">
+      <c r="D28" s="40" t="inlineStr">
         <is>
           <t>Identical logic/criteria to pcie_manticore_provision, keyed on component name "Hydra".</t>
         </is>
       </c>
-      <c r="E30" s="40" t="inlineStr">
+      <c r="E28" s="40" t="inlineStr">
         <is>
           <t>Security/identity-relevant, one-time step. Structurally identical to Manticore provisioning, same 3-cert fuse order Device ID → Root CA → Intermediate CA).</t>
         </is>
       </c>
-      <c r="F30" s="75" t="n"/>
-      <c r="G30" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="H30" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="I30" s="55" t="n"/>
-      <c r="J30" s="55" t="n"/>
-      <c r="K30" s="39" t="n"/>
-      <c r="L30" s="51" t="n"/>
-    </row>
-    <row r="31" customFormat="1" s="33">
-      <c r="A31" s="81" t="n">
-        <v>29</v>
-      </c>
-      <c r="B31" s="82" t="inlineStr">
+      <c r="F28" s="75" t="n"/>
+      <c r="G28" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="H28" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="I28" s="55" t="n"/>
+      <c r="J28" s="55" t="n"/>
+      <c r="K28" s="39" t="n"/>
+      <c r="L28" s="51" t="n"/>
+    </row>
+    <row r="29" customFormat="1" s="33">
+      <c r="A29" s="81" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" s="82" t="inlineStr">
         <is>
           <t>pcie_tip_pcd_chk</t>
         </is>
       </c>
-      <c r="C31" s="82" t="inlineStr">
+      <c r="C29" s="82" t="inlineStr">
         <is>
           <t>BMC TIP - PCD ID and platform check</t>
         </is>
       </c>
-      <c r="D31" s="83" t="inlineStr">
+      <c r="D29" s="83" t="inlineStr">
         <is>
           <t>Pass - return 0; Fail - return 1</t>
         </is>
       </c>
-      <c r="E31" s="83" t="inlineStr">
+      <c r="E29" s="83" t="inlineStr">
         <is>
           <t>&gt;&gt;&gt; EV CRD does not define it.
 &gt;&gt;&gt; Remove grey remark for pcie_tip_pcd_chk and pcie_tip_cfm_chk since those need to be reay in DV.  However, no CFM/PCD function at this moment.  Create bug in advance during DV M1/M3 Diag dev. and validation.
 &gt;&gt;&gt;Task #2568301</t>
         </is>
       </c>
-      <c r="F31" s="84" t="inlineStr">
+      <c r="F29" s="84" t="inlineStr">
         <is>
           <t>[Check PCD Version ID]
 {CERBERUS_UTILITY} -e 0x0c pcdid 0
@@ -7494,44 +7413,44 @@
 ipmitool mc reset cold</t>
         </is>
       </c>
-      <c r="G31" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="H31" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="I31" s="84" t="n"/>
-      <c r="J31" s="84" t="n"/>
-      <c r="K31" s="85" t="n"/>
-      <c r="L31" s="86" t="n"/>
-    </row>
-    <row r="32" customFormat="1" s="33">
-      <c r="A32" s="81" t="n">
-        <v>30</v>
-      </c>
-      <c r="B32" s="82" t="inlineStr">
+      <c r="G29" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="H29" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="I29" s="84" t="n"/>
+      <c r="J29" s="84" t="n"/>
+      <c r="K29" s="85" t="n"/>
+      <c r="L29" s="86" t="n"/>
+    </row>
+    <row r="30" customFormat="1" s="33">
+      <c r="A30" s="81" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" s="82" t="inlineStr">
         <is>
           <t>pcie_tip_cfm_chk</t>
         </is>
       </c>
-      <c r="C32" s="82" t="inlineStr">
+      <c r="C30" s="82" t="inlineStr">
         <is>
           <t>Get DC-SCM TIP Version ID and Platform ID</t>
         </is>
       </c>
-      <c r="D32" s="83" t="inlineStr">
+      <c r="D30" s="83" t="inlineStr">
         <is>
           <t>Pass - return 0; Fail - return 1</t>
         </is>
       </c>
-      <c r="E32" s="83" t="inlineStr">
+      <c r="E30" s="83" t="inlineStr">
         <is>
           <t>&gt;&gt;&gt; EV CRD does not define it.
 &gt;&gt;&gt; Remove grey remark for pcie_tip_pcd_chk and pcie_tip_cfm_chk since those need to be reay in DV.  However, no CFM/PCD function at this moment.  Create bug in advance during DV M1/M3 Diag dev. and validation.
 &gt;&gt;&gt;Task #2568301</t>
         </is>
       </c>
-      <c r="F32" s="84" t="inlineStr">
+      <c r="F30" s="84" t="inlineStr">
         <is>
           <t>[Check CFM Version ID]
 {CERBERUS_UTILITY} -e 0x0c cfmid 0 0
@@ -7547,75 +7466,75 @@
 {CERBERUS_UTILITY} -e 0x0c compstate</t>
         </is>
       </c>
-      <c r="G32" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="H32" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="I32" s="84" t="n"/>
-      <c r="J32" s="84" t="n"/>
-      <c r="K32" s="85" t="n"/>
-      <c r="L32" s="86" t="n"/>
-    </row>
-    <row r="33" ht="135" customFormat="1" customHeight="1" s="33">
-      <c r="A33" s="76" t="n">
-        <v>31</v>
-      </c>
-      <c r="B33" s="43" t="inlineStr">
+      <c r="G30" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="H30" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="I30" s="84" t="n"/>
+      <c r="J30" s="84" t="n"/>
+      <c r="K30" s="85" t="n"/>
+      <c r="L30" s="86" t="n"/>
+    </row>
+    <row r="31" ht="135" customFormat="1" customHeight="1" s="33">
+      <c r="A31" s="76" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" s="43" t="inlineStr">
         <is>
           <t>fpga_gp_cerberus_provision</t>
         </is>
       </c>
-      <c r="C33" s="43" t="inlineStr">
+      <c r="C31" s="43" t="inlineStr">
         <is>
           <t>One-time provisioning of the GlacierPeak's own Cerberus security chip (distinct from Agilex slots above) — fuses Device ID/Root CA/Intermediate CA certs via a UART/SSH session directly into the GlacierPeak SoC console.</t>
         </is>
       </c>
-      <c r="D33" s="40" t="inlineStr">
+      <c r="D31" s="40" t="inlineStr">
         <is>
           <t>PASS if pcie_tool.is_provision("Cerberus") already shows complete, or if all three certs are fused successfully and a post-check confirms completion.</t>
         </is>
       </c>
-      <c r="E33" s="40" t="inlineStr">
+      <c r="E31" s="40" t="inlineStr">
         <is>
           <t>Two very different code paths: 
 - for prj_stage == "M5" it SFTP-uploads the three HWKEY .bin files to the BMC, then uses a shell command list over usb0 (10.235.100.0/31 point-to-point link) with scp -P 2200 to pull each key onto the GlacierPeak SoC and run cerberus_utility importsignedcert locally there — all three fuse commands (root CA idx 1, intermediate idx 2, device ID idx 0) run under a single rscm_lock.
 - For other stages it uses a raw pxssh session direct to the GlacierPeak SoC on port 8295 (user admin/admin), with up to 2 retries and a 90s backoff between attempts if the SoC is "busy". HWKey files are deleted from the BMC after fusing in both paths.</t>
         </is>
       </c>
-      <c r="F33" s="75" t="n"/>
-      <c r="G33" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="H33" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="I33" s="55" t="n"/>
-      <c r="J33" s="55" t="n"/>
-      <c r="K33" s="39" t="n"/>
-      <c r="L33" s="51" t="n"/>
-    </row>
-    <row r="34" ht="121.5" customFormat="1" customHeight="1" s="33">
-      <c r="A34" s="76" t="n">
-        <v>32</v>
-      </c>
-      <c r="B34" s="43" t="inlineStr">
+      <c r="F31" s="75" t="n"/>
+      <c r="G31" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="H31" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="I31" s="55" t="n"/>
+      <c r="J31" s="55" t="n"/>
+      <c r="K31" s="39" t="n"/>
+      <c r="L31" s="51" t="n"/>
+    </row>
+    <row r="32" ht="121.5" customFormat="1" customHeight="1" s="33">
+      <c r="A32" s="76" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" s="43" t="inlineStr">
         <is>
           <t>fpga_gp_agilex_provision</t>
         </is>
       </c>
-      <c r="C34" s="43" t="inlineStr">
+      <c r="C32" s="43" t="inlineStr">
         <is>
           <t>One-time provisioning of the GlacierPeak Agilex FPGA's two certificate slots via the fpgasec tool — slot 0 for "Intel IPCS" (Agilex_mfg) and slot 1 for "Microsoft" (Agilex_msft), each independently skippable if already provisioned.</t>
         </is>
       </c>
-      <c r="D34" s="40" t="inlineStr">
+      <c r="D32" s="40" t="inlineStr">
         <is>
           <t>PASS if both slot0 and slot1 report provisioned after the flow (checked via _is_gp_agilex_provision). FAIL if the fpgasec_{ver} tool is missing, cert files can't be obtained/uploaded, -setCertificate fails, or the final status check still shows either slot unprovisioned.</t>
         </is>
       </c>
-      <c r="E34" s="40" t="inlineStr">
+      <c r="E32" s="40" t="inlineStr">
         <is>
           <t>- Security/identity-relevant, one-time step, M3-only. 
 - Unlike the Manticore/TIP flow this checks each slot independently — a partially-provisioned board (e.g. slot0 done, slot1 not) only provisions the missing slot. 
@@ -7624,6 +7543,78 @@
 - After both slots are set, it resets the FPGA and sleeps 300s before the final confirmation check.</t>
         </is>
       </c>
+      <c r="F32" s="75" t="n"/>
+      <c r="G32" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="H32" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="I32" s="55" t="n"/>
+      <c r="J32" s="55" t="n"/>
+      <c r="K32" s="39" t="n"/>
+      <c r="L32" s="51" t="n"/>
+    </row>
+    <row r="33" ht="40.5" customFormat="1" customHeight="1" s="33">
+      <c r="A33" s="76" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" s="43" t="inlineStr">
+        <is>
+          <t>uut_ac_cycle</t>
+        </is>
+      </c>
+      <c r="C33" s="43" t="inlineStr">
+        <is>
+          <t>AC power-cycle using an OEM raw IPMI command (rather than a standard power-control command)</t>
+        </is>
+      </c>
+      <c r="D33" s="40" t="inlineStr">
+        <is>
+          <t>PASS if the AC power-cycle execute successfully.</t>
+        </is>
+      </c>
+      <c r="E33" s="40" t="inlineStr">
+        <is>
+          <t>If a FW update is performed and an AC power cycle is required for the update to take effect, this test item will be triggered. Otherwise, this test item will be skipped.</t>
+        </is>
+      </c>
+      <c r="F33" s="75" t="n"/>
+      <c r="G33" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="H33" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="I33" s="55" t="n"/>
+      <c r="J33" s="55" t="n"/>
+      <c r="K33" s="39" t="n"/>
+      <c r="L33" s="51" t="n"/>
+    </row>
+    <row r="34" ht="15" customFormat="1" customHeight="1" s="33">
+      <c r="A34" s="76" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" s="43" t="inlineStr">
+        <is>
+          <t>ccr_switch_chk</t>
+        </is>
+      </c>
+      <c r="C34" s="43" t="inlineStr">
+        <is>
+          <t>Check and show switch config</t>
+        </is>
+      </c>
+      <c r="D34" s="40" t="inlineStr">
+        <is>
+          <t>Pass - return 0; Fail - return 1</t>
+        </is>
+      </c>
+      <c r="E34" s="40" t="inlineStr">
+        <is>
+          <t>only applies to the master blade</t>
+        </is>
+      </c>
       <c r="F34" s="75" t="n"/>
       <c r="G34" s="55" t="b">
         <v>0</v>
@@ -7636,30 +7627,18 @@
       <c r="K34" s="39" t="n"/>
       <c r="L34" s="51" t="n"/>
     </row>
-    <row r="35" ht="40.5" customFormat="1" customHeight="1" s="33">
+    <row r="35" ht="15" customFormat="1" customHeight="1" s="33">
       <c r="A35" s="76" t="n">
         <v>33</v>
       </c>
       <c r="B35" s="43" t="inlineStr">
         <is>
-          <t>uut_ac_cycle</t>
-        </is>
-      </c>
-      <c r="C35" s="43" t="inlineStr">
-        <is>
-          <t>AC power-cycle using an OEM raw IPMI command (rather than a standard power-control command)</t>
-        </is>
-      </c>
-      <c r="D35" s="40" t="inlineStr">
-        <is>
-          <t>PASS if the AC power-cycle execute successfully.</t>
-        </is>
-      </c>
-      <c r="E35" s="40" t="inlineStr">
-        <is>
-          <t>If a FW update is performed and an AC power cycle is required for the update to take effect, this test item will be triggered. Otherwise, this test item will be skipped.</t>
-        </is>
-      </c>
+          <t>set_ssd_spf_mode</t>
+        </is>
+      </c>
+      <c r="C35" s="43" t="n"/>
+      <c r="D35" s="40" t="n"/>
+      <c r="E35" s="40" t="n"/>
       <c r="F35" s="75" t="n"/>
       <c r="G35" s="55" t="b">
         <v>0</v>
@@ -7672,28 +7651,28 @@
       <c r="K35" s="39" t="n"/>
       <c r="L35" s="51" t="n"/>
     </row>
-    <row r="36" ht="15" customFormat="1" customHeight="1" s="33">
+    <row r="36" ht="27" customFormat="1" customHeight="1" s="33">
       <c r="A36" s="76" t="n">
         <v>34</v>
       </c>
       <c r="B36" s="43" t="inlineStr">
         <is>
-          <t>ccr_switch_chk</t>
+          <t>bmc_sel_clear</t>
         </is>
       </c>
       <c r="C36" s="43" t="inlineStr">
         <is>
-          <t>Check and show switch config</t>
+          <t>Clear BMC System Event Log (SEL) and verify it is cleared correctly.</t>
         </is>
       </c>
       <c r="D36" s="40" t="inlineStr">
         <is>
-          <t>Pass - return 0; Fail - return 1</t>
+          <t>SEL clear command executes successfully and log ID changes after clear.</t>
         </is>
       </c>
       <c r="E36" s="40" t="inlineStr">
         <is>
-          <t>only applies to the master blade</t>
+          <t>Logs SEL before clearing for traceability; verifies clear status by comparing log ID.</t>
         </is>
       </c>
       <c r="F36" s="75" t="n"/>
@@ -7708,29 +7687,47 @@
       <c r="K36" s="39" t="n"/>
       <c r="L36" s="51" t="n"/>
     </row>
-    <row r="37" ht="15" customFormat="1" customHeight="1" s="33">
-      <c r="A37" s="76" t="n">
+    <row r="37" customFormat="1" s="33">
+      <c r="A37" s="81" t="n">
         <v>35</v>
       </c>
-      <c r="B37" s="43" t="inlineStr">
-        <is>
-          <t>set_ssd_spf_mode</t>
-        </is>
-      </c>
-      <c r="C37" s="43" t="n"/>
-      <c r="D37" s="40" t="n"/>
-      <c r="E37" s="40" t="n"/>
-      <c r="F37" s="75" t="n"/>
-      <c r="G37" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="H37" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="I37" s="55" t="n"/>
-      <c r="J37" s="55" t="n"/>
-      <c r="K37" s="39" t="n"/>
-      <c r="L37" s="51" t="n"/>
+      <c r="B37" s="82" t="inlineStr">
+        <is>
+          <t>bmc_boot_sel_check</t>
+        </is>
+      </c>
+      <c r="C37" s="82" t="inlineStr">
+        <is>
+          <t>Verify BMC SEL after UUT boot (System Event Log) events during testing to ensure no unexpected events have occurred.</t>
+        </is>
+      </c>
+      <c r="D37" s="83" t="inlineStr">
+        <is>
+          <t>SEL event counts should not exceed the defined thresholds based on testing duration.</t>
+        </is>
+      </c>
+      <c r="E37" s="83" t="inlineStr">
+        <is>
+          <t>Fail log will be saved in project folder if abnormal events are detected.</t>
+        </is>
+      </c>
+      <c r="F37" s="84" t="inlineStr">
+        <is>
+          <t>[Get BMC SEL Log]
+CMD: ipmitool sel elist -v &gt; sel.log
+Parse the sel.log and compare with allowed list</t>
+        </is>
+      </c>
+      <c r="G37" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="H37" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="I37" s="84" t="n"/>
+      <c r="J37" s="84" t="n"/>
+      <c r="K37" s="85" t="n"/>
+      <c r="L37" s="86" t="n"/>
     </row>
     <row r="38" ht="27" customFormat="1" customHeight="1" s="33">
       <c r="A38" s="76" t="n">
@@ -7738,22 +7735,22 @@
       </c>
       <c r="B38" s="43" t="inlineStr">
         <is>
-          <t>bmc_sel_clear</t>
+          <t>bmc_sdr_chk</t>
         </is>
       </c>
       <c r="C38" s="43" t="inlineStr">
         <is>
-          <t>Clear BMC System Event Log (SEL) and verify it is cleared correctly.</t>
+          <t>Verify BMC Sensor Data Records (SDR) by checking sensor list output and filtering unexpected entries.</t>
         </is>
       </c>
       <c r="D38" s="40" t="inlineStr">
         <is>
-          <t>SEL clear command executes successfully and log ID changes after clear.</t>
+          <t>No unexpected or unmasked SDR entries found in BMCSDR.log.</t>
         </is>
       </c>
       <c r="E38" s="40" t="inlineStr">
         <is>
-          <t>Logs SEL before clearing for traceability; verifies clear status by comparing log ID.</t>
+          <t>Test fails if filtered output is not empty.</t>
         </is>
       </c>
       <c r="F38" s="75" t="n"/>
@@ -7768,47 +7765,41 @@
       <c r="K38" s="39" t="n"/>
       <c r="L38" s="51" t="n"/>
     </row>
-    <row r="39" customFormat="1" s="33">
-      <c r="A39" s="81" t="n">
+    <row r="39" ht="27" customFormat="1" customHeight="1" s="33">
+      <c r="A39" s="76" t="n">
         <v>37</v>
       </c>
-      <c r="B39" s="82" t="inlineStr">
-        <is>
-          <t>bmc_boot_sel_check</t>
-        </is>
-      </c>
-      <c r="C39" s="82" t="inlineStr">
-        <is>
-          <t>Verify BMC SEL after UUT boot (System Event Log) events during testing to ensure no unexpected events have occurred.</t>
-        </is>
-      </c>
-      <c r="D39" s="83" t="inlineStr">
-        <is>
-          <t>SEL event counts should not exceed the defined thresholds based on testing duration.</t>
-        </is>
-      </c>
-      <c r="E39" s="83" t="inlineStr">
-        <is>
-          <t>Fail log will be saved in project folder if abnormal events are detected.</t>
-        </is>
-      </c>
-      <c r="F39" s="84" t="inlineStr">
-        <is>
-          <t>[Get BMC SEL Log]
-CMD: ipmitool sel elist -v &gt; sel.log
-Parse the sel.log and compare with allowed list</t>
-        </is>
-      </c>
-      <c r="G39" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="H39" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="I39" s="84" t="n"/>
-      <c r="J39" s="84" t="n"/>
-      <c r="K39" s="85" t="n"/>
-      <c r="L39" s="86" t="n"/>
+      <c r="B39" s="43" t="inlineStr">
+        <is>
+          <t>uut_dmesg_chk</t>
+        </is>
+      </c>
+      <c r="C39" s="43" t="inlineStr">
+        <is>
+          <t>Check UUT dmesg log for unexpected error messages and record PCI device status.</t>
+        </is>
+      </c>
+      <c r="D39" s="40" t="inlineStr">
+        <is>
+          <t>No unmasked error messages found in dmesg and all expected messages are properly filtered.</t>
+        </is>
+      </c>
+      <c r="E39" s="40" t="inlineStr">
+        <is>
+          <t>Filter list (filter_list.csv) and error map (err_map.ini) are required for filtering and mapping errors.</t>
+        </is>
+      </c>
+      <c r="F39" s="75" t="n"/>
+      <c r="G39" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="H39" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="I39" s="55" t="n"/>
+      <c r="J39" s="55" t="n"/>
+      <c r="K39" s="39" t="n"/>
+      <c r="L39" s="51" t="n"/>
     </row>
     <row r="40" ht="27" customFormat="1" customHeight="1" s="33">
       <c r="A40" s="76" t="n">
@@ -7816,24 +7807,20 @@
       </c>
       <c r="B40" s="43" t="inlineStr">
         <is>
-          <t>bmc_sdr_chk</t>
+          <t>uut_syslog_chk</t>
         </is>
       </c>
       <c r="C40" s="43" t="inlineStr">
         <is>
-          <t>Verify BMC Sensor Data Records (SDR) by checking sensor list output and filtering unexpected entries.</t>
+          <t>Check and record UUT system log (syslog/messages) to ensure no unexpected errors.</t>
         </is>
       </c>
       <c r="D40" s="40" t="inlineStr">
         <is>
-          <t>No unexpected or unmasked SDR entries found in BMCSDR.log.</t>
-        </is>
-      </c>
-      <c r="E40" s="40" t="inlineStr">
-        <is>
-          <t>Test fails if filtered output is not empty.</t>
-        </is>
-      </c>
+          <t>UUT syslog must not contain unmasked error patterns, excluding skip patterns. Log file must exist and contain no unfiltered critical errors.</t>
+        </is>
+      </c>
+      <c r="E40" s="40" t="n"/>
       <c r="F40" s="75" t="n"/>
       <c r="G40" s="55" t="b">
         <v>0</v>
@@ -7846,28 +7833,28 @@
       <c r="K40" s="39" t="n"/>
       <c r="L40" s="51" t="n"/>
     </row>
-    <row r="41" ht="27" customFormat="1" customHeight="1" s="33">
+    <row r="41" ht="40.5" customFormat="1" customHeight="1" s="33">
       <c r="A41" s="76" t="n">
         <v>39</v>
       </c>
       <c r="B41" s="43" t="inlineStr">
         <is>
-          <t>uut_dmesg_chk</t>
+          <t>rm_fru_chk</t>
         </is>
       </c>
       <c r="C41" s="43" t="inlineStr">
         <is>
-          <t>Check UUT dmesg log for unexpected error messages and record PCI device status.</t>
+          <t>Check R-SCM FRU information</t>
         </is>
       </c>
       <c r="D41" s="40" t="inlineStr">
         <is>
-          <t>No unmasked error messages found in dmesg and all expected messages are properly filtered.</t>
+          <t>Pass Successfully retrieves the FRU data and the Product Serial Number matches the expected value from config. Fail Unable to retrieve FRU data or serial number does not match.</t>
         </is>
       </c>
       <c r="E41" s="40" t="inlineStr">
         <is>
-          <t>Filter list (filter_list.csv) and error map (err_map.ini) are required for filtering and mapping errors.</t>
+          <t>only applies to the master blade</t>
         </is>
       </c>
       <c r="F41" s="75" t="n"/>
@@ -7882,26 +7869,22 @@
       <c r="K41" s="39" t="n"/>
       <c r="L41" s="51" t="n"/>
     </row>
-    <row r="42" ht="27" customFormat="1" customHeight="1" s="33">
+    <row r="42" ht="15" customFormat="1" customHeight="1" s="33">
       <c r="A42" s="76" t="n">
         <v>40</v>
       </c>
       <c r="B42" s="43" t="inlineStr">
         <is>
-          <t>uut_syslog_chk</t>
-        </is>
-      </c>
-      <c r="C42" s="43" t="inlineStr">
-        <is>
-          <t>Check and record UUT system log (syslog/messages) to ensure no unexpected errors.</t>
-        </is>
-      </c>
-      <c r="D42" s="40" t="inlineStr">
-        <is>
-          <t>UUT syslog must not contain unmasked error patterns, excluding skip patterns. Log file must exist and contain no unfiltered critical errors.</t>
-        </is>
-      </c>
-      <c r="E42" s="40" t="n"/>
+          <t>rm_pmdu_fru_chk</t>
+        </is>
+      </c>
+      <c r="C42" s="43" t="n"/>
+      <c r="D42" s="40" t="n"/>
+      <c r="E42" s="40" t="inlineStr">
+        <is>
+          <t>only applies to the master blade</t>
+        </is>
+      </c>
       <c r="F42" s="75" t="n"/>
       <c r="G42" s="55" t="b">
         <v>0</v>
@@ -7914,25 +7897,17 @@
       <c r="K42" s="39" t="n"/>
       <c r="L42" s="51" t="n"/>
     </row>
-    <row r="43" ht="40.5" customFormat="1" customHeight="1" s="33">
+    <row r="43" ht="15" customFormat="1" customHeight="1" s="33">
       <c r="A43" s="76" t="n">
         <v>41</v>
       </c>
       <c r="B43" s="43" t="inlineStr">
         <is>
-          <t>rm_fru_chk</t>
-        </is>
-      </c>
-      <c r="C43" s="43" t="inlineStr">
-        <is>
-          <t>Check R-SCM FRU information</t>
-        </is>
-      </c>
-      <c r="D43" s="40" t="inlineStr">
-        <is>
-          <t>Pass Successfully retrieves the FRU data and the Product Serial Number matches the expected value from config. Fail Unable to retrieve FRU data or serial number does not match.</t>
-        </is>
-      </c>
+          <t>rm_acdc_fru_chk</t>
+        </is>
+      </c>
+      <c r="C43" s="43" t="n"/>
+      <c r="D43" s="40" t="n"/>
       <c r="E43" s="40" t="inlineStr">
         <is>
           <t>only applies to the master blade</t>
@@ -7956,16 +7931,20 @@
       </c>
       <c r="B44" s="43" t="inlineStr">
         <is>
-          <t>rm_pmdu_fru_chk</t>
-        </is>
-      </c>
-      <c r="C44" s="43" t="n"/>
-      <c r="D44" s="40" t="n"/>
-      <c r="E44" s="40" t="inlineStr">
-        <is>
-          <t>only applies to the master blade</t>
-        </is>
-      </c>
+          <t>rm_sys_fru_chk</t>
+        </is>
+      </c>
+      <c r="C44" s="43" t="inlineStr">
+        <is>
+          <t>Check System FRU via RSCM</t>
+        </is>
+      </c>
+      <c r="D44" s="40" t="inlineStr">
+        <is>
+          <t>Pass - return 0; Fail - return 1</t>
+        </is>
+      </c>
+      <c r="E44" s="40" t="n"/>
       <c r="F44" s="75" t="n"/>
       <c r="G44" s="55" t="b">
         <v>0</v>
@@ -7984,14 +7963,22 @@
       </c>
       <c r="B45" s="43" t="inlineStr">
         <is>
-          <t>rm_acdc_fru_chk</t>
-        </is>
-      </c>
-      <c r="C45" s="43" t="n"/>
-      <c r="D45" s="40" t="n"/>
+          <t>rm_scm_fru_chk</t>
+        </is>
+      </c>
+      <c r="C45" s="43" t="inlineStr">
+        <is>
+          <t>Check DC-SCM(M1120) FRU via R-SCM</t>
+        </is>
+      </c>
+      <c r="D45" s="40" t="inlineStr">
+        <is>
+          <t>Pass - return 0; Fail - return 1</t>
+        </is>
+      </c>
       <c r="E45" s="40" t="inlineStr">
         <is>
-          <t>only applies to the master blade</t>
+          <t>Check b oard s erial n umber</t>
         </is>
       </c>
       <c r="F45" s="75" t="n"/>
@@ -8012,12 +7999,12 @@
       </c>
       <c r="B46" s="43" t="inlineStr">
         <is>
-          <t>rm_sys_fru_chk</t>
+          <t>rm_gp_fru_chk</t>
         </is>
       </c>
       <c r="C46" s="43" t="inlineStr">
         <is>
-          <t>Check System FRU via RSCM</t>
+          <t>Check GlacierPeak FRU via R-SCM</t>
         </is>
       </c>
       <c r="D46" s="40" t="inlineStr">
@@ -8025,7 +8012,11 @@
           <t>Pass - return 0; Fail - return 1</t>
         </is>
       </c>
-      <c r="E46" s="40" t="n"/>
+      <c r="E46" s="40" t="inlineStr">
+        <is>
+          <t>Check b oard s erial n umber</t>
+        </is>
+      </c>
       <c r="F46" s="75" t="n"/>
       <c r="G46" s="55" t="b">
         <v>0</v>
@@ -8038,28 +8029,27 @@
       <c r="K46" s="39" t="n"/>
       <c r="L46" s="51" t="n"/>
     </row>
-    <row r="47" ht="15" customFormat="1" customHeight="1" s="33">
+    <row r="47" ht="53.25" customFormat="1" customHeight="1" s="33">
       <c r="A47" s="76" t="n">
         <v>45</v>
       </c>
       <c r="B47" s="43" t="inlineStr">
         <is>
-          <t>rm_scm_fru_chk</t>
+          <t>rm_relay_port_chk</t>
         </is>
       </c>
       <c r="C47" s="43" t="inlineStr">
         <is>
-          <t>Check DC-SCM(M1120) FRU via R-SCM</t>
-        </is>
-      </c>
-      <c r="D47" s="40" t="inlineStr">
-        <is>
-          <t>Pass - return 0; Fail - return 1</t>
-        </is>
-      </c>
+          <t>need to verify the status of the Relay Port Status - ON. Take CAUTION with turning ON state– delay for 20 second – then OFF state of the RELAY and OFF state – 20 seconds delay – ON state.</t>
+        </is>
+      </c>
+      <c r="D47" s="40" t="n"/>
       <c r="E47" s="40" t="inlineStr">
         <is>
-          <t>Check b oard s erial n umber</t>
+          <t>only applies to the master blade
+Feed1powerstatus = healthy
+Feed2powerstatus = healthy
+powerdrawninwatt &lt; maxpowerinwatts</t>
         </is>
       </c>
       <c r="F47" s="75" t="n"/>
@@ -8080,22 +8070,14 @@
       </c>
       <c r="B48" s="43" t="inlineStr">
         <is>
-          <t>rm_gp_fru_chk</t>
-        </is>
-      </c>
-      <c r="C48" s="43" t="inlineStr">
-        <is>
-          <t>Check GlacierPeak FRU via R-SCM</t>
-        </is>
-      </c>
-      <c r="D48" s="40" t="inlineStr">
-        <is>
-          <t>Pass - return 0; Fail - return 1</t>
-        </is>
-      </c>
+          <t>rm_power_reading_chk</t>
+        </is>
+      </c>
+      <c r="C48" s="43" t="n"/>
+      <c r="D48" s="40" t="n"/>
       <c r="E48" s="40" t="inlineStr">
         <is>
-          <t>Check b oard s erial n umber</t>
+          <t>only applies to the master blade</t>
         </is>
       </c>
       <c r="F48" s="75" t="n"/>
@@ -8110,27 +8092,28 @@
       <c r="K48" s="39" t="n"/>
       <c r="L48" s="51" t="n"/>
     </row>
-    <row r="49" ht="53.25" customFormat="1" customHeight="1" s="33">
+    <row r="49" ht="67.5" customFormat="1" customHeight="1" s="33">
       <c r="A49" s="76" t="n">
         <v>47</v>
       </c>
       <c r="B49" s="43" t="inlineStr">
         <is>
-          <t>rm_relay_port_chk</t>
+          <t>rm_power_capping_check</t>
         </is>
       </c>
       <c r="C49" s="43" t="inlineStr">
         <is>
-          <t>need to verify the status of the Relay Port Status - ON. Take CAUTION with turning ON state– delay for 20 second – then OFF state of the RELAY and OFF state – 20 seconds delay – ON state.</t>
-        </is>
-      </c>
-      <c r="D49" s="40" t="n"/>
+          <t>Validates RSCM rack-level power capping behavior, including: - DCMI-based static power limit control - PSU alert-triggered throttling (SM_ALERT)</t>
+        </is>
+      </c>
+      <c r="D49" s="40" t="inlineStr">
+        <is>
+          <t>- PASS when ALL are true: - Power limit successfully applied &amp; activated - System load is capped within expected power window (± tolerance) - After removing the cap → system power rebounds above limit - PSU alert scenario triggers throttling and later fully recovers (no SM_ALERT still active) - BMC SEL log contains no unexpected errors</t>
+        </is>
+      </c>
       <c r="E49" s="40" t="inlineStr">
         <is>
-          <t>only applies to the master blade
-Feed1powerstatus = healthy
-Feed2powerstatus = healthy
-powerdrawninwatt &lt; maxpowerinwatts</t>
+          <t>- Feature introduces POWER_CAPPING lock file to ensure only 1 DUT tests at a time - Test requires mprime stress load installed &amp; runnable - Test may cycle through high load &amp; recovery, ensure environment power is stable - SEL whitelist temporarily extended and restored afterward</t>
         </is>
       </c>
       <c r="F49" s="75" t="n"/>
@@ -8145,22 +8128,26 @@
       <c r="K49" s="39" t="n"/>
       <c r="L49" s="51" t="n"/>
     </row>
-    <row r="50" ht="15" customFormat="1" customHeight="1" s="33">
+    <row r="50" ht="40.5" customFormat="1" customHeight="1" s="33">
       <c r="A50" s="76" t="n">
         <v>48</v>
       </c>
       <c r="B50" s="43" t="inlineStr">
         <is>
-          <t>rm_power_reading_chk</t>
-        </is>
-      </c>
-      <c r="C50" s="43" t="n"/>
-      <c r="D50" s="40" t="n"/>
-      <c r="E50" s="40" t="inlineStr">
-        <is>
-          <t>only applies to the master blade</t>
-        </is>
-      </c>
+          <t>bios_dmidecode_fru_chk</t>
+        </is>
+      </c>
+      <c r="C50" s="43" t="inlineStr">
+        <is>
+          <t>Cross-checks dmidecode SMBIOS Type 1 (Product/System), Type 2 (Board), and Type 3 (Chassis) fields against the motherboard FRU (ipmitool fru print 0), using field-name mappings from bios_dmidecode_t1/t2/t3 config.</t>
+        </is>
+      </c>
+      <c r="D50" s="40" t="inlineStr">
+        <is>
+          <t>PASS only if every mapped field in all three checked SMBIOS types matches the corresponding FRU field exactly.</t>
+        </is>
+      </c>
+      <c r="E50" s="40" t="n"/>
       <c r="F50" s="75" t="n"/>
       <c r="G50" s="55" t="b">
         <v>0</v>
@@ -8173,30 +8160,26 @@
       <c r="K50" s="39" t="n"/>
       <c r="L50" s="51" t="n"/>
     </row>
-    <row r="51" ht="67.5" customFormat="1" customHeight="1" s="33">
+    <row r="51" ht="15" customFormat="1" customHeight="1" s="33">
       <c r="A51" s="76" t="n">
         <v>49</v>
       </c>
       <c r="B51" s="43" t="inlineStr">
         <is>
-          <t>rm_power_capping_check</t>
+          <t>bmc_mac_chk</t>
         </is>
       </c>
       <c r="C51" s="43" t="inlineStr">
         <is>
-          <t>Validates RSCM rack-level power capping behavior, including: - DCMI-based static power limit control - PSU alert-triggered throttling (SM_ALERT)</t>
+          <t>Checks the BMC's dedicated management NIC MAC address against SF.</t>
         </is>
       </c>
       <c r="D51" s="40" t="inlineStr">
         <is>
-          <t>- PASS when ALL are true: - Power limit successfully applied &amp; activated - System load is capped within expected power window (± tolerance) - After removing the cap → system power rebounds above limit - PSU alert scenario triggers throttling and later fully recovers (no SM_ALERT still active) - BMC SEL log contains no unexpected errors</t>
-        </is>
-      </c>
-      <c r="E51" s="40" t="inlineStr">
-        <is>
-          <t>- Feature introduces POWER_CAPPING lock file to ensure only 1 DUT tests at a time - Test requires mprime stress load installed &amp; runnable - Test may cycle through high load &amp; recovery, ensure environment power is stable - SEL whitelist temporarily extended and restored afterward</t>
-        </is>
-      </c>
+          <t>PASS if ipmitool lan print 1 MAC equals SF.</t>
+        </is>
+      </c>
+      <c r="E51" s="40" t="n"/>
       <c r="F51" s="75" t="n"/>
       <c r="G51" s="55" t="b">
         <v>0</v>
@@ -8209,26 +8192,30 @@
       <c r="K51" s="39" t="n"/>
       <c r="L51" s="51" t="n"/>
     </row>
-    <row r="52" ht="40.5" customFormat="1" customHeight="1" s="33">
+    <row r="52" ht="27" customFormat="1" customHeight="1" s="33">
       <c r="A52" s="76" t="n">
         <v>50</v>
       </c>
       <c r="B52" s="43" t="inlineStr">
         <is>
-          <t>bios_dmidecode_fru_chk</t>
+          <t>bmc_guid_chk</t>
         </is>
       </c>
       <c r="C52" s="43" t="inlineStr">
         <is>
-          <t>Cross-checks dmidecode SMBIOS Type 1 (Product/System), Type 2 (Board), and Type 3 (Chassis) fields against the motherboard FRU (ipmitool fru print 0), using field-name mappings from bios_dmidecode_t1/t2/t3 config.</t>
+          <t>Checks both the BMC "system GUID" (ipmitool mc guid) and "device GUID" (ipmitool raw 0x6 0x8) are not the all-ff placeholder value,.</t>
         </is>
       </c>
       <c r="D52" s="40" t="inlineStr">
         <is>
-          <t>PASS only if every mapped field in all three checked SMBIOS types matches the corresponding FRU field exactly.</t>
-        </is>
-      </c>
-      <c r="E52" s="40" t="n"/>
+          <t>PASS if neither GUID contains ffffffffffff.</t>
+        </is>
+      </c>
+      <c r="E52" s="40" t="inlineStr">
+        <is>
+          <t>If GUID is invalid, automatically trigger GUID re-write.</t>
+        </is>
+      </c>
       <c r="F52" s="75" t="n"/>
       <c r="G52" s="55" t="b">
         <v>0</v>
@@ -8241,23 +8228,23 @@
       <c r="K52" s="39" t="n"/>
       <c r="L52" s="51" t="n"/>
     </row>
-    <row r="53" ht="15" customFormat="1" customHeight="1" s="33">
+    <row r="53" ht="27" customFormat="1" customHeight="1" s="33">
       <c r="A53" s="76" t="n">
         <v>51</v>
       </c>
       <c r="B53" s="43" t="inlineStr">
         <is>
-          <t>bmc_mac_chk</t>
+          <t>bmc_scm_boardid_chk</t>
         </is>
       </c>
       <c r="C53" s="43" t="inlineStr">
         <is>
-          <t>Checks the BMC's dedicated management NIC MAC address against SF.</t>
+          <t>Reads the SCM board-revision ID via IPMI raw command and decodes specific bits to determine the board's build stage.</t>
         </is>
       </c>
       <c r="D53" s="40" t="inlineStr">
         <is>
-          <t>PASS if ipmitool lan print 1 MAC equals SF.</t>
+          <t>PASS if the decoded 3-bit board ID matches the code for the configured.</t>
         </is>
       </c>
       <c r="E53" s="40" t="n"/>
@@ -8273,41 +8260,42 @@
       <c r="K53" s="39" t="n"/>
       <c r="L53" s="51" t="n"/>
     </row>
-    <row r="54" ht="27" customFormat="1" customHeight="1" s="33">
-      <c r="A54" s="76" t="n">
+    <row r="54" customFormat="1" s="33">
+      <c r="A54" s="81" t="n">
         <v>52</v>
       </c>
-      <c r="B54" s="43" t="inlineStr">
-        <is>
-          <t>bmc_guid_chk</t>
-        </is>
-      </c>
-      <c r="C54" s="43" t="inlineStr">
-        <is>
-          <t>Checks both the BMC "system GUID" (ipmitool mc guid) and "device GUID" (ipmitool raw 0x6 0x8) are not the all-ff placeholder value,.</t>
-        </is>
-      </c>
-      <c r="D54" s="40" t="inlineStr">
-        <is>
-          <t>PASS if neither GUID contains ffffffffffff.</t>
-        </is>
-      </c>
-      <c r="E54" s="40" t="inlineStr">
-        <is>
-          <t>If GUID is invalid, automatically trigger GUID re-write.</t>
-        </is>
-      </c>
-      <c r="F54" s="75" t="n"/>
-      <c r="G54" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="H54" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="I54" s="55" t="n"/>
-      <c r="J54" s="55" t="n"/>
-      <c r="K54" s="39" t="n"/>
-      <c r="L54" s="51" t="n"/>
+      <c r="B54" s="82" t="inlineStr">
+        <is>
+          <t>bios_boardid_chk</t>
+        </is>
+      </c>
+      <c r="C54" s="82" t="inlineStr">
+        <is>
+          <t>Test mb board id reversion</t>
+        </is>
+      </c>
+      <c r="D54" s="83" t="inlineStr">
+        <is>
+          <t>The parsed current Board ID must match the expected ID for the given project and stage.</t>
+        </is>
+      </c>
+      <c r="E54" s="83" t="n"/>
+      <c r="F54" s="84" t="inlineStr">
+        <is>
+          <t>EVT CMD: ipmitool raw 0x36 0xf3 0x12 0xa6 0x02 0x00 0x18
+DVT CMD: ipmitool raw 0x36 0xf3 0x12 0xa6 0x02 0x00 0x12</t>
+        </is>
+      </c>
+      <c r="G54" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="H54" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="I54" s="84" t="n"/>
+      <c r="J54" s="84" t="n"/>
+      <c r="K54" s="85" t="n"/>
+      <c r="L54" s="86" t="n"/>
     </row>
     <row r="55" ht="27" customFormat="1" customHeight="1" s="33">
       <c r="A55" s="76" t="n">
@@ -8315,12 +8303,12 @@
       </c>
       <c r="B55" s="43" t="inlineStr">
         <is>
-          <t>bmc_scm_boardid_chk</t>
+          <t>bmc_hpm_boardid_chk</t>
         </is>
       </c>
       <c r="C55" s="43" t="inlineStr">
         <is>
-          <t>Reads the SCM board-revision ID via IPMI raw command and decodes specific bits to determine the board's build stage.</t>
+          <t>Reads the HPM board-revision ID via IPMI raw command and decodes specific bits to determine the board's build stage.</t>
         </is>
       </c>
       <c r="D55" s="40" t="inlineStr">
@@ -8347,95 +8335,26 @@
       </c>
       <c r="B56" s="82" t="inlineStr">
         <is>
-          <t>bios_boardid_chk</t>
+          <t>bmc_vr_chk</t>
         </is>
       </c>
       <c r="C56" s="82" t="inlineStr">
         <is>
-          <t>Test mb board id reversion</t>
+          <t>Verify BMC MB Voltage Regulator (VR) checksums.</t>
         </is>
       </c>
       <c r="D56" s="83" t="inlineStr">
         <is>
-          <t>The parsed current Board ID must match the expected ID for the given project and stage.</t>
-        </is>
-      </c>
-      <c r="E56" s="83" t="n"/>
-      <c r="F56" s="84" t="inlineStr">
-        <is>
-          <t>EVT CMD: ipmitool raw 0x36 0xf3 0x12 0xa6 0x02 0x00 0x18
-DVT CMD: ipmitool raw 0x36 0xf3 0x12 0xa6 0x02 0x00 0x12</t>
-        </is>
-      </c>
-      <c r="G56" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="H56" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="I56" s="84" t="n"/>
-      <c r="J56" s="84" t="n"/>
-      <c r="K56" s="85" t="n"/>
-      <c r="L56" s="86" t="n"/>
-    </row>
-    <row r="57" ht="27" customFormat="1" customHeight="1" s="33">
-      <c r="A57" s="76" t="n">
-        <v>55</v>
-      </c>
-      <c r="B57" s="43" t="inlineStr">
-        <is>
-          <t>bmc_hpm_boardid_chk</t>
-        </is>
-      </c>
-      <c r="C57" s="43" t="inlineStr">
-        <is>
-          <t>Reads the HPM board-revision ID via IPMI raw command and decodes specific bits to determine the board's build stage.</t>
-        </is>
-      </c>
-      <c r="D57" s="40" t="inlineStr">
-        <is>
-          <t>PASS if the decoded 3-bit board ID matches the code for the configured.</t>
-        </is>
-      </c>
-      <c r="E57" s="40" t="n"/>
-      <c r="F57" s="75" t="n"/>
-      <c r="G57" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="H57" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="I57" s="55" t="n"/>
-      <c r="J57" s="55" t="n"/>
-      <c r="K57" s="39" t="n"/>
-      <c r="L57" s="51" t="n"/>
-    </row>
-    <row r="58" customFormat="1" s="33">
-      <c r="A58" s="81" t="n">
-        <v>56</v>
-      </c>
-      <c r="B58" s="82" t="inlineStr">
-        <is>
-          <t>bmc_vr_chk</t>
-        </is>
-      </c>
-      <c r="C58" s="82" t="inlineStr">
-        <is>
-          <t>Verify BMC MB Voltage Regulator (VR) checksums.</t>
-        </is>
-      </c>
-      <c r="D58" s="83" t="inlineStr">
-        <is>
           <t>All VR checksums match expected values from config file.</t>
         </is>
       </c>
-      <c r="E58" s="83" t="inlineStr">
+      <c r="E56" s="83" t="inlineStr">
         <is>
           <t>- Supports 1 or 2 expected VR checksum sets and auto-selects correct group.
 - Fails if config values or commands are missing.</t>
         </is>
       </c>
-      <c r="F58" s="84" t="inlineStr">
+      <c r="F56" s="84" t="inlineStr">
         <is>
           <t>[Get VR version]
 Executing: ipmitool raw 0x36 0xf3 0x14 0xc0 0x00 0xfd 0x04 0x00 0x00 0x00 0x00&amp;&amp;ipmitool raw 0x36 0xf3 0x14 0xc0 0x00 0xfe 0x2d&amp;&amp;ipmitool raw 0x36 0xf3 0x14 0xc0 0x05 0xfd
@@ -8446,37 +8365,37 @@
 Executing: ipmitool raw 0x36 0xf3 0x16 0xd2 0x00 0xfd 0x04 0x00 0x00 0x00 0x00&amp;&amp;ipmitool raw 0x36 0xf3 0x16 0xd2 0x00 0xfe 0x2d&amp;&amp;ipmitool raw 0x36 0xf3 0x16 0xd2 0x05 0xfd</t>
         </is>
       </c>
-      <c r="G58" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="H58" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="I58" s="84" t="n"/>
-      <c r="J58" s="84" t="n"/>
-      <c r="K58" s="85" t="n"/>
-      <c r="L58" s="86" t="n"/>
-    </row>
-    <row r="59" customFormat="1" s="33">
-      <c r="A59" s="81" t="n">
-        <v>57</v>
-      </c>
-      <c r="B59" s="82" t="inlineStr">
+      <c r="G56" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="H56" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="I56" s="84" t="n"/>
+      <c r="J56" s="84" t="n"/>
+      <c r="K56" s="85" t="n"/>
+      <c r="L56" s="86" t="n"/>
+    </row>
+    <row r="57" customFormat="1" s="33">
+      <c r="A57" s="81" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" s="82" t="inlineStr">
         <is>
           <t>bmc_pdb_vr_chk</t>
         </is>
       </c>
-      <c r="C59" s="82" t="inlineStr">
+      <c r="C57" s="82" t="inlineStr">
         <is>
           <t>Verify BMC PDB Voltage Regulator (VR) checksums.</t>
         </is>
       </c>
-      <c r="D59" s="83" t="inlineStr">
+      <c r="D57" s="83" t="inlineStr">
         <is>
           <t>All VR checksums match expected values from config file.</t>
         </is>
       </c>
-      <c r="E59" s="83" t="inlineStr">
+      <c r="E57" s="83" t="inlineStr">
         <is>
           <t>- Supports 1 or 2 expected VR checksum sets and auto-selects correct group.
 - Fails if config values or commands are missing.
@@ -8485,7 +8404,7 @@
 &gt;&gt;&gt;PDB 2nd source has VR checksum. Wait for commodity and command to support this function. &gt;&gt;&gt;BMC RD updated the checksum.</t>
         </is>
       </c>
-      <c r="F59" s="84" t="inlineStr">
+      <c r="F57" s="84" t="inlineStr">
         <is>
           <t>[Get VR version]
 1. Check the PDB is main source or second soure.
@@ -8497,16 +8416,84 @@
 ./xdp711_crc.sh -b 31 -s 0x10</t>
         </is>
       </c>
-      <c r="G59" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="H59" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="I59" s="84" t="n"/>
-      <c r="J59" s="84" t="n"/>
-      <c r="K59" s="85" t="n"/>
-      <c r="L59" s="86" t="n"/>
+      <c r="G57" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="H57" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="I57" s="84" t="n"/>
+      <c r="J57" s="84" t="n"/>
+      <c r="K57" s="85" t="n"/>
+      <c r="L57" s="86" t="n"/>
+    </row>
+    <row r="58" ht="27" customFormat="1" customHeight="1" s="33">
+      <c r="A58" s="76" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" s="43" t="inlineStr">
+        <is>
+          <t>bmc_selftest_chk</t>
+        </is>
+      </c>
+      <c r="C58" s="43" t="inlineStr">
+        <is>
+          <t>Checks the BMC's own IPMI self-test result code against the expected "all subsystems healthy" value.</t>
+        </is>
+      </c>
+      <c r="D58" s="40" t="inlineStr">
+        <is>
+          <t>PASS if ipmitool raw 0x06 0x04 (whitespace-stripped) equals getConfigValue('bmc_selftest_rest').</t>
+        </is>
+      </c>
+      <c r="E58" s="40" t="inlineStr">
+        <is>
+          <t>A self-test failure is a hard FAIL with no retry/upgrade path.</t>
+        </is>
+      </c>
+      <c r="F58" s="75" t="n"/>
+      <c r="G58" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="H58" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="I58" s="55" t="n"/>
+      <c r="J58" s="55" t="n"/>
+      <c r="K58" s="39" t="n"/>
+      <c r="L58" s="51" t="n"/>
+    </row>
+    <row r="59" ht="27" customFormat="1" customHeight="1" s="33">
+      <c r="A59" s="76" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" s="43" t="inlineStr">
+        <is>
+          <t>bmc_func_test</t>
+        </is>
+      </c>
+      <c r="C59" s="43" t="inlineStr">
+        <is>
+          <t>Perform BMC functional test including Device ID, BMC version, self-test, chassis status, watchdog timer, and SDR check.</t>
+        </is>
+      </c>
+      <c r="D59" s="40" t="inlineStr">
+        <is>
+          <t>PASS if function test returns 0. On failure, greps LogFile.log for Failed entries and logs them alongside the detailed log.</t>
+        </is>
+      </c>
+      <c r="E59" s="40" t="n"/>
+      <c r="F59" s="75" t="n"/>
+      <c r="G59" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="H59" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="I59" s="55" t="n"/>
+      <c r="J59" s="55" t="n"/>
+      <c r="K59" s="39" t="n"/>
+      <c r="L59" s="51" t="n"/>
     </row>
     <row r="60" ht="27" customFormat="1" customHeight="1" s="33">
       <c r="A60" s="76" t="n">
@@ -8514,22 +8501,22 @@
       </c>
       <c r="B60" s="43" t="inlineStr">
         <is>
-          <t>bmc_selftest_chk</t>
+          <t>bmc_i2c_test</t>
         </is>
       </c>
       <c r="C60" s="43" t="inlineStr">
         <is>
-          <t>Checks the BMC's own IPMI self-test result code against the expected "all subsystems healthy" value.</t>
+          <t>Runs an on-BMC I2C stress-test script against MB/PDB/FAN buses, uploaded and executed live over SSH, with a BMC-SEL check both before and after.</t>
         </is>
       </c>
       <c r="D60" s="40" t="inlineStr">
         <is>
-          <t>PASS if ipmitool raw 0x06 0x04 (whitespace-stripped) equals getConfigValue('bmc_selftest_rest').</t>
+          <t>PASS if the uploaded script's log reports "Test successful" (no "Test Failed" / "No such file or directory" lines) AND the post-test BMC SEL check is clean.</t>
         </is>
       </c>
       <c r="E60" s="40" t="inlineStr">
         <is>
-          <t>A self-test failure is a hard FAIL with no retry/upgrade path.</t>
+          <t>SEL is explicitly cleared right before the I2C run so the post-run SEL check only reflects entries from this test.</t>
         </is>
       </c>
       <c r="F60" s="75" t="n"/>
@@ -8544,127 +8531,59 @@
       <c r="K60" s="39" t="n"/>
       <c r="L60" s="51" t="n"/>
     </row>
-    <row r="61" ht="27" customFormat="1" customHeight="1" s="33">
-      <c r="A61" s="76" t="n">
+    <row r="61" customFormat="1" s="33">
+      <c r="A61" s="81" t="n">
         <v>59</v>
       </c>
-      <c r="B61" s="43" t="inlineStr">
-        <is>
-          <t>bmc_func_test</t>
-        </is>
-      </c>
-      <c r="C61" s="43" t="inlineStr">
-        <is>
-          <t>Perform BMC functional test including Device ID, BMC version, self-test, chassis status, watchdog timer, and SDR check.</t>
-        </is>
-      </c>
-      <c r="D61" s="40" t="inlineStr">
-        <is>
-          <t>PASS if function test returns 0. On failure, greps LogFile.log for Failed entries and logs them alongside the detailed log.</t>
-        </is>
-      </c>
-      <c r="E61" s="40" t="n"/>
-      <c r="F61" s="75" t="n"/>
-      <c r="G61" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="H61" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="I61" s="55" t="n"/>
-      <c r="J61" s="55" t="n"/>
-      <c r="K61" s="39" t="n"/>
-      <c r="L61" s="51" t="n"/>
-    </row>
-    <row r="62" ht="27" customFormat="1" customHeight="1" s="33">
-      <c r="A62" s="76" t="n">
-        <v>60</v>
-      </c>
-      <c r="B62" s="43" t="inlineStr">
-        <is>
-          <t>bmc_i2c_test</t>
-        </is>
-      </c>
-      <c r="C62" s="43" t="inlineStr">
-        <is>
-          <t>Runs an on-BMC I2C stress-test script against MB/PDB/FAN buses, uploaded and executed live over SSH, with a BMC-SEL check both before and after.</t>
-        </is>
-      </c>
-      <c r="D62" s="40" t="inlineStr">
-        <is>
-          <t>PASS if the uploaded script's log reports "Test successful" (no "Test Failed" / "No such file or directory" lines) AND the post-test BMC SEL check is clean.</t>
-        </is>
-      </c>
-      <c r="E62" s="40" t="inlineStr">
-        <is>
-          <t>SEL is explicitly cleared right before the I2C run so the post-run SEL check only reflects entries from this test.</t>
-        </is>
-      </c>
-      <c r="F62" s="75" t="n"/>
-      <c r="G62" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="H62" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="I62" s="55" t="n"/>
-      <c r="J62" s="55" t="n"/>
-      <c r="K62" s="39" t="n"/>
-      <c r="L62" s="51" t="n"/>
-    </row>
-    <row r="63" customFormat="1" s="33">
-      <c r="A63" s="81" t="n">
-        <v>61</v>
-      </c>
-      <c r="B63" s="82" t="inlineStr">
+      <c r="B61" s="82" t="inlineStr">
         <is>
           <t>bmc_i3c_test</t>
         </is>
       </c>
-      <c r="C63" s="82" t="inlineStr">
+      <c r="C61" s="82" t="inlineStr">
         <is>
           <t>Check bmc i3c test and sel log check only for Castle Peak</t>
         </is>
       </c>
-      <c r="D63" s="83" t="inlineStr">
+      <c r="D61" s="83" t="inlineStr">
         <is>
           <t>Pass - return 0; Fail - return 1
 Pass - return 0; Fail - return 1</t>
         </is>
       </c>
-      <c r="E63" s="83" t="inlineStr">
+      <c r="E61" s="83" t="inlineStr">
         <is>
           <t>&gt;&gt;&gt; Will be implemented in DVT.</t>
         </is>
       </c>
-      <c r="F63" s="84" t="inlineStr">
+      <c r="F61" s="84" t="inlineStr">
         <is>
           <t>apml_tool 1 --showtsiregister
 apml_tool 2 --showtsiregister
 ===&gt; tu7_dvt_i2c_i3c_stress.sh 1 i3c</t>
         </is>
       </c>
-      <c r="G63" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="H63" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="I63" s="84" t="n"/>
-      <c r="J63" s="84" t="n"/>
-      <c r="K63" s="85" t="n"/>
-      <c r="L63" s="86" t="n"/>
-    </row>
-    <row r="64" customFormat="1" s="33">
-      <c r="A64" s="81" t="n">
-        <v>62</v>
-      </c>
-      <c r="B64" s="82" t="inlineStr">
+      <c r="G61" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="H61" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="I61" s="84" t="n"/>
+      <c r="J61" s="84" t="n"/>
+      <c r="K61" s="85" t="n"/>
+      <c r="L61" s="86" t="n"/>
+    </row>
+    <row r="62" customFormat="1" s="33">
+      <c r="A62" s="81" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" s="82" t="inlineStr">
         <is>
           <t>bmc_cpld_security_chk</t>
         </is>
       </c>
-      <c r="C64" s="82" t="inlineStr">
+      <c r="C62" s="82" t="inlineStr">
         <is>
           <t>Check all SCM/HPM CPLD information status via bmc jtag raw command
 SCM CPLD Criteria:
@@ -8700,8 +8619,8 @@
 HPM CPLD CENTRAL LOCK check</t>
         </is>
       </c>
-      <c r="D64" s="83" t="n"/>
-      <c r="E64" s="83" t="inlineStr">
+      <c r="D62" s="83" t="n"/>
+      <c r="E62" s="83" t="inlineStr">
         <is>
           <t>- Follow C44AD to combine bmc_cpld_security_chk and bmc_hpm_cpld_security_chk.
 &gt;&gt;&gt;bmc_cpld_security_chk will be implemented in DVT Canary.
@@ -8709,7 +8628,7 @@
 &gt;&gt;&gt; Waiver for ship the Canary demand with CPLD Ping-pong mode. WAIVER 3622374</t>
         </is>
       </c>
-      <c r="F64" s="84">
+      <c r="F62" s="84">
         <f>======= [ SCM CPLD ] ========
 [Get SCM Pull JTAG_BMC_OE_N Low]
 ipmitool raw 0x30 0xe0 0 8 1 0
@@ -8786,52 +8705,125 @@
 jtag-rbpi -if /var/wcs/home/Read_Lock_Sector.stp -m fwupdate -t HPM -j /usr/share/cpld-config/configurations/cpld-config.json -o /xyz/openbmc_project/software/HPM_CPLD -debug</f>
         <v/>
       </c>
-      <c r="G64" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="H64" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="I64" s="84" t="n"/>
-      <c r="J64" s="84" t="n"/>
-      <c r="K64" s="85" t="n"/>
-      <c r="L64" s="86" t="n"/>
-    </row>
-    <row r="65" customFormat="1" s="33">
-      <c r="A65" s="81" t="n">
+      <c r="G62" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="H62" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="I62" s="84" t="n"/>
+      <c r="J62" s="84" t="n"/>
+      <c r="K62" s="85" t="n"/>
+      <c r="L62" s="86" t="n"/>
+    </row>
+    <row r="63" customFormat="1" s="33">
+      <c r="A63" s="81" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" s="82" t="inlineStr">
+        <is>
+          <t>bmc_scm_cpu_uart_check</t>
+        </is>
+      </c>
+      <c r="C63" s="82" t="inlineStr">
+        <is>
+          <t>Check the UART0 path from SCM to CPU0 by validating SSH reachability through the chain: Host → BMC → Host. This ensures the SCM UART bus is working correctly by confirming that the BMC can relay communication back to the host system.</t>
+        </is>
+      </c>
+      <c r="D63" s="83" t="n"/>
+      <c r="E63" s="83" t="inlineStr">
+        <is>
+          <t>&gt;&gt;&gt; Will be implemented in DVT.</t>
+        </is>
+      </c>
+      <c r="F63" s="84" t="inlineStr">
+        <is>
+          <t>[Get BMC IP]</t>
+        </is>
+      </c>
+      <c r="G63" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="H63" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="I63" s="84" t="n"/>
+      <c r="J63" s="84" t="n"/>
+      <c r="K63" s="85" t="n"/>
+      <c r="L63" s="86" t="n"/>
+    </row>
+    <row r="64" ht="27" customFormat="1" customHeight="1" s="33">
+      <c r="A64" s="76" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" s="43" t="inlineStr">
+        <is>
+          <t>bmc_dedicate_chk</t>
+        </is>
+      </c>
+      <c r="C64" s="43" t="inlineStr">
+        <is>
+          <t>Verifies the BMC's dedicated management NIC is physically connected and DHCP-reachable by pinging it.</t>
+        </is>
+      </c>
+      <c r="D64" s="40" t="inlineStr">
+        <is>
+          <t>PASS if 5/5 pings succeed (or the RSCM-routed SSH connect succeeds).</t>
+        </is>
+      </c>
+      <c r="E64" s="40" t="inlineStr">
+        <is>
+          <t>M1/M3: via a direct ICMP ping
+M5: ping via an SSH-through-RSCM reachability check</t>
+        </is>
+      </c>
+      <c r="F64" s="75" t="n"/>
+      <c r="G64" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="H64" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="I64" s="55" t="n"/>
+      <c r="J64" s="55" t="n"/>
+      <c r="K64" s="39" t="n"/>
+      <c r="L64" s="51" t="n"/>
+    </row>
+    <row r="65" ht="27" customFormat="1" customHeight="1" s="33">
+      <c r="A65" s="76" t="n">
         <v>63</v>
       </c>
-      <c r="B65" s="82" t="inlineStr">
-        <is>
-          <t>bmc_scm_cpu_uart_check</t>
-        </is>
-      </c>
-      <c r="C65" s="82" t="inlineStr">
-        <is>
-          <t>Check the UART0 path from SCM to CPU0 by validating SSH reachability through the chain: Host → BMC → Host. This ensures the SCM UART bus is working correctly by confirming that the BMC can relay communication back to the host system.</t>
-        </is>
-      </c>
-      <c r="D65" s="83" t="n"/>
-      <c r="E65" s="83" t="inlineStr">
-        <is>
-          <t>&gt;&gt;&gt; Will be implemented in DVT.</t>
-        </is>
-      </c>
-      <c r="F65" s="84" t="inlineStr">
-        <is>
-          <t>[Get BMC IP]</t>
-        </is>
-      </c>
-      <c r="G65" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="H65" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="I65" s="84" t="n"/>
-      <c r="J65" s="84" t="n"/>
-      <c r="K65" s="85" t="n"/>
-      <c r="L65" s="86" t="n"/>
+      <c r="B65" s="43" t="inlineStr">
+        <is>
+          <t>cpu_qty_check</t>
+        </is>
+      </c>
+      <c r="C65" s="43" t="inlineStr">
+        <is>
+          <t>Checks the number of populated CPU sockets against SF-expected count.</t>
+        </is>
+      </c>
+      <c r="D65" s="40" t="inlineStr">
+        <is>
+          <t>PASS if grep 'physical id' /proc/cpuinfo | sort | uniq | wc -l equals getConfigValue('cpu_qty').</t>
+        </is>
+      </c>
+      <c r="E65" s="40" t="inlineStr">
+        <is>
+          <t>Straightforward count check, no upgrade/self-heal path (CPU quantity isn't something firmware can fix).</t>
+        </is>
+      </c>
+      <c r="F65" s="75" t="n"/>
+      <c r="G65" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="H65" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="I65" s="55" t="n"/>
+      <c r="J65" s="55" t="n"/>
+      <c r="K65" s="39" t="n"/>
+      <c r="L65" s="51" t="n"/>
     </row>
     <row r="66" ht="27" customFormat="1" customHeight="1" s="33">
       <c r="A66" s="76" t="n">
@@ -8839,23 +8831,22 @@
       </c>
       <c r="B66" s="43" t="inlineStr">
         <is>
-          <t>bmc_dedicate_chk</t>
+          <t>cpu_info_chk</t>
         </is>
       </c>
       <c r="C66" s="43" t="inlineStr">
         <is>
-          <t>Verifies the BMC's dedicated management NIC is physically connected and DHCP-reachable by pinging it.</t>
+          <t>Validate CPU information using dmidecode (type 4), comparing it with expected config values.</t>
         </is>
       </c>
       <c r="D66" s="40" t="inlineStr">
         <is>
-          <t>PASS if 5/5 pings succeed (or the RSCM-routed SSH connect succeeds).</t>
+          <t>PASS if, per CPU, the Manufacturer/Version/Speed combo, Signature, and Core Count all measure equal to expected.</t>
         </is>
       </c>
       <c r="E66" s="40" t="inlineStr">
         <is>
-          <t>M1/M3: via a direct ICMP ping
-M5: ping via an SSH-through-RSCM reachability check</t>
+          <t>In L6 prj_level, all checks are informational-only.</t>
         </is>
       </c>
       <c r="F66" s="75" t="n"/>
@@ -8876,22 +8867,22 @@
       </c>
       <c r="B67" s="43" t="inlineStr">
         <is>
-          <t>cpu_qty_check</t>
+          <t>cpu_func_test</t>
         </is>
       </c>
       <c r="C67" s="43" t="inlineStr">
         <is>
-          <t>Checks the number of populated CPU sockets against SF-expected count.</t>
+          <t>Runs a sequence of CPU feature functional tests (Cache, FPU, MMX, SSE, SSE2, SSE3, x64Cap, SMP, SMP-cache-coherency, AES, SSE4).</t>
         </is>
       </c>
       <c r="D67" s="40" t="inlineStr">
         <is>
-          <t>PASS if grep 'physical id' /proc/cpuinfo | sort | uniq | wc -l equals getConfigValue('cpu_qty').</t>
+          <t>PASS only if every sub-test in the sequence returns exit code 0; the function returns 1 immediately on the first sub-test failure.</t>
         </is>
       </c>
       <c r="E67" s="40" t="inlineStr">
         <is>
-          <t>Straightforward count check, no upgrade/self-heal path (CPU quantity isn't something firmware can fix).</t>
+          <t>Fail-fast means a Cache-test failure prevents FPU/MMX/etc.</t>
         </is>
       </c>
       <c r="F67" s="75" t="n"/>
@@ -8906,93 +8897,21 @@
       <c r="K67" s="39" t="n"/>
       <c r="L67" s="51" t="n"/>
     </row>
-    <row r="68" ht="27" customFormat="1" customHeight="1" s="33">
-      <c r="A68" s="76" t="n">
+    <row r="68" customFormat="1" s="33">
+      <c r="A68" s="81" t="n">
         <v>66</v>
       </c>
-      <c r="B68" s="43" t="inlineStr">
-        <is>
-          <t>cpu_info_chk</t>
-        </is>
-      </c>
-      <c r="C68" s="43" t="inlineStr">
-        <is>
-          <t>Validate CPU information using dmidecode (type 4), comparing it with expected config values.</t>
-        </is>
-      </c>
-      <c r="D68" s="40" t="inlineStr">
-        <is>
-          <t>PASS if, per CPU, the Manufacturer/Version/Speed combo, Signature, and Core Count all measure equal to expected.</t>
-        </is>
-      </c>
-      <c r="E68" s="40" t="inlineStr">
-        <is>
-          <t>In L6 prj_level, all checks are informational-only.</t>
-        </is>
-      </c>
-      <c r="F68" s="75" t="n"/>
-      <c r="G68" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="H68" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="I68" s="55" t="n"/>
-      <c r="J68" s="55" t="n"/>
-      <c r="K68" s="39" t="n"/>
-      <c r="L68" s="51" t="n"/>
-    </row>
-    <row r="69" ht="27" customFormat="1" customHeight="1" s="33">
-      <c r="A69" s="76" t="n">
-        <v>67</v>
-      </c>
-      <c r="B69" s="43" t="inlineStr">
-        <is>
-          <t>cpu_func_test</t>
-        </is>
-      </c>
-      <c r="C69" s="43" t="inlineStr">
-        <is>
-          <t>Runs a sequence of CPU feature functional tests (Cache, FPU, MMX, SSE, SSE2, SSE3, x64Cap, SMP, SMP-cache-coherency, AES, SSE4).</t>
-        </is>
-      </c>
-      <c r="D69" s="40" t="inlineStr">
-        <is>
-          <t>PASS only if every sub-test in the sequence returns exit code 0; the function returns 1 immediately on the first sub-test failure.</t>
-        </is>
-      </c>
-      <c r="E69" s="40" t="inlineStr">
-        <is>
-          <t>Fail-fast means a Cache-test failure prevents FPU/MMX/etc.</t>
-        </is>
-      </c>
-      <c r="F69" s="75" t="n"/>
-      <c r="G69" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="H69" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="I69" s="55" t="n"/>
-      <c r="J69" s="55" t="n"/>
-      <c r="K69" s="39" t="n"/>
-      <c r="L69" s="51" t="n"/>
-    </row>
-    <row r="70" s="80">
-      <c r="A70" s="81" t="n">
-        <v>68</v>
-      </c>
-      <c r="B70" s="82" t="inlineStr">
+      <c r="B68" s="82" t="inlineStr">
         <is>
           <t>cpu_xgmi</t>
         </is>
       </c>
-      <c r="C70" s="82" t="inlineStr">
+      <c r="C68" s="82" t="inlineStr">
         <is>
           <t>This test verifies the status and configuration of AMD's XGMI (inter-socket high-speed link) functionality between CPUs.</t>
         </is>
       </c>
-      <c r="D70" s="83" t="inlineStr">
+      <c r="D68" s="83" t="inlineStr">
         <is>
           <t>The XGMI links between CPUs must be:
 - Detected successfully by the system
@@ -9000,39 +8919,39 @@
 - All links must pass without errors or degradation</t>
         </is>
       </c>
-      <c r="E70" s="83" t="inlineStr">
+      <c r="E68" s="83" t="inlineStr">
         <is>
           <t>&gt;&gt;&gt;Secured CPU has Bug#3771751, which plan to be resolved in 1A21.</t>
         </is>
       </c>
-      <c r="F70" s="84" t="inlineStr">
+      <c r="F68" s="84" t="inlineStr">
         <is>
           <t>./AMDXIO -i=0:,1:,2:,3: -xgmi -linkstatus ===&gt; dpkg -i …amdxio_nda.deb</t>
         </is>
       </c>
-      <c r="G70" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="H70" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="I70" s="84" t="n"/>
-      <c r="J70" s="84" t="n"/>
-      <c r="K70" s="85" t="n"/>
-      <c r="L70" s="86" t="n"/>
-    </row>
-    <row r="71" s="80">
-      <c r="A71" s="81" t="n">
-        <v>69</v>
-      </c>
-      <c r="B71" s="82" t="inlineStr">
+      <c r="G68" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="H68" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="I68" s="84" t="n"/>
+      <c r="J68" s="84" t="n"/>
+      <c r="K68" s="85" t="n"/>
+      <c r="L68" s="86" t="n"/>
+    </row>
+    <row r="69" customFormat="1" s="33">
+      <c r="A69" s="81" t="n">
+        <v>67</v>
+      </c>
+      <c r="B69" s="82" t="inlineStr">
         <is>
           <t>cpu_xgmi_bw</t>
         </is>
       </c>
-      <c r="C71" s="82" t="n"/>
-      <c r="D71" s="83" t="n"/>
-      <c r="E71" s="83" t="inlineStr">
+      <c r="C69" s="82" t="n"/>
+      <c r="D69" s="83" t="n"/>
+      <c r="E69" s="83" t="inlineStr">
         <is>
           <t>"cpu_xgmi" test failed with secured PC CPU.
 The Alternative method (MLC+APML tool) to to verify xGMI bandwidth/xGMI connection (1 cable-connected, 2 on-board trace)
@@ -9042,30 +8961,30 @@
 &gt;&gt;&gt;This test item can be removed when AMD provides a workable xgmi tool.</t>
         </is>
       </c>
-      <c r="F71" s="84" t="n"/>
-      <c r="G71" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="H71" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="I71" s="84" t="n"/>
-      <c r="J71" s="84" t="n"/>
-      <c r="K71" s="85" t="n"/>
-      <c r="L71" s="86" t="n"/>
-    </row>
-    <row r="72" s="80">
-      <c r="A72" s="81" t="n">
-        <v>70</v>
-      </c>
-      <c r="B72" s="82" t="inlineStr">
+      <c r="F69" s="84" t="n"/>
+      <c r="G69" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="H69" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="I69" s="84" t="n"/>
+      <c r="J69" s="84" t="n"/>
+      <c r="K69" s="85" t="n"/>
+      <c r="L69" s="86" t="n"/>
+    </row>
+    <row r="70" s="80">
+      <c r="A70" s="81" t="n">
+        <v>68</v>
+      </c>
+      <c r="B70" s="82" t="inlineStr">
         <is>
           <t>cpu_esmi_xgmi_link_speed</t>
         </is>
       </c>
-      <c r="C72" s="82" t="n"/>
-      <c r="D72" s="83" t="n"/>
-      <c r="E72" s="83" t="inlineStr">
+      <c r="C70" s="82" t="n"/>
+      <c r="D70" s="83" t="n"/>
+      <c r="E70" s="83" t="inlineStr">
         <is>
           <t>to verify the configured xGMI link speed
 &gt;&gt;&gt;Move cpu_esmi_xgmi_link_speed from L10 FAT to L11 Pretest since E-SMI work with L11 Canary CRD BIOS 1A20.
@@ -9074,35 +8993,89 @@
 &gt;&gt;&gt;This test item can be removed when AMD provides a workable xgmi tool.</t>
         </is>
       </c>
-      <c r="F72" s="84" t="n"/>
-      <c r="G72" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="H72" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="I72" s="84" t="n"/>
-      <c r="J72" s="84" t="n"/>
-      <c r="K72" s="85" t="n"/>
-      <c r="L72" s="86" t="n"/>
+      <c r="F70" s="84" t="n"/>
+      <c r="G70" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="H70" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="I70" s="84" t="n"/>
+      <c r="J70" s="84" t="n"/>
+      <c r="K70" s="85" t="n"/>
+      <c r="L70" s="86" t="n"/>
+    </row>
+    <row r="71" ht="27" customHeight="1" s="80">
+      <c r="A71" s="76" t="n">
+        <v>69</v>
+      </c>
+      <c r="B71" s="43" t="inlineStr">
+        <is>
+          <t>mem_info_chk</t>
+        </is>
+      </c>
+      <c r="C71" s="43" t="inlineStr">
+        <is>
+          <t>Checks each populated DIMM slot's Size/Speed/Manufacturer/Part-Number against SF-expected mem list, parsed from a filtered dmidecode -t 17 dump.</t>
+        </is>
+      </c>
+      <c r="D71" s="40" t="inlineStr">
+        <is>
+          <t>PASS if every slot's manf,size,speed,PN string matches the corresponding SF entry exactly.</t>
+        </is>
+      </c>
+      <c r="E71" s="40" t="n"/>
+      <c r="F71" s="75" t="n"/>
+      <c r="G71" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="H71" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="I71" s="55" t="n"/>
+      <c r="J71" s="55" t="n"/>
+      <c r="K71" s="39" t="n"/>
+      <c r="L71" s="51" t="n"/>
+    </row>
+    <row r="72" ht="15" customHeight="1" s="80">
+      <c r="A72" s="76" t="n"/>
+      <c r="B72" s="43" t="inlineStr">
+        <is>
+          <t>rm_mem_size_chk</t>
+        </is>
+      </c>
+      <c r="C72" s="43" t="n"/>
+      <c r="D72" s="40" t="n"/>
+      <c r="E72" s="40" t="n"/>
+      <c r="F72" s="75" t="n"/>
+      <c r="G72" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="H72" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="I72" s="55" t="n"/>
+      <c r="J72" s="55" t="n"/>
+      <c r="K72" s="39" t="n"/>
+      <c r="L72" s="51" t="n"/>
     </row>
     <row r="73" ht="27" customHeight="1" s="80">
       <c r="A73" s="76" t="n">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="B73" s="43" t="inlineStr">
         <is>
-          <t>mem_info_chk</t>
+          <t>mem_size_chk</t>
         </is>
       </c>
       <c r="C73" s="43" t="inlineStr">
         <is>
-          <t>Checks each populated DIMM slot's Size/Speed/Manufacturer/Part-Number against SF-expected mem list, parsed from a filtered dmidecode -t 17 dump.</t>
+          <t>Cross-checks total populated-DIMM count and per-DIMM size (in the detected unit, MB or GB) against SF's mem_num/mem_size.</t>
         </is>
       </c>
       <c r="D73" s="40" t="inlineStr">
         <is>
-          <t>PASS if every slot's manf,size,speed,PN string matches the corresponding SF entry exactly.</t>
+          <t>PASS if the count of DIMMs reporting the dominant size equals mem_num AND that size (converted to the detected unit) equals mem_size.</t>
         </is>
       </c>
       <c r="E73" s="40" t="n"/>
@@ -9118,16 +9091,30 @@
       <c r="K73" s="39" t="n"/>
       <c r="L73" s="51" t="n"/>
     </row>
-    <row r="74" ht="15" customHeight="1" s="80">
-      <c r="A74" s="76" t="n"/>
+    <row r="74" ht="27" customHeight="1" s="80">
+      <c r="A74" s="76" t="n">
+        <v>71</v>
+      </c>
       <c r="B74" s="43" t="inlineStr">
         <is>
-          <t>rm_mem_size_chk</t>
-        </is>
-      </c>
-      <c r="C74" s="43" t="n"/>
-      <c r="D74" s="40" t="n"/>
-      <c r="E74" s="40" t="n"/>
+          <t>mem_func_test</t>
+        </is>
+      </c>
+      <c r="C74" s="43" t="inlineStr">
+        <is>
+          <t>Runs a memory read/write functional stress test with swap disabled during the run.</t>
+        </is>
+      </c>
+      <c r="D74" s="40" t="inlineStr">
+        <is>
+          <t>PASS if the test command's exit code is 0.</t>
+        </is>
+      </c>
+      <c r="E74" s="40" t="inlineStr">
+        <is>
+          <t>Maps specific nonzero return codes to human-readable error names in the failure log message.</t>
+        </is>
+      </c>
       <c r="F74" s="75" t="n"/>
       <c r="G74" s="55" t="b">
         <v>0</v>
@@ -9140,26 +9127,30 @@
       <c r="K74" s="39" t="n"/>
       <c r="L74" s="51" t="n"/>
     </row>
-    <row r="75" ht="27" customHeight="1" s="80">
+    <row r="75" ht="67.5" customHeight="1" s="80">
       <c r="A75" s="76" t="n">
         <v>72</v>
       </c>
       <c r="B75" s="43" t="inlineStr">
         <is>
-          <t>mem_size_chk</t>
+          <t>pcie_manticore_log_chk</t>
         </is>
       </c>
       <c r="C75" s="43" t="inlineStr">
         <is>
-          <t>Cross-checks total populated-DIMM count and per-DIMM size (in the detected unit, MB or GB) against SF's mem_num/mem_size.</t>
+          <t>Reads the Manticore chip's debug log (cerberus_utility debuglogread), verifies the FW version recorded in the log matches expected, checks CS0/CS1 flash device consistency, scans for uncleared error codes since the last boot, and scans for unfiltered Warning/Error lines against a configurable skip-pattern list — clearing the log only after a full PASS.</t>
         </is>
       </c>
       <c r="D75" s="40" t="inlineStr">
         <is>
-          <t>PASS if the count of DIMMs reporting the dominant size equals mem_num AND that size (converted to the detected unit) equals mem_size.</t>
-        </is>
-      </c>
-      <c r="E75" s="40" t="n"/>
+          <t>PASS only if: (1) FW version found in log matches pcie_manticore_ver, (2) Port 1 CS0/CS1 vendor+device+capacity match each other, (3) no known bad error codes (0x7f001e0c/0d/0e, 0x7f001d05, 0x7f001d10) appear after the last-boot marker, (4) no unfiltered Warning/Error lines appear after the last-boot marker.</t>
+        </is>
+      </c>
+      <c r="E75" s="40" t="inlineStr">
+        <is>
+          <t>If the log is completely empty of a FW-version line, it triggers an AC power cycle as a recovery action and still FAILs the current pass (log message: "please AC the server"). pcie_manticore_debuglog_skip config defines patterns to exclude from the Warning/Error scan</t>
+        </is>
+      </c>
       <c r="F75" s="75" t="n"/>
       <c r="G75" s="55" t="b">
         <v>0</v>
@@ -9172,28 +9163,28 @@
       <c r="K75" s="39" t="n"/>
       <c r="L75" s="51" t="n"/>
     </row>
-    <row r="76" ht="27" customHeight="1" s="80">
+    <row r="76" ht="67.5" customHeight="1" s="80">
       <c r="A76" s="76" t="n">
         <v>73</v>
       </c>
       <c r="B76" s="43" t="inlineStr">
         <is>
-          <t>mem_func_test</t>
+          <t>pcie_tip_log_chk</t>
         </is>
       </c>
       <c r="C76" s="43" t="inlineStr">
         <is>
-          <t>Runs a memory read/write functional stress test with swap disabled during the run.</t>
+          <t>Reads the Hydra/TIP chip's debug log (cerberus_utility debuglogread), verifies the FW version recorded in the log matches expected, checks CS0/CS1 flash device consistency, scans for uncleared error codes since the last boot, and scans for unfiltered Warning/Error lines against a configurable skip-pattern list — clearing the log only after a full PASS.</t>
         </is>
       </c>
       <c r="D76" s="40" t="inlineStr">
         <is>
-          <t>PASS if the test command's exit code is 0.</t>
+          <t>PASS if: (1) the log contains a "Cerberus main flash" entry at all (else AC-cycle + FAIL), (2) main/recovery flash vendor+device+capacity match, (3) no unfiltered Warning/Error tagged lines appear after the last-boot marker.</t>
         </is>
       </c>
       <c r="E76" s="40" t="inlineStr">
         <is>
-          <t>Maps specific nonzero return codes to human-readable error names in the failure log message.</t>
+          <t>The Warning/Error scan here additionally requires the tag field (3rd |-delimited column) itself contain "Warning" or "Error", not just the whole line.</t>
         </is>
       </c>
       <c r="F76" s="75" t="n"/>
@@ -9208,287 +9199,131 @@
       <c r="K76" s="39" t="n"/>
       <c r="L76" s="51" t="n"/>
     </row>
-    <row r="77" s="80">
-      <c r="A77" s="81" t="n">
+    <row r="77" ht="27" customHeight="1" s="80">
+      <c r="A77" s="76" t="n">
         <v>74</v>
       </c>
-      <c r="B77" s="82" t="inlineStr">
-        <is>
-          <t>nic_mac_chk</t>
-        </is>
-      </c>
-      <c r="C77" s="82" t="inlineStr">
-        <is>
-          <t>Check Mellanox MAC and retrieve Mellanox device number</t>
-        </is>
-      </c>
-      <c r="D77" s="83" t="inlineStr">
-        <is>
-          <t>- Check CX8 quantity/qty
-- MAC must match configuration.</t>
-        </is>
-      </c>
-      <c r="E77" s="83" t="inlineStr">
-        <is>
-          <t>&gt;&gt;&gt; Enable this check only for CX8 SKU</t>
-        </is>
-      </c>
-      <c r="F77" s="84" t="inlineStr">
-        <is>
-          <t>[CMD] mlxfwmanager --query | grep 'Device #'| wc -l</t>
-        </is>
-      </c>
-      <c r="G77" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="H77" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="I77" s="84" t="n"/>
-      <c r="J77" s="84" t="n"/>
-      <c r="K77" s="85" t="n"/>
-      <c r="L77" s="86" t="n"/>
-    </row>
-    <row r="78" s="80">
-      <c r="A78" s="81" t="n">
+      <c r="B77" s="43" t="inlineStr">
+        <is>
+          <t>fpga_gp_mac_chk</t>
+        </is>
+      </c>
+      <c r="C77" s="43" t="inlineStr">
+        <is>
+          <t>Checks the GlacierPeak's own network interface MAC address (read via ifconfig enm0 over SSH to the GP SoC) against mac[0].</t>
+        </is>
+      </c>
+      <c r="D77" s="40" t="inlineStr">
+        <is>
+          <t>PASS if the parsed ether MAC equals getConfigValue('mac')[0] (uppercased, colon-stripped).</t>
+        </is>
+      </c>
+      <c r="E77" s="40" t="n"/>
+      <c r="F77" s="75" t="n"/>
+      <c r="G77" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="H77" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="I77" s="55" t="n"/>
+      <c r="J77" s="55" t="n"/>
+      <c r="K77" s="39" t="n"/>
+      <c r="L77" s="51" t="n"/>
+    </row>
+    <row r="78" ht="135" customHeight="1" s="80">
+      <c r="A78" s="76" t="n">
         <v>75</v>
       </c>
-      <c r="B78" s="82" t="inlineStr">
-        <is>
-          <t>nic_ib_speed_test</t>
-        </is>
-      </c>
-      <c r="C78" s="82" t="inlineStr">
-        <is>
-          <t>Test CX8 InfiniBand Speed</t>
-        </is>
-      </c>
-      <c r="D78" s="83" t="inlineStr">
-        <is>
-          <t>Pass – Speed meets the required standard; Fail –Speed does not meet the required standard</t>
-        </is>
-      </c>
-      <c r="E78" s="83" t="inlineStr">
-        <is>
-          <t>- CX8 port connect to CX8 port in L10.
-- CX8 port connect to XDR switch test fixture in L11.
-&gt;&gt;&gt;MSFT agreed to waive in EVT. (ADO#2992170)
-&gt;&gt;&gt; Enable this check only for CX8 SKU + IB</t>
-        </is>
-      </c>
-      <c r="F78" s="84" t="inlineStr">
-        <is>
-          <t>[CMD]</t>
-        </is>
-      </c>
-      <c r="G78" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="H78" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="I78" s="84" t="n"/>
-      <c r="J78" s="84" t="n"/>
-      <c r="K78" s="85" t="n"/>
-      <c r="L78" s="86" t="n"/>
-    </row>
-    <row r="79" ht="67.5" customFormat="1" customHeight="1" s="55">
-      <c r="A79" s="76" t="n">
+      <c r="B78" s="43" t="inlineStr">
+        <is>
+          <t>fpga_gp_status_chk</t>
+        </is>
+      </c>
+      <c r="C78" s="43" t="inlineStr">
+        <is>
+          <t>Runs fpgadiagnostics -dumpHealth (via a stage-appropriate SSH route: direct M3, RSCM-jumper M3, or RSCM-serial-proxy M5) and parses per-subsystem [FPGA-XXX] health lines, with specific waivers for known FPGA-NETWORK and FPGA-CONFIG warnings, and a one-time auto-reboot self-heal if the PCIe link status reads "WARNING" while in App mode.</t>
+        </is>
+      </c>
+      <c r="D78" s="40" t="inlineStr">
+        <is>
+          <t>PASS if no un-waived [FPGA-XXX] line fails its ] OK [ check.</t>
+        </is>
+      </c>
+      <c r="E78" s="40" t="inlineStr">
+        <is>
+          <t>Likely bug: in the FPGA-NETWORK-on-M5 branch, the failure path does isfail += 1 — but the function only ever initializes a variable named fail = 0, never isfail. If that exact branch is hit (M5 stage, FPGA-NETWORK reports non-OK, and the message isn't the specific waived "one or more network links down" string), this will raise NameError: name 'isfail' is not defined instead of cleanly failing the test. Also implements a reboot self-heal: if PCIe status is "WARNING" while FPGA is in App mode (config_status == "0") and no .reboot marker file exists yet for this unit, it touches the marker and issues reboot immediately rather than failing — the next run after reboot either clears (marker removed, PASS) or fails hard if the WARNING persists (marker already present).</t>
+        </is>
+      </c>
+      <c r="F78" s="75" t="n"/>
+      <c r="G78" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="H78" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="I78" s="55" t="n"/>
+      <c r="J78" s="55" t="n"/>
+      <c r="K78" s="39" t="n"/>
+      <c r="L78" s="51" t="n"/>
+    </row>
+    <row r="79" customFormat="1" s="55">
+      <c r="A79" s="81" t="n">
         <v>76</v>
       </c>
-      <c r="B79" s="43" t="inlineStr">
-        <is>
-          <t>pcie_manticore_log_chk</t>
-        </is>
-      </c>
-      <c r="C79" s="43" t="inlineStr">
-        <is>
-          <t>Reads the Manticore chip's debug log (cerberus_utility debuglogread), verifies the FW version recorded in the log matches expected, checks CS0/CS1 flash device consistency, scans for uncleared error codes since the last boot, and scans for unfiltered Warning/Error lines against a configurable skip-pattern list — clearing the log only after a full PASS.</t>
-        </is>
-      </c>
-      <c r="D79" s="40" t="inlineStr">
-        <is>
-          <t>PASS only if: (1) FW version found in log matches pcie_manticore_ver, (2) Port 1 CS0/CS1 vendor+device+capacity match each other, (3) no known bad error codes (0x7f001e0c/0d/0e, 0x7f001d05, 0x7f001d10) appear after the last-boot marker, (4) no unfiltered Warning/Error lines appear after the last-boot marker.</t>
-        </is>
-      </c>
-      <c r="E79" s="40" t="inlineStr">
-        <is>
-          <t>If the log is completely empty of a FW-version line, it triggers an AC power cycle as a recovery action and still FAILs the current pass (log message: "please AC the server"). pcie_manticore_debuglog_skip config defines patterns to exclude from the Warning/Error scan</t>
-        </is>
-      </c>
-      <c r="F79" s="75" t="n"/>
-      <c r="G79" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="H79" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="I79" s="55" t="n"/>
-      <c r="J79" s="55" t="n"/>
-      <c r="K79" s="39" t="n"/>
-      <c r="L79" s="51" t="n"/>
-    </row>
-    <row r="80" ht="67.5" customHeight="1" s="80">
-      <c r="A80" s="76" t="n">
-        <v>77</v>
-      </c>
-      <c r="B80" s="43" t="inlineStr">
-        <is>
-          <t>pcie_tip_log_chk</t>
-        </is>
-      </c>
-      <c r="C80" s="43" t="inlineStr">
-        <is>
-          <t>Reads the Hydra/TIP chip's debug log (cerberus_utility debuglogread), verifies the FW version recorded in the log matches expected, checks CS0/CS1 flash device consistency, scans for uncleared error codes since the last boot, and scans for unfiltered Warning/Error lines against a configurable skip-pattern list — clearing the log only after a full PASS.</t>
-        </is>
-      </c>
-      <c r="D80" s="40" t="inlineStr">
-        <is>
-          <t>PASS if: (1) the log contains a "Cerberus main flash" entry at all (else AC-cycle + FAIL), (2) main/recovery flash vendor+device+capacity match, (3) no unfiltered Warning/Error tagged lines appear after the last-boot marker.</t>
-        </is>
-      </c>
-      <c r="E80" s="40" t="inlineStr">
-        <is>
-          <t>The Warning/Error scan here additionally requires the tag field (3rd |-delimited column) itself contain "Warning" or "Error", not just the whole line.</t>
-        </is>
-      </c>
-      <c r="F80" s="75" t="n"/>
-      <c r="G80" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="H80" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="I80" s="55" t="n"/>
-      <c r="J80" s="55" t="n"/>
-      <c r="K80" s="39" t="n"/>
-      <c r="L80" s="51" t="n"/>
-    </row>
-    <row r="81" ht="27" customHeight="1" s="80">
-      <c r="A81" s="76" t="n">
-        <v>78</v>
-      </c>
-      <c r="B81" s="43" t="inlineStr">
-        <is>
-          <t>fpga_gp_mac_chk</t>
-        </is>
-      </c>
-      <c r="C81" s="43" t="inlineStr">
-        <is>
-          <t>Checks the GlacierPeak's own network interface MAC address (read via ifconfig enm0 over SSH to the GP SoC) against mac[0].</t>
-        </is>
-      </c>
-      <c r="D81" s="40" t="inlineStr">
-        <is>
-          <t>PASS if the parsed ether MAC equals getConfigValue('mac')[0] (uppercased, colon-stripped).</t>
-        </is>
-      </c>
-      <c r="E81" s="40" t="n"/>
-      <c r="F81" s="75" t="n"/>
-      <c r="G81" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="H81" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="I81" s="55" t="n"/>
-      <c r="J81" s="55" t="n"/>
-      <c r="K81" s="39" t="n"/>
-      <c r="L81" s="51" t="n"/>
-    </row>
-    <row r="82" ht="135" customHeight="1" s="80">
-      <c r="A82" s="76" t="n">
-        <v>79</v>
-      </c>
-      <c r="B82" s="43" t="inlineStr">
-        <is>
-          <t>fpga_gp_status_chk</t>
-        </is>
-      </c>
-      <c r="C82" s="43" t="inlineStr">
-        <is>
-          <t>Runs fpgadiagnostics -dumpHealth (via a stage-appropriate SSH route: direct M3, RSCM-jumper M3, or RSCM-serial-proxy M5) and parses per-subsystem [FPGA-XXX] health lines, with specific waivers for known FPGA-NETWORK and FPGA-CONFIG warnings, and a one-time auto-reboot self-heal if the PCIe link status reads "WARNING" while in App mode.</t>
-        </is>
-      </c>
-      <c r="D82" s="40" t="inlineStr">
-        <is>
-          <t>PASS if no un-waived [FPGA-XXX] line fails its ] OK [ check.</t>
-        </is>
-      </c>
-      <c r="E82" s="40" t="inlineStr">
-        <is>
-          <t>Likely bug: in the FPGA-NETWORK-on-M5 branch, the failure path does isfail += 1 — but the function only ever initializes a variable named fail = 0, never isfail. If that exact branch is hit (M5 stage, FPGA-NETWORK reports non-OK, and the message isn't the specific waived "one or more network links down" string), this will raise NameError: name 'isfail' is not defined instead of cleanly failing the test. Also implements a reboot self-heal: if PCIe status is "WARNING" while FPGA is in App mode (config_status == "0") and no .reboot marker file exists yet for this unit, it touches the marker and issues reboot immediately rather than failing — the next run after reboot either clears (marker removed, PASS) or fails hard if the WARNING persists (marker already present).</t>
-        </is>
-      </c>
-      <c r="F82" s="75" t="n"/>
-      <c r="G82" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="H82" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="I82" s="55" t="n"/>
-      <c r="J82" s="55" t="n"/>
-      <c r="K82" s="39" t="n"/>
-      <c r="L82" s="51" t="n"/>
-    </row>
-    <row r="83" s="80">
-      <c r="A83" s="81" t="n">
-        <v>80</v>
-      </c>
-      <c r="B83" s="82" t="inlineStr">
+      <c r="B79" s="82" t="inlineStr">
         <is>
           <t>pcie_cap_uart_chk</t>
         </is>
       </c>
-      <c r="C83" s="82" t="inlineStr">
+      <c r="C79" s="82" t="inlineStr">
         <is>
           <t>This test verifies the UART communication link between the BMC and the Castle Peak (CaP) card. It ensures that the BMC can successfully establish a UART session with the CaP device.</t>
         </is>
       </c>
-      <c r="D83" s="83" t="inlineStr">
+      <c r="D79" s="83" t="inlineStr">
         <is>
           <t>- BMC must be able to initiate and maintain a stable UART connection to the CaP card
 - The terminal must respond with expected outputs or prompt</t>
         </is>
       </c>
-      <c r="E83" s="83" t="n"/>
-      <c r="F83" s="84" t="inlineStr">
+      <c r="E79" s="83" t="n"/>
+      <c r="F79" s="84" t="inlineStr">
         <is>
           <t>[CMD] Send ssh command</t>
         </is>
       </c>
-      <c r="G83" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="H83" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="I83" s="84" t="n"/>
-      <c r="J83" s="84" t="n"/>
-      <c r="K83" s="85" t="n"/>
-      <c r="L83" s="86" t="n"/>
-    </row>
-    <row r="84" s="80">
-      <c r="A84" s="81" t="n">
-        <v>81</v>
-      </c>
-      <c r="B84" s="82" t="inlineStr">
+      <c r="G79" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="H79" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="I79" s="84" t="n"/>
+      <c r="J79" s="84" t="n"/>
+      <c r="K79" s="85" t="n"/>
+      <c r="L79" s="86" t="n"/>
+    </row>
+    <row r="80" s="80">
+      <c r="A80" s="81" t="n">
+        <v>77</v>
+      </c>
+      <c r="B80" s="82" t="inlineStr">
         <is>
           <t>pcie_cap_ppk_security_chk</t>
         </is>
       </c>
-      <c r="C84" s="82" t="inlineStr">
+      <c r="C80" s="82" t="inlineStr">
         <is>
           <t>Execute PPK test to check CaP card secure status.</t>
         </is>
       </c>
-      <c r="D84" s="83" t="inlineStr">
+      <c r="D80" s="83" t="inlineStr">
         <is>
           <t>Pass - return 0; Fail - return 1</t>
         </is>
       </c>
-      <c r="E84" s="83" t="inlineStr">
+      <c r="E80" s="83" t="inlineStr">
         <is>
           <t>- CMC (Tahoe)
 - OMC (Overlake Mgmt. Controller)
@@ -9500,45 +9335,189 @@
 &gt;&gt;&gt; Will be implemented in DVT.</t>
         </is>
       </c>
-      <c r="F84" s="84" t="inlineStr">
+      <c r="F80" s="84" t="inlineStr">
         <is>
           <t>"cerberus_utility fwversion
 cat obmc-console-OVL.log"</t>
         </is>
       </c>
-      <c r="G84" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="H84" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="I84" s="84" t="n"/>
-      <c r="J84" s="84" t="n"/>
-      <c r="K84" s="85" t="n"/>
-      <c r="L84" s="86" t="n"/>
-    </row>
-    <row r="85" ht="27" customHeight="1" s="80">
+      <c r="G80" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="H80" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="I80" s="84" t="n"/>
+      <c r="J80" s="84" t="n"/>
+      <c r="K80" s="85" t="n"/>
+      <c r="L80" s="86" t="n"/>
+    </row>
+    <row r="81" ht="27" customHeight="1" s="80">
+      <c r="A81" s="76" t="n">
+        <v>78</v>
+      </c>
+      <c r="B81" s="43" t="inlineStr">
+        <is>
+          <t>bmc_fan_qty_chk</t>
+        </is>
+      </c>
+      <c r="C81" s="43" t="inlineStr">
+        <is>
+          <t>Checks the number of fans reporting an "OK" SDR state against SF's bmc_fan_qty.</t>
+        </is>
+      </c>
+      <c r="D81" s="40" t="inlineStr">
+        <is>
+          <t>PASS if ipmitool sdr elist | grep -E "^Fan" | grep -ic ok equals getConfigValue('bmc_fan_qty').</t>
+        </is>
+      </c>
+      <c r="E81" s="40" t="inlineStr">
+        <is>
+          <t>Simple count check; no self-heal (a missing/failed fan is a physical issue, not a firmware one).</t>
+        </is>
+      </c>
+      <c r="F81" s="75" t="n"/>
+      <c r="G81" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="H81" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="I81" s="55" t="n"/>
+      <c r="J81" s="55" t="n"/>
+      <c r="K81" s="39" t="n"/>
+      <c r="L81" s="51" t="n"/>
+    </row>
+    <row r="82" ht="40.5" customHeight="1" s="80">
+      <c r="A82" s="76" t="n">
+        <v>79</v>
+      </c>
+      <c r="B82" s="43" t="inlineStr">
+        <is>
+          <t>bmc_fan_speed_chk</t>
+        </is>
+      </c>
+      <c r="C82" s="43" t="inlineStr">
+        <is>
+          <t>Sweeps fan duty cycle through 100%/50%/30% (100% skipped at M1 stage per an old thermal-noise waiver) and checks each fan's measured RPM against inlet/outlet min/max bounds for the detected fan vendor.</t>
+        </is>
+      </c>
+      <c r="D82" s="40" t="inlineStr">
+        <is>
+          <t>PASS if every fan's RPM at every tested duty point falls within its vendor-specific inlet/outlet min/max range.</t>
+        </is>
+      </c>
+      <c r="E82" s="40" t="inlineStr">
+        <is>
+          <t>After the sweep, fan mode is forced back to auto unconditionally, and at M1 stage specifically it's additionally set to a fixed 50% manual.</t>
+        </is>
+      </c>
+      <c r="F82" s="75" t="n"/>
+      <c r="G82" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="H82" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="I82" s="55" t="n"/>
+      <c r="J82" s="55" t="n"/>
+      <c r="K82" s="39" t="n"/>
+      <c r="L82" s="51" t="n"/>
+    </row>
+    <row r="83" ht="53.25" customHeight="1" s="80">
+      <c r="A83" s="76" t="n">
+        <v>80</v>
+      </c>
+      <c r="B83" s="43" t="inlineStr">
+        <is>
+          <t>storage_nvme_quantity_chk</t>
+        </is>
+      </c>
+      <c r="C83" s="43" t="inlineStr">
+        <is>
+          <t>Checks the number of enumerated NVMe devices against stge_nvme_cnt, with a self-heal attempt if more drives are found than expected</t>
+        </is>
+      </c>
+      <c r="D83" s="40" t="inlineStr">
+        <is>
+          <t>PASS if NVMe count equals stge_nvme_cnt (or the M1-stage E1.S-specific count variants).</t>
+        </is>
+      </c>
+      <c r="E83" s="40" t="inlineStr">
+        <is>
+          <t>Task 40165: "E1.S may arrive in MPF/TCG-locked state (e.g. swapped E1.S_2 with half-finished TCG)" — the recovery workaround is only attempted when the count is higher than expected, not lower; a lower-than-expected count goes straight to FAIL with no remediation.</t>
+        </is>
+      </c>
+      <c r="F83" s="75" t="n"/>
+      <c r="G83" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="H83" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="I83" s="55" t="n"/>
+      <c r="J83" s="55" t="n"/>
+      <c r="K83" s="39" t="n"/>
+      <c r="L83" s="51" t="n"/>
+    </row>
+    <row r="84" ht="40.5" customHeight="1" s="80">
+      <c r="A84" s="76" t="n">
+        <v>81</v>
+      </c>
+      <c r="B84" s="43" t="inlineStr">
+        <is>
+          <t>storage_hdd_func_test</t>
+        </is>
+      </c>
+      <c r="C84" s="43" t="inlineStr">
+        <is>
+          <t>Runs a random-access read/write functional test (tools/HDDtest --random) against every enumerated SATA and NVMe device.</t>
+        </is>
+      </c>
+      <c r="D84" s="40" t="inlineStr">
+        <is>
+          <t>PASS only if every device's HDDtest --random run returns 0; fails fast on the first bad device.</t>
+        </is>
+      </c>
+      <c r="E84" s="40" t="inlineStr">
+        <is>
+          <t>No retry/self-heal — a single device failure stops the loop and fails the whole test item immediately, so devices later in the enumeration order are never tested in that pass.</t>
+        </is>
+      </c>
+      <c r="F84" s="75" t="n"/>
+      <c r="G84" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="H84" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="I84" s="55" t="n"/>
+      <c r="J84" s="55" t="n"/>
+      <c r="K84" s="39" t="n"/>
+      <c r="L84" s="51" t="n"/>
+    </row>
+    <row r="85" ht="40.5" customHeight="1" s="80">
       <c r="A85" s="76" t="n">
         <v>82</v>
       </c>
       <c r="B85" s="43" t="inlineStr">
         <is>
-          <t>bmc_fan_qty_chk</t>
+          <t>storage_nvme_smart_chk</t>
         </is>
       </c>
       <c r="C85" s="43" t="inlineStr">
         <is>
-          <t>Checks the number of fans reporting an "OK" SDR state against SF's bmc_fan_qty.</t>
+          <t>Reads nvme smart-log for every enumerated NVMe device and checks Critical Warning, Percentage Used, Available Spare, Media Errors, and (Intel-only) CRC Error Count against thresholds.</t>
         </is>
       </c>
       <c r="D85" s="40" t="inlineStr">
         <is>
-          <t>PASS if ipmitool sdr elist | grep -E "^Fan" | grep -ic ok equals getConfigValue('bmc_fan_qty').</t>
+          <t>PASS if, per device: critical_warning == 0 (hex), percentage_used under threshold, available_spare &gt;= 99%, media_errors == 0, and (Intel drives only) CRC error count hasn't increased since the last recorded check.</t>
         </is>
       </c>
       <c r="E85" s="40" t="inlineStr">
         <is>
-          <t>Simple count check; no self-heal (a missing/failed fan is a physical issue, not a firmware one).</t>
+          <t>Percentage-Used check has a two-stage threshold — primary 5%; if exceeded, re-checked against stge_scale_pu_threshold config and only fails if it also exceeds that secondary threshold..</t>
         </is>
       </c>
       <c r="F85" s="75" t="n"/>
@@ -9553,28 +9532,28 @@
       <c r="K85" s="39" t="n"/>
       <c r="L85" s="51" t="n"/>
     </row>
-    <row r="86" ht="40.5" customHeight="1" s="80">
+    <row r="86" ht="53.25" customHeight="1" s="80">
       <c r="A86" s="76" t="n">
         <v>83</v>
       </c>
       <c r="B86" s="43" t="inlineStr">
         <is>
-          <t>bmc_fan_speed_chk</t>
+          <t>pcie_device_chk</t>
         </is>
       </c>
       <c r="C86" s="43" t="inlineStr">
         <is>
-          <t>Sweeps fan duty cycle through 100%/50%/30% (100% skipped at M1 stage per an old thermal-noise waiver) and checks each fan's measured RPM against inlet/outlet min/max bounds for the detected fan vendor.</t>
+          <t>Checks each configured PCIe device's link speed, width, and (optionally) vendor:device ID against a hardcoded expected list, plus verifies all E1.S slots use a consistent vendor (no mixed Samsung/Hynix).</t>
         </is>
       </c>
       <c r="D86" s="40" t="inlineStr">
         <is>
-          <t>PASS if every fan's RPM at every tested duty point falls within its vendor-specific inlet/outlet min/max range.</t>
+          <t>PASS if, for every entry in the resolved pcie device list, the lspci -D -nn -vvv reported speed/width (and vendor:device ID, if the config line includes it) match, AND all E1.S bus entries report the same vendor ID. FAIL on any mismatch or malformed config-line entry.</t>
         </is>
       </c>
       <c r="E86" s="40" t="inlineStr">
         <is>
-          <t>After the sweep, fan mode is forced back to auto unconditionally, and at M1 stage specifically it's additionally set to a fixed 50% manual.</t>
+          <t>VID:PID checking can be disabled via an args={"viddid": False} option.</t>
         </is>
       </c>
       <c r="F86" s="75" t="n"/>
@@ -9589,28 +9568,28 @@
       <c r="K86" s="39" t="n"/>
       <c r="L86" s="51" t="n"/>
     </row>
-    <row r="87" ht="53.25" customHeight="1" s="80">
+    <row r="87" ht="27" customHeight="1" s="80">
       <c r="A87" s="76" t="n">
         <v>84</v>
       </c>
       <c r="B87" s="43" t="inlineStr">
         <is>
-          <t>storage_nvme_quantity_chk</t>
+          <t>pcie_cmp_chk</t>
         </is>
       </c>
       <c r="C87" s="43" t="inlineStr">
         <is>
-          <t>Checks the number of enumerated NVMe devices against stge_nvme_cnt, with a self-heal attempt if more drives are found than expected</t>
+          <t>Compares the full enumerated PCIe device topology (PCIe_py -c) against a golden reference file specific to this model/PN/M.2-vendor/E1.S-vendor.</t>
         </is>
       </c>
       <c r="D87" s="40" t="inlineStr">
         <is>
-          <t>PASS if NVMe count equals stge_nvme_cnt (or the M1-stage E1.S-specific count variants).</t>
+          <t>PASS if PCIe_py -c {goldenfile} returns 0.</t>
         </is>
       </c>
       <c r="E87" s="40" t="inlineStr">
         <is>
-          <t>Task 40165: "E1.S may arrive in MPF/TCG-locked state (e.g. swapped E1.S_2 with half-finished TCG)" — the recovery workaround is only attempted when the count is higher than expected, not lower; a lower-than-expected count goes straight to FAIL with no remediation.</t>
+          <t>Auto-generating the golden file on first run for a given combination.</t>
         </is>
       </c>
       <c r="F87" s="75" t="n"/>
@@ -9625,28 +9604,28 @@
       <c r="K87" s="39" t="n"/>
       <c r="L87" s="51" t="n"/>
     </row>
-    <row r="88" ht="40.5" customHeight="1" s="80">
+    <row r="88" ht="27" customHeight="1" s="80">
       <c r="A88" s="76" t="n">
         <v>85</v>
       </c>
       <c r="B88" s="43" t="inlineStr">
         <is>
-          <t>storage_hdd_func_test</t>
+          <t>bmc_batvolt_chk</t>
         </is>
       </c>
       <c r="C88" s="43" t="inlineStr">
         <is>
-          <t>Runs a random-access read/write functional test (tools/HDDtest --random) against every enumerated SATA and NVMe device.</t>
+          <t>Checks the RTC/CMOS battery voltage sensor reading against a configured lower bound.</t>
         </is>
       </c>
       <c r="D88" s="40" t="inlineStr">
         <is>
-          <t>PASS only if every device's HDDtest --random run returns 0; fails fast on the first bad device.</t>
+          <t>PASS if ipmitool sdr elist | grep 'BAT' | awk '{print $9}' (as float) is &gt;= bmc_batvolt_lower_bound.</t>
         </is>
       </c>
       <c r="E88" s="40" t="inlineStr">
         <is>
-          <t>No retry/self-heal — a single device failure stops the loop and fails the whole test item immediately, so devices later in the enumeration order are never tested in that pass.</t>
+          <t>FAILs explicitly if ipmitool can't detect the battery voltage sensor at all — distinguished from a low-but-present reading.</t>
         </is>
       </c>
       <c r="F88" s="75" t="n"/>
@@ -9661,30 +9640,26 @@
       <c r="K88" s="39" t="n"/>
       <c r="L88" s="51" t="n"/>
     </row>
-    <row r="89" ht="40.5" customHeight="1" s="80">
+    <row r="89" ht="27" customHeight="1" s="80">
       <c r="A89" s="76" t="n">
         <v>86</v>
       </c>
       <c r="B89" s="43" t="inlineStr">
         <is>
-          <t>storage_nvme_smart_chk</t>
+          <t>tpm_qty_chk</t>
         </is>
       </c>
       <c r="C89" s="43" t="inlineStr">
         <is>
-          <t>Reads nvme smart-log for every enumerated NVMe device and checks Critical Warning, Percentage Used, Available Spare, Media Errors, and (Intel-only) CRC Error Count against thresholds.</t>
+          <t>Checks the number of detected TPM 2.0 devices against an internal expected count (self._tpm_num, a class attribute rather than an SF config value).</t>
         </is>
       </c>
       <c r="D89" s="40" t="inlineStr">
         <is>
-          <t>PASS if, per device: critical_warning == 0 (hex), percentage_used under threshold, available_spare &gt;= 99%, media_errors == 0, and (Intel drives only) CRC error count hasn't increased since the last recorded check.</t>
-        </is>
-      </c>
-      <c r="E89" s="40" t="inlineStr">
-        <is>
-          <t>Percentage-Used check has a two-stage threshold — primary 5%; if exceeded, re-checked against stge_scale_pu_threshold config and only fails if it also exceeds that secondary threshold..</t>
-        </is>
-      </c>
+          <t>PASS if ls /dev/tpm* | grep -v tpmrm | wc -l equals self._tpm_num.</t>
+        </is>
+      </c>
+      <c r="E89" s="40" t="n"/>
       <c r="F89" s="75" t="n"/>
       <c r="G89" s="55" t="b">
         <v>0</v>
@@ -9697,184 +9672,44 @@
       <c r="K89" s="39" t="n"/>
       <c r="L89" s="51" t="n"/>
     </row>
-    <row r="90" ht="53.25" customHeight="1" s="80">
+    <row r="90" ht="27" customHeight="1" s="80">
       <c r="A90" s="76" t="n">
         <v>87</v>
       </c>
       <c r="B90" s="43" t="inlineStr">
         <is>
-          <t>pcie_device_chk</t>
+          <t>tpm_func_test</t>
         </is>
       </c>
       <c r="C90" s="43" t="inlineStr">
         <is>
-          <t>Checks each configured PCIe device's link speed, width, and (optionally) vendor:device ID against a hardcoded expected list, plus verifies all E1.S slots use a consistent vendor (no mixed Samsung/Hynix).</t>
+          <t>Runs the TPM 2.0 full and not-full self-tests (eltt2 -t full / eltt2 -t not_full) and a "get value" sanity read (eltt2 -g).</t>
         </is>
       </c>
       <c r="D90" s="40" t="inlineStr">
         <is>
-          <t>PASS if, for every entry in the resolved pcie device list, the lspci -D -nn -vvv reported speed/width (and vendor:device ID, if the config line includes it) match, AND all E1.S bus entries report the same vendor ID. FAIL on any mismatch or malformed config-line entry.</t>
-        </is>
-      </c>
-      <c r="E90" s="40" t="inlineStr">
-        <is>
-          <t>VID:PID checking can be disabled via an args={"viddid": False} option.</t>
-        </is>
-      </c>
-      <c r="F90" s="75" t="n"/>
-      <c r="G90" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="H90" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="I90" s="55" t="n"/>
-      <c r="J90" s="55" t="n"/>
-      <c r="K90" s="39" t="n"/>
-      <c r="L90" s="51" t="n"/>
-    </row>
-    <row r="91" ht="27" customHeight="1" s="80">
-      <c r="A91" s="76" t="n">
-        <v>88</v>
-      </c>
-      <c r="B91" s="43" t="inlineStr">
-        <is>
-          <t>pcie_cmp_chk</t>
-        </is>
-      </c>
-      <c r="C91" s="43" t="inlineStr">
-        <is>
-          <t>Compares the full enumerated PCIe device topology (PCIe_py -c) against a golden reference file specific to this model/PN/M.2-vendor/E1.S-vendor.</t>
-        </is>
-      </c>
-      <c r="D91" s="40" t="inlineStr">
-        <is>
-          <t>PASS if PCIe_py -c {goldenfile} returns 0.</t>
-        </is>
-      </c>
-      <c r="E91" s="40" t="inlineStr">
-        <is>
-          <t>Auto-generating the golden file on first run for a given combination.</t>
-        </is>
-      </c>
-      <c r="F91" s="75" t="n"/>
-      <c r="G91" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="H91" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="I91" s="55" t="n"/>
-      <c r="J91" s="55" t="n"/>
-      <c r="K91" s="39" t="n"/>
-      <c r="L91" s="51" t="n"/>
-    </row>
-    <row r="92" ht="27" customHeight="1" s="80">
-      <c r="A92" s="76" t="n">
-        <v>89</v>
-      </c>
-      <c r="B92" s="43" t="inlineStr">
-        <is>
-          <t>bmc_batvolt_chk</t>
-        </is>
-      </c>
-      <c r="C92" s="43" t="inlineStr">
-        <is>
-          <t>Checks the RTC/CMOS battery voltage sensor reading against a configured lower bound.</t>
-        </is>
-      </c>
-      <c r="D92" s="40" t="inlineStr">
-        <is>
-          <t>PASS if ipmitool sdr elist | grep 'BAT' | awk '{print $9}' (as float) is &gt;= bmc_batvolt_lower_bound.</t>
-        </is>
-      </c>
-      <c r="E92" s="40" t="inlineStr">
-        <is>
-          <t>FAILs explicitly if ipmitool can't detect the battery voltage sensor at all — distinguished from a low-but-present reading.</t>
-        </is>
-      </c>
-      <c r="F92" s="75" t="n"/>
-      <c r="G92" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="H92" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="I92" s="55" t="n"/>
-      <c r="J92" s="55" t="n"/>
-      <c r="K92" s="39" t="n"/>
-      <c r="L92" s="51" t="n"/>
-    </row>
-    <row r="93" ht="27" customHeight="1" s="80">
-      <c r="A93" s="76" t="n">
-        <v>90</v>
-      </c>
-      <c r="B93" s="43" t="inlineStr">
-        <is>
-          <t>tpm_qty_chk</t>
-        </is>
-      </c>
-      <c r="C93" s="43" t="inlineStr">
-        <is>
-          <t>Checks the number of detected TPM 2.0 devices against an internal expected count (self._tpm_num, a class attribute rather than an SF config value).</t>
-        </is>
-      </c>
-      <c r="D93" s="40" t="inlineStr">
-        <is>
-          <t>PASS if ls /dev/tpm* | grep -v tpmrm | wc -l equals self._tpm_num.</t>
-        </is>
-      </c>
-      <c r="E93" s="40" t="n"/>
-      <c r="F93" s="75" t="n"/>
-      <c r="G93" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="H93" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="I93" s="55" t="n"/>
-      <c r="J93" s="55" t="n"/>
-      <c r="K93" s="39" t="n"/>
-      <c r="L93" s="51" t="n"/>
-    </row>
-    <row r="94" ht="27" customHeight="1" s="80">
-      <c r="A94" s="76" t="n">
-        <v>91</v>
-      </c>
-      <c r="B94" s="43" t="inlineStr">
-        <is>
-          <t>tpm_func_test</t>
-        </is>
-      </c>
-      <c r="C94" s="43" t="inlineStr">
-        <is>
-          <t>Runs the TPM 2.0 full and not-full self-tests (eltt2 -t full / eltt2 -t not_full) and a "get value" sanity read (eltt2 -g).</t>
-        </is>
-      </c>
-      <c r="D94" s="40" t="inlineStr">
-        <is>
           <t>PASS only if all three sub-commands (full selftest, not-full selftest, get-value) return exit code 0.</t>
         </is>
       </c>
-      <c r="E94" s="40" t="n"/>
-      <c r="F94" s="43" t="inlineStr">
+      <c r="E90" s="40" t="n"/>
+      <c r="F90" s="43" t="inlineStr">
         <is>
           <t>[ Check powershelf firmware version ] show powershelf psu info -s {INDEX} Capability IC Device ID Manufacturer ID Manufacturer Model Manufacturer Revision Manufacturer Serial Completion Code - - - - - If mismatch - - - - - [ Upgrade Rack SCM firmware version ] C heck fw package exists in RSCM show manager tftp list Upload fw to Rack-SCM set manager tftp get -s {IP} -f {FILE} Fw Upgrade set manager cerberus cmd -c pcdupdate /usr/srvroot/shared/{FILE}</t>
         </is>
       </c>
-      <c r="G94" s="47" t="n"/>
-      <c r="H94" s="47" t="b">
+      <c r="G90" s="47" t="n"/>
+      <c r="H90" s="47" t="b">
         <v>1</v>
       </c>
-      <c r="I94" s="41" t="inlineStr">
+      <c r="I90" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">PSU SN (traceability only, not a pass/fail criterion): ['P831061850674041', 'P831061851642041', 'P831061851637041', 'P831061850968041', 'P831061824386041', 'P831061851683041']
 [PASS] Check PSU location PASS
 </t>
         </is>
       </c>
-      <c r="J94" s="41" t="n"/>
-      <c r="K94" s="42" t="inlineStr">
+      <c r="J90" s="41" t="n"/>
+      <c r="K90" s="42" t="inlineStr">
         <is>
           <t>Rack SCM Powershelf PSU 1 Version Check PASS. EXP: 000F0F00 GET: 000F0F00
 Rack SCM Powershelf PSU 2 Version Check PASS. EXP: 000F0F00 GET: 000F0F00
@@ -9886,41 +9721,41 @@
 [PASS] Rack Power Shelf(PSU) FW CHECK PASS</t>
         </is>
       </c>
-      <c r="L94" s="31" t="n"/>
-      <c r="M94" s="18" t="n"/>
-      <c r="N94" s="37" t="n"/>
-      <c r="O94" s="18" t="n"/>
-      <c r="P94" s="19" t="n"/>
-      <c r="Q94" s="17" t="n"/>
-      <c r="R94" s="17" t="n"/>
-      <c r="S94" s="17" t="n"/>
-      <c r="T94" s="17" t="n"/>
-      <c r="U94" s="17" t="n"/>
-      <c r="V94" s="17" t="n"/>
-      <c r="W94" s="17" t="n"/>
-      <c r="X94" s="17" t="n"/>
-      <c r="Y94" s="17" t="n"/>
-    </row>
-    <row r="95" s="80">
-      <c r="A95" s="81" t="n">
-        <v>92</v>
-      </c>
-      <c r="B95" s="82" t="inlineStr">
+      <c r="L90" s="31" t="n"/>
+      <c r="M90" s="18" t="n"/>
+      <c r="N90" s="37" t="n"/>
+      <c r="O90" s="18" t="n"/>
+      <c r="P90" s="19" t="n"/>
+      <c r="Q90" s="17" t="n"/>
+      <c r="R90" s="17" t="n"/>
+      <c r="S90" s="17" t="n"/>
+      <c r="T90" s="17" t="n"/>
+      <c r="U90" s="17" t="n"/>
+      <c r="V90" s="17" t="n"/>
+      <c r="W90" s="17" t="n"/>
+      <c r="X90" s="17" t="n"/>
+      <c r="Y90" s="17" t="n"/>
+    </row>
+    <row r="91" s="80">
+      <c r="A91" s="81" t="n">
+        <v>88</v>
+      </c>
+      <c r="B91" s="82" t="inlineStr">
         <is>
           <t>ccr_test</t>
         </is>
       </c>
-      <c r="C95" s="82" t="inlineStr">
+      <c r="C91" s="82" t="inlineStr">
         <is>
           <t>Check switch cable mapping</t>
         </is>
       </c>
-      <c r="D95" s="83" t="inlineStr">
+      <c r="D91" s="83" t="inlineStr">
         <is>
           <t>Pass - return 0; Fail - return 1</t>
         </is>
       </c>
-      <c r="E95" s="83" t="inlineStr">
+      <c r="E91" s="83" t="inlineStr">
         <is>
           <t>- Only the master node initiates mapping and updates `mac_table.txt`.
 - Slave nodes wait for the file and perform comparison based on it.
@@ -9929,52 +9764,52 @@
 &gt;&gt;&gt;For DV NV rack only.</t>
         </is>
       </c>
-      <c r="F95" s="84" t="n"/>
-      <c r="G95" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="H95" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="I95" s="84" t="n"/>
-      <c r="J95" s="84" t="n"/>
-      <c r="K95" s="85" t="n"/>
-      <c r="L95" s="86" t="n"/>
-    </row>
-    <row r="96" s="80">
-      <c r="A96" s="76" t="n">
-        <v>93</v>
-      </c>
-      <c r="B96" s="43" t="inlineStr">
+      <c r="F91" s="84" t="n"/>
+      <c r="G91" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="H91" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="I91" s="84" t="n"/>
+      <c r="J91" s="84" t="n"/>
+      <c r="K91" s="85" t="n"/>
+      <c r="L91" s="86" t="n"/>
+    </row>
+    <row r="92" s="80">
+      <c r="A92" s="76" t="n">
+        <v>89</v>
+      </c>
+      <c r="B92" s="43" t="inlineStr">
         <is>
           <t>uut_pic_test</t>
         </is>
       </c>
-      <c r="C96" s="43" t="inlineStr">
+      <c r="C92" s="43" t="inlineStr">
         <is>
           <t>Runs a PIC (Programmable Interrupt Controller) functional test command.</t>
         </is>
       </c>
-      <c r="D96" s="40" t="inlineStr">
+      <c r="D92" s="40" t="inlineStr">
         <is>
           <t>PASS if self.cmd_lst['uut_test_pic'] returns exit code 0.</t>
         </is>
       </c>
-      <c r="E96" s="40" t="inlineStr">
+      <c r="E92" s="40" t="inlineStr">
         <is>
           <t>Minimal wrapper, no special edge cases.</t>
         </is>
       </c>
-      <c r="F96" s="43" t="inlineStr">
+      <c r="F92" s="43" t="inlineStr">
         <is>
           <t>[Check RSCM Cerberus Version] show manager cerberus version - - - - - If mismatch - - - - - [Upgrade RSCM Cerberus] set manager cerberus update -f {FILE} [Check RSCM Cerberus PCD ID] set manager cerberus cmd -c pcdid - - - - - If mismatch - - - - - [Upgrade RSCM Cerberus PCD ID] set manager cerberus cmd -c pcdupdate /usr/srvroot/shared/{FILE} [Check RSCM Cerberus PFM ID] show manager cerberus pfm id -p 1 -r 0 - - - - - If mismatch - - - - - [Upgrade RSCM Cerberus PFM ID] set manager cerberus pfm update -f {FILE} -p 1 [Get RSCM information FAIL] show manager version - - - - - If mismatch - - - - - [Upgrade RSCM information] set manager fwupdate -f {FILE} [Check RSCM CPLD version] show manager cpld version - - - - - If mismatch - - - - - [Upgrade RSCM CPLD version] set manager cpld update -f {FILE}</t>
         </is>
       </c>
-      <c r="G96" s="47" t="n"/>
-      <c r="H96" s="47" t="b">
+      <c r="G92" s="47" t="n"/>
+      <c r="H92" s="47" t="b">
         <v>1</v>
       </c>
-      <c r="I96" s="41" t="inlineStr">
+      <c r="I92" s="41" t="inlineStr">
         <is>
           <t>Rack SCM Powershelf PSU 1 Version Check PASS. EXP: 000F0F00 GET: 000F0F00
 ...
@@ -9983,8 +9818,8 @@
 [PASS] Rack Power Shelf(PSU) FW CHECK PASS</t>
         </is>
       </c>
-      <c r="J96" s="41" t="n"/>
-      <c r="K96" s="42" t="inlineStr">
+      <c r="J92" s="41" t="n"/>
+      <c r="K92" s="42" t="inlineStr">
         <is>
           <t>Check RSCM Cerberus Version PASS. Exp:1.5.7.5 Get:1.5.7.5
 Check RSCM PCD Version ID PASS. SF:0x1 Get:0x1
@@ -9999,11 +9834,227 @@
 Check All RSCM Version PASS.</t>
         </is>
       </c>
-      <c r="L96" s="31" t="inlineStr">
+      <c r="L92" s="31" t="inlineStr">
         <is>
           <t>Matches CRD: Cerberus 1.5.7.5, PFMID 0x3DA, PCD M4011/0x1, R-SCM 1.31.6, CPLD V3.5.</t>
         </is>
       </c>
+      <c r="M92" s="18" t="n"/>
+      <c r="N92" s="37" t="n"/>
+      <c r="O92" s="18" t="n"/>
+      <c r="P92" s="19" t="n"/>
+      <c r="Q92" s="17" t="n"/>
+      <c r="R92" s="17" t="n"/>
+      <c r="S92" s="17" t="n"/>
+      <c r="T92" s="17" t="n"/>
+      <c r="U92" s="17" t="n"/>
+      <c r="V92" s="17" t="n"/>
+      <c r="W92" s="17" t="n"/>
+      <c r="X92" s="17" t="n"/>
+      <c r="Y92" s="17" t="n"/>
+    </row>
+    <row r="93" s="80">
+      <c r="A93" s="76" t="n">
+        <v>90</v>
+      </c>
+      <c r="B93" s="43" t="inlineStr">
+        <is>
+          <t>uut_hpet_test</t>
+        </is>
+      </c>
+      <c r="C93" s="43" t="inlineStr">
+        <is>
+          <t>Runs an HPET (High Precision Event Timer) functional test command.</t>
+        </is>
+      </c>
+      <c r="D93" s="40" t="inlineStr">
+        <is>
+          <t>PASS if self.cmd_lst['uut_test_hpet'] returns exit code 0.</t>
+        </is>
+      </c>
+      <c r="E93" s="40" t="inlineStr">
+        <is>
+          <t>Minimal wrapper, structurally identical to uut_pic_test.</t>
+        </is>
+      </c>
+      <c r="F93" s="43" t="inlineStr">
+        <is>
+          <t>[ Get system info via R-SCM ] show system info -i { RM_PORT } Mac Address SerialNumber BiosVersion BMCVersion CpldVersion DCSCMCpldVersion Count TotalSystemMemoryGib - - - - - If mismatch - - - - - [ Upgrade system firmware version ] set system file put -i {PORT} -f {FILE} set system bios update -i {PORT} -f {FILE} set system bmc update -i {PORT} -f {FILE}</t>
+        </is>
+      </c>
+      <c r="G93" s="47" t="b">
+        <v>1</v>
+      </c>
+      <c r="H93" s="47" t="b">
+        <v>1</v>
+      </c>
+      <c r="I93" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mac Address              check PASS. Get:             0427283DD689, Exp:             0427283DD689
+SerialNumber             check PASS. Get:         P54376354001203A, Exp:         P54376354001203A
+BiosVersion              check PASS. Get:     C44AD.0.BS.1C11.GN.1, Exp:     C44AD.0.BS.1C11.GN.1
+BMCVersion               check PASS. Get:                  26.4.24, Exp:                  26.4.24
+ CpldVersion             check PASS. Get:                 02.06.00, Exp:                 02.06.00
+DCSCMCpldVersion         check PASS. Get:                 03.06.00, Exp:                 03.06.00
+Count                    check PASS. Get:                        2, Exp:                        2
+TotalSystemMemoryGib     check PASS. Get:                      512, Exp:                      512
+[PASS] Check system info via R-SCM PASS
+</t>
+        </is>
+      </c>
+      <c r="J93" s="41" t="n"/>
+      <c r="K93" s="42" t="inlineStr">
+        <is>
+          <t>Mac Address              check PASS. Get:             0427283DD689, Exp:             0427283DD689
+SerialNumber             check PASS. Get:         P54376354001203A, Exp:         P54376354001203A
+BiosVersion              check PASS. Get:     C44AD.0.BS.1C11.GN.1, Exp:     C44AD.0.BS.1C11.GN.1
+BMCVersion               check PASS. Get:                  26.4.24, Exp:                  26.4.24
+CpldVersion             check PASS. Get:                 02.06.00, Exp:                 02.06.00
+DCSCMCpldVersion         check PASS. Get:                 03.06.00, Exp:                 03.06.00
+Count                    check PASS. Get:                        2, Exp:                        2
+TotalSystemMemoryGib     check PASS. Get:                      512, Exp:                      512
+[PASS] Check system info via R-SCM PASS"</t>
+        </is>
+      </c>
+      <c r="L93" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Matches CRD: BIOS C44AD.0.BS.1C11.GN.1, BMC 26.04.24, MB CPLD 02.06.00, DC-SCM CPLD 03.06.00, 512 GiB, 2 CPU.
+</t>
+        </is>
+      </c>
+      <c r="M93" s="18" t="n"/>
+      <c r="N93" s="37" t="n"/>
+      <c r="O93" s="18" t="n"/>
+      <c r="P93" s="19" t="n"/>
+      <c r="Q93" s="17" t="n"/>
+      <c r="R93" s="17" t="n"/>
+      <c r="S93" s="17" t="n"/>
+      <c r="T93" s="17" t="n"/>
+      <c r="U93" s="17" t="n"/>
+      <c r="V93" s="17" t="n"/>
+      <c r="W93" s="17" t="n"/>
+      <c r="X93" s="17" t="n"/>
+      <c r="Y93" s="17" t="n"/>
+    </row>
+    <row r="94" s="80">
+      <c r="A94" s="81" t="n">
+        <v>91</v>
+      </c>
+      <c r="B94" s="82" t="inlineStr">
+        <is>
+          <t>bios_cmos_test</t>
+        </is>
+      </c>
+      <c r="C94" s="82" t="inlineStr">
+        <is>
+          <t>Test the BIOS CMOS functionality by verifying the read/write capability of CMOS registers and checking battery and CMOS operation status.</t>
+        </is>
+      </c>
+      <c r="D94" s="83" t="inlineStr">
+        <is>
+          <t>Pass - return 0; Fail - return 1</t>
+        </is>
+      </c>
+      <c r="E94" s="83" t="inlineStr">
+        <is>
+          <t>&gt;&gt;&gt;MTE agreed to waive in EVT. ADO#2909063</t>
+        </is>
+      </c>
+      <c r="F94" s="84" t="inlineStr">
+        <is>
+          <t>[Execute CMOS test]
+CMOStest -d</t>
+        </is>
+      </c>
+      <c r="G94" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="H94" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="I94" s="84" t="n"/>
+      <c r="J94" s="84" t="n"/>
+      <c r="K94" s="85" t="n"/>
+      <c r="L94" s="86" t="n"/>
+    </row>
+    <row r="95" ht="27" customHeight="1" s="80">
+      <c r="A95" s="76" t="n">
+        <v>92</v>
+      </c>
+      <c r="B95" s="43" t="inlineStr">
+        <is>
+          <t>bmc_sel_chk</t>
+        </is>
+      </c>
+      <c r="C95" s="43" t="inlineStr">
+        <is>
+          <t>A plain BMC SEL check, run late in the flow after all functional tests have completed, right before the final SDR/dmesg/syslog snapshot and SEL clear.</t>
+        </is>
+      </c>
+      <c r="D95" s="40" t="inlineStr">
+        <is>
+          <t>PASS if returns truthy (no un-whitelisted SEL entries found). FAIL otherwise.</t>
+        </is>
+      </c>
+      <c r="E95" s="40" t="inlineStr">
+        <is>
+          <t>Different call site/intent (post-functional-test SEL sweep vs. pre-test boot-time SEL sweep), same underlying logic.</t>
+        </is>
+      </c>
+      <c r="F95" s="75" t="n"/>
+      <c r="G95" s="78" t="b">
+        <v>0</v>
+      </c>
+      <c r="H95" s="78" t="b">
+        <v>0</v>
+      </c>
+      <c r="I95" s="55" t="n"/>
+      <c r="J95" s="55" t="n"/>
+      <c r="L95" s="31" t="n"/>
+      <c r="M95" s="18" t="n"/>
+      <c r="N95" s="37" t="n"/>
+      <c r="O95" s="18" t="n"/>
+      <c r="P95" s="19" t="n"/>
+      <c r="Q95" s="17" t="n"/>
+      <c r="R95" s="17" t="n"/>
+      <c r="S95" s="17" t="n"/>
+      <c r="T95" s="17" t="n"/>
+      <c r="U95" s="17" t="n"/>
+      <c r="V95" s="17" t="n"/>
+      <c r="W95" s="17" t="n"/>
+      <c r="X95" s="17" t="n"/>
+      <c r="Y95" s="17" t="n"/>
+    </row>
+    <row r="96" ht="27" customHeight="1" s="80">
+      <c r="A96" s="76" t="n">
+        <v>93</v>
+      </c>
+      <c r="B96" s="43" t="inlineStr">
+        <is>
+          <t>bmc_sdr_chk</t>
+        </is>
+      </c>
+      <c r="C96" s="43" t="inlineStr">
+        <is>
+          <t>Validates BMC Sensor Data Record contents (all sensor readings within expected bounds).</t>
+        </is>
+      </c>
+      <c r="D96" s="40" t="inlineStr">
+        <is>
+          <t>PASS if ipmitool sdr elist succeeds. FAIL otherwise.</t>
+        </is>
+      </c>
+      <c r="E96" s="40" t="n"/>
+      <c r="F96" s="75" t="n"/>
+      <c r="G96" s="78" t="b">
+        <v>0</v>
+      </c>
+      <c r="H96" s="78" t="b">
+        <v>0</v>
+      </c>
+      <c r="I96" s="55" t="n"/>
+      <c r="J96" s="55" t="n"/>
+      <c r="L96" s="31" t="n"/>
       <c r="M96" s="18" t="n"/>
       <c r="N96" s="37" t="n"/>
       <c r="O96" s="18" t="n"/>
@@ -10018,75 +10069,36 @@
       <c r="X96" s="17" t="n"/>
       <c r="Y96" s="17" t="n"/>
     </row>
-    <row r="97" s="80">
+    <row r="97" ht="27" customHeight="1" s="80">
       <c r="A97" s="76" t="n">
         <v>94</v>
       </c>
       <c r="B97" s="43" t="inlineStr">
         <is>
-          <t>uut_hpet_test</t>
+          <t>uut_dmesg_chk</t>
         </is>
       </c>
       <c r="C97" s="43" t="inlineStr">
         <is>
-          <t>Runs an HPET (High Precision Event Timer) functional test command.</t>
+          <t>Captures dmesg, lspci -vvv, and ras-mc-ctl --errors, then filters against an allow-list and a CSV-driven bypass filter list to detect real kernel errors.</t>
         </is>
       </c>
       <c r="D97" s="40" t="inlineStr">
         <is>
-          <t>PASS if self.cmd_lst['uut_test_hpet'] returns exit code 0.</t>
-        </is>
-      </c>
-      <c r="E97" s="40" t="inlineStr">
-        <is>
-          <t>Minimal wrapper, structurally identical to uut_pic_test.</t>
-        </is>
-      </c>
-      <c r="F97" s="43" t="inlineStr">
-        <is>
-          <t>[ Get system info via R-SCM ] show system info -i { RM_PORT } Mac Address SerialNumber BiosVersion BMCVersion CpldVersion DCSCMCpldVersion Count TotalSystemMemoryGib - - - - - If mismatch - - - - - [ Upgrade system firmware version ] set system file put -i {PORT} -f {FILE} set system bios update -i {PORT} -f {FILE} set system bmc update -i {PORT} -f {FILE}</t>
-        </is>
-      </c>
-      <c r="G97" s="47" t="b">
-        <v>1</v>
-      </c>
-      <c r="H97" s="47" t="b">
-        <v>1</v>
-      </c>
-      <c r="I97" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mac Address              check PASS. Get:             0427283DD689, Exp:             0427283DD689
-SerialNumber             check PASS. Get:         P54376354001203A, Exp:         P54376354001203A
-BiosVersion              check PASS. Get:     C44AD.0.BS.1C11.GN.1, Exp:     C44AD.0.BS.1C11.GN.1
-BMCVersion               check PASS. Get:                  26.4.24, Exp:                  26.4.24
- CpldVersion             check PASS. Get:                 02.06.00, Exp:                 02.06.00
-DCSCMCpldVersion         check PASS. Get:                 03.06.00, Exp:                 03.06.00
-Count                    check PASS. Get:                        2, Exp:                        2
-TotalSystemMemoryGib     check PASS. Get:                      512, Exp:                      512
-[PASS] Check system info via R-SCM PASS
-</t>
-        </is>
-      </c>
-      <c r="J97" s="41" t="n"/>
-      <c r="K97" s="42" t="inlineStr">
-        <is>
-          <t>Mac Address              check PASS. Get:             0427283DD689, Exp:             0427283DD689
-SerialNumber             check PASS. Get:         P54376354001203A, Exp:         P54376354001203A
-BiosVersion              check PASS. Get:     C44AD.0.BS.1C11.GN.1, Exp:     C44AD.0.BS.1C11.GN.1
-BMCVersion               check PASS. Get:                  26.4.24, Exp:                  26.4.24
-CpldVersion             check PASS. Get:                 02.06.00, Exp:                 02.06.00
-DCSCMCpldVersion         check PASS. Get:                 03.06.00, Exp:                 03.06.00
-Count                    check PASS. Get:                        2, Exp:                        2
-TotalSystemMemoryGib     check PASS. Get:                      512, Exp:                      512
-[PASS] Check system info via R-SCM PASS"</t>
-        </is>
-      </c>
-      <c r="L97" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Matches CRD: BIOS C44AD.0.BS.1C11.GN.1, BMC 26.04.24, MB CPLD 02.06.00, DC-SCM CPLD 03.06.00, 512 GiB, 2 CPU.
-</t>
-        </is>
-      </c>
+          <t>PASS if, after filtering, no un-bypassed error lines remain in dmesg. FAIL if any survive filtering, or if the filter list file is missing/fails.</t>
+        </is>
+      </c>
+      <c r="E97" s="40" t="n"/>
+      <c r="F97" s="75" t="n"/>
+      <c r="G97" s="78" t="b">
+        <v>0</v>
+      </c>
+      <c r="H97" s="78" t="b">
+        <v>0</v>
+      </c>
+      <c r="I97" s="55" t="n"/>
+      <c r="J97" s="55" t="n"/>
+      <c r="L97" s="31" t="n"/>
       <c r="M97" s="18" t="n"/>
       <c r="N97" s="37" t="n"/>
       <c r="O97" s="18" t="n"/>
@@ -10101,46 +10113,49 @@
       <c r="X97" s="17" t="n"/>
       <c r="Y97" s="17" t="n"/>
     </row>
-    <row r="98" s="80">
-      <c r="A98" s="81" t="n">
+    <row r="98" ht="27" customHeight="1" s="80">
+      <c r="A98" s="76" t="n">
         <v>95</v>
       </c>
-      <c r="B98" s="82" t="inlineStr">
-        <is>
-          <t>bios_cmos_test</t>
-        </is>
-      </c>
-      <c r="C98" s="82" t="inlineStr">
-        <is>
-          <t>Test the BIOS CMOS functionality by verifying the read/write capability of CMOS registers and checking battery and CMOS operation status.</t>
-        </is>
-      </c>
-      <c r="D98" s="83" t="inlineStr">
-        <is>
-          <t>Pass - return 0; Fail - return 1</t>
-        </is>
-      </c>
-      <c r="E98" s="83" t="inlineStr">
-        <is>
-          <t>&gt;&gt;&gt;MTE agreed to waive in EVT. ADO#2909063</t>
-        </is>
-      </c>
-      <c r="F98" s="84" t="inlineStr">
-        <is>
-          <t>[Execute CMOS test]
-CMOStest -d</t>
-        </is>
-      </c>
-      <c r="G98" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="H98" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="I98" s="84" t="n"/>
-      <c r="J98" s="84" t="n"/>
-      <c r="K98" s="85" t="n"/>
-      <c r="L98" s="86" t="n"/>
+      <c r="B98" s="43" t="inlineStr">
+        <is>
+          <t>uut_syslog_chk</t>
+        </is>
+      </c>
+      <c r="C98" s="43" t="inlineStr">
+        <is>
+          <t>Detects OS kernel, regenerates /var/log/syslog via journalctl -b --no-pager, and filters for errors using an allow-list + CSV bypass.</t>
+        </is>
+      </c>
+      <c r="D98" s="40" t="inlineStr">
+        <is>
+          <t>PASS if, after filtering, no un-bypassed error lines remain in dmesg. FAIL if any survive filtering, or if the filter list file is missing/fails.</t>
+        </is>
+      </c>
+      <c r="E98" s="40" t="n"/>
+      <c r="F98" s="75" t="n"/>
+      <c r="G98" s="78" t="b">
+        <v>0</v>
+      </c>
+      <c r="H98" s="78" t="b">
+        <v>0</v>
+      </c>
+      <c r="I98" s="55" t="n"/>
+      <c r="J98" s="55" t="n"/>
+      <c r="L98" s="31" t="n"/>
+      <c r="M98" s="18" t="n"/>
+      <c r="N98" s="37" t="n"/>
+      <c r="O98" s="18" t="n"/>
+      <c r="P98" s="19" t="n"/>
+      <c r="Q98" s="17" t="n"/>
+      <c r="R98" s="17" t="n"/>
+      <c r="S98" s="17" t="n"/>
+      <c r="T98" s="17" t="n"/>
+      <c r="U98" s="17" t="n"/>
+      <c r="V98" s="17" t="n"/>
+      <c r="W98" s="17" t="n"/>
+      <c r="X98" s="17" t="n"/>
+      <c r="Y98" s="17" t="n"/>
     </row>
     <row r="99" ht="27" customHeight="1" s="80">
       <c r="A99" s="76" t="n">
@@ -10148,24 +10163,20 @@
       </c>
       <c r="B99" s="43" t="inlineStr">
         <is>
-          <t>bmc_sel_chk</t>
+          <t>bmc_sel_clear</t>
         </is>
       </c>
       <c r="C99" s="43" t="inlineStr">
         <is>
-          <t>A plain BMC SEL check, run late in the flow after all functional tests have completed, right before the final SDR/dmesg/syslog snapshot and SEL clear.</t>
+          <t>Records the current BMC SEL to a log file, then clears the SEL (System Event Log).</t>
         </is>
       </c>
       <c r="D99" s="40" t="inlineStr">
         <is>
-          <t>PASS if returns truthy (no un-whitelisted SEL entries found). FAIL otherwise.</t>
-        </is>
-      </c>
-      <c r="E99" s="40" t="inlineStr">
-        <is>
-          <t>Different call site/intent (post-functional-test SEL sweep vs. pre-test boot-time SEL sweep), same underlying logic.</t>
-        </is>
-      </c>
+          <t>PASS if ipmitool sel clear succeeds. FAIL otherwise.</t>
+        </is>
+      </c>
+      <c r="E99" s="40" t="n"/>
       <c r="F99" s="75" t="n"/>
       <c r="G99" s="78" t="b">
         <v>0</v>
@@ -10196,34 +10207,59 @@
       </c>
       <c r="B100" s="43" t="inlineStr">
         <is>
-          <t>bmc_sdr_chk</t>
+          <t>uut_boot_change</t>
         </is>
       </c>
       <c r="C100" s="43" t="inlineStr">
         <is>
-          <t>Validates BMC Sensor Data Record contents (all sensor readings within expected bounds).</t>
-        </is>
-      </c>
-      <c r="D100" s="40" t="inlineStr">
-        <is>
-          <t>PASS if ipmitool sdr elist succeeds. FAIL otherwise.</t>
-        </is>
-      </c>
+          <t>change boot option to windows env. for window testing.
+AC cycle so the UUT boots into Windows</t>
+        </is>
+      </c>
+      <c r="D100" s="40" t="n"/>
       <c r="E100" s="40" t="n"/>
-      <c r="F100" s="75" t="n"/>
-      <c r="G100" s="78" t="b">
-        <v>0</v>
-      </c>
-      <c r="H100" s="78" t="b">
-        <v>0</v>
-      </c>
-      <c r="I100" s="55" t="n"/>
-      <c r="J100" s="55" t="n"/>
-      <c r="L100" s="31" t="n"/>
-      <c r="M100" s="18" t="n"/>
-      <c r="N100" s="37" t="n"/>
-      <c r="O100" s="18" t="n"/>
-      <c r="P100" s="19" t="n"/>
+      <c r="F100" s="43" t="inlineStr">
+        <is>
+          <t>[ Get version of below items ] Inventory ipmitool raw 0x36 0xd2 1 0x01 PowerCapping ipmitool raw 0x36 0xd2 3 0x01 FanTable ipmitool raw 0x36 0xd2 4 0x01 SDRGenerator ipmitool raw 0x36 0xd2 6 0x01</t>
+        </is>
+      </c>
+      <c r="G100" s="47" t="b">
+        <v>1</v>
+      </c>
+      <c r="H100" s="47" t="b">
+        <v>1</v>
+      </c>
+      <c r="I100" s="41" t="inlineStr">
+        <is>
+          <t>Measuring Get Inventory Version:1.9.2, equal to 1.9.2
+Measuring Get PowerCapping Version:3.9.1, equal to 3.9.1
+Measuring Get FanTable Version:4.9.2, equal to 4.9.2
+Measuring Get SDRGenerator Version:6.9.2, equal to 6.9.2
+[BMC_SKU_INFO] JSON File Version Check PASS.
+[PASS] BMC SKU Info Check PASS.</t>
+        </is>
+      </c>
+      <c r="J100" s="41" t="n"/>
+      <c r="K100" s="42" t="inlineStr">
+        <is>
+          <t>Measuring Get Inventory Version:1.9.2, equal to 1.9.2
+Measuring Get PowerCapping Version:3.9.1, equal to 3.9.1
+Measuring Get FanTable Version:4.9.2, equal to 4.9.2
+Measuring Get SDRGenerator Version:6.9.2, equal to 6.9.2
+[BMC_SKU_INFO] JSON File Version Check PASS.
+[PASS] BMC SKU Info Check PASS.</t>
+        </is>
+      </c>
+      <c r="L100" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Matches CRD (FanTable 4.9.2, Inventory 1.9.2, PowerCapping 3.9.1, SDRGenerator 6.9.2). CRD PCBA table still lists SDRGenerator 6.9.1 (System table says 6.9.2).
+</t>
+        </is>
+      </c>
+      <c r="M100" s="20" t="n"/>
+      <c r="N100" s="20" t="n"/>
+      <c r="O100" s="20" t="n"/>
+      <c r="P100" s="20" t="n"/>
       <c r="Q100" s="17" t="n"/>
       <c r="R100" s="17" t="n"/>
       <c r="S100" s="17" t="n"/>
@@ -10234,49 +10270,50 @@
       <c r="X100" s="17" t="n"/>
       <c r="Y100" s="17" t="n"/>
     </row>
-    <row r="101" ht="27" customHeight="1" s="80">
+    <row r="101" ht="53.25" customHeight="1" s="80">
       <c r="A101" s="76" t="n">
         <v>98</v>
       </c>
       <c r="B101" s="43" t="inlineStr">
         <is>
-          <t>uut_dmesg_chk</t>
+          <t>tcg_spf_mode_chk</t>
         </is>
       </c>
       <c r="C101" s="43" t="inlineStr">
         <is>
-          <t>Captures dmesg, lspci -vvv, and ras-mc-ctl --errors, then filters against an allow-list and a CSV-driven bypass filter list to detect real kernel errors.</t>
+          <t>Prepare TCG testing in Linux. WinPE ipxe menu override set.
+Switch target system to WinPE by updating PXE boot configuration and collecting Windows logs/config.</t>
         </is>
       </c>
       <c r="D101" s="40" t="inlineStr">
         <is>
-          <t>PASS if, after filtering, no un-bypassed error lines remain in dmesg. FAIL if any survive filtering, or if the filter list file is missing/fails.</t>
-        </is>
-      </c>
-      <c r="E101" s="40" t="n"/>
-      <c r="F101" s="75" t="n"/>
-      <c r="G101" s="78" t="b">
-        <v>0</v>
-      </c>
-      <c r="H101" s="78" t="b">
-        <v>0</v>
-      </c>
-      <c r="I101" s="55" t="n"/>
-      <c r="J101" s="55" t="n"/>
-      <c r="L101" s="31" t="n"/>
-      <c r="M101" s="18" t="n"/>
-      <c r="N101" s="37" t="n"/>
-      <c r="O101" s="18" t="n"/>
-      <c r="P101" s="19" t="n"/>
-      <c r="Q101" s="17" t="n"/>
-      <c r="R101" s="17" t="n"/>
-      <c r="S101" s="17" t="n"/>
-      <c r="T101" s="17" t="n"/>
-      <c r="U101" s="17" t="n"/>
-      <c r="V101" s="17" t="n"/>
-      <c r="W101" s="17" t="n"/>
-      <c r="X101" s="17" t="n"/>
-      <c r="Y101" s="17" t="n"/>
+          <t>Windows config and log directories must be created. Log files must be collected and stored correctly. PXE boot script must exist and execute without error.</t>
+        </is>
+      </c>
+      <c r="E101" s="40" t="inlineStr">
+        <is>
+          <t>This function prepares and stores Windows logs to specific locations under /testlog/&lt;project&gt;/windows/ PXE boot config is changed by uploading specific iPXE script based on MAC address. If the shell script is missing or fails, the system will exit or log failure to SF.</t>
+        </is>
+      </c>
+      <c r="F101" s="43" t="inlineStr">
+        <is>
+          <t>[ Get Boot MAC ] ifconfig -a | egrep "eth" | egrep "ether" | awk '{print $2}' - - - - - If b oot method is ipxe - - - - - Replace set menu-default with winpe - - - - - If b oot method is not ipxe - - - - - [ Set Boot Device to disk ] ipmitool chassis bootdev disk [ Format nvme devices ] nvme format /dev/nvme0n1 Install a Windows ISO to /dev/nvme0n1 [ Execute AC Cycle ] ipmitool raw 0x30 0xe0 116 1 1</t>
+        </is>
+      </c>
+      <c r="G101" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="H101" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="I101" s="45" t="n"/>
+      <c r="J101" s="45" t="n"/>
+      <c r="K101" s="42" t="inlineStr">
+        <is>
+          <t>[PASS] WinPE ipxe menu override set.</t>
+        </is>
+      </c>
+      <c r="L101" s="52" t="n"/>
     </row>
     <row r="102" ht="27" customHeight="1" s="80">
       <c r="A102" s="76" t="n">
@@ -10284,248 +10321,46 @@
       </c>
       <c r="B102" s="43" t="inlineStr">
         <is>
-          <t>uut_syslog_chk</t>
+          <t>bios_boot_option_set_default</t>
         </is>
       </c>
       <c r="C102" s="43" t="inlineStr">
-        <is>
-          <t>Detects OS kernel, regenerates /var/log/syslog via journalctl -b --no-pager, and filters for errors using an allow-list + CSV bypass.</t>
-        </is>
-      </c>
-      <c r="D102" s="40" t="inlineStr">
-        <is>
-          <t>PASS if, after filtering, no un-bypassed error lines remain in dmesg. FAIL if any survive filtering, or if the filter list file is missing/fails.</t>
-        </is>
-      </c>
-      <c r="E102" s="40" t="n"/>
-      <c r="F102" s="75" t="n"/>
-      <c r="G102" s="78" t="b">
-        <v>0</v>
-      </c>
-      <c r="H102" s="78" t="b">
-        <v>0</v>
-      </c>
-      <c r="I102" s="55" t="n"/>
-      <c r="J102" s="55" t="n"/>
-      <c r="L102" s="31" t="n"/>
-      <c r="M102" s="18" t="n"/>
-      <c r="N102" s="37" t="n"/>
-      <c r="O102" s="18" t="n"/>
-      <c r="P102" s="19" t="n"/>
-      <c r="Q102" s="17" t="n"/>
-      <c r="R102" s="17" t="n"/>
-      <c r="S102" s="17" t="n"/>
-      <c r="T102" s="17" t="n"/>
-      <c r="U102" s="17" t="n"/>
-      <c r="V102" s="17" t="n"/>
-      <c r="W102" s="17" t="n"/>
-      <c r="X102" s="17" t="n"/>
-      <c r="Y102" s="17" t="n"/>
-    </row>
-    <row r="103" ht="27" customHeight="1" s="80">
-      <c r="A103" s="76" t="n">
-        <v>100</v>
-      </c>
-      <c r="B103" s="43" t="inlineStr">
-        <is>
-          <t>bmc_sel_clear</t>
-        </is>
-      </c>
-      <c r="C103" s="43" t="inlineStr">
-        <is>
-          <t>Records the current BMC SEL to a log file, then clears the SEL (System Event Log).</t>
-        </is>
-      </c>
-      <c r="D103" s="40" t="inlineStr">
-        <is>
-          <t>PASS if ipmitool sel clear succeeds. FAIL otherwise.</t>
-        </is>
-      </c>
-      <c r="E103" s="40" t="n"/>
-      <c r="F103" s="75" t="n"/>
-      <c r="G103" s="78" t="b">
-        <v>0</v>
-      </c>
-      <c r="H103" s="78" t="b">
-        <v>0</v>
-      </c>
-      <c r="I103" s="55" t="n"/>
-      <c r="J103" s="55" t="n"/>
-      <c r="L103" s="31" t="n"/>
-      <c r="M103" s="18" t="n"/>
-      <c r="N103" s="37" t="n"/>
-      <c r="O103" s="18" t="n"/>
-      <c r="P103" s="19" t="n"/>
-      <c r="Q103" s="17" t="n"/>
-      <c r="R103" s="17" t="n"/>
-      <c r="S103" s="17" t="n"/>
-      <c r="T103" s="17" t="n"/>
-      <c r="U103" s="17" t="n"/>
-      <c r="V103" s="17" t="n"/>
-      <c r="W103" s="17" t="n"/>
-      <c r="X103" s="17" t="n"/>
-      <c r="Y103" s="17" t="n"/>
-    </row>
-    <row r="104" ht="27" customHeight="1" s="80">
-      <c r="A104" s="76" t="n">
-        <v>101</v>
-      </c>
-      <c r="B104" s="43" t="inlineStr">
-        <is>
-          <t>uut_boot_change</t>
-        </is>
-      </c>
-      <c r="C104" s="43" t="inlineStr">
-        <is>
-          <t>change boot option to windows env. for window testing.
-AC cycle so the UUT boots into Windows</t>
-        </is>
-      </c>
-      <c r="D104" s="40" t="n"/>
-      <c r="E104" s="40" t="n"/>
-      <c r="F104" s="43" t="inlineStr">
-        <is>
-          <t>[ Get version of below items ] Inventory ipmitool raw 0x36 0xd2 1 0x01 PowerCapping ipmitool raw 0x36 0xd2 3 0x01 FanTable ipmitool raw 0x36 0xd2 4 0x01 SDRGenerator ipmitool raw 0x36 0xd2 6 0x01</t>
-        </is>
-      </c>
-      <c r="G104" s="47" t="b">
-        <v>1</v>
-      </c>
-      <c r="H104" s="47" t="b">
-        <v>1</v>
-      </c>
-      <c r="I104" s="41" t="inlineStr">
-        <is>
-          <t>Measuring Get Inventory Version:1.9.2, equal to 1.9.2
-Measuring Get PowerCapping Version:3.9.1, equal to 3.9.1
-Measuring Get FanTable Version:4.9.2, equal to 4.9.2
-Measuring Get SDRGenerator Version:6.9.2, equal to 6.9.2
-[BMC_SKU_INFO] JSON File Version Check PASS.
-[PASS] BMC SKU Info Check PASS.</t>
-        </is>
-      </c>
-      <c r="J104" s="41" t="n"/>
-      <c r="K104" s="42" t="inlineStr">
-        <is>
-          <t>Measuring Get Inventory Version:1.9.2, equal to 1.9.2
-Measuring Get PowerCapping Version:3.9.1, equal to 3.9.1
-Measuring Get FanTable Version:4.9.2, equal to 4.9.2
-Measuring Get SDRGenerator Version:6.9.2, equal to 6.9.2
-[BMC_SKU_INFO] JSON File Version Check PASS.
-[PASS] BMC SKU Info Check PASS.</t>
-        </is>
-      </c>
-      <c r="L104" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Matches CRD (FanTable 4.9.2, Inventory 1.9.2, PowerCapping 3.9.1, SDRGenerator 6.9.2). CRD PCBA table still lists SDRGenerator 6.9.1 (System table says 6.9.2).
-</t>
-        </is>
-      </c>
-      <c r="M104" s="20" t="n"/>
-      <c r="N104" s="20" t="n"/>
-      <c r="O104" s="20" t="n"/>
-      <c r="P104" s="20" t="n"/>
-      <c r="Q104" s="17" t="n"/>
-      <c r="R104" s="17" t="n"/>
-      <c r="S104" s="17" t="n"/>
-      <c r="T104" s="17" t="n"/>
-      <c r="U104" s="17" t="n"/>
-      <c r="V104" s="17" t="n"/>
-      <c r="W104" s="17" t="n"/>
-      <c r="X104" s="17" t="n"/>
-      <c r="Y104" s="17" t="n"/>
-    </row>
-    <row r="105" ht="53.25" customHeight="1" s="80">
-      <c r="A105" s="76" t="n">
-        <v>102</v>
-      </c>
-      <c r="B105" s="43" t="inlineStr">
-        <is>
-          <t>tcg_spf_mode_chk</t>
-        </is>
-      </c>
-      <c r="C105" s="43" t="inlineStr">
-        <is>
-          <t>Prepare TCG testing in Linux. WinPE ipxe menu override set.
-Switch target system to WinPE by updating PXE boot configuration and collecting Windows logs/config.</t>
-        </is>
-      </c>
-      <c r="D105" s="40" t="inlineStr">
-        <is>
-          <t>Windows config and log directories must be created. Log files must be collected and stored correctly. PXE boot script must exist and execute without error.</t>
-        </is>
-      </c>
-      <c r="E105" s="40" t="inlineStr">
-        <is>
-          <t>This function prepares and stores Windows logs to specific locations under /testlog/&lt;project&gt;/windows/ PXE boot config is changed by uploading specific iPXE script based on MAC address. If the shell script is missing or fails, the system will exit or log failure to SF.</t>
-        </is>
-      </c>
-      <c r="F105" s="43" t="inlineStr">
-        <is>
-          <t>[ Get Boot MAC ] ifconfig -a | egrep "eth" | egrep "ether" | awk '{print $2}' - - - - - If b oot method is ipxe - - - - - Replace set menu-default with winpe - - - - - If b oot method is not ipxe - - - - - [ Set Boot Device to disk ] ipmitool chassis bootdev disk [ Format nvme devices ] nvme format /dev/nvme0n1 Install a Windows ISO to /dev/nvme0n1 [ Execute AC Cycle ] ipmitool raw 0x30 0xe0 116 1 1</t>
-        </is>
-      </c>
-      <c r="G105" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="H105" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="I105" s="45" t="n"/>
-      <c r="J105" s="45" t="n"/>
-      <c r="K105" s="42" t="inlineStr">
-        <is>
-          <t>[PASS] WinPE ipxe menu override set.</t>
-        </is>
-      </c>
-      <c r="L105" s="52" t="n"/>
-    </row>
-    <row r="106" ht="27" customHeight="1" s="80">
-      <c r="A106" s="76" t="n">
-        <v>103</v>
-      </c>
-      <c r="B106" s="43" t="inlineStr">
-        <is>
-          <t>bios_boot_option_set_default</t>
-        </is>
-      </c>
-      <c r="C106" s="43" t="inlineStr">
         <is>
           <t>change boot option to linux env. for next station Linux testing.
 AC cycle so the UUT boots into Linux</t>
         </is>
       </c>
-      <c r="D106" s="40" t="n"/>
-      <c r="E106" s="40" t="n"/>
-      <c r="F106" s="43" t="inlineStr">
+      <c r="D102" s="40" t="n"/>
+      <c r="E102" s="40" t="n"/>
+      <c r="F102" s="43" t="inlineStr">
         <is>
           <t>ipmitool chassis bootdev disk options=persistent
 AC cycle so the UUT boots into Windows</t>
         </is>
       </c>
-      <c r="G106" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="H106" s="47" t="b">
+      <c r="G102" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="H102" s="47" t="b">
         <v>1</v>
       </c>
-      <c r="K106" s="39" t="inlineStr">
+      <c r="K102" s="39" t="inlineStr">
         <is>
           <t>[PASS] Already AC-cycled into disk-Windows, continue to next item</t>
         </is>
       </c>
-      <c r="L106" s="52" t="n"/>
-      <c r="M106" s="55" t="n"/>
-      <c r="N106" s="55" t="n"/>
-      <c r="O106" s="55" t="n"/>
-      <c r="P106" s="55" t="n"/>
-    </row>
-    <row r="107" s="80"/>
-    <row r="108" s="80">
-      <c r="G108" s="49" t="n">
+      <c r="L102" s="52" t="n"/>
+      <c r="M102" s="55" t="n"/>
+      <c r="N102" s="55" t="n"/>
+      <c r="O102" s="55" t="n"/>
+      <c r="P102" s="55" t="n"/>
+    </row>
+    <row r="103" s="80"/>
+    <row r="104" s="80">
+      <c r="G104" s="49" t="n">
         <v>6</v>
       </c>
-      <c r="H108" s="49" t="inlineStr">
+      <c r="H104" s="49" t="inlineStr">
         <is>
           <t>Hours</t>
         </is>
@@ -11341,7 +11176,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="12.75"/>
   <cols>
     <col width="5.7109375" customWidth="1" style="20" min="1" max="1"/>
@@ -11600,32 +11435,40 @@
         </is>
       </c>
     </row>
-    <row r="9" s="80">
-      <c r="A9" s="81" t="n">
+    <row r="9" ht="27" customHeight="1" s="80">
+      <c r="A9" s="76" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="82" t="inlineStr">
-        <is>
-          <t>nic_fw_chk</t>
-        </is>
-      </c>
-      <c r="C9" s="82" t="inlineStr">
-        <is>
-          <t>Check LAN FW and quantity</t>
-        </is>
-      </c>
-      <c r="D9" s="83" t="n"/>
-      <c r="E9" s="83" t="inlineStr">
-        <is>
-          <t>&gt;&gt;&gt; Enable this check only for CX8 SKU</t>
-        </is>
-      </c>
-      <c r="F9" s="82" t="inlineStr">
-        <is>
-          <t>mlxfwmanger_x86_64/lspci</t>
-        </is>
-      </c>
-      <c r="G9" s="87" t="n"/>
+      <c r="B9" s="43" t="inlineStr">
+        <is>
+          <t>nic_mac_chk</t>
+        </is>
+      </c>
+      <c r="C9" s="43" t="inlineStr">
+        <is>
+          <t>Validate system NIC MAC addresses against expected SFC-defined MAC list.</t>
+        </is>
+      </c>
+      <c r="D9" s="43" t="inlineStr">
+        <is>
+          <t>Compare each NIC port MAC with corresponding expected MAC. All MAC addresses must match.</t>
+        </is>
+      </c>
+      <c r="E9" s="43" t="inlineStr">
+        <is>
+          <t>C44AD models skip idx 0 (GP MAC). If NIC MAC cannot be read, fallback to tools/ mlxfwmanager query.</t>
+        </is>
+      </c>
+      <c r="F9" s="43" t="inlineStr">
+        <is>
+          <t>[Get LAN MAC by port index] ifconfig -a | awk 'BEGIN{n=0}{if (/^eth/){print $1;n=1};if(n==1 &amp;&amp; $1==\"ether\"){print $2;n=0}}' [If NIC MAC cannot be read…] {TOOL_FILE} --query | grep -i -A10 'ConnectX6'| grep 'Base GUID:'</t>
+        </is>
+      </c>
+      <c r="G9" s="48" t="inlineStr">
+        <is>
+          <t>[PASS] LAN MAC check PASS</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="27" customHeight="1" s="80">
       <c r="A10" s="76" t="n">
@@ -11633,61 +11476,26 @@
       </c>
       <c r="B10" s="43" t="inlineStr">
         <is>
-          <t>nic_mac_chk</t>
+          <t>pcie_device_chk</t>
         </is>
       </c>
       <c r="C10" s="43" t="inlineStr">
         <is>
-          <t>Validate system NIC MAC addresses against expected SFC-defined MAC list.</t>
+          <t>Perform a PCIe device validation by verifying each device's link speed and width against expected values.</t>
         </is>
       </c>
       <c r="D10" s="43" t="inlineStr">
         <is>
-          <t>Compare each NIC port MAC with corresponding expected MAC. All MAC addresses must match.</t>
-        </is>
-      </c>
-      <c r="E10" s="43" t="inlineStr">
-        <is>
-          <t>C44AD models skip idx 0 (GP MAC). If NIC MAC cannot be read, fallback to tools/ mlxfwmanager query.</t>
-        </is>
-      </c>
+          <t>Pass - return 0; Fail - return 1</t>
+        </is>
+      </c>
+      <c r="E10" s="43" t="n"/>
       <c r="F10" s="43" t="inlineStr">
         <is>
-          <t>[Get LAN MAC by port index] ifconfig -a | awk 'BEGIN{n=0}{if (/^eth/){print $1;n=1};if(n==1 &amp;&amp; $1==\"ether\"){print $2;n=0}}' [If NIC MAC cannot be read…] {TOOL_FILE} --query | grep -i -A10 'ConnectX6'| grep 'Base GUID:'</t>
-        </is>
-      </c>
-      <c r="G10" s="48" t="inlineStr">
-        <is>
-          <t>[PASS] LAN MAC check PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="27" customHeight="1" s="80">
-      <c r="A11" s="76" t="n">
-        <v>9</v>
-      </c>
-      <c r="B11" s="43" t="inlineStr">
-        <is>
-          <t>pcie_device_chk</t>
-        </is>
-      </c>
-      <c r="C11" s="43" t="inlineStr">
-        <is>
-          <t>Perform a PCIe device validation by verifying each device's link speed and width against expected values.</t>
-        </is>
-      </c>
-      <c r="D11" s="43" t="inlineStr">
-        <is>
-          <t>Pass - return 0; Fail - return 1</t>
-        </is>
-      </c>
-      <c r="E11" s="43" t="n"/>
-      <c r="F11" s="43" t="inlineStr">
-        <is>
           <t>[ Get s pecified location PCIe devices ] lspci -n -s {PCIE_ADDR} -vvv</t>
         </is>
       </c>
-      <c r="G11" s="31" t="inlineStr">
+      <c r="G10" s="31" t="inlineStr">
         <is>
           <t>[PASS] PCIE 4c:00.0 M.2 CPU0 check PASS, GET_SPEED=8GT, GET_WIDTH=x4, GET_VIDDID=144d:a80e
 [PASS] PCIE b8:00.0 E1.S Cassette 1 check PASS, GET_SPEED=32GT, GET_WIDTH=x4, GET_VIDDID=1c5c:2069
@@ -11709,31 +11517,31 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="67.5" customHeight="1" s="80">
-      <c r="A12" s="76" t="n">
-        <v>10</v>
-      </c>
-      <c r="B12" s="43" t="inlineStr">
+    <row r="11" ht="67.5" customHeight="1" s="80">
+      <c r="A11" s="76" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="43" t="inlineStr">
         <is>
           <t>lan_check</t>
         </is>
       </c>
-      <c r="C12" s="43" t="inlineStr">
+      <c r="C11" s="43" t="inlineStr">
         <is>
           <t>Performs a LAN pair test to validate GP network connectivity, switch configuration, and performance between the UUT and TOR switches. Executing stress and performance checks using iperf.</t>
         </is>
       </c>
-      <c r="D12" s="43" t="inlineStr">
+      <c r="D11" s="43" t="inlineStr">
         <is>
           <t>Switch &amp; Port Validation Both TOR A (Upper) and TOR B (Lower) switch ports must be detected and validated. LAN Performance Stress test must complete successfully for both client and server roles. iperf performance must meet or exceed defined thresholds. Ping Verification UUT must successfully ping the configured test server within timeout limits.</t>
         </is>
       </c>
-      <c r="E12" s="43" t="inlineStr">
+      <c r="E11" s="43" t="inlineStr">
         <is>
           <t>TorA_port/TorB_port are computed from ccr_table_file and must resolve to the GP/NIC port (the one wired to eth0)</t>
         </is>
       </c>
-      <c r="F12" s="43" t="inlineStr">
+      <c r="F11" s="43" t="inlineStr">
         <is>
           <t>[ Configure NIC ] ifconfig eth0 mtu 9000; sysctl net.core.rmem_max/wmem_max, net.ipv4.tcp_rmem/tcp_wmem
 [ Locate TOR switches ] resolve TOR mgmt IP from its RJ45 debug port MAC; get TorA_port/TorB_port from ccr_table_file
@@ -11743,7 +11551,7 @@
 [ Final check ] ping {test server}</t>
         </is>
       </c>
-      <c r="G12" s="43" t="inlineStr">
+      <c r="G11" s="43" t="inlineStr">
         <is>
           <t>[Configure Iperf Settings] ==========
 ifconfig eth0 mtu 9000
@@ -11771,38 +11579,73 @@
         </is>
       </c>
     </row>
+    <row r="12" ht="27" customHeight="1" s="80">
+      <c r="A12" s="76" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="43" t="inlineStr">
+        <is>
+          <t>bmc_sel_chk</t>
+        </is>
+      </c>
+      <c r="C12" s="43" t="inlineStr">
+        <is>
+          <t>Verify BMC SEL (System Event Log) events during testing to ensure no unexpected events have occurred.</t>
+        </is>
+      </c>
+      <c r="D12" s="43" t="inlineStr">
+        <is>
+          <t>SEL event counts should not exceed the defined thresholds based on testing duration.</t>
+        </is>
+      </c>
+      <c r="E12" s="43" t="inlineStr">
+        <is>
+          <t>Fail log will be saved in project folder if abnormal events are detected.</t>
+        </is>
+      </c>
+      <c r="F12" s="43" t="inlineStr">
+        <is>
+          <t>[ Get BMC SEL Log ] ipmiutil sel &gt; sel.log Parse the sel.log and compare with allowed list</t>
+        </is>
+      </c>
+      <c r="G12" s="39" t="inlineStr">
+        <is>
+          <t>[PASS] BMC SEL Check PASS!</t>
+        </is>
+      </c>
+    </row>
     <row r="13" ht="27" customHeight="1" s="80">
       <c r="A13" s="76" t="n">
         <v>11</v>
       </c>
       <c r="B13" s="43" t="inlineStr">
         <is>
-          <t>bmc_sel_chk</t>
+          <t>bmc_sdr_chk</t>
         </is>
       </c>
       <c r="C13" s="43" t="inlineStr">
         <is>
-          <t>Verify BMC SEL (System Event Log) events during testing to ensure no unexpected events have occurred.</t>
+          <t>Verify BMC Sensor Data Records (SDR) by checking sensor list output and filtering unexpected entries.</t>
         </is>
       </c>
       <c r="D13" s="43" t="inlineStr">
         <is>
-          <t>SEL event counts should not exceed the defined thresholds based on testing duration.</t>
+          <t>No unexpected or unmasked SDR entries found in BMCSDR.log.</t>
         </is>
       </c>
       <c r="E13" s="43" t="inlineStr">
         <is>
-          <t>Fail log will be saved in project folder if abnormal events are detected.</t>
+          <t>Test fails if filtered output is not empty.</t>
         </is>
       </c>
       <c r="F13" s="43" t="inlineStr">
         <is>
-          <t>[ Get BMC SEL Log ] ipmiutil sel &gt; sel.log Parse the sel.log and compare with allowed list</t>
-        </is>
-      </c>
-      <c r="G13" s="39" t="inlineStr">
-        <is>
-          <t>[PASS] BMC SEL Check PASS!</t>
+          <t>[ Get BMC sensor list ] ipmitool sdr elist &gt; BMCSDR.log Parse the BMCSDR.log and compare with allowed list</t>
+        </is>
+      </c>
+      <c r="G13" s="48" t="inlineStr">
+        <is>
+          <t>[PASS] BMC SDR check PASS</t>
         </is>
       </c>
     </row>
@@ -11812,32 +11655,32 @@
       </c>
       <c r="B14" s="43" t="inlineStr">
         <is>
-          <t>bmc_sdr_chk</t>
+          <t>uut_dmesg_chk</t>
         </is>
       </c>
       <c r="C14" s="43" t="inlineStr">
         <is>
-          <t>Verify BMC Sensor Data Records (SDR) by checking sensor list output and filtering unexpected entries.</t>
+          <t>Check UUT dmesg log for unexpected error messages and record PCI device status.</t>
         </is>
       </c>
       <c r="D14" s="43" t="inlineStr">
         <is>
-          <t>No unexpected or unmasked SDR entries found in BMCSDR.log.</t>
+          <t>No unmasked error messages found in dmesg and all expected messages are properly filtered.</t>
         </is>
       </c>
       <c r="E14" s="43" t="inlineStr">
         <is>
-          <t>Test fails if filtered output is not empty.</t>
+          <t>Filter list (filter_list.csv) and error map (err_map.ini) are required for filtering and mapping errors.</t>
         </is>
       </c>
       <c r="F14" s="43" t="inlineStr">
         <is>
-          <t>[ Get BMC sensor list ] ipmitool sdr elist &gt; BMCSDR.log Parse the BMCSDR.log and compare with allowed list</t>
+          <t>[ List error DMESG] dmesg | egrep - i { errStrings} |egrep - v {skipStrings } &gt; t_dmesg Filter the rest of the dmesg with filter_list.csv - - - - - If DMESG check fail - - - - - [Record SEL Log] ipmitool sel elist &gt; t_sel ipmitool sel elist -v &gt; t_selv</t>
         </is>
       </c>
       <c r="G14" s="48" t="inlineStr">
         <is>
-          <t>[PASS] BMC SDR check PASS</t>
+          <t>[PASS] DMESG check Pass</t>
         </is>
       </c>
     </row>
@@ -11847,32 +11690,28 @@
       </c>
       <c r="B15" s="43" t="inlineStr">
         <is>
-          <t>uut_dmesg_chk</t>
+          <t>uut_syslog_chk</t>
         </is>
       </c>
       <c r="C15" s="43" t="inlineStr">
         <is>
-          <t>Check UUT dmesg log for unexpected error messages and record PCI device status.</t>
+          <t>Check and record UUT system log (syslog/messages) to ensure no unexpected errors.</t>
         </is>
       </c>
       <c r="D15" s="43" t="inlineStr">
         <is>
-          <t>No unmasked error messages found in dmesg and all expected messages are properly filtered.</t>
-        </is>
-      </c>
-      <c r="E15" s="43" t="inlineStr">
-        <is>
-          <t>Filter list (filter_list.csv) and error map (err_map.ini) are required for filtering and mapping errors.</t>
-        </is>
-      </c>
+          <t>UUT syslog must not contain unmasked error patterns, excluding skip patterns. Log file must exist and contain no unfiltered critical errors.</t>
+        </is>
+      </c>
+      <c r="E15" s="43" t="n"/>
       <c r="F15" s="43" t="inlineStr">
         <is>
-          <t>[ List error DMESG] dmesg | egrep - i { errStrings} |egrep - v {skipStrings } &gt; t_dmesg Filter the rest of the dmesg with filter_list.csv - - - - - If DMESG check fail - - - - - [Record SEL Log] ipmitool sel elist &gt; t_sel ipmitool sel elist -v &gt; t_selv</t>
+          <t>[List error syslog ] journalctl -b --no-pager | egrep -i {errStrings} |egrep -v {skipStrings} Filter the rest of the log with filter_list.csv</t>
         </is>
       </c>
       <c r="G15" s="48" t="inlineStr">
         <is>
-          <t>[PASS] DMESG check Pass</t>
+          <t>[PASS] SYSLOG check PASS</t>
         </is>
       </c>
     </row>
@@ -11882,61 +11721,30 @@
       </c>
       <c r="B16" s="43" t="inlineStr">
         <is>
-          <t>uut_syslog_chk</t>
+          <t>bmc_sel_clear</t>
         </is>
       </c>
       <c r="C16" s="43" t="inlineStr">
         <is>
-          <t>Check and record UUT system log (syslog/messages) to ensure no unexpected errors.</t>
+          <t>Clear BMC System Event Log (SEL) and verify it is cleared correctly.</t>
         </is>
       </c>
       <c r="D16" s="43" t="inlineStr">
         <is>
-          <t>UUT syslog must not contain unmasked error patterns, excluding skip patterns. Log file must exist and contain no unfiltered critical errors.</t>
-        </is>
-      </c>
-      <c r="E16" s="43" t="n"/>
+          <t>SEL clear command executes successfully and log ID changes after clear.</t>
+        </is>
+      </c>
+      <c r="E16" s="43" t="inlineStr">
+        <is>
+          <t>Logs SEL before clearing for traceability; verifies clear status by comparing log ID.</t>
+        </is>
+      </c>
       <c r="F16" s="43" t="inlineStr">
         <is>
-          <t>[List error syslog ] journalctl -b --no-pager | egrep -i {errStrings} |egrep -v {skipStrings} Filter the rest of the log with filter_list.csv</t>
+          <t>[ Record SEL ] ipmitool sel elist ipmitool sel elist –v | egrep -i 'Event Data|Record ID' &gt;&gt; t_sel [ Clear SEL ] ipmitool sel clear &gt; /dev/null</t>
         </is>
       </c>
       <c r="G16" s="48" t="inlineStr">
-        <is>
-          <t>[PASS] SYSLOG check PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="27" customHeight="1" s="80">
-      <c r="A17" s="76" t="n">
-        <v>15</v>
-      </c>
-      <c r="B17" s="43" t="inlineStr">
-        <is>
-          <t>bmc_sel_clear</t>
-        </is>
-      </c>
-      <c r="C17" s="43" t="inlineStr">
-        <is>
-          <t>Clear BMC System Event Log (SEL) and verify it is cleared correctly.</t>
-        </is>
-      </c>
-      <c r="D17" s="43" t="inlineStr">
-        <is>
-          <t>SEL clear command executes successfully and log ID changes after clear.</t>
-        </is>
-      </c>
-      <c r="E17" s="43" t="inlineStr">
-        <is>
-          <t>Logs SEL before clearing for traceability; verifies clear status by comparing log ID.</t>
-        </is>
-      </c>
-      <c r="F17" s="43" t="inlineStr">
-        <is>
-          <t>[ Record SEL ] ipmitool sel elist ipmitool sel elist –v | egrep -i 'Event Data|Record ID' &gt;&gt; t_sel [ Clear SEL ] ipmitool sel clear &gt; /dev/null</t>
-        </is>
-      </c>
-      <c r="G17" s="48" t="inlineStr">
         <is>
           <t>[PASS] BMC Clear SEL Pass</t>
         </is>
@@ -11956,7 +11764,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L93"/>
+  <dimension ref="A1:L90"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
     <col width="5.7109375" customWidth="1" style="20" min="1" max="1"/>
@@ -12527,15 +12335,15 @@
 -        Completion Code</t>
         </is>
       </c>
-      <c r="G13" s="88" t="b">
-        <v>0</v>
-      </c>
-      <c r="H13" s="88" t="b">
-        <v>0</v>
-      </c>
-      <c r="I13" s="89" t="n"/>
-      <c r="J13" s="89" t="n"/>
-      <c r="K13" s="87" t="n"/>
+      <c r="G13" s="87" t="b">
+        <v>0</v>
+      </c>
+      <c r="H13" s="87" t="b">
+        <v>0</v>
+      </c>
+      <c r="I13" s="88" t="n"/>
+      <c r="J13" s="88" t="n"/>
+      <c r="K13" s="89" t="n"/>
       <c r="L13" s="90" t="n"/>
     </row>
     <row r="14" s="80">
@@ -12564,15 +12372,15 @@
           <t>Command: show powershelf psu state</t>
         </is>
       </c>
-      <c r="G14" s="88" t="b">
-        <v>0</v>
-      </c>
-      <c r="H14" s="88" t="b">
-        <v>0</v>
-      </c>
-      <c r="I14" s="89" t="n"/>
-      <c r="J14" s="89" t="n"/>
-      <c r="K14" s="87" t="n"/>
+      <c r="G14" s="87" t="b">
+        <v>0</v>
+      </c>
+      <c r="H14" s="87" t="b">
+        <v>0</v>
+      </c>
+      <c r="I14" s="88" t="n"/>
+      <c r="J14" s="88" t="n"/>
+      <c r="K14" s="89" t="n"/>
       <c r="L14" s="90" t="n"/>
     </row>
     <row r="15" s="80">
@@ -12597,15 +12405,15 @@
           <t>show manager type</t>
         </is>
       </c>
-      <c r="G15" s="88" t="b">
-        <v>0</v>
-      </c>
-      <c r="H15" s="88" t="b">
-        <v>0</v>
-      </c>
-      <c r="I15" s="89" t="n"/>
-      <c r="J15" s="89" t="n"/>
-      <c r="K15" s="87" t="n"/>
+      <c r="G15" s="87" t="b">
+        <v>0</v>
+      </c>
+      <c r="H15" s="87" t="b">
+        <v>0</v>
+      </c>
+      <c r="I15" s="88" t="n"/>
+      <c r="J15" s="88" t="n"/>
+      <c r="K15" s="89" t="n"/>
       <c r="L15" s="90" t="n"/>
     </row>
     <row r="16" ht="67.5" customHeight="1" s="80">
@@ -13190,15 +12998,15 @@
 DVT CMD: ipmitool raw 0x36 0xf3 0x12 0xa6 0x02 0x00 0x12</t>
         </is>
       </c>
-      <c r="G32" s="88" t="b">
-        <v>0</v>
-      </c>
-      <c r="H32" s="88" t="b">
-        <v>0</v>
-      </c>
-      <c r="I32" s="89" t="n"/>
-      <c r="J32" s="89" t="n"/>
-      <c r="K32" s="87" t="n"/>
+      <c r="G32" s="87" t="b">
+        <v>0</v>
+      </c>
+      <c r="H32" s="87" t="b">
+        <v>0</v>
+      </c>
+      <c r="I32" s="88" t="n"/>
+      <c r="J32" s="88" t="n"/>
+      <c r="K32" s="89" t="n"/>
       <c r="L32" s="90" t="n"/>
     </row>
     <row r="33" ht="27" customHeight="1" s="80">
@@ -13262,15 +13070,15 @@
           <t>[Get VR version]</t>
         </is>
       </c>
-      <c r="G34" s="88" t="b">
-        <v>0</v>
-      </c>
-      <c r="H34" s="88" t="b">
-        <v>0</v>
-      </c>
-      <c r="I34" s="89" t="n"/>
-      <c r="J34" s="89" t="n"/>
-      <c r="K34" s="87" t="n"/>
+      <c r="G34" s="87" t="b">
+        <v>0</v>
+      </c>
+      <c r="H34" s="87" t="b">
+        <v>0</v>
+      </c>
+      <c r="I34" s="88" t="n"/>
+      <c r="J34" s="88" t="n"/>
+      <c r="K34" s="89" t="n"/>
       <c r="L34" s="90" t="n"/>
     </row>
     <row r="35" s="80">
@@ -13313,15 +13121,15 @@
 ./xdp711_crc.sh -b 31 -s 0x10</t>
         </is>
       </c>
-      <c r="G35" s="88" t="b">
-        <v>0</v>
-      </c>
-      <c r="H35" s="88" t="b">
-        <v>0</v>
-      </c>
-      <c r="I35" s="89" t="n"/>
-      <c r="J35" s="89" t="n"/>
-      <c r="K35" s="87" t="n"/>
+      <c r="G35" s="87" t="b">
+        <v>0</v>
+      </c>
+      <c r="H35" s="87" t="b">
+        <v>0</v>
+      </c>
+      <c r="I35" s="88" t="n"/>
+      <c r="J35" s="88" t="n"/>
+      <c r="K35" s="89" t="n"/>
       <c r="L35" s="90" t="n"/>
     </row>
     <row r="36" ht="27" customHeight="1" s="80">
@@ -13456,15 +13264,15 @@
 apml_tool 2 --showtsiregister</t>
         </is>
       </c>
-      <c r="G39" s="88" t="b">
-        <v>0</v>
-      </c>
-      <c r="H39" s="88" t="b">
-        <v>0</v>
-      </c>
-      <c r="I39" s="89" t="n"/>
-      <c r="J39" s="89" t="n"/>
-      <c r="K39" s="87" t="n"/>
+      <c r="G39" s="87" t="b">
+        <v>0</v>
+      </c>
+      <c r="H39" s="87" t="b">
+        <v>0</v>
+      </c>
+      <c r="I39" s="88" t="n"/>
+      <c r="J39" s="88" t="n"/>
+      <c r="K39" s="89" t="n"/>
       <c r="L39" s="90" t="n"/>
     </row>
     <row r="40" s="80">
@@ -13499,15 +13307,15 @@
 nc {bmc_ip} {"22"} &lt; /dev/null &gt;/dev/null 2&gt;&amp;1 &amp;&amp; echo 0 || echo 1</t>
         </is>
       </c>
-      <c r="G40" s="88" t="b">
-        <v>0</v>
-      </c>
-      <c r="H40" s="88" t="b">
-        <v>0</v>
-      </c>
-      <c r="I40" s="89" t="n"/>
-      <c r="J40" s="89" t="n"/>
-      <c r="K40" s="87" t="n"/>
+      <c r="G40" s="87" t="b">
+        <v>0</v>
+      </c>
+      <c r="H40" s="87" t="b">
+        <v>0</v>
+      </c>
+      <c r="I40" s="88" t="n"/>
+      <c r="J40" s="88" t="n"/>
+      <c r="K40" s="89" t="n"/>
       <c r="L40" s="90" t="n"/>
     </row>
     <row r="41" s="80">
@@ -13641,15 +13449,15 @@
 jtag-rbpi -if /var/wcs/home/Read_Lock_Sector.stp -m fwupdate -t HPM -j /usr/share/cpld-config/configurations/cpld-config.json -o /xyz/openbmc_project/software/HPM_CPLD -debug</f>
         <v/>
       </c>
-      <c r="G41" s="88" t="b">
-        <v>0</v>
-      </c>
-      <c r="H41" s="88" t="b">
-        <v>0</v>
-      </c>
-      <c r="I41" s="89" t="n"/>
-      <c r="J41" s="89" t="n"/>
-      <c r="K41" s="87" t="n"/>
+      <c r="G41" s="87" t="b">
+        <v>0</v>
+      </c>
+      <c r="H41" s="87" t="b">
+        <v>0</v>
+      </c>
+      <c r="I41" s="88" t="n"/>
+      <c r="J41" s="88" t="n"/>
+      <c r="K41" s="89" t="n"/>
       <c r="L41" s="90" t="n"/>
     </row>
     <row r="42" ht="27" customHeight="1" s="80">
@@ -13825,15 +13633,15 @@
           <t>./AMDXIO -i=0:,1:,2:,3: -xgmi -linkstatus</t>
         </is>
       </c>
-      <c r="G46" s="88" t="b">
-        <v>0</v>
-      </c>
-      <c r="H46" s="88" t="b">
-        <v>0</v>
-      </c>
-      <c r="I46" s="89" t="n"/>
-      <c r="J46" s="89" t="n"/>
-      <c r="K46" s="87" t="n"/>
+      <c r="G46" s="87" t="b">
+        <v>0</v>
+      </c>
+      <c r="H46" s="87" t="b">
+        <v>0</v>
+      </c>
+      <c r="I46" s="88" t="n"/>
+      <c r="J46" s="88" t="n"/>
+      <c r="K46" s="89" t="n"/>
       <c r="L46" s="90" t="n"/>
     </row>
     <row r="47" s="80">
@@ -13857,15 +13665,15 @@
         </is>
       </c>
       <c r="F47" s="82" t="n"/>
-      <c r="G47" s="88" t="b">
-        <v>0</v>
-      </c>
-      <c r="H47" s="88" t="b">
-        <v>0</v>
-      </c>
-      <c r="I47" s="89" t="n"/>
-      <c r="J47" s="89" t="n"/>
-      <c r="K47" s="87" t="n"/>
+      <c r="G47" s="87" t="b">
+        <v>0</v>
+      </c>
+      <c r="H47" s="87" t="b">
+        <v>0</v>
+      </c>
+      <c r="I47" s="88" t="n"/>
+      <c r="J47" s="88" t="n"/>
+      <c r="K47" s="89" t="n"/>
       <c r="L47" s="90" t="n"/>
     </row>
     <row r="48" s="80">
@@ -13889,15 +13697,15 @@
         </is>
       </c>
       <c r="F48" s="82" t="n"/>
-      <c r="G48" s="88" t="b">
-        <v>0</v>
-      </c>
-      <c r="H48" s="88" t="b">
-        <v>0</v>
-      </c>
-      <c r="I48" s="89" t="n"/>
-      <c r="J48" s="89" t="n"/>
-      <c r="K48" s="87" t="n"/>
+      <c r="G48" s="87" t="b">
+        <v>0</v>
+      </c>
+      <c r="H48" s="87" t="b">
+        <v>0</v>
+      </c>
+      <c r="I48" s="88" t="n"/>
+      <c r="J48" s="88" t="n"/>
+      <c r="K48" s="89" t="n"/>
       <c r="L48" s="90" t="n"/>
     </row>
     <row r="49" ht="27" customHeight="1" s="80">
@@ -14020,129 +13828,112 @@
       <c r="J52" s="48" t="n"/>
       <c r="L52" s="31" t="n"/>
     </row>
-    <row r="53" s="80">
-      <c r="A53" s="81" t="n">
+    <row r="53" ht="40.5" customHeight="1" s="80">
+      <c r="A53" s="76" t="n">
         <v>51</v>
       </c>
-      <c r="B53" s="82" t="inlineStr">
-        <is>
-          <t>nic_fw_chk</t>
-        </is>
-      </c>
-      <c r="C53" s="82" t="inlineStr">
-        <is>
-          <t>NIC CX8 FW check</t>
-        </is>
-      </c>
-      <c r="D53" s="82" t="inlineStr">
-        <is>
-          <t>Pass - match; Fail – mismatch</t>
-        </is>
-      </c>
-      <c r="E53" s="82" t="inlineStr">
-        <is>
-          <t>&gt;&gt;&gt; Enable this check only for CX8 SKU</t>
-        </is>
-      </c>
-      <c r="F53" s="82" t="inlineStr">
-        <is>
-          <t>[CMD]</t>
-        </is>
-      </c>
-      <c r="G53" s="88" t="b">
-        <v>0</v>
-      </c>
-      <c r="H53" s="88" t="b">
-        <v>0</v>
-      </c>
-      <c r="I53" s="89" t="n"/>
-      <c r="J53" s="89" t="n"/>
-      <c r="K53" s="87" t="n"/>
-      <c r="L53" s="90" t="n"/>
-    </row>
-    <row r="54" s="80">
-      <c r="A54" s="81" t="n">
+      <c r="B53" s="43" t="inlineStr">
+        <is>
+          <t>pcie_manticore_chk</t>
+        </is>
+      </c>
+      <c r="C53" s="43" t="inlineStr">
+        <is>
+          <t>Check DC-SCM Manticore firmware version. If a mismatch is detected, an automatic upgrade will be performed.</t>
+        </is>
+      </c>
+      <c r="D53" s="43" t="inlineStr">
+        <is>
+          <t>Pass - match; Fail - mismatch</t>
+        </is>
+      </c>
+      <c r="E53" s="43" t="inlineStr">
+        <is>
+          <t>Automatically upgrade Manticore FW if version mismatch and upgrade flag is set. M1 - Check only M3/M5 - Check and upgrade at Pretest. Check only at the other stations</t>
+        </is>
+      </c>
+      <c r="F53" s="43" t="n"/>
+      <c r="G53" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="H53" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="I53" s="48" t="n"/>
+      <c r="J53" s="48" t="n"/>
+      <c r="L53" s="31" t="n"/>
+    </row>
+    <row r="54" ht="135" customHeight="1" s="80">
+      <c r="A54" s="76" t="n">
         <v>52</v>
       </c>
-      <c r="B54" s="82" t="inlineStr">
-        <is>
-          <t>nic_mac_chk</t>
-        </is>
-      </c>
-      <c r="C54" s="82" t="inlineStr">
-        <is>
-          <t>Check Mellanox MAC and retrieve Mellanox device number</t>
-        </is>
-      </c>
-      <c r="D54" s="82" t="inlineStr">
-        <is>
-          <t>- Check CX8 quantity/qty
-- MAC must match configuration.</t>
-        </is>
-      </c>
-      <c r="E54" s="82" t="inlineStr">
-        <is>
-          <t>&gt;&gt;&gt; Enable this check only for CX8 SKU</t>
-        </is>
-      </c>
-      <c r="F54" s="82" t="inlineStr">
-        <is>
-          <t>[CMD] mlxfwmanager --query | grep 'Device #'| wc -l</t>
-        </is>
-      </c>
-      <c r="G54" s="88" t="b">
-        <v>0</v>
-      </c>
-      <c r="H54" s="88" t="b">
-        <v>0</v>
-      </c>
-      <c r="I54" s="89" t="n"/>
-      <c r="J54" s="89" t="n"/>
-      <c r="K54" s="87" t="n"/>
-      <c r="L54" s="90" t="n"/>
-    </row>
-    <row r="55" s="80">
-      <c r="A55" s="81" t="n">
+      <c r="B54" s="43" t="inlineStr">
+        <is>
+          <t>pcie_manticore_provision_chk</t>
+        </is>
+      </c>
+      <c r="C54" s="43" t="inlineStr">
+        <is>
+          <t>One-time factory provisioning of the DC-SCM Manticore (Cerberus v2) security chip's certificate chain — Device ID, Root CA, and Intermediate CA certificates are fused into the chip via cerberus_utility importsignedcert.</t>
+        </is>
+      </c>
+      <c r="D54" s="43" t="inlineStr">
+        <is>
+          <t>PASS if the chip already shows a complete signed certificate chain, or if all three cerberus_fuse() calls succeed and a post-fuse is_provision check confirms completion.</t>
+        </is>
+      </c>
+      <c r="E54" s="43" t="inlineStr">
+        <is>
+          <t>- Security/identity-relevant, one-time step. Uses is_provision("Manticore") to skip entirely if already provisioned (idempotent). If the public key harvested from the chip (CSR) doesn't match what SF (the factory server / key-management system) has on file, it is treated as a "re-harvest" condition.
+- Certificate fusing order is Device ID (HWKey1, cert index 0/file index 1) → Root CA (HWKey3, cert index 1/file index 3) → Intermediate CA (HWKey2, cert index 2/file index 2). 
+- cerberus_fuse() treats IPMI return code 74 ("Certificate provisioning locked") as a soft-success, not a failure, since re-fusing an already-locked slot is expected on retries.</t>
+        </is>
+      </c>
+      <c r="F54" s="43" t="n"/>
+      <c r="G54" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="H54" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="I54" s="48" t="n"/>
+      <c r="J54" s="48" t="n"/>
+      <c r="L54" s="31" t="n"/>
+    </row>
+    <row r="55" ht="67.5" customHeight="1" s="80">
+      <c r="A55" s="76" t="n">
         <v>53</v>
       </c>
-      <c r="B55" s="82" t="inlineStr">
-        <is>
-          <t>nic_ib_speed_test</t>
-        </is>
-      </c>
-      <c r="C55" s="82" t="inlineStr">
-        <is>
-          <t>Test CX8 InfiniBand Speed</t>
-        </is>
-      </c>
-      <c r="D55" s="82" t="inlineStr">
-        <is>
-          <t>Pass – Speed meets the required standard; Fail –Speed does not meet the required standard</t>
-        </is>
-      </c>
-      <c r="E55" s="82" t="inlineStr">
-        <is>
-          <t>- CX8 port connect to CX8 port in L10.
-- CX8 port connect to XDR switch test fixture in L11.
-&gt;&gt;&gt;MSFT agreed to waive in EVT. (ADO#2992170)
-&gt;&gt;&gt; Enable this check only for CX8 SKU + IB</t>
-        </is>
-      </c>
-      <c r="F55" s="82" t="inlineStr">
-        <is>
-          <t>[CMD]</t>
-        </is>
-      </c>
-      <c r="G55" s="88" t="b">
-        <v>0</v>
-      </c>
-      <c r="H55" s="88" t="b">
-        <v>0</v>
-      </c>
-      <c r="I55" s="89" t="n"/>
-      <c r="J55" s="89" t="n"/>
-      <c r="K55" s="87" t="n"/>
-      <c r="L55" s="90" t="n"/>
+      <c r="B55" s="43" t="inlineStr">
+        <is>
+          <t>pcie_manticore_log_chk</t>
+        </is>
+      </c>
+      <c r="C55" s="43" t="inlineStr">
+        <is>
+          <t>Reads the Manticore chip's debug log (cerberus_utility debuglogread), verifies the FW version recorded in the log matches expected, checks CS0/CS1 flash device consistency, scans for uncleared error codes since the last boot, and scans for unfiltered Warning/Error lines against a configurable skip-pattern list — clearing the log only after a full PASS.</t>
+        </is>
+      </c>
+      <c r="D55" s="43" t="inlineStr">
+        <is>
+          <t>PASS only if: (1) FW version found in log matches pcie_manticore_ver, (2) Port 1 CS0/CS1 vendor+device+capacity match each other, (3) no known bad error codes (0x7f001e0c/0d/0e, 0x7f001d05, 0x7f001d10) appear after the last-boot marker, (4) no unfiltered Warning/Error lines appear after the last-boot marker.</t>
+        </is>
+      </c>
+      <c r="E55" s="43" t="inlineStr">
+        <is>
+          <t>If the log is completely empty of a FW-version line, it triggers an AC power cycle as a recovery action and still FAILs the current pass (log message: "please AC the server"). pcie_manticore_debuglog_skip config defines patterns to exclude from the Warning/Error scan</t>
+        </is>
+      </c>
+      <c r="F55" s="43" t="n"/>
+      <c r="G55" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="H55" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="I55" s="48" t="n"/>
+      <c r="J55" s="48" t="n"/>
+      <c r="L55" s="31" t="n"/>
     </row>
     <row r="56" ht="40.5" customHeight="1" s="80">
       <c r="A56" s="76" t="n">
@@ -14150,17 +13941,17 @@
       </c>
       <c r="B56" s="43" t="inlineStr">
         <is>
-          <t>pcie_manticore_chk</t>
+          <t>pcie_tip_chk</t>
         </is>
       </c>
       <c r="C56" s="43" t="inlineStr">
         <is>
-          <t>Check DC-SCM Manticore firmware version. If a mismatch is detected, an automatic upgrade will be performed.</t>
+          <t>Check DC-SCM Hydra TIP firmware version. If a mismatch is detected, an automatic upgrade will be performed.</t>
         </is>
       </c>
       <c r="D56" s="43" t="inlineStr">
         <is>
-          <t>Pass - match; Fail - mismatch</t>
+          <t>Pass - match; Fail – mismatch</t>
         </is>
       </c>
       <c r="E56" s="43" t="inlineStr">
@@ -14179,30 +13970,28 @@
       <c r="J56" s="48" t="n"/>
       <c r="L56" s="31" t="n"/>
     </row>
-    <row r="57" ht="135" customHeight="1" s="80">
+    <row r="57" ht="40.5" customHeight="1" s="80">
       <c r="A57" s="76" t="n">
         <v>55</v>
       </c>
       <c r="B57" s="43" t="inlineStr">
         <is>
-          <t>pcie_manticore_provision_chk</t>
+          <t>pcie_tip_provision_chk</t>
         </is>
       </c>
       <c r="C57" s="43" t="inlineStr">
         <is>
-          <t>One-time factory provisioning of the DC-SCM Manticore (Cerberus v2) security chip's certificate chain — Device ID, Root CA, and Intermediate CA certificates are fused into the chip via cerberus_utility importsignedcert.</t>
+          <t>Same one-time provisioning flow as pcie_manticore_provision, but for the DC-SCM Hydra/TIP security chip (BMC-side security control introduced with M1120).</t>
         </is>
       </c>
       <c r="D57" s="43" t="inlineStr">
         <is>
-          <t>PASS if the chip already shows a complete signed certificate chain, or if all three cerberus_fuse() calls succeed and a post-fuse is_provision check confirms completion.</t>
+          <t>Identical logic/criteria to pcie_manticore_provision, keyed on component name "Hydra".</t>
         </is>
       </c>
       <c r="E57" s="43" t="inlineStr">
         <is>
-          <t>- Security/identity-relevant, one-time step. Uses is_provision("Manticore") to skip entirely if already provisioned (idempotent). If the public key harvested from the chip (CSR) doesn't match what SF (the factory server / key-management system) has on file, it is treated as a "re-harvest" condition.
-- Certificate fusing order is Device ID (HWKey1, cert index 0/file index 1) → Root CA (HWKey3, cert index 1/file index 3) → Intermediate CA (HWKey2, cert index 2/file index 2). 
-- cerberus_fuse() treats IPMI return code 74 ("Certificate provisioning locked") as a soft-success, not a failure, since re-fusing an already-locked slot is expected on retries.</t>
+          <t>Security/identity-relevant, one-time step. Structurally identical to Manticore provisioning, same 3-cert fuse order Device ID → Root CA → Intermediate CA).</t>
         </is>
       </c>
       <c r="F57" s="43" t="n"/>
@@ -14222,22 +14011,22 @@
       </c>
       <c r="B58" s="43" t="inlineStr">
         <is>
-          <t>pcie_manticore_log_chk</t>
+          <t>pcie_tip_log_chk</t>
         </is>
       </c>
       <c r="C58" s="43" t="inlineStr">
         <is>
-          <t>Reads the Manticore chip's debug log (cerberus_utility debuglogread), verifies the FW version recorded in the log matches expected, checks CS0/CS1 flash device consistency, scans for uncleared error codes since the last boot, and scans for unfiltered Warning/Error lines against a configurable skip-pattern list — clearing the log only after a full PASS.</t>
+          <t>Reads the Hydra/TIP chip's debug log (cerberus_utility debuglogread), verifies the FW version recorded in the log matches expected, checks CS0/CS1 flash device consistency, scans for uncleared error codes since the last boot, and scans for unfiltered Warning/Error lines against a configurable skip-pattern list — clearing the log only after a full PASS.</t>
         </is>
       </c>
       <c r="D58" s="43" t="inlineStr">
         <is>
-          <t>PASS only if: (1) FW version found in log matches pcie_manticore_ver, (2) Port 1 CS0/CS1 vendor+device+capacity match each other, (3) no known bad error codes (0x7f001e0c/0d/0e, 0x7f001d05, 0x7f001d10) appear after the last-boot marker, (4) no unfiltered Warning/Error lines appear after the last-boot marker.</t>
+          <t>PASS if: (1) the log contains a "Cerberus main flash" entry at all (else AC-cycle + FAIL), (2) main/recovery flash vendor+device+capacity match, (3) no unfiltered Warning/Error tagged lines appear after the last-boot marker.</t>
         </is>
       </c>
       <c r="E58" s="43" t="inlineStr">
         <is>
-          <t>If the log is completely empty of a FW-version line, it triggers an AC power cycle as a recovery action and still FAILs the current pass (log message: "please AC the server"). pcie_manticore_debuglog_skip config defines patterns to exclude from the Warning/Error scan</t>
+          <t>The Warning/Error scan here additionally requires the tag field (3rd |-delimited column) itself contain "Warning" or "Error", not just the whole line.</t>
         </is>
       </c>
       <c r="F58" s="43" t="n"/>
@@ -14251,30 +14040,26 @@
       <c r="J58" s="48" t="n"/>
       <c r="L58" s="31" t="n"/>
     </row>
-    <row r="59" ht="40.5" customHeight="1" s="80">
+    <row r="59" ht="27" customHeight="1" s="80">
       <c r="A59" s="76" t="n">
         <v>57</v>
       </c>
       <c r="B59" s="43" t="inlineStr">
         <is>
-          <t>pcie_tip_chk</t>
+          <t>fpga_gp_mac_chk</t>
         </is>
       </c>
       <c r="C59" s="43" t="inlineStr">
         <is>
-          <t>Check DC-SCM Hydra TIP firmware version. If a mismatch is detected, an automatic upgrade will be performed.</t>
+          <t>Checks the GlacierPeak's own network interface MAC address (read via ifconfig enm0 over SSH to the GP SoC) against mac[0].</t>
         </is>
       </c>
       <c r="D59" s="43" t="inlineStr">
         <is>
-          <t>Pass - match; Fail – mismatch</t>
-        </is>
-      </c>
-      <c r="E59" s="43" t="inlineStr">
-        <is>
-          <t>Automatically upgrade Manticore FW if version mismatch and upgrade flag is set. M1 - Check only M3/M5 - Check and upgrade at Pretest. Check only at the other stations</t>
-        </is>
-      </c>
+          <t>PASS if the parsed ether MAC equals getConfigValue('mac')[0] (uppercased, colon-stripped).</t>
+        </is>
+      </c>
+      <c r="E59" s="43" t="n"/>
       <c r="F59" s="43" t="n"/>
       <c r="G59" s="47" t="b">
         <v>0</v>
@@ -14286,28 +14071,28 @@
       <c r="J59" s="48" t="n"/>
       <c r="L59" s="31" t="n"/>
     </row>
-    <row r="60" ht="40.5" customHeight="1" s="80">
+    <row r="60" ht="135" customHeight="1" s="80">
       <c r="A60" s="76" t="n">
         <v>58</v>
       </c>
       <c r="B60" s="43" t="inlineStr">
         <is>
-          <t>pcie_tip_provision_chk</t>
+          <t>fpga_gp_status_chk</t>
         </is>
       </c>
       <c r="C60" s="43" t="inlineStr">
         <is>
-          <t>Same one-time provisioning flow as pcie_manticore_provision, but for the DC-SCM Hydra/TIP security chip (BMC-side security control introduced with M1120).</t>
+          <t>Runs fpgadiagnostics -dumpHealth (via a stage-appropriate SSH route: direct M3, RSCM-jumper M3, or RSCM-serial-proxy M5) and parses per-subsystem [FPGA-XXX] health lines, with specific waivers for known FPGA-NETWORK and FPGA-CONFIG warnings, and a one-time auto-reboot self-heal if the PCIe link status reads "WARNING" while in App mode.</t>
         </is>
       </c>
       <c r="D60" s="43" t="inlineStr">
         <is>
-          <t>Identical logic/criteria to pcie_manticore_provision, keyed on component name "Hydra".</t>
+          <t>PASS if no un-waived [FPGA-XXX] line fails its ] OK [ check.</t>
         </is>
       </c>
       <c r="E60" s="43" t="inlineStr">
         <is>
-          <t>Security/identity-relevant, one-time step. Structurally identical to Manticore provisioning, same 3-cert fuse order Device ID → Root CA → Intermediate CA).</t>
+          <t>Likely bug: in the FPGA-NETWORK-on-M5 branch, the failure path does isfail += 1 — but the function only ever initializes a variable named fail = 0, never isfail. If that exact branch is hit (M5 stage, FPGA-NETWORK reports non-OK, and the message isn't the specific waived "one or more network links down" string), this will raise NameError: name 'isfail' is not defined instead of cleanly failing the test. Also implements a reboot self-heal: if PCIe status is "WARNING" while FPGA is in App mode (config_status == "0") and no .reboot marker file exists yet for this unit, it touches the marker and issues reboot immediately rather than failing — the next run after reboot either clears (marker removed, PASS) or fails hard if the WARNING persists (marker already present).</t>
         </is>
       </c>
       <c r="F60" s="43" t="n"/>
@@ -14321,28 +14106,28 @@
       <c r="J60" s="48" t="n"/>
       <c r="L60" s="31" t="n"/>
     </row>
-    <row r="61" ht="67.5" customHeight="1" s="80">
+    <row r="61" ht="108" customHeight="1" s="80">
       <c r="A61" s="76" t="n">
         <v>59</v>
       </c>
       <c r="B61" s="43" t="inlineStr">
         <is>
-          <t>pcie_tip_log_chk</t>
+          <t>fpga_gp_fw_chk</t>
         </is>
       </c>
       <c r="C61" s="43" t="inlineStr">
         <is>
-          <t>Reads the Hydra/TIP chip's debug log (cerberus_utility debuglogread), verifies the FW version recorded in the log matches expected, checks CS0/CS1 flash device consistency, scans for uncleared error codes since the last boot, and scans for unfiltered Warning/Error lines against a configurable skip-pattern list — clearing the log only after a full PASS.</t>
+          <t>The most comprehensive FPGA firmware check in this station — validates Cerberus FW, Cyclone V PFM Device/Platform ID + image version, SoC PFM Device/Platform ID, SoC FIP firmware, SoC OS version, Linux kernel version, and FPGA diagnostic tools version, all read from a single batched SSH session to the GlacierPeak SoC console — with a coordinated multi-component upgrade sequence (in a specific vendor-mandated order) if any check fails and upgrades are allowed.</t>
         </is>
       </c>
       <c r="D61" s="43" t="inlineStr">
         <is>
-          <t>PASS if: (1) the log contains a "Cerberus main flash" entry at all (else AC-cycle + FAIL), (2) main/recovery flash vendor+device+capacity match, (3) no unfiltered Warning/Error tagged lines appear after the last-boot marker.</t>
+          <t>PASS only if every one of the 11 checked version/ID pairs matches (SoC OS version additionally requires the SoC's boot mode to be 0/PXE — a match while in a non-PXE bootmode is treated as needing a re-image and still counts as a failure needing upgrade).</t>
         </is>
       </c>
       <c r="E61" s="43" t="inlineStr">
         <is>
-          <t>The Warning/Error scan here additionally requires the tag field (3rd |-delimited column) itself contain "Warning" or "Error", not just the whole line.</t>
+          <t>Upgrade ordering follows a documented vendor spec (comment cites "M1195579 RevD A2051 GLACIER PEAK INTEGRATION REQUIREMENTS"): Cerberus FW → SoC PFM ID → Cyclone V PFM ID → SoC FIP → SoC OS Image → Cyclone V FPGA Image → Agilex FPGA APP/SoftNIC Image. SoC Linux Kernel version and SoC FPGA Tools version are explicitly flagged as non-upgradable — a mismatch there just fails, with no remediation path. A successful PFM/FIP/OS-image/App-image upgrade sets an is_reset flag that triggers gp_reset() (an AC-cycle-equivalent reset+power-cycle-and-wait) at the very end.</t>
         </is>
       </c>
       <c r="F61" s="43" t="n"/>
@@ -14356,26 +14141,30 @@
       <c r="J61" s="48" t="n"/>
       <c r="L61" s="31" t="n"/>
     </row>
-    <row r="62" ht="27" customHeight="1" s="80">
+    <row r="62" ht="148.5" customHeight="1" s="80">
       <c r="A62" s="76" t="n">
         <v>60</v>
       </c>
       <c r="B62" s="43" t="inlineStr">
         <is>
-          <t>fpga_gp_mac_chk</t>
+          <t>fpga_gp_softnic_ver_chk</t>
         </is>
       </c>
       <c r="C62" s="43" t="inlineStr">
         <is>
-          <t>Checks the GlacierPeak's own network interface MAC address (read via ifconfig enm0 over SSH to the GP SoC) against mac[0].</t>
+          <t>Checks the GlacierPeak Agilex FPGA SoftNIC image version by putting the GP into "golden mode" (boot mode 0) and reading recorded register values (role 65/101) from a status log left on the BMC filesystem.</t>
         </is>
       </c>
       <c r="D62" s="43" t="inlineStr">
         <is>
-          <t>PASS if the parsed ether MAC equals getConfigValue('mac')[0] (uppercased, colon-stripped).</t>
-        </is>
-      </c>
-      <c r="E62" s="43" t="n"/>
+          <t>PASS when the recorded role_id role_ver equals fpga_gp_softnic_ver. FAIL on SSH/SFTP failure, on failure to reach golden boot mode, or on version mismatch when upgrade is disabled/fails.</t>
+        </is>
+      </c>
+      <c r="E62" s="43" t="inlineStr">
+        <is>
+          <t>Multi-stage, stateful check keyed on the presence of /vol/data/persistent/tests/golden_status.txt on the BMC. If the log doesn't exist yet, the function uploads SoCFPGAGoldenTestSvc.service and fpga_golden_check.py to the BMC, switches GP into golden boot mode (cerberus_utility fpgasetbootmode 0), forces an AC cycle (RSCM rscm_system_ac on M5, gs_pdb_ac_cycle otherwise) to make the mode take effect, and then returns 1 — meaning the first pass of this item after an image/config change always intentionally fails and needs a subsequent PRETEST re-run to actually validate the version. On version mismatch with fpga_gp_fw_upgrade TRUE, it calls _gp_fpga_softnic_upgrade() and then re-generates the golden log (also returning 1) rather than re-checking in the same pass.</t>
+        </is>
+      </c>
       <c r="F62" s="43" t="n"/>
       <c r="G62" s="47" t="b">
         <v>0</v>
@@ -14393,22 +14182,24 @@
       </c>
       <c r="B63" s="43" t="inlineStr">
         <is>
-          <t>fpga_gp_status_chk</t>
+          <t>fpga_gp_cerberus_provision_chk</t>
         </is>
       </c>
       <c r="C63" s="43" t="inlineStr">
         <is>
-          <t>Runs fpgadiagnostics -dumpHealth (via a stage-appropriate SSH route: direct M3, RSCM-jumper M3, or RSCM-serial-proxy M5) and parses per-subsystem [FPGA-XXX] health lines, with specific waivers for known FPGA-NETWORK and FPGA-CONFIG warnings, and a one-time auto-reboot self-heal if the PCIe link status reads "WARNING" while in App mode.</t>
+          <t>One-time provisioning of the GlacierPeak's own Cerberus security chip (distinct from Agilex slots above) — fuses Device ID/Root CA/Intermediate CA certs via a UART/SSH session directly into the GlacierPeak SoC console.</t>
         </is>
       </c>
       <c r="D63" s="43" t="inlineStr">
         <is>
-          <t>PASS if no un-waived [FPGA-XXX] line fails its ] OK [ check.</t>
+          <t>PASS if pcie_tool.is_provision("Cerberus") already shows complete, or if all three certs are fused successfully and a post-check confirms completion.</t>
         </is>
       </c>
       <c r="E63" s="43" t="inlineStr">
         <is>
-          <t>Likely bug: in the FPGA-NETWORK-on-M5 branch, the failure path does isfail += 1 — but the function only ever initializes a variable named fail = 0, never isfail. If that exact branch is hit (M5 stage, FPGA-NETWORK reports non-OK, and the message isn't the specific waived "one or more network links down" string), this will raise NameError: name 'isfail' is not defined instead of cleanly failing the test. Also implements a reboot self-heal: if PCIe status is "WARNING" while FPGA is in App mode (config_status == "0") and no .reboot marker file exists yet for this unit, it touches the marker and issues reboot immediately rather than failing — the next run after reboot either clears (marker removed, PASS) or fails hard if the WARNING persists (marker already present).</t>
+          <t>Two very different code paths: 
+- for prj_stage == "M5" it SFTP-uploads the three HWKEY .bin files to the BMC, then uses a shell command list over usb0 (10.235.100.0/31 point-to-point link) with scp -P 2200 to pull each key onto the GlacierPeak SoC and run cerberus_utility importsignedcert locally there — all three fuse commands (root CA idx 1, intermediate idx 2, device ID idx 0) run under a single rscm_lock.
+- For other stages it uses a raw pxssh session direct to the GlacierPeak SoC on port 8295 (user admin/admin), with up to 2 retries and a 90s backoff between attempts if the SoC is "busy". HWKey files are deleted from the BMC after fusing in both paths.</t>
         </is>
       </c>
       <c r="F63" s="43" t="n"/>
@@ -14422,133 +14213,26 @@
       <c r="J63" s="48" t="n"/>
       <c r="L63" s="31" t="n"/>
     </row>
-    <row r="64" ht="108" customHeight="1" s="80">
+    <row r="64" ht="121.5" customHeight="1" s="80">
       <c r="A64" s="76" t="n">
         <v>62</v>
       </c>
       <c r="B64" s="43" t="inlineStr">
         <is>
-          <t>fpga_gp_fw_chk</t>
+          <t>fpga_gp_agilex_provision</t>
         </is>
       </c>
       <c r="C64" s="43" t="inlineStr">
         <is>
-          <t>The most comprehensive FPGA firmware check in this station — validates Cerberus FW, Cyclone V PFM Device/Platform ID + image version, SoC PFM Device/Platform ID, SoC FIP firmware, SoC OS version, Linux kernel version, and FPGA diagnostic tools version, all read from a single batched SSH session to the GlacierPeak SoC console — with a coordinated multi-component upgrade sequence (in a specific vendor-mandated order) if any check fails and upgrades are allowed.</t>
+          <t>One-time provisioning of the GlacierPeak Agilex FPGA's two certificate slots via the fpgasec tool — slot 0 for "Intel IPCS" (Agilex_mfg) and slot 1 for "Microsoft" (Agilex_msft), each independently skippable if already provisioned.</t>
         </is>
       </c>
       <c r="D64" s="43" t="inlineStr">
         <is>
-          <t>PASS only if every one of the 11 checked version/ID pairs matches (SoC OS version additionally requires the SoC's boot mode to be 0/PXE — a match while in a non-PXE bootmode is treated as needing a re-image and still counts as a failure needing upgrade).</t>
+          <t>PASS if both slot0 and slot1 report provisioned after the flow (checked via _is_gp_agilex_provision). FAIL if the fpgasec_{ver} tool is missing, cert files can't be obtained/uploaded, -setCertificate fails, or the final status check still shows either slot unprovisioned.</t>
         </is>
       </c>
       <c r="E64" s="43" t="inlineStr">
-        <is>
-          <t>Upgrade ordering follows a documented vendor spec (comment cites "M1195579 RevD A2051 GLACIER PEAK INTEGRATION REQUIREMENTS"): Cerberus FW → SoC PFM ID → Cyclone V PFM ID → SoC FIP → SoC OS Image → Cyclone V FPGA Image → Agilex FPGA APP/SoftNIC Image. SoC Linux Kernel version and SoC FPGA Tools version are explicitly flagged as non-upgradable — a mismatch there just fails, with no remediation path. A successful PFM/FIP/OS-image/App-image upgrade sets an is_reset flag that triggers gp_reset() (an AC-cycle-equivalent reset+power-cycle-and-wait) at the very end.</t>
-        </is>
-      </c>
-      <c r="F64" s="43" t="n"/>
-      <c r="G64" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="H64" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="I64" s="48" t="n"/>
-      <c r="J64" s="48" t="n"/>
-      <c r="L64" s="31" t="n"/>
-    </row>
-    <row r="65" ht="148.5" customHeight="1" s="80">
-      <c r="A65" s="76" t="n">
-        <v>63</v>
-      </c>
-      <c r="B65" s="43" t="inlineStr">
-        <is>
-          <t>fpga_gp_softnic_ver_chk</t>
-        </is>
-      </c>
-      <c r="C65" s="43" t="inlineStr">
-        <is>
-          <t>Checks the GlacierPeak Agilex FPGA SoftNIC image version by putting the GP into "golden mode" (boot mode 0) and reading recorded register values (role 65/101) from a status log left on the BMC filesystem.</t>
-        </is>
-      </c>
-      <c r="D65" s="43" t="inlineStr">
-        <is>
-          <t>PASS when the recorded role_id role_ver equals fpga_gp_softnic_ver. FAIL on SSH/SFTP failure, on failure to reach golden boot mode, or on version mismatch when upgrade is disabled/fails.</t>
-        </is>
-      </c>
-      <c r="E65" s="43" t="inlineStr">
-        <is>
-          <t>Multi-stage, stateful check keyed on the presence of /vol/data/persistent/tests/golden_status.txt on the BMC. If the log doesn't exist yet, the function uploads SoCFPGAGoldenTestSvc.service and fpga_golden_check.py to the BMC, switches GP into golden boot mode (cerberus_utility fpgasetbootmode 0), forces an AC cycle (RSCM rscm_system_ac on M5, gs_pdb_ac_cycle otherwise) to make the mode take effect, and then returns 1 — meaning the first pass of this item after an image/config change always intentionally fails and needs a subsequent PRETEST re-run to actually validate the version. On version mismatch with fpga_gp_fw_upgrade TRUE, it calls _gp_fpga_softnic_upgrade() and then re-generates the golden log (also returning 1) rather than re-checking in the same pass.</t>
-        </is>
-      </c>
-      <c r="F65" s="43" t="n"/>
-      <c r="G65" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="H65" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="I65" s="48" t="n"/>
-      <c r="J65" s="48" t="n"/>
-      <c r="L65" s="31" t="n"/>
-    </row>
-    <row r="66" ht="135" customHeight="1" s="80">
-      <c r="A66" s="76" t="n">
-        <v>64</v>
-      </c>
-      <c r="B66" s="43" t="inlineStr">
-        <is>
-          <t>fpga_gp_cerberus_provision_chk</t>
-        </is>
-      </c>
-      <c r="C66" s="43" t="inlineStr">
-        <is>
-          <t>One-time provisioning of the GlacierPeak's own Cerberus security chip (distinct from Agilex slots above) — fuses Device ID/Root CA/Intermediate CA certs via a UART/SSH session directly into the GlacierPeak SoC console.</t>
-        </is>
-      </c>
-      <c r="D66" s="43" t="inlineStr">
-        <is>
-          <t>PASS if pcie_tool.is_provision("Cerberus") already shows complete, or if all three certs are fused successfully and a post-check confirms completion.</t>
-        </is>
-      </c>
-      <c r="E66" s="43" t="inlineStr">
-        <is>
-          <t>Two very different code paths: 
-- for prj_stage == "M5" it SFTP-uploads the three HWKEY .bin files to the BMC, then uses a shell command list over usb0 (10.235.100.0/31 point-to-point link) with scp -P 2200 to pull each key onto the GlacierPeak SoC and run cerberus_utility importsignedcert locally there — all three fuse commands (root CA idx 1, intermediate idx 2, device ID idx 0) run under a single rscm_lock.
-- For other stages it uses a raw pxssh session direct to the GlacierPeak SoC on port 8295 (user admin/admin), with up to 2 retries and a 90s backoff between attempts if the SoC is "busy". HWKey files are deleted from the BMC after fusing in both paths.</t>
-        </is>
-      </c>
-      <c r="F66" s="43" t="n"/>
-      <c r="G66" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="H66" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="I66" s="48" t="n"/>
-      <c r="J66" s="48" t="n"/>
-      <c r="L66" s="31" t="n"/>
-    </row>
-    <row r="67" ht="121.5" customHeight="1" s="80">
-      <c r="A67" s="76" t="n">
-        <v>65</v>
-      </c>
-      <c r="B67" s="43" t="inlineStr">
-        <is>
-          <t>fpga_gp_agilex_provision</t>
-        </is>
-      </c>
-      <c r="C67" s="43" t="inlineStr">
-        <is>
-          <t>One-time provisioning of the GlacierPeak Agilex FPGA's two certificate slots via the fpgasec tool — slot 0 for "Intel IPCS" (Agilex_mfg) and slot 1 for "Microsoft" (Agilex_msft), each independently skippable if already provisioned.</t>
-        </is>
-      </c>
-      <c r="D67" s="43" t="inlineStr">
-        <is>
-          <t>PASS if both slot0 and slot1 report provisioned after the flow (checked via _is_gp_agilex_provision). FAIL if the fpgasec_{ver} tool is missing, cert files can't be obtained/uploaded, -setCertificate fails, or the final status check still shows either slot unprovisioned.</t>
-        </is>
-      </c>
-      <c r="E67" s="43" t="inlineStr">
         <is>
           <t>- Security/identity-relevant, one-time step, M3-only. 
 - Unlike the Manticore/TIP flow this checks each slot independently — a partially-provisioned board (e.g. slot0 done, slot1 not) only provisions the missing slot. 
@@ -14557,6 +14241,111 @@
 - After both slots are set, it resets the FPGA and sleeps 300s before the final confirmation check.</t>
         </is>
       </c>
+      <c r="F64" s="43" t="n"/>
+      <c r="G64" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="H64" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="I64" s="48" t="n"/>
+      <c r="J64" s="48" t="n"/>
+      <c r="L64" s="31" t="n"/>
+    </row>
+    <row r="65" ht="27" customHeight="1" s="80">
+      <c r="A65" s="76" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" s="43" t="inlineStr">
+        <is>
+          <t>bmc_fan_qty_chk</t>
+        </is>
+      </c>
+      <c r="C65" s="43" t="inlineStr">
+        <is>
+          <t>Checks the number of fans reporting an "OK" SDR state against SF's bmc_fan_qty.</t>
+        </is>
+      </c>
+      <c r="D65" s="43" t="inlineStr">
+        <is>
+          <t>PASS if ipmitool sdr elist | grep -E "^Fan" | grep -ic ok equals getConfigValue('bmc_fan_qty').</t>
+        </is>
+      </c>
+      <c r="E65" s="43" t="inlineStr">
+        <is>
+          <t>Simple count check; no self-heal (a missing/failed fan is a physical issue, not a firmware one).</t>
+        </is>
+      </c>
+      <c r="F65" s="43" t="n"/>
+      <c r="G65" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="H65" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="I65" s="48" t="n"/>
+      <c r="J65" s="48" t="n"/>
+      <c r="L65" s="31" t="n"/>
+    </row>
+    <row r="66" ht="40.5" customHeight="1" s="80">
+      <c r="A66" s="76" t="n">
+        <v>64</v>
+      </c>
+      <c r="B66" s="43" t="inlineStr">
+        <is>
+          <t>bmc_fan_speed_chk</t>
+        </is>
+      </c>
+      <c r="C66" s="43" t="inlineStr">
+        <is>
+          <t>Sweeps fan duty cycle through 100%/50%/30% (100% skipped at M1 stage per an old thermal-noise waiver) and checks each fan's measured RPM against inlet/outlet min/max bounds for the detected fan vendor.</t>
+        </is>
+      </c>
+      <c r="D66" s="43" t="inlineStr">
+        <is>
+          <t>PASS if every fan's RPM at every tested duty point falls within its vendor-specific inlet/outlet min/max range.</t>
+        </is>
+      </c>
+      <c r="E66" s="43" t="inlineStr">
+        <is>
+          <t>After the sweep, fan mode is forced back to auto unconditionally, and at M1 stage specifically it's additionally set to a fixed 50% manual.</t>
+        </is>
+      </c>
+      <c r="F66" s="43" t="n"/>
+      <c r="G66" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="H66" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="I66" s="48" t="n"/>
+      <c r="J66" s="48" t="n"/>
+      <c r="L66" s="31" t="n"/>
+    </row>
+    <row r="67" ht="27" customHeight="1" s="80">
+      <c r="A67" s="76" t="n">
+        <v>65</v>
+      </c>
+      <c r="B67" s="43" t="inlineStr">
+        <is>
+          <t>storage_hdd_info_chk</t>
+        </is>
+      </c>
+      <c r="C67" s="43" t="inlineStr">
+        <is>
+          <t>Check SATA/NVMe disk info (model, size, firmware) consistency between DUT and config file.</t>
+        </is>
+      </c>
+      <c r="D67" s="43" t="inlineStr">
+        <is>
+          <t>Disk count matches config. Each disk's model, size, and firmware match expected values.</t>
+        </is>
+      </c>
+      <c r="E67" s="43" t="inlineStr">
+        <is>
+          <t>EMPTY slots in config are skipped. M3/M5 Check and upgrade at Pretest. Check only at the other stations .</t>
+        </is>
+      </c>
       <c r="F67" s="43" t="n"/>
       <c r="G67" s="47" t="b">
         <v>0</v>
@@ -14574,22 +14363,22 @@
       </c>
       <c r="B68" s="43" t="inlineStr">
         <is>
-          <t>bmc_fan_qty_chk</t>
+          <t>storage_nvme_quantity_chk</t>
         </is>
       </c>
       <c r="C68" s="43" t="inlineStr">
         <is>
-          <t>Checks the number of fans reporting an "OK" SDR state against SF's bmc_fan_qty.</t>
+          <t>Verify the total number of detected NVM E drives matches the expected quantity.</t>
         </is>
       </c>
       <c r="D68" s="43" t="inlineStr">
         <is>
-          <t>PASS if ipmitool sdr elist | grep -E "^Fan" | grep -ic ok equals getConfigValue('bmc_fan_qty').</t>
+          <t>Pass - return 0; Fail - return 1</t>
         </is>
       </c>
       <c r="E68" s="43" t="inlineStr">
         <is>
-          <t>Simple count check; no self-heal (a missing/failed fan is a physical issue, not a firmware one).</t>
+          <t>M1 : expected count is determined by E1S2 or E1S4.</t>
         </is>
       </c>
       <c r="F68" s="43" t="n"/>
@@ -14603,30 +14392,26 @@
       <c r="J68" s="48" t="n"/>
       <c r="L68" s="31" t="n"/>
     </row>
-    <row r="69" ht="40.5" customHeight="1" s="80">
+    <row r="69" ht="13.5" customHeight="1" s="80">
       <c r="A69" s="76" t="n">
         <v>67</v>
       </c>
       <c r="B69" s="43" t="inlineStr">
         <is>
-          <t>bmc_fan_speed_chk</t>
+          <t>storage_hdd_func_test</t>
         </is>
       </c>
       <c r="C69" s="43" t="inlineStr">
         <is>
-          <t>Sweeps fan duty cycle through 100%/50%/30% (100% skipped at M1 stage per an old thermal-noise waiver) and checks each fan's measured RPM against inlet/outlet min/max bounds for the detected fan vendor.</t>
+          <t>Perform random read/write test on all HDDs and NVMEs.</t>
         </is>
       </c>
       <c r="D69" s="43" t="inlineStr">
         <is>
-          <t>PASS if every fan's RPM at every tested duty point falls within its vendor-specific inlet/outlet min/max range.</t>
-        </is>
-      </c>
-      <c r="E69" s="43" t="inlineStr">
-        <is>
-          <t>After the sweep, fan mode is forced back to auto unconditionally, and at M1 stage specifically it's additionally set to a fixed 50% manual.</t>
-        </is>
-      </c>
+          <t>Pass - return 0; Fail - return 1</t>
+        </is>
+      </c>
+      <c r="E69" s="43" t="n"/>
       <c r="F69" s="43" t="n"/>
       <c r="G69" s="47" t="b">
         <v>0</v>
@@ -14638,30 +14423,26 @@
       <c r="J69" s="48" t="n"/>
       <c r="L69" s="31" t="n"/>
     </row>
-    <row r="70" ht="27" customHeight="1" s="80">
+    <row r="70" ht="40.5" customHeight="1" s="80">
       <c r="A70" s="76" t="n">
         <v>68</v>
       </c>
       <c r="B70" s="43" t="inlineStr">
         <is>
-          <t>storage_hdd_info_chk</t>
+          <t>storage_nvme_smart_chk</t>
         </is>
       </c>
       <c r="C70" s="43" t="inlineStr">
         <is>
-          <t>Check SATA/NVMe disk info (model, size, firmware) consistency between DUT and config file.</t>
+          <t>Check NVMe SMART log parameters to ensure disk health is within acceptable thresholds.</t>
         </is>
       </c>
       <c r="D70" s="43" t="inlineStr">
         <is>
-          <t>Disk count matches config. Each disk's model, size, and firmware match expected values.</t>
-        </is>
-      </c>
-      <c r="E70" s="43" t="inlineStr">
-        <is>
-          <t>EMPTY slots in config are skipped. M3/M5 Check and upgrade at Pretest. Check only at the other stations .</t>
-        </is>
-      </c>
+          <t>All NVMe devices must meet: critical_warning == 0 temperature &lt; 70°C percentage_used &lt; 3% available_spare &gt;= 99% media_errors == 0 warning_temperature_time == 0</t>
+        </is>
+      </c>
+      <c r="E70" s="43" t="n"/>
       <c r="F70" s="43" t="n"/>
       <c r="G70" s="47" t="b">
         <v>0</v>
@@ -14679,22 +14460,22 @@
       </c>
       <c r="B71" s="43" t="inlineStr">
         <is>
-          <t>storage_nvme_quantity_chk</t>
+          <t>bmc_batvolt_chk</t>
         </is>
       </c>
       <c r="C71" s="43" t="inlineStr">
         <is>
-          <t>Verify the total number of detected NVM E drives matches the expected quantity.</t>
+          <t>Checks the RTC/CMOS battery voltage sensor reading against a configured lower bound.</t>
         </is>
       </c>
       <c r="D71" s="43" t="inlineStr">
         <is>
-          <t>Pass - return 0; Fail - return 1</t>
+          <t>PASS if ipmitool sdr elist | grep 'BAT' | awk '{print $9}' (as float) is &gt;= bmc_batvolt_lower_bound.</t>
         </is>
       </c>
       <c r="E71" s="43" t="inlineStr">
         <is>
-          <t>M1 : expected count is determined by E1S2 or E1S4.</t>
+          <t>FAILs explicitly if ipmitool can't detect the battery voltage sensor at all — distinguished from a low-but-present reading.</t>
         </is>
       </c>
       <c r="F71" s="43" t="n"/>
@@ -14708,26 +14489,30 @@
       <c r="J71" s="48" t="n"/>
       <c r="L71" s="31" t="n"/>
     </row>
-    <row r="72" ht="13.5" customHeight="1" s="80">
+    <row r="72" ht="27" customHeight="1" s="80">
       <c r="A72" s="76" t="n">
         <v>70</v>
       </c>
       <c r="B72" s="43" t="inlineStr">
         <is>
-          <t>storage_hdd_func_test</t>
+          <t>tpm_ver_chk</t>
         </is>
       </c>
       <c r="C72" s="43" t="inlineStr">
         <is>
-          <t>Perform random read/write test on all HDDs and NVMEs.</t>
+          <t>Checks the TPM's FIRMWARE_VERSION value against tpm_ver, upgrades and re-checks if mismatched and upgrade is allowed.</t>
         </is>
       </c>
       <c r="D72" s="43" t="inlineStr">
         <is>
-          <t>Pass - return 0; Fail - return 1</t>
-        </is>
-      </c>
-      <c r="E72" s="43" t="n"/>
+          <t>PASS if the parsed firmware version equals getConfigValue('tpm_ver').</t>
+        </is>
+      </c>
+      <c r="E72" s="43" t="inlineStr">
+        <is>
+          <t>On successful update, recursively re-check version.</t>
+        </is>
+      </c>
       <c r="F72" s="43" t="n"/>
       <c r="G72" s="47" t="b">
         <v>0</v>
@@ -14739,23 +14524,23 @@
       <c r="J72" s="48" t="n"/>
       <c r="L72" s="31" t="n"/>
     </row>
-    <row r="73" ht="40.5" customHeight="1" s="80">
+    <row r="73" ht="27" customHeight="1" s="80">
       <c r="A73" s="76" t="n">
         <v>71</v>
       </c>
       <c r="B73" s="43" t="inlineStr">
         <is>
-          <t>storage_nvme_smart_chk</t>
+          <t>tpm_qty_chk</t>
         </is>
       </c>
       <c r="C73" s="43" t="inlineStr">
         <is>
-          <t>Check NVMe SMART log parameters to ensure disk health is within acceptable thresholds.</t>
+          <t>Checks the number of detected TPM 2.0 devices against an internal expected count (self._tpm_num, a class attribute rather than an SF config value).</t>
         </is>
       </c>
       <c r="D73" s="43" t="inlineStr">
         <is>
-          <t>All NVMe devices must meet: critical_warning == 0 temperature &lt; 70°C percentage_used &lt; 3% available_spare &gt;= 99% media_errors == 0 warning_temperature_time == 0</t>
+          <t>PASS if ls /dev/tpm* | grep -v tpmrm | wc -l equals self._tpm_num.</t>
         </is>
       </c>
       <c r="E73" s="43" t="n"/>
@@ -14776,24 +14561,20 @@
       </c>
       <c r="B74" s="43" t="inlineStr">
         <is>
-          <t>bmc_batvolt_chk</t>
+          <t>tpm_func_test</t>
         </is>
       </c>
       <c r="C74" s="43" t="inlineStr">
         <is>
-          <t>Checks the RTC/CMOS battery voltage sensor reading against a configured lower bound.</t>
+          <t>Runs the TPM 2.0 full and not-full self-tests (eltt2 -t full / eltt2 -t not_full) and a "get value" sanity read (eltt2 -g).</t>
         </is>
       </c>
       <c r="D74" s="43" t="inlineStr">
         <is>
-          <t>PASS if ipmitool sdr elist | grep 'BAT' | awk '{print $9}' (as float) is &gt;= bmc_batvolt_lower_bound.</t>
-        </is>
-      </c>
-      <c r="E74" s="43" t="inlineStr">
-        <is>
-          <t>FAILs explicitly if ipmitool can't detect the battery voltage sensor at all — distinguished from a low-but-present reading.</t>
-        </is>
-      </c>
+          <t>PASS only if all three sub-commands (full selftest, not-full selftest, get-value) return exit code 0.</t>
+        </is>
+      </c>
+      <c r="E74" s="43" t="n"/>
       <c r="F74" s="43" t="n"/>
       <c r="G74" s="47" t="b">
         <v>0</v>
@@ -14805,28 +14586,28 @@
       <c r="J74" s="48" t="n"/>
       <c r="L74" s="31" t="n"/>
     </row>
-    <row r="75" ht="27" customHeight="1" s="80">
+    <row r="75" ht="13.5" customHeight="1" s="80">
       <c r="A75" s="76" t="n">
         <v>73</v>
       </c>
       <c r="B75" s="43" t="inlineStr">
         <is>
-          <t>tpm_ver_chk</t>
+          <t>uut_pic_test</t>
         </is>
       </c>
       <c r="C75" s="43" t="inlineStr">
         <is>
-          <t>Checks the TPM's FIRMWARE_VERSION value against tpm_ver, upgrades and re-checks if mismatched and upgrade is allowed.</t>
+          <t>Runs a PIC (Programmable Interrupt Controller) functional test command.</t>
         </is>
       </c>
       <c r="D75" s="43" t="inlineStr">
         <is>
-          <t>PASS if the parsed firmware version equals getConfigValue('tpm_ver').</t>
+          <t>PASS if self.cmd_lst['uut_test_pic'] returns exit code 0.</t>
         </is>
       </c>
       <c r="E75" s="43" t="inlineStr">
         <is>
-          <t>On successful update, recursively re-check version.</t>
+          <t>Minimal wrapper, no special edge cases.</t>
         </is>
       </c>
       <c r="F75" s="43" t="n"/>
@@ -14840,26 +14621,30 @@
       <c r="J75" s="48" t="n"/>
       <c r="L75" s="31" t="n"/>
     </row>
-    <row r="76" ht="27" customHeight="1" s="80">
+    <row r="76" ht="13.5" customHeight="1" s="80">
       <c r="A76" s="76" t="n">
         <v>74</v>
       </c>
       <c r="B76" s="43" t="inlineStr">
         <is>
-          <t>tpm_qty_chk</t>
+          <t>uut_hpet_test</t>
         </is>
       </c>
       <c r="C76" s="43" t="inlineStr">
         <is>
-          <t>Checks the number of detected TPM 2.0 devices against an internal expected count (self._tpm_num, a class attribute rather than an SF config value).</t>
+          <t>Runs an HPET (High Precision Event Timer) functional test command.</t>
         </is>
       </c>
       <c r="D76" s="43" t="inlineStr">
         <is>
-          <t>PASS if ls /dev/tpm* | grep -v tpmrm | wc -l equals self._tpm_num.</t>
-        </is>
-      </c>
-      <c r="E76" s="43" t="n"/>
+          <t>PASS if self.cmd_lst['uut_test_hpet'] returns exit code 0.</t>
+        </is>
+      </c>
+      <c r="E76" s="43" t="inlineStr">
+        <is>
+          <t>Minimal wrapper, structurally identical to uut_pic_test.</t>
+        </is>
+      </c>
       <c r="F76" s="43" t="n"/>
       <c r="G76" s="47" t="b">
         <v>0</v>
@@ -14871,169 +14656,68 @@
       <c r="J76" s="48" t="n"/>
       <c r="L76" s="31" t="n"/>
     </row>
-    <row r="77" ht="27" customHeight="1" s="80">
-      <c r="A77" s="76" t="n">
+    <row r="77" s="80">
+      <c r="A77" s="81" t="n">
         <v>75</v>
       </c>
-      <c r="B77" s="43" t="inlineStr">
-        <is>
-          <t>tpm_func_test</t>
-        </is>
-      </c>
-      <c r="C77" s="43" t="inlineStr">
-        <is>
-          <t>Runs the TPM 2.0 full and not-full self-tests (eltt2 -t full / eltt2 -t not_full) and a "get value" sanity read (eltt2 -g).</t>
-        </is>
-      </c>
-      <c r="D77" s="43" t="inlineStr">
-        <is>
-          <t>PASS only if all three sub-commands (full selftest, not-full selftest, get-value) return exit code 0.</t>
-        </is>
-      </c>
-      <c r="E77" s="43" t="n"/>
-      <c r="F77" s="43" t="n"/>
-      <c r="G77" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="H77" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="I77" s="48" t="n"/>
-      <c r="J77" s="48" t="n"/>
-      <c r="L77" s="31" t="n"/>
-    </row>
-    <row r="78" ht="13.5" customHeight="1" s="80">
-      <c r="A78" s="76" t="n">
-        <v>76</v>
-      </c>
-      <c r="B78" s="43" t="inlineStr">
-        <is>
-          <t>uut_pic_test</t>
-        </is>
-      </c>
-      <c r="C78" s="43" t="inlineStr">
-        <is>
-          <t>Runs a PIC (Programmable Interrupt Controller) functional test command.</t>
-        </is>
-      </c>
-      <c r="D78" s="43" t="inlineStr">
-        <is>
-          <t>PASS if self.cmd_lst['uut_test_pic'] returns exit code 0.</t>
-        </is>
-      </c>
-      <c r="E78" s="43" t="inlineStr">
-        <is>
-          <t>Minimal wrapper, no special edge cases.</t>
-        </is>
-      </c>
-      <c r="F78" s="43" t="n"/>
-      <c r="G78" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="H78" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="I78" s="48" t="n"/>
-      <c r="J78" s="48" t="n"/>
-      <c r="L78" s="31" t="n"/>
-    </row>
-    <row r="79" ht="13.5" customHeight="1" s="80">
-      <c r="A79" s="76" t="n">
-        <v>77</v>
-      </c>
-      <c r="B79" s="43" t="inlineStr">
-        <is>
-          <t>uut_hpet_test</t>
-        </is>
-      </c>
-      <c r="C79" s="43" t="inlineStr">
-        <is>
-          <t>Runs an HPET (High Precision Event Timer) functional test command.</t>
-        </is>
-      </c>
-      <c r="D79" s="43" t="inlineStr">
-        <is>
-          <t>PASS if self.cmd_lst['uut_test_hpet'] returns exit code 0.</t>
-        </is>
-      </c>
-      <c r="E79" s="43" t="inlineStr">
-        <is>
-          <t>Minimal wrapper, structurally identical to uut_pic_test.</t>
-        </is>
-      </c>
-      <c r="F79" s="43" t="n"/>
-      <c r="G79" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="H79" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="I79" s="48" t="n"/>
-      <c r="J79" s="48" t="n"/>
-      <c r="L79" s="31" t="n"/>
-    </row>
-    <row r="80" s="80">
-      <c r="A80" s="81" t="n">
-        <v>78</v>
-      </c>
-      <c r="B80" s="82" t="inlineStr">
+      <c r="B77" s="82" t="inlineStr">
         <is>
           <t>bios_cmos_test</t>
         </is>
       </c>
-      <c r="C80" s="82" t="inlineStr">
+      <c r="C77" s="82" t="inlineStr">
         <is>
           <t>Test the BIOS CMOS functionality by verifying the read/write capability of CMOS registers and checking battery and CMOS operation status.</t>
         </is>
       </c>
-      <c r="D80" s="82" t="inlineStr">
+      <c r="D77" s="82" t="inlineStr">
         <is>
           <t>Pass - return 0; Fail - return 1</t>
         </is>
       </c>
-      <c r="E80" s="82" t="inlineStr">
+      <c r="E77" s="82" t="inlineStr">
         <is>
           <t>&gt;&gt;&gt;MTE agreed to waive in EVT. ADO#2909063</t>
         </is>
       </c>
-      <c r="F80" s="82" t="inlineStr">
+      <c r="F77" s="82" t="inlineStr">
         <is>
           <t>[Execute CMOS test]
 CMOStest -d</t>
         </is>
       </c>
-      <c r="G80" s="88" t="b">
-        <v>0</v>
-      </c>
-      <c r="H80" s="88" t="b">
-        <v>0</v>
-      </c>
-      <c r="I80" s="89" t="n"/>
-      <c r="J80" s="89" t="n"/>
-      <c r="K80" s="87" t="n"/>
-      <c r="L80" s="90" t="n"/>
-    </row>
-    <row r="81" s="80">
-      <c r="A81" s="81" t="n">
-        <v>79</v>
-      </c>
-      <c r="B81" s="82" t="inlineStr">
+      <c r="G77" s="87" t="b">
+        <v>0</v>
+      </c>
+      <c r="H77" s="87" t="b">
+        <v>0</v>
+      </c>
+      <c r="I77" s="88" t="n"/>
+      <c r="J77" s="88" t="n"/>
+      <c r="K77" s="89" t="n"/>
+      <c r="L77" s="90" t="n"/>
+    </row>
+    <row r="78" s="80">
+      <c r="A78" s="81" t="n">
+        <v>76</v>
+      </c>
+      <c r="B78" s="82" t="inlineStr">
         <is>
           <t>ccr_switch_chk</t>
         </is>
       </c>
-      <c r="C81" s="82" t="inlineStr">
+      <c r="C78" s="82" t="inlineStr">
         <is>
           <t>Check and show switch config</t>
         </is>
       </c>
-      <c r="D81" s="82" t="inlineStr">
+      <c r="D78" s="82" t="inlineStr">
         <is>
           <t>Pass - return 0; Fail - return 1</t>
         </is>
       </c>
-      <c r="E81" s="82" t="n"/>
-      <c r="F81" s="82" t="inlineStr">
+      <c r="E78" s="82" t="n"/>
+      <c r="F78" s="82" t="inlineStr">
         <is>
           <t>[Get Switch Information]
 version_info: show version
@@ -15042,16 +14726,121 @@
 cable_status: show muxcable status</t>
         </is>
       </c>
-      <c r="G81" s="88" t="b">
-        <v>0</v>
-      </c>
-      <c r="H81" s="88" t="b">
-        <v>0</v>
-      </c>
-      <c r="I81" s="89" t="n"/>
-      <c r="J81" s="89" t="n"/>
-      <c r="K81" s="87" t="n"/>
-      <c r="L81" s="90" t="n"/>
+      <c r="G78" s="87" t="b">
+        <v>0</v>
+      </c>
+      <c r="H78" s="87" t="b">
+        <v>0</v>
+      </c>
+      <c r="I78" s="88" t="n"/>
+      <c r="J78" s="88" t="n"/>
+      <c r="K78" s="89" t="n"/>
+      <c r="L78" s="90" t="n"/>
+    </row>
+    <row r="79" ht="27" customHeight="1" s="80">
+      <c r="A79" s="76" t="n">
+        <v>77</v>
+      </c>
+      <c r="B79" s="43" t="inlineStr">
+        <is>
+          <t>bmc_sel_chk</t>
+        </is>
+      </c>
+      <c r="C79" s="43" t="inlineStr">
+        <is>
+          <t>V erif y BMC SEL (System Event Log) events during testing to ensure no unexpected events have occurred.</t>
+        </is>
+      </c>
+      <c r="D79" s="43" t="inlineStr">
+        <is>
+          <t>SEL event counts should not exceed the defined thresholds based on testing duration.</t>
+        </is>
+      </c>
+      <c r="E79" s="43" t="inlineStr">
+        <is>
+          <t>Fail log will be saved in project folder if abnormal events are detected.</t>
+        </is>
+      </c>
+      <c r="F79" s="43" t="n"/>
+      <c r="G79" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="H79" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="I79" s="48" t="n"/>
+      <c r="J79" s="48" t="n"/>
+      <c r="L79" s="31" t="n"/>
+    </row>
+    <row r="80" ht="27" customHeight="1" s="80">
+      <c r="A80" s="76" t="n">
+        <v>78</v>
+      </c>
+      <c r="B80" s="43" t="inlineStr">
+        <is>
+          <t>bmc_sdr_chk</t>
+        </is>
+      </c>
+      <c r="C80" s="43" t="inlineStr">
+        <is>
+          <t>Verify BMC Sensor Data Records (SDR) by checking sensor list output and filtering unexpected entries.</t>
+        </is>
+      </c>
+      <c r="D80" s="43" t="inlineStr">
+        <is>
+          <t>No unexpected or unmasked SDR entries found in BMCSDR.log.</t>
+        </is>
+      </c>
+      <c r="E80" s="43" t="inlineStr">
+        <is>
+          <t>Test fails if filtered output is not empty.</t>
+        </is>
+      </c>
+      <c r="F80" s="43" t="n"/>
+      <c r="G80" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="H80" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="I80" s="48" t="n"/>
+      <c r="J80" s="48" t="n"/>
+      <c r="L80" s="31" t="n"/>
+    </row>
+    <row r="81" ht="27" customHeight="1" s="80">
+      <c r="A81" s="76" t="n">
+        <v>79</v>
+      </c>
+      <c r="B81" s="43" t="inlineStr">
+        <is>
+          <t>uut_dmesg_chk</t>
+        </is>
+      </c>
+      <c r="C81" s="43" t="inlineStr">
+        <is>
+          <t>Check UUT dmesg log for unexpected error messages and record PCI device status.</t>
+        </is>
+      </c>
+      <c r="D81" s="43" t="inlineStr">
+        <is>
+          <t>No unmasked error messages found in dmesg and all expected messages are properly filtered.</t>
+        </is>
+      </c>
+      <c r="E81" s="43" t="inlineStr">
+        <is>
+          <t>Filter list (filter_list.csv) and error map (err_map.ini) are required for filtering and mapping errors.</t>
+        </is>
+      </c>
+      <c r="F81" s="43" t="n"/>
+      <c r="G81" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="H81" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="I81" s="48" t="n"/>
+      <c r="J81" s="48" t="n"/>
+      <c r="L81" s="31" t="n"/>
     </row>
     <row r="82" ht="27" customHeight="1" s="80">
       <c r="A82" s="76" t="n">
@@ -15059,24 +14848,20 @@
       </c>
       <c r="B82" s="43" t="inlineStr">
         <is>
-          <t>bmc_sel_chk</t>
+          <t>uut_syslog_chk</t>
         </is>
       </c>
       <c r="C82" s="43" t="inlineStr">
         <is>
-          <t>V erif y BMC SEL (System Event Log) events during testing to ensure no unexpected events have occurred.</t>
+          <t>Check and record UUT system log (syslog/messages) to ensure no unexpected errors.</t>
         </is>
       </c>
       <c r="D82" s="43" t="inlineStr">
         <is>
-          <t>SEL event counts should not exceed the defined thresholds based on testing duration.</t>
-        </is>
-      </c>
-      <c r="E82" s="43" t="inlineStr">
-        <is>
-          <t>Fail log will be saved in project folder if abnormal events are detected.</t>
-        </is>
-      </c>
+          <t>UUT syslog must not contain unmasked error patterns, excluding skip patterns. Log file must exist and contain no unfiltered critical errors.</t>
+        </is>
+      </c>
+      <c r="E82" s="43" t="n"/>
       <c r="F82" s="43" t="n"/>
       <c r="G82" s="47" t="b">
         <v>0</v>
@@ -15094,22 +14879,22 @@
       </c>
       <c r="B83" s="43" t="inlineStr">
         <is>
-          <t>bmc_sdr_chk</t>
+          <t>bmc_sel_clear</t>
         </is>
       </c>
       <c r="C83" s="43" t="inlineStr">
         <is>
-          <t>Verify BMC Sensor Data Records (SDR) by checking sensor list output and filtering unexpected entries.</t>
+          <t>Clear BMC System Event Log (SEL) and verify it is cleared correctly.</t>
         </is>
       </c>
       <c r="D83" s="43" t="inlineStr">
         <is>
-          <t>No unexpected or unmasked SDR entries found in BMCSDR.log.</t>
+          <t>SEL clear command executes successfully and log ID changes after clear.</t>
         </is>
       </c>
       <c r="E83" s="43" t="inlineStr">
         <is>
-          <t>Test fails if filtered output is not empty.</t>
+          <t>Logs SEL before clearing for traceability; verifies clear status by comparing log ID.</t>
         </is>
       </c>
       <c r="F83" s="43" t="n"/>
@@ -15123,134 +14908,33 @@
       <c r="J83" s="48" t="n"/>
       <c r="L83" s="31" t="n"/>
     </row>
-    <row r="84" ht="27" customHeight="1" s="80">
-      <c r="A84" s="76" t="n">
+    <row r="84" s="80">
+      <c r="A84" s="81" t="n">
         <v>82</v>
       </c>
-      <c r="B84" s="43" t="inlineStr">
-        <is>
-          <t>uut_dmesg_chk</t>
-        </is>
-      </c>
-      <c r="C84" s="43" t="inlineStr">
-        <is>
-          <t>Check UUT dmesg log for unexpected error messages and record PCI device status.</t>
-        </is>
-      </c>
-      <c r="D84" s="43" t="inlineStr">
-        <is>
-          <t>No unmasked error messages found in dmesg and all expected messages are properly filtered.</t>
-        </is>
-      </c>
-      <c r="E84" s="43" t="inlineStr">
-        <is>
-          <t>Filter list (filter_list.csv) and error map (err_map.ini) are required for filtering and mapping errors.</t>
-        </is>
-      </c>
-      <c r="F84" s="43" t="n"/>
-      <c r="G84" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="H84" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="I84" s="48" t="n"/>
-      <c r="J84" s="48" t="n"/>
-      <c r="L84" s="31" t="n"/>
-    </row>
-    <row r="85" ht="27" customHeight="1" s="80">
-      <c r="A85" s="76" t="n">
-        <v>83</v>
-      </c>
-      <c r="B85" s="43" t="inlineStr">
-        <is>
-          <t>uut_syslog_chk</t>
-        </is>
-      </c>
-      <c r="C85" s="43" t="inlineStr">
-        <is>
-          <t>Check and record UUT system log (syslog/messages) to ensure no unexpected errors.</t>
-        </is>
-      </c>
-      <c r="D85" s="43" t="inlineStr">
-        <is>
-          <t>UUT syslog must not contain unmasked error patterns, excluding skip patterns. Log file must exist and contain no unfiltered critical errors.</t>
-        </is>
-      </c>
-      <c r="E85" s="43" t="n"/>
-      <c r="F85" s="43" t="n"/>
-      <c r="G85" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="H85" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="I85" s="48" t="n"/>
-      <c r="J85" s="48" t="n"/>
-      <c r="L85" s="31" t="n"/>
-    </row>
-    <row r="86" ht="27" customHeight="1" s="80">
-      <c r="A86" s="76" t="n">
-        <v>84</v>
-      </c>
-      <c r="B86" s="43" t="inlineStr">
-        <is>
-          <t>bmc_sel_clear</t>
-        </is>
-      </c>
-      <c r="C86" s="43" t="inlineStr">
-        <is>
-          <t>Clear BMC System Event Log (SEL) and verify it is cleared correctly.</t>
-        </is>
-      </c>
-      <c r="D86" s="43" t="inlineStr">
-        <is>
-          <t>SEL clear command executes successfully and log ID changes after clear.</t>
-        </is>
-      </c>
-      <c r="E86" s="43" t="inlineStr">
-        <is>
-          <t>Logs SEL before clearing for traceability; verifies clear status by comparing log ID.</t>
-        </is>
-      </c>
-      <c r="F86" s="43" t="n"/>
-      <c r="G86" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="H86" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="I86" s="48" t="n"/>
-      <c r="J86" s="48" t="n"/>
-      <c r="L86" s="31" t="n"/>
-    </row>
-    <row r="87" s="80">
-      <c r="A87" s="81" t="n">
-        <v>85</v>
-      </c>
-      <c r="B87" s="82" t="inlineStr">
+      <c r="B84" s="82" t="inlineStr">
         <is>
           <t>pcie_manticore_reset_lock</t>
         </is>
       </c>
-      <c r="C87" s="82" t="inlineStr">
+      <c r="C84" s="82" t="inlineStr">
         <is>
           <t>Reset intrusion count and lock a Manticore PCIe device using Cerberus utility.</t>
         </is>
       </c>
-      <c r="D87" s="82" t="inlineStr">
+      <c r="D84" s="82" t="inlineStr">
         <is>
           <t>- Intrusion count and state reset successfully (validated by expected outputs).
 - Device locked successfully. Return 0 on success, 1 on failure.</t>
         </is>
       </c>
-      <c r="E87" s="82" t="inlineStr">
+      <c r="E84" s="82" t="inlineStr">
         <is>
           <t>- If device is already locked, manual TE intervention is required.
 - Device lock requires AC power cycle to take effect.</t>
         </is>
       </c>
-      <c r="F87" s="82" t="inlineStr">
+      <c r="F84" s="82" t="inlineStr">
         <is>
           <t>{CERBERUS_UTILITY} -e 40 msft getlockstatus
 {CERBERUS_UTILITY} -e 0x40 msft intrusiondetection
@@ -15260,43 +14944,43 @@
 {CERBERUS_UTILITY} -e 40 msft lockdevice</t>
         </is>
       </c>
-      <c r="G87" s="88" t="b">
-        <v>0</v>
-      </c>
-      <c r="H87" s="88" t="b">
-        <v>0</v>
-      </c>
-      <c r="I87" s="89" t="n"/>
-      <c r="J87" s="89" t="n"/>
-      <c r="K87" s="87" t="n"/>
-      <c r="L87" s="90" t="n"/>
-    </row>
-    <row r="88" s="80">
-      <c r="A88" s="81" t="n">
-        <v>86</v>
-      </c>
-      <c r="B88" s="82" t="inlineStr">
+      <c r="G84" s="87" t="b">
+        <v>0</v>
+      </c>
+      <c r="H84" s="87" t="b">
+        <v>0</v>
+      </c>
+      <c r="I84" s="88" t="n"/>
+      <c r="J84" s="88" t="n"/>
+      <c r="K84" s="89" t="n"/>
+      <c r="L84" s="90" t="n"/>
+    </row>
+    <row r="85" s="80">
+      <c r="A85" s="81" t="n">
+        <v>83</v>
+      </c>
+      <c r="B85" s="82" t="inlineStr">
         <is>
           <t>uut_poweroff_wakeup</t>
         </is>
       </c>
-      <c r="C88" s="82" t="inlineStr">
+      <c r="C85" s="82" t="inlineStr">
         <is>
           <t>Check poweroff log file</t>
         </is>
       </c>
-      <c r="D88" s="82" t="inlineStr">
+      <c r="D85" s="82" t="inlineStr">
         <is>
           <t>Pass - return 0 ; Fail - return 1</t>
         </is>
       </c>
-      <c r="E88" s="82" t="inlineStr">
+      <c r="E85" s="82" t="inlineStr">
         <is>
           <t>None
 &gt;&gt;&gt; This is AC cycle for above intrusion lock and below compstate/attestation test, which included in pcie_tip_pcd_chk and pcie_tip_cfm_chk.  All of the above test items will be skipped after the AC cycle to save testing time.</t>
         </is>
       </c>
-      <c r="F88" s="82" t="inlineStr">
+      <c r="F85" s="82" t="inlineStr">
         <is>
           <t>--- Check log POWEROFF_WAKEUP ---
 - Not present → set to POWEROFF_1
@@ -15311,37 +14995,140 @@
 - Return 0 (proceed to next test item)</t>
         </is>
       </c>
-      <c r="G88" s="88" t="b">
-        <v>0</v>
-      </c>
-      <c r="H88" s="88" t="b">
-        <v>0</v>
-      </c>
-      <c r="I88" s="89" t="n"/>
-      <c r="J88" s="89" t="n"/>
-      <c r="K88" s="87" t="n"/>
-      <c r="L88" s="90" t="n"/>
-    </row>
-    <row r="89" ht="27" customHeight="1" s="80">
+      <c r="G85" s="87" t="b">
+        <v>0</v>
+      </c>
+      <c r="H85" s="87" t="b">
+        <v>0</v>
+      </c>
+      <c r="I85" s="88" t="n"/>
+      <c r="J85" s="88" t="n"/>
+      <c r="K85" s="89" t="n"/>
+      <c r="L85" s="90" t="n"/>
+    </row>
+    <row r="86" ht="27" customHeight="1" s="80">
+      <c r="A86" s="76" t="n">
+        <v>84</v>
+      </c>
+      <c r="B86" s="43" t="inlineStr">
+        <is>
+          <t>bmc_synctime_upload</t>
+        </is>
+      </c>
+      <c r="C86" s="43" t="inlineStr">
+        <is>
+          <t>Upload NTP time sync config file (mtadams-ntp.conf) to BMC system to configure time synchronization.</t>
+        </is>
+      </c>
+      <c r="D86" s="43" t="inlineStr">
+        <is>
+          <t>PASS if the file upload (gs_tool_upload) succeeds.</t>
+        </is>
+      </c>
+      <c r="E86" s="43" t="n"/>
+      <c r="F86" s="43" t="n"/>
+      <c r="G86" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="H86" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="I86" s="48" t="n"/>
+      <c r="J86" s="48" t="n"/>
+      <c r="L86" s="31" t="n"/>
+    </row>
+    <row r="87" ht="27" customHeight="1" s="80">
+      <c r="A87" s="76" t="n">
+        <v>85</v>
+      </c>
+      <c r="B87" s="43" t="inlineStr">
+        <is>
+          <t>bios_load_default</t>
+        </is>
+      </c>
+      <c r="C87" s="43" t="inlineStr">
+        <is>
+          <t>The final item in the FFT flow — resets BIOS/CMOS settings to factory default via an IPMI OEM raw command to ensure a clean BIOS configuration.</t>
+        </is>
+      </c>
+      <c r="D87" s="43" t="inlineStr">
+        <is>
+          <t>PASS if ipmitool raw 0x00 0x08 0x05 0xa0 0x80 0x00 0x00 0x00 succeeds.</t>
+        </is>
+      </c>
+      <c r="E87" s="43" t="n"/>
+      <c r="F87" s="43" t="n"/>
+      <c r="G87" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="H87" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="I87" s="48" t="n"/>
+      <c r="J87" s="48" t="n"/>
+      <c r="L87" s="31" t="n"/>
+    </row>
+    <row r="88" ht="40.5" customHeight="1" s="80">
+      <c r="A88" s="76" t="n">
+        <v>86</v>
+      </c>
+      <c r="B88" s="64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pcie_tip_pcd_chk
+&gt;&gt;&gt;Has not been defined in CRD and disabled in DVT. </t>
+        </is>
+      </c>
+      <c r="C88" s="61" t="inlineStr">
+        <is>
+          <t>BMC TIP - PCD ID and platform check</t>
+        </is>
+      </c>
+      <c r="D88" s="61" t="inlineStr">
+        <is>
+          <t>Pass - return 0; Fail - return 1</t>
+        </is>
+      </c>
+      <c r="E88" s="61" t="inlineStr">
+        <is>
+          <t>- Only in FFT or FST stations will automatic TIP PCD update be triggered upon invalid PCD detection - After firmware update, the script will reset the BMC and retry fetching the PCD information</t>
+        </is>
+      </c>
+      <c r="F88" s="43" t="n"/>
+      <c r="G88" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="H88" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="I88" s="48" t="n"/>
+      <c r="J88" s="48" t="n"/>
+      <c r="L88" s="31" t="n"/>
+    </row>
+    <row r="89" ht="81" customHeight="1" s="80">
       <c r="A89" s="76" t="n">
         <v>87</v>
       </c>
-      <c r="B89" s="43" t="inlineStr">
-        <is>
-          <t>bmc_synctime_upload</t>
-        </is>
-      </c>
-      <c r="C89" s="43" t="inlineStr">
-        <is>
-          <t>Upload NTP time sync config file (mtadams-ntp.conf) to BMC system to configure time synchronization.</t>
-        </is>
-      </c>
-      <c r="D89" s="43" t="inlineStr">
-        <is>
-          <t>PASS if the file upload (gs_tool_upload) succeeds.</t>
-        </is>
-      </c>
-      <c r="E89" s="43" t="n"/>
+      <c r="B89" s="64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pcie_tip_cfm_chk
+&gt;&gt;&gt;Has not been defined in CRD and disabled in DVT. </t>
+        </is>
+      </c>
+      <c r="C89" s="61" t="inlineStr">
+        <is>
+          <t>Get DC-SCM TIP Version ID and Platform ID</t>
+        </is>
+      </c>
+      <c r="D89" s="61" t="inlineStr">
+        <is>
+          <t>Pass - return 0; Fail - return 1</t>
+        </is>
+      </c>
+      <c r="E89" s="61" t="inlineStr">
+        <is>
+          <t>- PCD/CFM can only be updated when "No valid found". If DS-SCM is already active, need to clear PCD/CFM via HKMS first - CFM auto-update only triggers under FFT or FST station and when CFM is invalid - After firmware update, system will cold-reset BMC, wait for recovery, and do AC cycle to take effect - tip_cfm_components_chk(): If component attestation fails, will dump Cerberus debug log automatically</t>
+        </is>
+      </c>
       <c r="F89" s="43" t="n"/>
       <c r="G89" s="47" t="b">
         <v>0</v>
@@ -15353,115 +15140,12 @@
       <c r="J89" s="48" t="n"/>
       <c r="L89" s="31" t="n"/>
     </row>
-    <row r="90" ht="27" customHeight="1" s="80">
-      <c r="A90" s="76" t="n">
-        <v>88</v>
-      </c>
-      <c r="B90" s="43" t="inlineStr">
-        <is>
-          <t>bios_load_default</t>
-        </is>
-      </c>
-      <c r="C90" s="43" t="inlineStr">
-        <is>
-          <t>The final item in the FFT flow — resets BIOS/CMOS settings to factory default via an IPMI OEM raw command to ensure a clean BIOS configuration.</t>
-        </is>
-      </c>
-      <c r="D90" s="43" t="inlineStr">
-        <is>
-          <t>PASS if ipmitool raw 0x00 0x08 0x05 0xa0 0x80 0x00 0x00 0x00 succeeds.</t>
-        </is>
-      </c>
-      <c r="E90" s="43" t="n"/>
-      <c r="F90" s="43" t="n"/>
-      <c r="G90" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="H90" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="I90" s="48" t="n"/>
-      <c r="J90" s="48" t="n"/>
-      <c r="L90" s="31" t="n"/>
-    </row>
-    <row r="91" ht="40.5" customHeight="1" s="80">
-      <c r="A91" s="76" t="n">
-        <v>89</v>
-      </c>
-      <c r="B91" s="64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pcie_tip_pcd_chk
-&gt;&gt;&gt;Has not been defined in CRD and disabled in DVT. </t>
-        </is>
-      </c>
-      <c r="C91" s="61" t="inlineStr">
-        <is>
-          <t>BMC TIP - PCD ID and platform check</t>
-        </is>
-      </c>
-      <c r="D91" s="61" t="inlineStr">
-        <is>
-          <t>Pass - return 0; Fail - return 1</t>
-        </is>
-      </c>
-      <c r="E91" s="61" t="inlineStr">
-        <is>
-          <t>- Only in FFT or FST stations will automatic TIP PCD update be triggered upon invalid PCD detection - After firmware update, the script will reset the BMC and retry fetching the PCD information</t>
-        </is>
-      </c>
-      <c r="F91" s="43" t="n"/>
-      <c r="G91" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="H91" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="I91" s="48" t="n"/>
-      <c r="J91" s="48" t="n"/>
-      <c r="L91" s="31" t="n"/>
-    </row>
-    <row r="92" ht="81" customHeight="1" s="80">
-      <c r="A92" s="76" t="n">
-        <v>90</v>
-      </c>
-      <c r="B92" s="64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pcie_tip_cfm_chk
-&gt;&gt;&gt;Has not been defined in CRD and disabled in DVT. </t>
-        </is>
-      </c>
-      <c r="C92" s="61" t="inlineStr">
-        <is>
-          <t>Get DC-SCM TIP Version ID and Platform ID</t>
-        </is>
-      </c>
-      <c r="D92" s="61" t="inlineStr">
-        <is>
-          <t>Pass - return 0; Fail - return 1</t>
-        </is>
-      </c>
-      <c r="E92" s="61" t="inlineStr">
-        <is>
-          <t>- PCD/CFM can only be updated when "No valid found". If DS-SCM is already active, need to clear PCD/CFM via HKMS first - CFM auto-update only triggers under FFT or FST station and when CFM is invalid - After firmware update, system will cold-reset BMC, wait for recovery, and do AC cycle to take effect - tip_cfm_components_chk(): If component attestation fails, will dump Cerberus debug log automatically</t>
-        </is>
-      </c>
-      <c r="F92" s="43" t="n"/>
-      <c r="G92" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="H92" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="I92" s="48" t="n"/>
-      <c r="J92" s="48" t="n"/>
-      <c r="L92" s="31" t="n"/>
-    </row>
-    <row r="93" ht="14.25" customHeight="1" s="80">
-      <c r="G93" s="30" t="n">
+    <row r="90" ht="14.25" customHeight="1" s="80">
+      <c r="G90" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="H93" s="30" t="n"/>
-      <c r="I93" s="30" t="inlineStr">
+      <c r="H90" s="30" t="n"/>
+      <c r="I90" s="30" t="inlineStr">
         <is>
           <t>Hour1</t>
         </is>

--- a/C219B_L10_L11_TestPlan_PV_1A00_added.xlsx
+++ b/C219B_L10_L11_TestPlan_PV_1A00_added.xlsx
@@ -1883,6 +1883,7 @@
         </is>
       </c>
     </row>
+    <row r="5"/>
     <row r="6">
       <c r="A6" s="29" t="n"/>
       <c r="B6" s="28" t="n"/>
@@ -1992,7 +1993,7 @@
       </c>
       <c r="C2" s="11" t="inlineStr">
         <is>
-          <t>Update BIOS/BMC FW files by RSCM</t>
+          <t>Update BIOS/BMC FW files by RM</t>
         </is>
       </c>
       <c r="D2" s="11" t="inlineStr">
@@ -2160,7 +2161,7 @@
       </c>
       <c r="E5" s="11" t="inlineStr">
         <is>
-          <t>Multi-stage, stateful check keyed on the presence of /vol/data/persistent/tests/golden_status.txt on the BMC. If the log doesn't exist yet, the function uploads SoCFPGAGoldenTestSvc.service and fpga_golden_check.py to the BMC, switches GP into golden boot mode (cerberus_utility fpgasetbootmode 0), forces an AC cycle (RSCM rscm_system_ac on M5, gs_pdb_ac_cycle otherwise) to make the mode take effect, and then returns 1 — meaning the first pass of this item after an image/config change always intentionally fails and needs a subsequent PRETEST re-run to actually validate the version. On version mismatch with fpga_gp_fw_upgrade TRUE, it calls _gp_fpga_softnic_upgrade() and then re-generates the golden log (also returning 1) rather than re-checking in the same pass.</t>
+          <t>Multi-stage, stateful check keyed on the presence of /vol/data/persistent/tests/golden_status.txt on the BMC. If the log doesn't exist yet, the function uploads SoCFPGAGoldenTestSvc.service and fpga_golden_check.py to the BMC, switches GP into golden boot mode (cerberus_utility fpgasetbootmode 0), forces an AC cycle (RM rm_system_ac on M5, gs_pdb_ac_cycle otherwise) to make the mode take effect, and then returns 1 — meaning the first pass of this item after an image/config change always intentionally fails and needs a subsequent PRETEST re-run to actually validate the version. On version mismatch with fpga_gp_fw_upgrade TRUE, it calls _gp_fpga_softnic_upgrade() and then re-generates the golden log (also returning 1) rather than re-checking in the same pass.</t>
         </is>
       </c>
     </row>
@@ -2678,7 +2679,7 @@
       <c r="E26" s="74" t="inlineStr">
         <is>
           <t>Two very different code paths: 
-- for prj_stage == "M5" it SFTP-uploads the three HWKEY .bin files to the BMC, then uses a shell command list over usb0 (10.235.100.0/31 point-to-point link) with scp -P 2200 to pull each key onto the GlacierPeak SoC and run cerberus_utility importsignedcert locally there — all three fuse commands (root CA idx 1, intermediate idx 2, device ID idx 0) run under a single rscm_lock.
+- for prj_stage == "M5" it SFTP-uploads the three HWKEY .bin files to the BMC, then uses a shell command list over usb0 (10.235.100.0/31 point-to-point link) with scp -P 2200 to pull each key onto the GlacierPeak SoC and run cerberus_utility importsignedcert locally there — all three fuse commands (root CA idx 1, intermediate idx 2, device ID idx 0) run under a single rm_lock.
 - For other stages it uses a raw pxssh session direct to the GlacierPeak SoC on port 8295 (user admin/admin), with up to 2 retries and a 90s backoff between attempts if the SoC is "busy". HWKey files are deleted from the BMC after fusing in both paths.</t>
         </is>
       </c>
@@ -2708,7 +2709,7 @@
           <t>- Security/identity-relevant, one-time step, M3-only. 
 - Unlike the Manticore/TIP flow this checks each slot independently — a partially-provisioned board (e.g. slot0 done, slot1 not) only provisions the missing slot. 
 - No verification of the -setCertificate output content is performed. 
-- Uses self.rscm_lock("RSCM", ...) around the actual burn to avoid concurrent RSCM access from other test threads.
+- Uses self.rm_lock("RM", ...) around the actual burn to avoid concurrent RM access from other test threads.
 - After both slots are set, it resets the FPGA and sleeps 300s before the final confirmation check.</t>
         </is>
       </c>
@@ -3125,13 +3126,13 @@
       </c>
       <c r="D45" s="11" t="inlineStr">
         <is>
-          <t>PASS if 5/5 pings succeed (or the RSCM-routed SSH connect succeeds).</t>
+          <t>PASS if 5/5 pings succeed (or the RM-routed SSH connect succeeds).</t>
         </is>
       </c>
       <c r="E45" s="11" t="inlineStr">
         <is>
           <t>M1/M3: via a direct ICMP ping
-M5: ping via an SSH-through-RSCM reachability check</t>
+M5: ping via an SSH-through-RM reachability check</t>
         </is>
       </c>
     </row>
@@ -3369,7 +3370,7 @@
       </c>
       <c r="C55" s="13" t="inlineStr">
         <is>
-          <t>Runs fpgadiagnostics -dumpHealth (via a stage-appropriate SSH route: direct M3, RSCM-jumper M3, or RSCM-serial-proxy M5) and parses per-subsystem [FPGA-XXX] health lines, with specific waivers for known FPGA-NETWORK and FPGA-CONFIG warnings, and a one-time auto-reboot self-heal if the PCIe link status reads "WARNING" while in App mode.</t>
+          <t>Runs fpgadiagnostics -dumpHealth (via a stage-appropriate SSH route: direct M3, RM-jumper M3, or RM-serial-proxy M5) and parses per-subsystem [FPGA-XXX] health lines, with specific waivers for known FPGA-NETWORK and FPGA-CONFIG warnings, and a one-time auto-reboot self-heal if the PCIe link status reads "WARNING" while in App mode.</t>
         </is>
       </c>
       <c r="D55" s="13" t="inlineStr">
@@ -4172,7 +4173,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Security/identity-relevant, one-time step, M3-only. Unlike the Manticore/TIP flow this checks each slot independently — a partially-provisioned board (e.g. slot0 done, slot1 not) only provisions the missing slot. No verification of the -setCertificate output content is performed ("Aligned with T6F, based on MTE/Casper approval, no check is required in set Cert" — the old response-code check is commented out). Uses self.rscm_lock("RSCM", ...) around the actual burn to avoid concurrent RSCM access from other test threads. After both slots are set, it resets the FPGA (gp_fpga_reset via cerberus_utility) and sleeps 300s before the final confirmation check.</t>
+          <t>Security/identity-relevant, one-time step, M3-only. Unlike the Manticore/TIP flow this checks each slot independently — a partially-provisioned board (e.g. slot0 done, slot1 not) only provisions the missing slot. No verification of the -setCertificate output content is performed ("Aligned with T6F, based on MTE/Casper approval, no check is required in set Cert" — the old response-code check is commented out). Uses self.rm_lock("RM", ...) around the actual burn to avoid concurrent RM access from other test threads. After both slots are set, it resets the FPGA (gp_fpga_reset via cerberus_utility) and sleeps 300s before the final confirmation check.</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -4203,7 +4204,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Security/identity-relevant, one-time step. Migrated/renamed from pcie.py (per docstring, 20260422). Docstring explicitly calls out a fix for error 0x2904: "modified the provisioning order to ensure the root CA is written before the Device ID". Two very different code paths: for prj_stage == "M5" it SFTP-uploads the three HWKEY .bin files to the BMC, then uses a shell command list over usb0 (10.235.100.0/31 point-to-point link) with scp -P 2200 to pull each key onto the GlacierPeak SoC and run cerberus_utility importsignedcert locally there — all three fuse commands (root CA idx 1, intermediate idx 2, device ID idx 0) run under a single rscm_lock. For other stages it uses a raw pxssh session direct to the GlacierPeak SoC on port 8295 (user admin/admin), with up to 2 retries and a 90s backoff between attempts if the SoC is "busy". HWKey files are deleted from the BMC after fusing in both paths.</t>
+          <t>Security/identity-relevant, one-time step. Migrated/renamed from pcie.py (per docstring, 20260422). Docstring explicitly calls out a fix for error 0x2904: "modified the provisioning order to ensure the root CA is written before the Device ID". Two very different code paths: for prj_stage == "M5" it SFTP-uploads the three HWKEY .bin files to the BMC, then uses a shell command list over usb0 (10.235.100.0/31 point-to-point link) with scp -P 2200 to pull each key onto the GlacierPeak SoC and run cerberus_utility importsignedcert locally there — all three fuse commands (root CA idx 1, intermediate idx 2, device ID idx 0) run under a single rm_lock. For other stages it uses a raw pxssh session direct to the GlacierPeak SoC on port 8295 (user admin/admin), with up to 2 retries and a 90s backoff between attempts if the SoC is "busy". HWKey files are deleted from the BMC after fusing in both paths.</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -4540,7 +4541,7 @@
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>"For SKU1 and L11 only" per docstring. SN-format heuristic: a 13-character alphanumeric string is treated as already-correct; anything else is assumed hex-encoded and is bytes.fromhex().decode('ascii')-converted. If conversion fails or the format is still wrong, it uploads rtx-pro-6000-fru-repair_v4.sh and rtx-pro-6000-fru-write_v1.sh to the BMC and runs a repair pipeline (read raw FRU → hexdump → repair script → write script) under an rscm_lock, for cassette 8 (102) and cassette 10 (106) targets.</t>
+          <t>"For SKU1 and L11 only" per docstring. SN-format heuristic: a 13-character alphanumeric string is treated as already-correct; anything else is assumed hex-encoded and is bytes.fromhex().decode('ascii')-converted. If conversion fails or the format is still wrong, it uploads rtx-pro-6000-fru-repair_v4.sh and rtx-pro-6000-fru-write_v1.sh to the BMC and runs a repair pipeline (read raw FRU → hexdump → repair script → write script) under an rm_lock, for cassette 8 (102) and cassette 10 (106) targets.</t>
         </is>
       </c>
       <c r="F22" s="6" t="inlineStr">
@@ -5062,13 +5063,13 @@
       </c>
       <c r="D40" s="7" t="inlineStr">
         <is>
-          <t>PASS if 5/5 pings succeed (or the RSCM-routed SSH connect succeeds).</t>
+          <t>PASS if 5/5 pings succeed (or the RM-routed SSH connect succeeds).</t>
         </is>
       </c>
       <c r="E40" s="7" t="inlineStr">
         <is>
           <t>M1/M3: via a direct ICMP ping
-M5: ping via an SSH-through-RSCM reachability check</t>
+M5: ping via an SSH-through-RM reachability check</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
@@ -5612,7 +5613,7 @@
       </c>
       <c r="C59" s="7" t="inlineStr">
         <is>
-          <t>Runs fpgadiagnostics -dumpHealth (via a stage-appropriate SSH route: direct M3, RSCM-jumper M3, or RSCM-serial-proxy M5) and parses per-subsystem [FPGA-XXX] health lines, with specific waivers for known FPGA-NETWORK and FPGA-CONFIG warnings, and a one-time auto-reboot self-heal if the PCIe link status reads "WARNING" while in App mode.</t>
+          <t>Runs fpgadiagnostics -dumpHealth (via a stage-appropriate SSH route: direct M3, RM-jumper M3, or RM-serial-proxy M5) and parses per-subsystem [FPGA-XXX] health lines, with specific waivers for known FPGA-NETWORK and FPGA-CONFIG warnings, and a one-time auto-reboot self-heal if the PCIe link status reads "WARNING" while in App mode.</t>
         </is>
       </c>
       <c r="D59" s="7" t="inlineStr">
@@ -6327,7 +6328,7 @@
     <col width="9.140625" customWidth="1" style="21" min="14" max="14"/>
     <col width="9.140625" customWidth="1" style="21" min="15" max="15"/>
     <col width="9.140625" customWidth="1" style="22" min="16" max="16"/>
-    <col hidden="1" style="80" min="17" max="25"/>
+    <col hidden="1" width="13" customWidth="1" style="80" min="17" max="25"/>
   </cols>
   <sheetData>
     <row r="1" ht="15" customFormat="1" customHeight="1" s="1">
@@ -6577,7 +6578,7 @@
       </c>
       <c r="C7" s="43" t="inlineStr">
         <is>
-          <t>Check RSCM firmware and configuration versions (Cerberus, PCD ID, PFM ID, AM64 stack, CPLD). Auto-update if mismatch and upgrade is allowed.</t>
+          <t>Check RM firmware and configuration versions (Cerberus, PCD ID, PFM ID, AM64 stack, CPLD). Auto-update if mismatch and upgrade is allowed.</t>
         </is>
       </c>
       <c r="D7" s="40" t="inlineStr">
@@ -6613,7 +6614,7 @@
       </c>
       <c r="C8" s="82" t="inlineStr">
         <is>
-          <t>Check RSCM Health Status</t>
+          <t>Check RM Health Status</t>
         </is>
       </c>
       <c r="D8" s="83" t="inlineStr">
@@ -6652,7 +6653,7 @@
       <c r="C9" s="82" t="inlineStr">
         <is>
           <t>Check POWERSHELF Product Name
-Check RSCM Manager Type</t>
+Check RM Manager Type</t>
         </is>
       </c>
       <c r="D9" s="83" t="n"/>
@@ -6684,12 +6685,12 @@
       </c>
       <c r="C10" s="43" t="inlineStr">
         <is>
-          <t>Checks UUT system information via the R-SCM interface and compares it with the expected configuration values .</t>
+          <t>Checks UUT system information via the RM interface and compares it with the expected configuration values .</t>
         </is>
       </c>
       <c r="D10" s="40" t="inlineStr">
         <is>
-          <t>Pass All fields (MAC, SN, BIOS version, BMC version, CPLD versions, CPU count, and memory size) match expected values. Or mismatched fields are successfully auto-updated (if allowed). Fail Unable to retrieve system info from R-SCM. Mismatched field(s) and auto-upgrade is either disabled or unsuccessful.</t>
+          <t>Pass All fields (MAC, SN, BIOS version, BMC version, CPLD versions, CPU count, and memory size) match expected values. Or mismatched fields are successfully auto-updated (if allowed). Fail Unable to retrieve system info from RM. Mismatched field(s) and auto-upgrade is either disabled or unsuccessful.</t>
         </is>
       </c>
       <c r="E10" s="40" t="n"/>
@@ -6762,7 +6763,7 @@
       </c>
       <c r="E12" s="40" t="inlineStr">
         <is>
-          <t>Multi-stage, stateful check keyed on the presence of /vol/data/persistent/tests/golden_status.txt on the BMC. If the log doesn't exist yet, the function uploads SoCFPGAGoldenTestSvc.service and fpga_golden_check.py to the BMC, switches GP into golden boot mode (cerberus_utility fpgasetbootmode 0), forces an AC cycle (RSCM rscm_system_ac on M5, gs_pdb_ac_cycle otherwise) to make the mode take effect, and then returns 1 — meaning the first pass of this item after an image/config change always intentionally fails and needs a subsequent PRETEST re-run to actually validate the version. On version mismatch with fpga_gp_fw_upgrade TRUE, it calls _gp_fpga_softnic_upgrade() and then re-generates the golden log (also returning 1) rather than re-checking in the same pass.</t>
+          <t>Multi-stage, stateful check keyed on the presence of /vol/data/persistent/tests/golden_status.txt on the BMC. If the log doesn't exist yet, the function uploads SoCFPGAGoldenTestSvc.service and fpga_golden_check.py to the BMC, switches GP into golden boot mode (cerberus_utility fpgasetbootmode 0), forces an AC cycle (RM rm_system_ac on M5, gs_pdb_ac_cycle otherwise) to make the mode take effect, and then returns 1 — meaning the first pass of this item after an image/config change always intentionally fails and needs a subsequent PRETEST re-run to actually validate the version. On version mismatch with fpga_gp_fw_upgrade TRUE, it calls _gp_fpga_softnic_upgrade() and then re-generates the golden log (also returning 1) rather than re-checking in the same pass.</t>
         </is>
       </c>
       <c r="F12" s="75" t="n"/>
@@ -7244,7 +7245,7 @@
       </c>
       <c r="C26" s="82" t="inlineStr">
         <is>
-          <t>Check the PSU firmware version on the power shelf via R-SCM for the current UUT. This function only performs the check on master nodes.</t>
+          <t>Check the PSU firmware version on the power shelf via RM for the current UUT. This function only performs the check on master nodes.</t>
         </is>
       </c>
       <c r="D26" s="83" t="inlineStr">
@@ -7253,7 +7254,7 @@
 - UUT is a master node.
 - All PSU serial numbers, manufacturers, and firmware versions match expected values.
 - Fail
-- Unable to get R-SCM IP.
+- Unable to get RM IP.
 - PSU information cannot be retrieved or parsed.
 - PSU not found in the expected list.
 - Firmware version mismatch and auto-upgrade fails.</t>
@@ -7280,12 +7281,12 @@
 -        Completion Code
 - - - - -  If mismatch - - - - -
 [Upgrade PSU firmware version]
-Check fw package exists in RSCM:
+Check fw package exists in RM:
 -        show manager tftp list
 Upload fw to Rack-SCM
 -        set manager tftp get -s {IP} -f {FILE}
 Fw Upgrade
--       rscm_psu_upgrade = set powershelf psu update -s {INDEX} -f {FILE}</t>
+-       rm_psu_upgrade = set powershelf psu update -s {INDEX} -f {FILE}</t>
         </is>
       </c>
       <c r="G26" s="84" t="b">
@@ -7499,7 +7500,7 @@
       <c r="E31" s="40" t="inlineStr">
         <is>
           <t>Two very different code paths: 
-- for prj_stage == "M5" it SFTP-uploads the three HWKEY .bin files to the BMC, then uses a shell command list over usb0 (10.235.100.0/31 point-to-point link) with scp -P 2200 to pull each key onto the GlacierPeak SoC and run cerberus_utility importsignedcert locally there — all three fuse commands (root CA idx 1, intermediate idx 2, device ID idx 0) run under a single rscm_lock.
+- for prj_stage == "M5" it SFTP-uploads the three HWKEY .bin files to the BMC, then uses a shell command list over usb0 (10.235.100.0/31 point-to-point link) with scp -P 2200 to pull each key onto the GlacierPeak SoC and run cerberus_utility importsignedcert locally there — all three fuse commands (root CA idx 1, intermediate idx 2, device ID idx 0) run under a single rm_lock.
 - For other stages it uses a raw pxssh session direct to the GlacierPeak SoC on port 8295 (user admin/admin), with up to 2 retries and a 90s backoff between attempts if the SoC is "busy". HWKey files are deleted from the BMC after fusing in both paths.</t>
         </is>
       </c>
@@ -7539,7 +7540,7 @@
           <t>- Security/identity-relevant, one-time step, M3-only. 
 - Unlike the Manticore/TIP flow this checks each slot independently — a partially-provisioned board (e.g. slot0 done, slot1 not) only provisions the missing slot. 
 - No verification of the -setCertificate output content is performed. 
-- Uses self.rscm_lock("RSCM", ...) around the actual burn to avoid concurrent RSCM access from other test threads.
+- Uses self.rm_lock("RM", ...) around the actual burn to avoid concurrent RM access from other test threads.
 - After both slots are set, it resets the FPGA and sleeps 300s before the final confirmation check.</t>
         </is>
       </c>
@@ -7844,7 +7845,7 @@
       </c>
       <c r="C41" s="43" t="inlineStr">
         <is>
-          <t>Check R-SCM FRU information</t>
+          <t>Check RM FRU information</t>
         </is>
       </c>
       <c r="D41" s="40" t="inlineStr">
@@ -7936,7 +7937,7 @@
       </c>
       <c r="C44" s="43" t="inlineStr">
         <is>
-          <t>Check System FRU via RSCM</t>
+          <t>Check System FRU via RM</t>
         </is>
       </c>
       <c r="D44" s="40" t="inlineStr">
@@ -7968,7 +7969,7 @@
       </c>
       <c r="C45" s="43" t="inlineStr">
         <is>
-          <t>Check DC-SCM(M1120) FRU via R-SCM</t>
+          <t>Check DC-SCM(M1120) FRU via RM</t>
         </is>
       </c>
       <c r="D45" s="40" t="inlineStr">
@@ -8004,7 +8005,7 @@
       </c>
       <c r="C46" s="43" t="inlineStr">
         <is>
-          <t>Check GlacierPeak FRU via R-SCM</t>
+          <t>Check GlacierPeak FRU via RM</t>
         </is>
       </c>
       <c r="D46" s="40" t="inlineStr">
@@ -8103,7 +8104,7 @@
       </c>
       <c r="C49" s="43" t="inlineStr">
         <is>
-          <t>Validates RSCM rack-level power capping behavior, including: - DCMI-based static power limit control - PSU alert-triggered throttling (SM_ALERT)</t>
+          <t>Validates RM rack-level power capping behavior, including: - DCMI-based static power limit control - PSU alert-triggered throttling (SM_ALERT)</t>
         </is>
       </c>
       <c r="D49" s="40" t="inlineStr">
@@ -8768,13 +8769,13 @@
       </c>
       <c r="D64" s="40" t="inlineStr">
         <is>
-          <t>PASS if 5/5 pings succeed (or the RSCM-routed SSH connect succeeds).</t>
+          <t>PASS if 5/5 pings succeed (or the RM-routed SSH connect succeeds).</t>
         </is>
       </c>
       <c r="E64" s="40" t="inlineStr">
         <is>
           <t>M1/M3: via a direct ICMP ping
-M5: ping via an SSH-through-RSCM reachability check</t>
+M5: ping via an SSH-through-RM reachability check</t>
         </is>
       </c>
       <c r="F64" s="75" t="n"/>
@@ -9242,7 +9243,7 @@
       </c>
       <c r="C78" s="43" t="inlineStr">
         <is>
-          <t>Runs fpgadiagnostics -dumpHealth (via a stage-appropriate SSH route: direct M3, RSCM-jumper M3, or RSCM-serial-proxy M5) and parses per-subsystem [FPGA-XXX] health lines, with specific waivers for known FPGA-NETWORK and FPGA-CONFIG warnings, and a one-time auto-reboot self-heal if the PCIe link status reads "WARNING" while in App mode.</t>
+          <t>Runs fpgadiagnostics -dumpHealth (via a stage-appropriate SSH route: direct M3, RM-jumper M3, or RM-serial-proxy M5) and parses per-subsystem [FPGA-XXX] health lines, with specific waivers for known FPGA-NETWORK and FPGA-CONFIG warnings, and a one-time auto-reboot self-heal if the PCIe link status reads "WARNING" while in App mode.</t>
         </is>
       </c>
       <c r="D78" s="40" t="inlineStr">
@@ -9694,7 +9695,7 @@
       <c r="E90" s="40" t="n"/>
       <c r="F90" s="43" t="inlineStr">
         <is>
-          <t>[ Check powershelf firmware version ] show powershelf psu info -s {INDEX} Capability IC Device ID Manufacturer ID Manufacturer Model Manufacturer Revision Manufacturer Serial Completion Code - - - - - If mismatch - - - - - [ Upgrade Rack SCM firmware version ] C heck fw package exists in RSCM show manager tftp list Upload fw to Rack-SCM set manager tftp get -s {IP} -f {FILE} Fw Upgrade set manager cerberus cmd -c pcdupdate /usr/srvroot/shared/{FILE}</t>
+          <t>[ Check powershelf firmware version ] show powershelf psu info -s {INDEX} Capability IC Device ID Manufacturer ID Manufacturer Model Manufacturer Revision Manufacturer Serial Completion Code - - - - - If mismatch - - - - - [ Upgrade Rack SCM firmware version ] C heck fw package exists in RM show manager tftp list Upload fw to Rack-SCM set manager tftp get -s {IP} -f {FILE} Fw Upgrade set manager cerberus cmd -c pcdupdate /usr/srvroot/shared/{FILE}</t>
         </is>
       </c>
       <c r="G90" s="47" t="n"/>
@@ -9802,7 +9803,7 @@
       </c>
       <c r="F92" s="43" t="inlineStr">
         <is>
-          <t>[Check RSCM Cerberus Version] show manager cerberus version - - - - - If mismatch - - - - - [Upgrade RSCM Cerberus] set manager cerberus update -f {FILE} [Check RSCM Cerberus PCD ID] set manager cerberus cmd -c pcdid - - - - - If mismatch - - - - - [Upgrade RSCM Cerberus PCD ID] set manager cerberus cmd -c pcdupdate /usr/srvroot/shared/{FILE} [Check RSCM Cerberus PFM ID] show manager cerberus pfm id -p 1 -r 0 - - - - - If mismatch - - - - - [Upgrade RSCM Cerberus PFM ID] set manager cerberus pfm update -f {FILE} -p 1 [Get RSCM information FAIL] show manager version - - - - - If mismatch - - - - - [Upgrade RSCM information] set manager fwupdate -f {FILE} [Check RSCM CPLD version] show manager cpld version - - - - - If mismatch - - - - - [Upgrade RSCM CPLD version] set manager cpld update -f {FILE}</t>
+          <t>[Check RM Cerberus Version] show manager cerberus version - - - - - If mismatch - - - - - [Upgrade RM Cerberus] set manager cerberus update -f {FILE} [Check RM Cerberus PCD ID] set manager cerberus cmd -c pcdid - - - - - If mismatch - - - - - [Upgrade RM Cerberus PCD ID] set manager cerberus cmd -c pcdupdate /usr/srvroot/shared/{FILE} [Check RM Cerberus PFM ID] show manager cerberus pfm id -p 1 -r 0 - - - - - If mismatch - - - - - [Upgrade RM Cerberus PFM ID] set manager cerberus pfm update -f {FILE} -p 1 [Get RM information FAIL] show manager version - - - - - If mismatch - - - - - [Upgrade RM information] set manager fwupdate -f {FILE} [Check RM CPLD version] show manager cpld version - - - - - If mismatch - - - - - [Upgrade RM CPLD version] set manager cpld update -f {FILE}</t>
         </is>
       </c>
       <c r="G92" s="47" t="n"/>
@@ -9821,22 +9822,22 @@
       <c r="J92" s="41" t="n"/>
       <c r="K92" s="42" t="inlineStr">
         <is>
-          <t>Check RSCM Cerberus Version PASS. Exp:1.5.7.5 Get:1.5.7.5
-Check RSCM PCD Version ID PASS. SF:0x1 Get:0x1
-Check RSCM PCD Platform ID PASS. SF:M4011 Get:M4011
-Check RSCM PFM ID Version PASS. Exp:0x3DA Get:0x3da
-Check RSCM information PASS. Exp:1.31.6, get_rootfs:1.31.6, get_kernel:1.31.6, get_package:1.31.6, get_device_tree:1.31.6
-Check RSCM CPLD Version PASS. Exp:V3.5 Get:V3.5
-Get RSCM Manager Type PASS. GET : 3OU_POWER_SHELF; EXP : 3OU_POWER_SHELF
-Get RSCM Host Name PASS. GET : rscm-hs-sr2-m4010; EXP : rscm-hs-sr2-m4010
-Get RSCM Uboot Version PASS. GET : 2021.01; EXP : 2021.01
-Get RSCM NTP Server PASS. GET : 172.52.0.1; EXP : 172.52.0.1
-Check All RSCM Version PASS.</t>
+          <t>Check RM Cerberus Version PASS. Exp:1.5.7.5 Get:1.5.7.5
+Check RM PCD Version ID PASS. SF:0x1 Get:0x1
+Check RM PCD Platform ID PASS. SF:M4011 Get:M4011
+Check RM PFM ID Version PASS. Exp:0x3DA Get:0x3da
+Check RM information PASS. Exp:1.31.6, get_rootfs:1.31.6, get_kernel:1.31.6, get_package:1.31.6, get_device_tree:1.31.6
+Check RM CPLD Version PASS. Exp:V3.5 Get:V3.5
+Get RM Manager Type PASS. GET : 3OU_POWER_SHELF; EXP : 3OU_POWER_SHELF
+Get RM Host Name PASS. GET : rm-hs-sr2-m4010; EXP : rm-hs-sr2-m4010
+Get RM Uboot Version PASS. GET : 2021.01; EXP : 2021.01
+Get RM NTP Server PASS. GET : 172.52.0.1; EXP : 172.52.0.1
+Check All RM Version PASS.</t>
         </is>
       </c>
       <c r="L92" s="31" t="inlineStr">
         <is>
-          <t>Matches CRD: Cerberus 1.5.7.5, PFMID 0x3DA, PCD M4011/0x1, R-SCM 1.31.6, CPLD V3.5.</t>
+          <t>Matches CRD: Cerberus 1.5.7.5, PFMID 0x3DA, PCD M4011/0x1, RM 1.31.6, CPLD V3.5.</t>
         </is>
       </c>
       <c r="M92" s="18" t="n"/>
@@ -9879,7 +9880,7 @@
       </c>
       <c r="F93" s="43" t="inlineStr">
         <is>
-          <t>[ Get system info via R-SCM ] show system info -i { RM_PORT } Mac Address SerialNumber BiosVersion BMCVersion CpldVersion DCSCMCpldVersion Count TotalSystemMemoryGib - - - - - If mismatch - - - - - [ Upgrade system firmware version ] set system file put -i {PORT} -f {FILE} set system bios update -i {PORT} -f {FILE} set system bmc update -i {PORT} -f {FILE}</t>
+          <t>[ Get system info via RM ] show system info -i { RM_PORT } Mac Address SerialNumber BiosVersion BMCVersion CpldVersion DCSCMCpldVersion Count TotalSystemMemoryGib - - - - - If mismatch - - - - - [ Upgrade system firmware version ] set system file put -i {PORT} -f {FILE} set system bios update -i {PORT} -f {FILE} set system bmc update -i {PORT} -f {FILE}</t>
         </is>
       </c>
       <c r="G93" s="47" t="b">
@@ -9898,7 +9899,7 @@
 DCSCMCpldVersion         check PASS. Get:                 03.06.00, Exp:                 03.06.00
 Count                    check PASS. Get:                        2, Exp:                        2
 TotalSystemMemoryGib     check PASS. Get:                      512, Exp:                      512
-[PASS] Check system info via R-SCM PASS
+[PASS] Check system info via RM PASS
 </t>
         </is>
       </c>
@@ -9913,7 +9914,7 @@
 DCSCMCpldVersion         check PASS. Get:                 03.06.00, Exp:                 03.06.00
 Count                    check PASS. Get:                        2, Exp:                        2
 TotalSystemMemoryGib     check PASS. Get:                      512, Exp:                      512
-[PASS] Check system info via R-SCM PASS"</t>
+[PASS] Check system info via RM PASS"</t>
         </is>
       </c>
       <c r="L93" s="31" t="inlineStr">
@@ -10854,7 +10855,7 @@
       </c>
       <c r="E14" s="43" t="inlineStr">
         <is>
-          <t>Uses Context.save_boot_state()/gs_load_ctx() to track reboot_count across the AC cycle. On M5 stage, routes the AC command through RSCM SSH instead of direct BMC IPMI.</t>
+          <t>Uses Context.save_boot_state()/gs_load_ctx() to track reboot_count across the AC cycle. On M5 stage, routes the AC command through RM SSH instead of direct BMC IPMI.</t>
         </is>
       </c>
       <c r="F14" s="43" t="inlineStr">
@@ -12248,7 +12249,7 @@
       </c>
       <c r="F12" s="43" t="inlineStr">
         <is>
-          <t>[Check RSCM Cerberus Version] show manager cerberus version - - - - - If mismatch - - - - - [Upgrade RSCM Cerberus] set manager cerberus update -f {FILE} [Check RSCM Cerberus PCD ID] set manager cerberus cmd -c pcdid - - - - - If mismatch - - - - - [Upgrade RSCM Cerberus PCD ID] set manager cerberus cmd -c pcdupdate /usr/srvroot/shared/{FILE} [Check RSCM Cerberus PFM ID] show manager cerberus pfm id -p 1 -r 0 - - - - - If mismatch - - - - - [Upgrade RSCM Cerberus PFM ID] set manager cerberus pfm update -f {FILE} -p 1 [Get RSCM information FAIL] show manager version - - - - - If mismatch - - - - - [Upgrade RSCM information] set manager fwupdate -f {FILE} [Check RSCM CPLD version] show manager cpld version - - - - - If mismatch - - - - - [Upgrade RSCM CPLD version] set manager cpld update -f {FILE}</t>
+          <t>[Check RM Cerberus Version] show manager cerberus version - - - - - If mismatch - - - - - [Upgrade RM Cerberus] set manager cerberus update -f {FILE} [Check RM Cerberus PCD ID] set manager cerberus cmd -c pcdid - - - - - If mismatch - - - - - [Upgrade RM Cerberus PCD ID] set manager cerberus cmd -c pcdupdate /usr/srvroot/shared/{FILE} [Check RM Cerberus PFM ID] show manager cerberus pfm id -p 1 -r 0 - - - - - If mismatch - - - - - [Upgrade RM Cerberus PFM ID] set manager cerberus pfm update -f {FILE} -p 1 [Get RM information FAIL] show manager version - - - - - If mismatch - - - - - [Upgrade RM information] set manager fwupdate -f {FILE} [Check RM CPLD version] show manager cpld version - - - - - If mismatch - - - - - [Upgrade RM CPLD version] set manager cpld update -f {FILE}</t>
         </is>
       </c>
       <c r="G12" s="47" t="n"/>
@@ -12257,34 +12258,34 @@
       </c>
       <c r="I12" s="63" t="inlineStr">
         <is>
-          <t>No rscm powershelf master in LAB. Waive</t>
+          <t>No rm powershelf master in LAB. Waive</t>
         </is>
       </c>
       <c r="J12" s="48" t="n"/>
       <c r="K12" s="42" t="inlineStr">
         <is>
-          <t>Check RSCM Cerberus Version PASS. Exp:1.5.7.5 Get:1.5.7.5
-Check RSCM PCD Version ID PASS. SF:0x1 Get:0x1
-Check RSCM PCD Platform ID PASS. SF:M4011 Get:M4011
-Check RSCM PFM ID Version PASS. Exp:0x3DA Get:0x3da
-Check RSCM information PASS. Exp:1.31.6, get_rootfs:1.31.6, get_kernel:1.31.6, get_package:1.31.6, get_device_tree:1.31.6
-Check RSCM CPLD Version PASS. Exp:V3.5 Get:V3.5
-Get RSCM Manager Type PASS. GET : 3OU_POWER_SHELF; EXP : 3OU_POWER_SHELF
-Get RSCM Host Name PASS. GET : rscm-hs-sr2-m4010; EXP : rscm-hs-sr2-m4010
-Get RSCM Uboot Version PASS. GET : 2021.01; EXP : 2021.01
-Get RSCM NTP Server PASS. GET : 172.52.0.1; EXP : 172.52.0.1
-Check All RSCM Version PASS.</t>
+          <t>Check RM Cerberus Version PASS. Exp:1.5.7.5 Get:1.5.7.5
+Check RM PCD Version ID PASS. SF:0x1 Get:0x1
+Check RM PCD Platform ID PASS. SF:M4011 Get:M4011
+Check RM PFM ID Version PASS. Exp:0x3DA Get:0x3da
+Check RM information PASS. Exp:1.31.6, get_rootfs:1.31.6, get_kernel:1.31.6, get_package:1.31.6, get_device_tree:1.31.6
+Check RM CPLD Version PASS. Exp:V3.5 Get:V3.5
+Get RM Manager Type PASS. GET : 3OU_POWER_SHELF; EXP : 3OU_POWER_SHELF
+Get RM Host Name PASS. GET : rm-hs-sr2-m4010; EXP : rm-hs-sr2-m4010
+Get RM Uboot Version PASS. GET : 2021.01; EXP : 2021.01
+Get RM NTP Server PASS. GET : 172.52.0.1; EXP : 172.52.0.1
+Check All RM Version PASS.</t>
         </is>
       </c>
       <c r="L12" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">Matches CRD
-R-SCM Cerberus 1.5.7.5
-R-SCM Cerberus PCD Version ID 0x1
-R-SCM Cerberus PCD Platform ID M4011
-R-SCM PFMID value 0x3DA
-R-SCM Firmware 1.31.6
-R-SCM CPLD V3.5
+RM Cerberus 1.5.7.5
+RM Cerberus PCD Version ID 0x1
+RM Cerberus PCD Platform ID M4011
+RM PFMID value 0x3DA
+RM Firmware 1.31.6
+RM CPLD V3.5
 </t>
         </is>
       </c>
@@ -12300,7 +12301,7 @@
       </c>
       <c r="C13" s="82" t="inlineStr">
         <is>
-          <t>Check the PSU firmware version on the power shelf via R-SCM for the current UUT. This function only performs the check on master nodes.</t>
+          <t>Check the PSU firmware version on the power shelf via RM for the current UUT. This function only performs the check on master nodes.</t>
         </is>
       </c>
       <c r="D13" s="82" t="inlineStr">
@@ -12309,7 +12310,7 @@
 - UUT is a master node.
 - All PSU serial numbers, manufacturers, and firmware versions match expected values.
 - Fail
-- Unable to get R-SCM IP.
+- Unable to get RM IP.
 - PSU information cannot be retrieved or parsed.
 - PSU not found in the expected list.
 - Firmware version mismatch and auto-upgrade fails.</t>
@@ -12357,7 +12358,7 @@
       </c>
       <c r="C14" s="82" t="inlineStr">
         <is>
-          <t>Check RSCM Health Status</t>
+          <t>Check RM Health Status</t>
         </is>
       </c>
       <c r="D14" s="82" t="inlineStr">
@@ -12395,7 +12396,7 @@
       <c r="C15" s="82" t="inlineStr">
         <is>
           <t>Check POWERSHELF Product Name
-Check RSCM Manager Type</t>
+Check RM Manager Type</t>
         </is>
       </c>
       <c r="D15" s="82" t="n"/>
@@ -12427,12 +12428,12 @@
       </c>
       <c r="C16" s="43" t="inlineStr">
         <is>
-          <t>C hecks UUT system information via the R-SCM interface and compares it with the expected configuration values .</t>
+          <t>C hecks UUT system information via the RM interface and compares it with the expected configuration values .</t>
         </is>
       </c>
       <c r="D16" s="43" t="inlineStr">
         <is>
-          <t>Pass All fields (MAC, SN, BIOS version, BMC version, CPLD versions, CPU count, and memory size) match expected values. Or mismatched fields are successfully auto-updated (if allowed). Fail Unable to retrieve system info from R-SCM. Mismatched field(s) and auto-upgrade is either disabled or unsuccessful.</t>
+          <t>Pass All fields (MAC, SN, BIOS version, BMC version, CPLD versions, CPU count, and memory size) match expected values. Or mismatched fields are successfully auto-updated (if allowed). Fail Unable to retrieve system info from RM. Mismatched field(s) and auto-upgrade is either disabled or unsuccessful.</t>
         </is>
       </c>
       <c r="E16" s="43" t="inlineStr">
@@ -12442,7 +12443,7 @@
       </c>
       <c r="F16" s="43" t="inlineStr">
         <is>
-          <t>[ Get system info via R-SCM ] show system info -i { RM_PORT } Mac Address SerialNumber BiosVersion BMCVersion CpldVersion DCSCMCpldVersion Count TotalSystemMemoryGib - - - - - If mismatch - - - - - [ Upgrade system firmware version ] set system file put -i {PORT} -f {FILE} set system bios update -i {PORT} -f {FILE} set system bmc update -i {PORT} -f {FILE}</t>
+          <t>[ Get system info via RM ] show system info -i { RM_PORT } Mac Address SerialNumber BiosVersion BMCVersion CpldVersion DCSCMCpldVersion Count TotalSystemMemoryGib - - - - - If mismatch - - - - - [ Upgrade system firmware version ] set system file put -i {PORT} -f {FILE} set system bios update -i {PORT} -f {FILE} set system bmc update -i {PORT} -f {FILE}</t>
         </is>
       </c>
       <c r="G16" s="47" t="b">
@@ -12463,7 +12464,7 @@
 DCSCMCpldVersion         check PASS. Get:                 03.06.00, Exp:                 03.06.00
 Count                    check PASS. Get:                        2, Exp:                        2
 TotalSystemMemoryGib     check PASS. Get:                      512, Exp:                      512
-[PASS] Check system info via R-SCM PASS"</t>
+[PASS] Check system info via RM PASS"</t>
         </is>
       </c>
       <c r="L16" s="31" t="inlineStr">
@@ -12484,7 +12485,7 @@
       </c>
       <c r="C17" s="43" t="inlineStr">
         <is>
-          <t>Check R-SCM FRU information</t>
+          <t>Check RM FRU information</t>
         </is>
       </c>
       <c r="D17" s="43" t="inlineStr">
@@ -12573,7 +12574,7 @@
       </c>
       <c r="C20" s="43" t="inlineStr">
         <is>
-          <t>Check System FRU via RSCM</t>
+          <t>Check System FRU via RM</t>
         </is>
       </c>
       <c r="D20" s="43" t="inlineStr">
@@ -12604,7 +12605,7 @@
       </c>
       <c r="C21" s="43" t="inlineStr">
         <is>
-          <t>Check DC-SCM(M1120) FRU via R-SCM</t>
+          <t>Check DC-SCM(M1120) FRU via RM</t>
         </is>
       </c>
       <c r="D21" s="43" t="inlineStr">
@@ -12639,7 +12640,7 @@
       </c>
       <c r="C22" s="43" t="inlineStr">
         <is>
-          <t>Check GlacierPeak FRU via R-SCM</t>
+          <t>Check GlacierPeak FRU via RM</t>
         </is>
       </c>
       <c r="D22" s="43" t="inlineStr">
@@ -13476,13 +13477,13 @@
       </c>
       <c r="D42" s="43" t="inlineStr">
         <is>
-          <t>PASS if 5/5 pings succeed (or the RSCM-routed SSH connect succeeds).</t>
+          <t>PASS if 5/5 pings succeed (or the RM-routed SSH connect succeeds).</t>
         </is>
       </c>
       <c r="E42" s="43" t="inlineStr">
         <is>
           <t>M1/M3: via a direct ICMP ping
-M5: ping via an SSH-through-RSCM reachability check</t>
+M5: ping via an SSH-through-RM reachability check</t>
         </is>
       </c>
       <c r="F42" s="43" t="n"/>
@@ -14082,7 +14083,7 @@
       </c>
       <c r="C60" s="43" t="inlineStr">
         <is>
-          <t>Runs fpgadiagnostics -dumpHealth (via a stage-appropriate SSH route: direct M3, RSCM-jumper M3, or RSCM-serial-proxy M5) and parses per-subsystem [FPGA-XXX] health lines, with specific waivers for known FPGA-NETWORK and FPGA-CONFIG warnings, and a one-time auto-reboot self-heal if the PCIe link status reads "WARNING" while in App mode.</t>
+          <t>Runs fpgadiagnostics -dumpHealth (via a stage-appropriate SSH route: direct M3, RM-jumper M3, or RM-serial-proxy M5) and parses per-subsystem [FPGA-XXX] health lines, with specific waivers for known FPGA-NETWORK and FPGA-CONFIG warnings, and a one-time auto-reboot self-heal if the PCIe link status reads "WARNING" while in App mode.</t>
         </is>
       </c>
       <c r="D60" s="43" t="inlineStr">
@@ -14162,7 +14163,7 @@
       </c>
       <c r="E62" s="43" t="inlineStr">
         <is>
-          <t>Multi-stage, stateful check keyed on the presence of /vol/data/persistent/tests/golden_status.txt on the BMC. If the log doesn't exist yet, the function uploads SoCFPGAGoldenTestSvc.service and fpga_golden_check.py to the BMC, switches GP into golden boot mode (cerberus_utility fpgasetbootmode 0), forces an AC cycle (RSCM rscm_system_ac on M5, gs_pdb_ac_cycle otherwise) to make the mode take effect, and then returns 1 — meaning the first pass of this item after an image/config change always intentionally fails and needs a subsequent PRETEST re-run to actually validate the version. On version mismatch with fpga_gp_fw_upgrade TRUE, it calls _gp_fpga_softnic_upgrade() and then re-generates the golden log (also returning 1) rather than re-checking in the same pass.</t>
+          <t>Multi-stage, stateful check keyed on the presence of /vol/data/persistent/tests/golden_status.txt on the BMC. If the log doesn't exist yet, the function uploads SoCFPGAGoldenTestSvc.service and fpga_golden_check.py to the BMC, switches GP into golden boot mode (cerberus_utility fpgasetbootmode 0), forces an AC cycle (RM rm_system_ac on M5, gs_pdb_ac_cycle otherwise) to make the mode take effect, and then returns 1 — meaning the first pass of this item after an image/config change always intentionally fails and needs a subsequent PRETEST re-run to actually validate the version. On version mismatch with fpga_gp_fw_upgrade TRUE, it calls _gp_fpga_softnic_upgrade() and then re-generates the golden log (also returning 1) rather than re-checking in the same pass.</t>
         </is>
       </c>
       <c r="F62" s="43" t="n"/>
@@ -14198,7 +14199,7 @@
       <c r="E63" s="43" t="inlineStr">
         <is>
           <t>Two very different code paths: 
-- for prj_stage == "M5" it SFTP-uploads the three HWKEY .bin files to the BMC, then uses a shell command list over usb0 (10.235.100.0/31 point-to-point link) with scp -P 2200 to pull each key onto the GlacierPeak SoC and run cerberus_utility importsignedcert locally there — all three fuse commands (root CA idx 1, intermediate idx 2, device ID idx 0) run under a single rscm_lock.
+- for prj_stage == "M5" it SFTP-uploads the three HWKEY .bin files to the BMC, then uses a shell command list over usb0 (10.235.100.0/31 point-to-point link) with scp -P 2200 to pull each key onto the GlacierPeak SoC and run cerberus_utility importsignedcert locally there — all three fuse commands (root CA idx 1, intermediate idx 2, device ID idx 0) run under a single rm_lock.
 - For other stages it uses a raw pxssh session direct to the GlacierPeak SoC on port 8295 (user admin/admin), with up to 2 retries and a 90s backoff between attempts if the SoC is "busy". HWKey files are deleted from the BMC after fusing in both paths.</t>
         </is>
       </c>
@@ -14237,7 +14238,7 @@
           <t>- Security/identity-relevant, one-time step, M3-only. 
 - Unlike the Manticore/TIP flow this checks each slot independently — a partially-provisioned board (e.g. slot0 done, slot1 not) only provisions the missing slot. 
 - No verification of the -setCertificate output content is performed. 
-- Uses self.rscm_lock("RSCM", ...) around the actual burn to avoid concurrent RSCM access from other test threads.
+- Uses self.rm_lock("RM", ...) around the actual burn to avoid concurrent RM access from other test threads.
 - After both slots are set, it resets the FPGA and sleeps 300s before the final confirmation check.</t>
         </is>
       </c>

--- a/C219B_L10_L11_TestPlan_PV_1A00_added.xlsx
+++ b/C219B_L10_L11_TestPlan_PV_1A00_added.xlsx
@@ -1397,8 +1397,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表格1" displayName="表格1" ref="A1:L102" headerRowCount="1" totalsRowShown="0" headerRowDxfId="44" dataDxfId="43" tableBorderDxfId="42">
-  <autoFilter ref="A1:L102">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="表格1" displayName="表格1" ref="A1:L99" headerRowCount="1" totalsRowShown="0" headerRowDxfId="44" dataDxfId="43" tableBorderDxfId="42">
+  <autoFilter ref="A1:L99">
     <filterColumn colId="0" hiddenButton="1" showButton="1"/>
     <filterColumn colId="1" hiddenButton="1" showButton="1"/>
     <filterColumn colId="2" hiddenButton="1" showButton="1"/>
@@ -1479,8 +1479,8 @@
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="表格4" displayName="表格4" ref="A1:L89" headerRowCount="1" totalsRowShown="0" dataDxfId="12">
-  <autoFilter ref="A1:L89">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="表格4" displayName="表格4" ref="A1:L86" headerRowCount="1" totalsRowShown="0" dataDxfId="12">
+  <autoFilter ref="A1:L86">
     <filterColumn colId="0" hiddenButton="1" showButton="1"/>
     <filterColumn colId="1" hiddenButton="1" showButton="1"/>
     <filterColumn colId="2" hiddenButton="1" showButton="1"/>
@@ -6313,7 +6313,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Y104"/>
+  <dimension ref="A1:Y101"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="14.25"/>
   <cols>
     <col width="5.7109375" customWidth="1" style="77" min="1" max="1"/>
@@ -6603,97 +6603,98 @@
       <c r="K7" s="39" t="n"/>
       <c r="L7" s="51" t="n"/>
     </row>
-    <row r="8" customFormat="1" s="33">
-      <c r="A8" s="81" t="n">
+    <row r="8" ht="67.5" customFormat="1" customHeight="1" s="33">
+      <c r="A8" s="76" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="82" t="inlineStr">
-        <is>
-          <t>rm_health_check</t>
-        </is>
-      </c>
-      <c r="C8" s="82" t="inlineStr">
-        <is>
-          <t>Check RM Health Status</t>
-        </is>
-      </c>
-      <c r="D8" s="83" t="inlineStr">
-        <is>
-          <t>PSU state should be “Healthy”.
-(Master Only)</t>
-        </is>
-      </c>
-      <c r="E8" s="83" t="n"/>
-      <c r="F8" s="84" t="inlineStr">
-        <is>
-          <t>Command: show powershelf psu state
-show manager health、show manager info -p -m</t>
-        </is>
-      </c>
-      <c r="G8" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="H8" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="I8" s="84" t="n"/>
-      <c r="J8" s="84" t="n"/>
-      <c r="K8" s="85" t="n"/>
-      <c r="L8" s="86" t="n"/>
-    </row>
-    <row r="9" customFormat="1" s="33">
-      <c r="A9" s="81" t="n">
+      <c r="B8" s="43" t="inlineStr">
+        <is>
+          <t>rm_uut_info_chk</t>
+        </is>
+      </c>
+      <c r="C8" s="43" t="inlineStr">
+        <is>
+          <t>Checks UUT system information via the RM interface and compares it with the expected configuration values .</t>
+        </is>
+      </c>
+      <c r="D8" s="40" t="inlineStr">
+        <is>
+          <t>Pass All fields (MAC, SN, BIOS version, BMC version, CPLD versions, CPU count, and memory size) match expected values. Or mismatched fields are successfully auto-updated (if allowed). Fail Unable to retrieve system info from RM. Mismatched field(s) and auto-upgrade is either disabled or unsuccessful.</t>
+        </is>
+      </c>
+      <c r="E8" s="40" t="n"/>
+      <c r="F8" s="75" t="n"/>
+      <c r="G8" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="H8" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="I8" s="55" t="n"/>
+      <c r="J8" s="55" t="n"/>
+      <c r="K8" s="39" t="n"/>
+      <c r="L8" s="51" t="n"/>
+    </row>
+    <row r="9" ht="108" customFormat="1" customHeight="1" s="33">
+      <c r="A9" s="76" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="82" t="inlineStr">
-        <is>
-          <t>rm_manager_type_check</t>
-        </is>
-      </c>
-      <c r="C9" s="82" t="inlineStr">
-        <is>
-          <t>Check POWERSHELF Product Name
-Check RM Manager Type</t>
-        </is>
-      </c>
-      <c r="D9" s="83" t="n"/>
-      <c r="E9" s="83" t="n"/>
-      <c r="F9" s="84" t="inlineStr">
-        <is>
-          <t>show manager type</t>
-        </is>
-      </c>
-      <c r="G9" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="H9" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="I9" s="84" t="n"/>
-      <c r="J9" s="84" t="n"/>
-      <c r="K9" s="85" t="n"/>
-      <c r="L9" s="86" t="n"/>
-    </row>
-    <row r="10" ht="67.5" customFormat="1" customHeight="1" s="33">
+      <c r="B9" s="43" t="inlineStr">
+        <is>
+          <t>fpga_gp_fw_chk</t>
+        </is>
+      </c>
+      <c r="C9" s="43" t="inlineStr">
+        <is>
+          <t>The most comprehensive FPGA firmware check in this station — validates Cerberus FW, Cyclone V PFM Device/Platform ID + image version, SoC PFM Device/Platform ID, SoC FIP firmware, SoC OS version, Linux kernel version, and FPGA diagnostic tools version, all read from a single batched SSH session to the GlacierPeak SoC console — with a coordinated multi-component upgrade sequence (in a specific vendor-mandated order) if any check fails and upgrades are allowed.</t>
+        </is>
+      </c>
+      <c r="D9" s="40" t="inlineStr">
+        <is>
+          <t>PASS only if every one of the 11 checked version/ID pairs matches (SoC OS version additionally requires the SoC's boot mode to be 0/PXE — a match while in a non-PXE bootmode is treated as needing a re-image and still counts as a failure needing upgrade).</t>
+        </is>
+      </c>
+      <c r="E9" s="40" t="inlineStr">
+        <is>
+          <t>Upgrade ordering follows a documented vendor spec (comment cites "M1195579 RevD A2051 GLACIER PEAK INTEGRATION REQUIREMENTS"): Cerberus FW → SoC PFM ID → Cyclone V PFM ID → SoC FIP → SoC OS Image → Cyclone V FPGA Image → Agilex FPGA APP/SoftNIC Image. SoC Linux Kernel version and SoC FPGA Tools version are explicitly flagged as non-upgradable — a mismatch there just fails, with no remediation path. A successful PFM/FIP/OS-image/App-image upgrade sets an is_reset flag that triggers gp_reset() (an AC-cycle-equivalent reset+power-cycle-and-wait) at the very end.</t>
+        </is>
+      </c>
+      <c r="F9" s="75" t="n"/>
+      <c r="G9" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="H9" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="I9" s="55" t="n"/>
+      <c r="J9" s="55" t="n"/>
+      <c r="K9" s="39" t="n"/>
+      <c r="L9" s="51" t="n"/>
+    </row>
+    <row r="10" ht="148.5" customFormat="1" customHeight="1" s="33">
       <c r="A10" s="76" t="n">
         <v>8</v>
       </c>
       <c r="B10" s="43" t="inlineStr">
         <is>
-          <t>rm_uut_info_chk</t>
+          <t>fpga_gp_softnic_ver_chk</t>
         </is>
       </c>
       <c r="C10" s="43" t="inlineStr">
         <is>
-          <t>Checks UUT system information via the RM interface and compares it with the expected configuration values .</t>
+          <t>Checks the GlacierPeak Agilex FPGA SoftNIC image version by putting the GP into "golden mode" (boot mode 0) and reading recorded register values (role 65/101) from a status log left on the BMC filesystem.</t>
         </is>
       </c>
       <c r="D10" s="40" t="inlineStr">
         <is>
-          <t>Pass All fields (MAC, SN, BIOS version, BMC version, CPLD versions, CPU count, and memory size) match expected values. Or mismatched fields are successfully auto-updated (if allowed). Fail Unable to retrieve system info from RM. Mismatched field(s) and auto-upgrade is either disabled or unsuccessful.</t>
-        </is>
-      </c>
-      <c r="E10" s="40" t="n"/>
+          <t>PASS when the recorded role_id role_ver equals fpga_gp_softnic_ver. FAIL on SSH/SFTP failure, on failure to reach golden boot mode, or on version mismatch when upgrade is disabled/fails.</t>
+        </is>
+      </c>
+      <c r="E10" s="40" t="inlineStr">
+        <is>
+          <t>Multi-stage, stateful check keyed on the presence of /vol/data/persistent/tests/golden_status.txt on the BMC. If the log doesn't exist yet, the function uploads SoCFPGAGoldenTestSvc.service and fpga_golden_check.py to the BMC, switches GP into golden boot mode (cerberus_utility fpgasetbootmode 0), forces an AC cycle (RM rm_system_ac on M5, gs_pdb_ac_cycle otherwise) to make the mode take effect, and then returns 1 — meaning the first pass of this item after an image/config change always intentionally fails and needs a subsequent PRETEST re-run to actually validate the version. On version mismatch with fpga_gp_fw_upgrade TRUE, it calls _gp_fpga_softnic_upgrade() and then re-generates the golden log (also returning 1) rather than re-checking in the same pass.</t>
+        </is>
+      </c>
       <c r="F10" s="75" t="n"/>
       <c r="G10" s="55" t="b">
         <v>0</v>
@@ -6706,28 +6707,28 @@
       <c r="K10" s="39" t="n"/>
       <c r="L10" s="51" t="n"/>
     </row>
-    <row r="11" ht="108" customFormat="1" customHeight="1" s="33">
+    <row r="11" ht="40.5" customFormat="1" customHeight="1" s="33">
       <c r="A11" s="76" t="n">
         <v>9</v>
       </c>
       <c r="B11" s="43" t="inlineStr">
         <is>
-          <t>fpga_gp_fw_chk</t>
+          <t>pcie_manticore_chk</t>
         </is>
       </c>
       <c r="C11" s="43" t="inlineStr">
         <is>
-          <t>The most comprehensive FPGA firmware check in this station — validates Cerberus FW, Cyclone V PFM Device/Platform ID + image version, SoC PFM Device/Platform ID, SoC FIP firmware, SoC OS version, Linux kernel version, and FPGA diagnostic tools version, all read from a single batched SSH session to the GlacierPeak SoC console — with a coordinated multi-component upgrade sequence (in a specific vendor-mandated order) if any check fails and upgrades are allowed.</t>
+          <t>Check DC-SCM Manticore firmware version. If a mismatch is detected, an automatic upgrade will be performed.</t>
         </is>
       </c>
       <c r="D11" s="40" t="inlineStr">
         <is>
-          <t>PASS only if every one of the 11 checked version/ID pairs matches (SoC OS version additionally requires the SoC's boot mode to be 0/PXE — a match while in a non-PXE bootmode is treated as needing a re-image and still counts as a failure needing upgrade).</t>
+          <t>Pass - match; Fail - mismatch</t>
         </is>
       </c>
       <c r="E11" s="40" t="inlineStr">
         <is>
-          <t>Upgrade ordering follows a documented vendor spec (comment cites "M1195579 RevD A2051 GLACIER PEAK INTEGRATION REQUIREMENTS"): Cerberus FW → SoC PFM ID → Cyclone V PFM ID → SoC FIP → SoC OS Image → Cyclone V FPGA Image → Agilex FPGA APP/SoftNIC Image. SoC Linux Kernel version and SoC FPGA Tools version are explicitly flagged as non-upgradable — a mismatch there just fails, with no remediation path. A successful PFM/FIP/OS-image/App-image upgrade sets an is_reset flag that triggers gp_reset() (an AC-cycle-equivalent reset+power-cycle-and-wait) at the very end.</t>
+          <t>Automatically upgrade Manticore FW if version mismatch and upgrade flag is set. M1 - Check only M3/M5 - Check and upgrade at Pretest. Check only at the other stations</t>
         </is>
       </c>
       <c r="F11" s="75" t="n"/>
@@ -6742,28 +6743,28 @@
       <c r="K11" s="39" t="n"/>
       <c r="L11" s="51" t="n"/>
     </row>
-    <row r="12" ht="148.5" customFormat="1" customHeight="1" s="33">
+    <row r="12" ht="40.5" customFormat="1" customHeight="1" s="33">
       <c r="A12" s="76" t="n">
         <v>10</v>
       </c>
       <c r="B12" s="43" t="inlineStr">
         <is>
-          <t>fpga_gp_softnic_ver_chk</t>
+          <t>pcie_tip_chk</t>
         </is>
       </c>
       <c r="C12" s="43" t="inlineStr">
         <is>
-          <t>Checks the GlacierPeak Agilex FPGA SoftNIC image version by putting the GP into "golden mode" (boot mode 0) and reading recorded register values (role 65/101) from a status log left on the BMC filesystem.</t>
+          <t>Check DC-SCM Hydra TIP firmware version. If a mismatch is detected, an automatic upgrade will be performed.</t>
         </is>
       </c>
       <c r="D12" s="40" t="inlineStr">
         <is>
-          <t>PASS when the recorded role_id role_ver equals fpga_gp_softnic_ver. FAIL on SSH/SFTP failure, on failure to reach golden boot mode, or on version mismatch when upgrade is disabled/fails.</t>
+          <t>Pass - match; Fail – mismatch</t>
         </is>
       </c>
       <c r="E12" s="40" t="inlineStr">
         <is>
-          <t>Multi-stage, stateful check keyed on the presence of /vol/data/persistent/tests/golden_status.txt on the BMC. If the log doesn't exist yet, the function uploads SoCFPGAGoldenTestSvc.service and fpga_golden_check.py to the BMC, switches GP into golden boot mode (cerberus_utility fpgasetbootmode 0), forces an AC cycle (RM rm_system_ac on M5, gs_pdb_ac_cycle otherwise) to make the mode take effect, and then returns 1 — meaning the first pass of this item after an image/config change always intentionally fails and needs a subsequent PRETEST re-run to actually validate the version. On version mismatch with fpga_gp_fw_upgrade TRUE, it calls _gp_fpga_softnic_upgrade() and then re-generates the golden log (also returning 1) rather than re-checking in the same pass.</t>
+          <t>Automatically upgrade Manticore FW if version mismatch and upgrade flag is set. M1 - Check only M3/M5 - Check and upgrade at Pretest. Check only at the other stations</t>
         </is>
       </c>
       <c r="F12" s="75" t="n"/>
@@ -6784,22 +6785,22 @@
       </c>
       <c r="B13" s="43" t="inlineStr">
         <is>
-          <t>pcie_manticore_chk</t>
+          <t>tpm_ver_chk</t>
         </is>
       </c>
       <c r="C13" s="43" t="inlineStr">
         <is>
-          <t>Check DC-SCM Manticore firmware version. If a mismatch is detected, an automatic upgrade will be performed.</t>
+          <t>Check TPM presence and validate firmware version against config.</t>
         </is>
       </c>
       <c r="D13" s="40" t="inlineStr">
         <is>
-          <t>Pass - match; Fail - mismatch</t>
+          <t>Pass - return 0; Fail - return 1</t>
         </is>
       </c>
       <c r="E13" s="40" t="inlineStr">
         <is>
-          <t>Automatically upgrade Manticore FW if version mismatch and upgrade flag is set. M1 - Check only M3/M5 - Check and upgrade at Pretest. Check only at the other stations</t>
+          <t>The current implementation uses the OS-level TPM driver ( /dev/tpm0 ) to access TPM data Before Check TPM 20 version, we do the TPM 20 full/not_full selftest first</t>
         </is>
       </c>
       <c r="F13" s="75" t="n"/>
@@ -6820,22 +6821,22 @@
       </c>
       <c r="B14" s="43" t="inlineStr">
         <is>
-          <t>pcie_tip_chk</t>
+          <t>uut_ac_cycle</t>
         </is>
       </c>
       <c r="C14" s="43" t="inlineStr">
         <is>
-          <t>Check DC-SCM Hydra TIP firmware version. If a mismatch is detected, an automatic upgrade will be performed.</t>
+          <t>AC power-cycle using an OEM raw IPMI command (rather than a standard power-control command)</t>
         </is>
       </c>
       <c r="D14" s="40" t="inlineStr">
         <is>
-          <t>Pass - match; Fail – mismatch</t>
+          <t>PASS if the AC power-cycle execute successfully.</t>
         </is>
       </c>
       <c r="E14" s="40" t="inlineStr">
         <is>
-          <t>Automatically upgrade Manticore FW if version mismatch and upgrade flag is set. M1 - Check only M3/M5 - Check and upgrade at Pretest. Check only at the other stations</t>
+          <t>If a FW update is performed and an AC power cycle is required for the update to take effect, this test item will be triggered. Otherwise, this test item will be skipped.</t>
         </is>
       </c>
       <c r="F14" s="75" t="n"/>
@@ -6850,28 +6851,28 @@
       <c r="K14" s="39" t="n"/>
       <c r="L14" s="51" t="n"/>
     </row>
-    <row r="15" ht="40.5" customFormat="1" customHeight="1" s="33">
+    <row r="15" ht="27" customFormat="1" customHeight="1" s="33">
       <c r="A15" s="76" t="n">
         <v>13</v>
       </c>
       <c r="B15" s="43" t="inlineStr">
         <is>
-          <t>tpm_ver_chk</t>
+          <t>bmc_fru_write</t>
         </is>
       </c>
       <c r="C15" s="43" t="inlineStr">
         <is>
-          <t>Check TPM presence and validate firmware version against config.</t>
+          <t>Writes the motherboard FRU EEPROM from the SF-sourced FRU template (MBPN.csv), first syncing BMC time to host time.</t>
         </is>
       </c>
       <c r="D15" s="40" t="inlineStr">
         <is>
-          <t>Pass - return 0; Fail - return 1</t>
+          <t>PASS when the FRU write completes without error. FAIL if function returns non-zero</t>
         </is>
       </c>
       <c r="E15" s="40" t="inlineStr">
         <is>
-          <t>The current implementation uses the OS-level TPM driver ( /dev/tpm0 ) to access TPM data Before Check TPM 20 version, we do the TPM 20 full/not_full selftest first</t>
+          <t>Since QMF may involve L10 units requiring repair, replacement, or return, a function to re-flash the FRU has been added.</t>
         </is>
       </c>
       <c r="F15" s="75" t="n"/>
@@ -6892,22 +6893,22 @@
       </c>
       <c r="B16" s="43" t="inlineStr">
         <is>
-          <t>uut_ac_cycle</t>
+          <t>bmc_sku_info_chk</t>
         </is>
       </c>
       <c r="C16" s="43" t="inlineStr">
         <is>
-          <t>AC power-cycle using an OEM raw IPMI command (rather than a standard power-control command)</t>
+          <t>Check BMC SKU JSON information to ensure correct versioning and system functionality. If a mismatch is detected, an automatic upgrade will be performed.</t>
         </is>
       </c>
       <c r="D16" s="40" t="inlineStr">
         <is>
-          <t>PASS if the AC power-cycle execute successfully.</t>
+          <t>Pass - match; Fail - mismatch</t>
         </is>
       </c>
       <c r="E16" s="40" t="inlineStr">
         <is>
-          <t>If a FW update is performed and an AC power cycle is required for the update to take effect, this test item will be triggered. Otherwise, this test item will be skipped.</t>
+          <t>Version check M1 - Check only M3/M5 Check and upgrade at Pretest. Check only at the other stations</t>
         </is>
       </c>
       <c r="F16" s="75" t="n"/>
@@ -6922,30 +6923,26 @@
       <c r="K16" s="39" t="n"/>
       <c r="L16" s="51" t="n"/>
     </row>
-    <row r="17" ht="27" customFormat="1" customHeight="1" s="33">
+    <row r="17" ht="15" customFormat="1" customHeight="1" s="33">
       <c r="A17" s="76" t="n">
         <v>15</v>
       </c>
       <c r="B17" s="43" t="inlineStr">
         <is>
-          <t>bmc_fru_write</t>
+          <t>bmc_retimer_fw_chk</t>
         </is>
       </c>
       <c r="C17" s="43" t="inlineStr">
         <is>
-          <t>Writes the motherboard FRU EEPROM from the SF-sourced FRU template (MBPN.csv), first syncing BMC time to host time.</t>
+          <t>Check the HPM retimer version</t>
         </is>
       </c>
       <c r="D17" s="40" t="inlineStr">
         <is>
-          <t>PASS when the FRU write completes without error. FAIL if function returns non-zero</t>
-        </is>
-      </c>
-      <c r="E17" s="40" t="inlineStr">
-        <is>
-          <t>Since QMF may involve L10 units requiring repair, replacement, or return, a function to re-flash the FRU has been added.</t>
-        </is>
-      </c>
+          <t>PASS if decoded version matches exactly.</t>
+        </is>
+      </c>
+      <c r="E17" s="40" t="n"/>
       <c r="F17" s="75" t="n"/>
       <c r="G17" s="55" t="b">
         <v>0</v>
@@ -6964,22 +6961,22 @@
       </c>
       <c r="B18" s="43" t="inlineStr">
         <is>
-          <t>bmc_sku_info_chk</t>
+          <t>storage_hdd_info_chk</t>
         </is>
       </c>
       <c r="C18" s="43" t="inlineStr">
         <is>
-          <t>Check BMC SKU JSON information to ensure correct versioning and system functionality. If a mismatch is detected, an automatic upgrade will be performed.</t>
+          <t>Enumerates all SATA+NVMe disks, maps each to its expected SF entry via PCIe mapping, and validates Model/Size/Firmware via tools/smartctl -i parsed with SmartCtlParser, with firmware auto-upgrade on mismatch.</t>
         </is>
       </c>
       <c r="D18" s="40" t="inlineStr">
         <is>
-          <t>Pass - match; Fail - mismatch</t>
+          <t>PASS if every disk's model, size, and firmware version match its mapped SF expectation (after any allowed firmware upgrade).</t>
         </is>
       </c>
       <c r="E18" s="40" t="inlineStr">
         <is>
-          <t>Version check M1 - Check only M3/M5 Check and upgrade at Pretest. Check only at the other stations</t>
+          <t>On a firmware mismatch with upgrade allowed, if the post-upgrade re-check still doesn't match, reboot and rerun after reboot to re-validate.</t>
         </is>
       </c>
       <c r="F18" s="75" t="n"/>
@@ -6994,23 +6991,23 @@
       <c r="K18" s="39" t="n"/>
       <c r="L18" s="51" t="n"/>
     </row>
-    <row r="19" ht="15" customFormat="1" customHeight="1" s="33">
+    <row r="19" ht="27" customFormat="1" customHeight="1" s="33">
       <c r="A19" s="76" t="n">
         <v>17</v>
       </c>
       <c r="B19" s="43" t="inlineStr">
         <is>
-          <t>bmc_retimer_fw_chk</t>
+          <t>bmc_psu_fw_chk</t>
         </is>
       </c>
       <c r="C19" s="43" t="inlineStr">
         <is>
-          <t>Check the HPM retimer version</t>
+          <t>Check the PSU version</t>
         </is>
       </c>
       <c r="D19" s="40" t="inlineStr">
         <is>
-          <t>PASS if decoded version matches exactly.</t>
+          <t>PASS if current version equals expected. On mismatch, if upgrade is allowed, attempts psu upgrade.</t>
         </is>
       </c>
       <c r="E19" s="40" t="n"/>
@@ -7032,22 +7029,22 @@
       </c>
       <c r="B20" s="43" t="inlineStr">
         <is>
-          <t>storage_hdd_info_chk</t>
+          <t>fpga_gp_cerberus_reharvest_chk</t>
         </is>
       </c>
       <c r="C20" s="43" t="inlineStr">
         <is>
-          <t>Enumerates all SATA+NVMe disks, maps each to its expected SF entry via PCIe mapping, and validates Model/Size/Firmware via tools/smartctl -i parsed with SmartCtlParser, with firmware auto-upgrade on mismatch.</t>
+          <t>Same re-harvest check pattern as the PCIe reharvest checks, but for the GlacierPeak Cerberus controller (uses self.pcie_tool rather than PCIE's own methods, since this lives in the FPGA engine class).</t>
         </is>
       </c>
       <c r="D20" s="40" t="inlineStr">
         <is>
-          <t>PASS if every disk's model, size, and firmware version match its mapped SF expectation (after any allowed firmware upgrade).</t>
+          <t>PASS when the public key matches or re-harvest succeeds. FAIL on pre-work hard error or upload_reharvest() failure.</t>
         </is>
       </c>
       <c r="E20" s="40" t="inlineStr">
         <is>
-          <t>On a firmware mismatch with upgrade allowed, if the post-upgrade re-check still doesn't match, reboot and rerun after reboot to re-validate.</t>
+          <t>A mismatch is not itself a failure, only a trigger for re-harvest.</t>
         </is>
       </c>
       <c r="F20" s="75" t="n"/>
@@ -7062,26 +7059,30 @@
       <c r="K20" s="39" t="n"/>
       <c r="L20" s="51" t="n"/>
     </row>
-    <row r="21" ht="27" customFormat="1" customHeight="1" s="33">
+    <row r="21" ht="40.5" customFormat="1" customHeight="1" s="33">
       <c r="A21" s="76" t="n">
         <v>19</v>
       </c>
       <c r="B21" s="43" t="inlineStr">
         <is>
-          <t>bmc_psu_fw_chk</t>
+          <t>pcie_manticore_reharvest_chk</t>
         </is>
       </c>
       <c r="C21" s="43" t="inlineStr">
         <is>
-          <t>Check the PSU version</t>
+          <t>Checks whether the DC-SCM Manticore controller's provisioned public key still matches the one on file (SF/HKMS), and re-harvests the CSR/certificate if it has drifted.</t>
         </is>
       </c>
       <c r="D21" s="40" t="inlineStr">
         <is>
-          <t>PASS if current version equals expected. On mismatch, if upgrade is allowed, attempts psu upgrade.</t>
-        </is>
-      </c>
-      <c r="E21" s="40" t="n"/>
+          <t>PASS when the public key matches (no re-harvest needed) or re-harvest completes successfully. FAIL if the pre-work step errors out (ret==1) or upload_reharvest() fails.</t>
+        </is>
+      </c>
+      <c r="E21" s="40" t="inlineStr">
+        <is>
+          <t>A mismatch is not itself a failure, only a trigger for re-harvest.</t>
+        </is>
+      </c>
       <c r="F21" s="75" t="n"/>
       <c r="G21" s="55" t="b">
         <v>0</v>
@@ -7100,12 +7101,12 @@
       </c>
       <c r="B22" s="43" t="inlineStr">
         <is>
-          <t>fpga_gp_cerberus_reharvest_chk</t>
+          <t>pcie_tip_reharvest_chk</t>
         </is>
       </c>
       <c r="C22" s="43" t="inlineStr">
         <is>
-          <t>Same re-harvest check pattern as the PCIe reharvest checks, but for the GlacierPeak Cerberus controller (uses self.pcie_tool rather than PCIE's own methods, since this lives in the FPGA engine class).</t>
+          <t>Checks whether the DC-SCM Hydra/TIP controller's provisioned public key still matches the one on file (SF/HKMS), and re-harvests the CSR/certificate if it has drifted.</t>
         </is>
       </c>
       <c r="D22" s="40" t="inlineStr">
@@ -7136,24 +7137,20 @@
       </c>
       <c r="B23" s="43" t="inlineStr">
         <is>
-          <t>pcie_manticore_reharvest_chk</t>
+          <t>tpm_ekey_chk</t>
         </is>
       </c>
       <c r="C23" s="43" t="inlineStr">
         <is>
-          <t>Checks whether the DC-SCM Manticore controller's provisioned public key still matches the one on file (SF/HKMS), and re-harvests the CSR/certificate if it has drifted.</t>
+          <t>Harvests the TPM's Endorsement Key (EK) certificate via tpm2_nvread, computes its SHA-256 hash, and compares against the expected TPMEKHASH value fetched from SF (or a local backup file when run with -no_sf).</t>
         </is>
       </c>
       <c r="D23" s="40" t="inlineStr">
         <is>
-          <t>PASS when the public key matches (no re-harvest needed) or re-harvest completes successfully. FAIL if the pre-work step errors out (ret==1) or upload_reharvest() fails.</t>
-        </is>
-      </c>
-      <c r="E23" s="40" t="inlineStr">
-        <is>
-          <t>A mismatch is not itself a failure, only a trigger for re-harvest.</t>
-        </is>
-      </c>
+          <t>PASS if the locally computed SHA-256 (base64) of the EK cert CSR equals the TPMEKHASH value from SF/backup.</t>
+        </is>
+      </c>
+      <c r="E23" s="40" t="n"/>
       <c r="F23" s="75" t="n"/>
       <c r="G23" s="55" t="b">
         <v>0</v>
@@ -7166,28 +7163,30 @@
       <c r="K23" s="39" t="n"/>
       <c r="L23" s="51" t="n"/>
     </row>
-    <row r="24" ht="40.5" customFormat="1" customHeight="1" s="33">
+    <row r="24" ht="135" customFormat="1" customHeight="1" s="33">
       <c r="A24" s="76" t="n">
         <v>22</v>
       </c>
       <c r="B24" s="43" t="inlineStr">
         <is>
-          <t>pcie_tip_reharvest_chk</t>
+          <t>pcie_manticore_provision</t>
         </is>
       </c>
       <c r="C24" s="43" t="inlineStr">
         <is>
-          <t>Checks whether the DC-SCM Hydra/TIP controller's provisioned public key still matches the one on file (SF/HKMS), and re-harvests the CSR/certificate if it has drifted.</t>
+          <t>One-time factory provisioning of the DC-SCM Manticore (Cerberus v2) security chip's certificate chain — Device ID, Root CA, and Intermediate CA certificates are fused into the chip via cerberus_utility importsignedcert.</t>
         </is>
       </c>
       <c r="D24" s="40" t="inlineStr">
         <is>
-          <t>PASS when the public key matches or re-harvest succeeds. FAIL on pre-work hard error or upload_reharvest() failure.</t>
+          <t>PASS if the chip already shows a complete signed certificate chain, or if all three cerberus_fuse() calls succeed and a post-fuse is_provision check confirms completion.</t>
         </is>
       </c>
       <c r="E24" s="40" t="inlineStr">
         <is>
-          <t>A mismatch is not itself a failure, only a trigger for re-harvest.</t>
+          <t>- Security/identity-relevant, one-time step. Uses is_provision("Manticore") to skip entirely if already provisioned (idempotent). If the public key harvested from the chip (CSR) doesn't match what SF (the factory server / key-management system) has on file, it is treated as a "re-harvest" condition.
+- Certificate fusing order is Device ID (HWKey1, cert index 0/file index 1) → Root CA (HWKey3, cert index 1/file index 3) → Intermediate CA (HWKey2, cert index 2/file index 2). 
+- cerberus_fuse() treats IPMI return code 74 ("Certificate provisioning locked") as a soft-success, not a failure, since re-fusing an already-locked slot is expected on retries.</t>
         </is>
       </c>
       <c r="F24" s="75" t="n"/>
@@ -7208,20 +7207,24 @@
       </c>
       <c r="B25" s="43" t="inlineStr">
         <is>
-          <t>tpm_ekey_chk</t>
+          <t>pcie_tip_provision</t>
         </is>
       </c>
       <c r="C25" s="43" t="inlineStr">
         <is>
-          <t>Harvests the TPM's Endorsement Key (EK) certificate via tpm2_nvread, computes its SHA-256 hash, and compares against the expected TPMEKHASH value fetched from SF (or a local backup file when run with -no_sf).</t>
+          <t>Same one-time provisioning flow as pcie_manticore_provision, but for the DC-SCM Hydra/TIP security chip (BMC-side security control introduced with M1120).</t>
         </is>
       </c>
       <c r="D25" s="40" t="inlineStr">
         <is>
-          <t>PASS if the locally computed SHA-256 (base64) of the EK cert CSR equals the TPMEKHASH value from SF/backup.</t>
-        </is>
-      </c>
-      <c r="E25" s="40" t="n"/>
+          <t>Identical logic/criteria to pcie_manticore_provision, keyed on component name "Hydra".</t>
+        </is>
+      </c>
+      <c r="E25" s="40" t="inlineStr">
+        <is>
+          <t>Security/identity-relevant, one-time step. Structurally identical to Manticore provisioning, same 3-cert fuse order Device ID → Root CA → Intermediate CA).</t>
+        </is>
+      </c>
       <c r="F25" s="75" t="n"/>
       <c r="G25" s="55" t="b">
         <v>0</v>
@@ -7240,167 +7243,27 @@
       </c>
       <c r="B26" s="82" t="inlineStr">
         <is>
-          <t>rm_powershelf_fw_chk</t>
+          <t>pcie_tip_pcd_chk</t>
         </is>
       </c>
       <c r="C26" s="82" t="inlineStr">
         <is>
-          <t>Check the PSU firmware version on the power shelf via RM for the current UUT. This function only performs the check on master nodes.</t>
+          <t>BMC TIP - PCD ID and platform check</t>
         </is>
       </c>
       <c r="D26" s="83" t="inlineStr">
         <is>
-          <t>- Pass:
-- UUT is a master node.
-- All PSU serial numbers, manufacturers, and firmware versions match expected values.
-- Fail
-- Unable to get RM IP.
-- PSU information cannot be retrieved or parsed.
-- PSU not found in the expected list.
-- Firmware version mismatch and auto-upgrade fails.</t>
+          <t>Pass - return 0; Fail - return 1</t>
         </is>
       </c>
       <c r="E26" s="83" t="inlineStr">
-        <is>
-          <t>- Only master nodes will perform the check.
-- Only master nodes in pretest station will perform the upgrade if mismatch
-- Location format: {RM_location}-{RM_port}-{UUT_location}-{BMC} (e.g., U26-6-U9-BMC0)
-(Master Only)</t>
-        </is>
-      </c>
-      <c r="F26" s="84" t="inlineStr">
-        <is>
-          <t>[Check powershelf firmware version]
-show powershelf psu info -s {INDEX}
-Capability
--        IC Device ID
--        Manufacturer ID
--        Manufacturer Model
--        Manufacturer Revision
--        Manufacturer Serial
--        Completion Code
-- - - - -  If mismatch - - - - -
-[Upgrade PSU firmware version]
-Check fw package exists in RM:
--        show manager tftp list
-Upload fw to Rack-SCM
--        set manager tftp get -s {IP} -f {FILE}
-Fw Upgrade
--       rm_psu_upgrade = set powershelf psu update -s {INDEX} -f {FILE}</t>
-        </is>
-      </c>
-      <c r="G26" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="H26" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="I26" s="84" t="n"/>
-      <c r="J26" s="84" t="n"/>
-      <c r="K26" s="85" t="n"/>
-      <c r="L26" s="86" t="n"/>
-    </row>
-    <row r="27" ht="135" customFormat="1" customHeight="1" s="33">
-      <c r="A27" s="76" t="n">
-        <v>25</v>
-      </c>
-      <c r="B27" s="43" t="inlineStr">
-        <is>
-          <t>pcie_manticore_provision</t>
-        </is>
-      </c>
-      <c r="C27" s="43" t="inlineStr">
-        <is>
-          <t>One-time factory provisioning of the DC-SCM Manticore (Cerberus v2) security chip's certificate chain — Device ID, Root CA, and Intermediate CA certificates are fused into the chip via cerberus_utility importsignedcert.</t>
-        </is>
-      </c>
-      <c r="D27" s="40" t="inlineStr">
-        <is>
-          <t>PASS if the chip already shows a complete signed certificate chain, or if all three cerberus_fuse() calls succeed and a post-fuse is_provision check confirms completion.</t>
-        </is>
-      </c>
-      <c r="E27" s="40" t="inlineStr">
-        <is>
-          <t>- Security/identity-relevant, one-time step. Uses is_provision("Manticore") to skip entirely if already provisioned (idempotent). If the public key harvested from the chip (CSR) doesn't match what SF (the factory server / key-management system) has on file, it is treated as a "re-harvest" condition.
-- Certificate fusing order is Device ID (HWKey1, cert index 0/file index 1) → Root CA (HWKey3, cert index 1/file index 3) → Intermediate CA (HWKey2, cert index 2/file index 2). 
-- cerberus_fuse() treats IPMI return code 74 ("Certificate provisioning locked") as a soft-success, not a failure, since re-fusing an already-locked slot is expected on retries.</t>
-        </is>
-      </c>
-      <c r="F27" s="75" t="n"/>
-      <c r="G27" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="H27" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="I27" s="55" t="n"/>
-      <c r="J27" s="55" t="n"/>
-      <c r="K27" s="39" t="n"/>
-      <c r="L27" s="51" t="n"/>
-    </row>
-    <row r="28" ht="40.5" customFormat="1" customHeight="1" s="33">
-      <c r="A28" s="76" t="n">
-        <v>26</v>
-      </c>
-      <c r="B28" s="43" t="inlineStr">
-        <is>
-          <t>pcie_tip_provision</t>
-        </is>
-      </c>
-      <c r="C28" s="43" t="inlineStr">
-        <is>
-          <t>Same one-time provisioning flow as pcie_manticore_provision, but for the DC-SCM Hydra/TIP security chip (BMC-side security control introduced with M1120).</t>
-        </is>
-      </c>
-      <c r="D28" s="40" t="inlineStr">
-        <is>
-          <t>Identical logic/criteria to pcie_manticore_provision, keyed on component name "Hydra".</t>
-        </is>
-      </c>
-      <c r="E28" s="40" t="inlineStr">
-        <is>
-          <t>Security/identity-relevant, one-time step. Structurally identical to Manticore provisioning, same 3-cert fuse order Device ID → Root CA → Intermediate CA).</t>
-        </is>
-      </c>
-      <c r="F28" s="75" t="n"/>
-      <c r="G28" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="H28" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="I28" s="55" t="n"/>
-      <c r="J28" s="55" t="n"/>
-      <c r="K28" s="39" t="n"/>
-      <c r="L28" s="51" t="n"/>
-    </row>
-    <row r="29" customFormat="1" s="33">
-      <c r="A29" s="81" t="n">
-        <v>27</v>
-      </c>
-      <c r="B29" s="82" t="inlineStr">
-        <is>
-          <t>pcie_tip_pcd_chk</t>
-        </is>
-      </c>
-      <c r="C29" s="82" t="inlineStr">
-        <is>
-          <t>BMC TIP - PCD ID and platform check</t>
-        </is>
-      </c>
-      <c r="D29" s="83" t="inlineStr">
-        <is>
-          <t>Pass - return 0; Fail - return 1</t>
-        </is>
-      </c>
-      <c r="E29" s="83" t="inlineStr">
         <is>
           <t>&gt;&gt;&gt; EV CRD does not define it.
 &gt;&gt;&gt; Remove grey remark for pcie_tip_pcd_chk and pcie_tip_cfm_chk since those need to be reay in DV.  However, no CFM/PCD function at this moment.  Create bug in advance during DV M1/M3 Diag dev. and validation.
 &gt;&gt;&gt;Task #2568301</t>
         </is>
       </c>
-      <c r="F29" s="84" t="inlineStr">
+      <c r="F26" s="84" t="inlineStr">
         <is>
           <t>[Check PCD Version ID]
 {CERBERUS_UTILITY} -e 0x0c pcdid 0
@@ -7414,44 +7277,44 @@
 ipmitool mc reset cold</t>
         </is>
       </c>
-      <c r="G29" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="H29" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="I29" s="84" t="n"/>
-      <c r="J29" s="84" t="n"/>
-      <c r="K29" s="85" t="n"/>
-      <c r="L29" s="86" t="n"/>
-    </row>
-    <row r="30" customFormat="1" s="33">
-      <c r="A30" s="81" t="n">
-        <v>28</v>
-      </c>
-      <c r="B30" s="82" t="inlineStr">
+      <c r="G26" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="H26" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="I26" s="84" t="n"/>
+      <c r="J26" s="84" t="n"/>
+      <c r="K26" s="85" t="n"/>
+      <c r="L26" s="86" t="n"/>
+    </row>
+    <row r="27" customFormat="1" s="33">
+      <c r="A27" s="81" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" s="82" t="inlineStr">
         <is>
           <t>pcie_tip_cfm_chk</t>
         </is>
       </c>
-      <c r="C30" s="82" t="inlineStr">
+      <c r="C27" s="82" t="inlineStr">
         <is>
           <t>Get DC-SCM TIP Version ID and Platform ID</t>
         </is>
       </c>
-      <c r="D30" s="83" t="inlineStr">
+      <c r="D27" s="83" t="inlineStr">
         <is>
           <t>Pass - return 0; Fail - return 1</t>
         </is>
       </c>
-      <c r="E30" s="83" t="inlineStr">
+      <c r="E27" s="83" t="inlineStr">
         <is>
           <t>&gt;&gt;&gt; EV CRD does not define it.
 &gt;&gt;&gt; Remove grey remark for pcie_tip_pcd_chk and pcie_tip_cfm_chk since those need to be reay in DV.  However, no CFM/PCD function at this moment.  Create bug in advance during DV M1/M3 Diag dev. and validation.
 &gt;&gt;&gt;Task #2568301</t>
         </is>
       </c>
-      <c r="F30" s="84" t="inlineStr">
+      <c r="F27" s="84" t="inlineStr">
         <is>
           <t>[Check CFM Version ID]
 {CERBERUS_UTILITY} -e 0x0c cfmid 0 0
@@ -7467,75 +7330,75 @@
 {CERBERUS_UTILITY} -e 0x0c compstate</t>
         </is>
       </c>
-      <c r="G30" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="H30" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="I30" s="84" t="n"/>
-      <c r="J30" s="84" t="n"/>
-      <c r="K30" s="85" t="n"/>
-      <c r="L30" s="86" t="n"/>
-    </row>
-    <row r="31" ht="135" customFormat="1" customHeight="1" s="33">
-      <c r="A31" s="76" t="n">
-        <v>29</v>
-      </c>
-      <c r="B31" s="43" t="inlineStr">
+      <c r="G27" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="H27" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="I27" s="84" t="n"/>
+      <c r="J27" s="84" t="n"/>
+      <c r="K27" s="85" t="n"/>
+      <c r="L27" s="86" t="n"/>
+    </row>
+    <row r="28" ht="135" customFormat="1" customHeight="1" s="33">
+      <c r="A28" s="76" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" s="43" t="inlineStr">
         <is>
           <t>fpga_gp_cerberus_provision</t>
         </is>
       </c>
-      <c r="C31" s="43" t="inlineStr">
+      <c r="C28" s="43" t="inlineStr">
         <is>
           <t>One-time provisioning of the GlacierPeak's own Cerberus security chip (distinct from Agilex slots above) — fuses Device ID/Root CA/Intermediate CA certs via a UART/SSH session directly into the GlacierPeak SoC console.</t>
         </is>
       </c>
-      <c r="D31" s="40" t="inlineStr">
+      <c r="D28" s="40" t="inlineStr">
         <is>
           <t>PASS if pcie_tool.is_provision("Cerberus") already shows complete, or if all three certs are fused successfully and a post-check confirms completion.</t>
         </is>
       </c>
-      <c r="E31" s="40" t="inlineStr">
+      <c r="E28" s="40" t="inlineStr">
         <is>
           <t>Two very different code paths: 
 - for prj_stage == "M5" it SFTP-uploads the three HWKEY .bin files to the BMC, then uses a shell command list over usb0 (10.235.100.0/31 point-to-point link) with scp -P 2200 to pull each key onto the GlacierPeak SoC and run cerberus_utility importsignedcert locally there — all three fuse commands (root CA idx 1, intermediate idx 2, device ID idx 0) run under a single rm_lock.
 - For other stages it uses a raw pxssh session direct to the GlacierPeak SoC on port 8295 (user admin/admin), with up to 2 retries and a 90s backoff between attempts if the SoC is "busy". HWKey files are deleted from the BMC after fusing in both paths.</t>
         </is>
       </c>
-      <c r="F31" s="75" t="n"/>
-      <c r="G31" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="H31" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="I31" s="55" t="n"/>
-      <c r="J31" s="55" t="n"/>
-      <c r="K31" s="39" t="n"/>
-      <c r="L31" s="51" t="n"/>
-    </row>
-    <row r="32" ht="121.5" customFormat="1" customHeight="1" s="33">
-      <c r="A32" s="76" t="n">
-        <v>30</v>
-      </c>
-      <c r="B32" s="43" t="inlineStr">
+      <c r="F28" s="75" t="n"/>
+      <c r="G28" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="H28" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="I28" s="55" t="n"/>
+      <c r="J28" s="55" t="n"/>
+      <c r="K28" s="39" t="n"/>
+      <c r="L28" s="51" t="n"/>
+    </row>
+    <row r="29" ht="121.5" customFormat="1" customHeight="1" s="33">
+      <c r="A29" s="76" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" s="43" t="inlineStr">
         <is>
           <t>fpga_gp_agilex_provision</t>
         </is>
       </c>
-      <c r="C32" s="43" t="inlineStr">
+      <c r="C29" s="43" t="inlineStr">
         <is>
           <t>One-time provisioning of the GlacierPeak Agilex FPGA's two certificate slots via the fpgasec tool — slot 0 for "Intel IPCS" (Agilex_mfg) and slot 1 for "Microsoft" (Agilex_msft), each independently skippable if already provisioned.</t>
         </is>
       </c>
-      <c r="D32" s="40" t="inlineStr">
+      <c r="D29" s="40" t="inlineStr">
         <is>
           <t>PASS if both slot0 and slot1 report provisioned after the flow (checked via _is_gp_agilex_provision). FAIL if the fpgasec_{ver} tool is missing, cert files can't be obtained/uploaded, -setCertificate fails, or the final status check still shows either slot unprovisioned.</t>
         </is>
       </c>
-      <c r="E32" s="40" t="inlineStr">
+      <c r="E29" s="40" t="inlineStr">
         <is>
           <t>- Security/identity-relevant, one-time step, M3-only. 
 - Unlike the Manticore/TIP flow this checks each slot independently — a partially-provisioned board (e.g. slot0 done, slot1 not) only provisions the missing slot. 
@@ -7544,6 +7407,102 @@
 - After both slots are set, it resets the FPGA and sleeps 300s before the final confirmation check.</t>
         </is>
       </c>
+      <c r="F29" s="75" t="n"/>
+      <c r="G29" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="H29" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="I29" s="55" t="n"/>
+      <c r="J29" s="55" t="n"/>
+      <c r="K29" s="39" t="n"/>
+      <c r="L29" s="51" t="n"/>
+    </row>
+    <row r="30" ht="40.5" customFormat="1" customHeight="1" s="33">
+      <c r="A30" s="76" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" s="43" t="inlineStr">
+        <is>
+          <t>uut_ac_cycle</t>
+        </is>
+      </c>
+      <c r="C30" s="43" t="inlineStr">
+        <is>
+          <t>AC power-cycle using an OEM raw IPMI command (rather than a standard power-control command)</t>
+        </is>
+      </c>
+      <c r="D30" s="40" t="inlineStr">
+        <is>
+          <t>PASS if the AC power-cycle execute successfully.</t>
+        </is>
+      </c>
+      <c r="E30" s="40" t="inlineStr">
+        <is>
+          <t>If a FW update is performed and an AC power cycle is required for the update to take effect, this test item will be triggered. Otherwise, this test item will be skipped.</t>
+        </is>
+      </c>
+      <c r="F30" s="75" t="n"/>
+      <c r="G30" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="H30" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="I30" s="55" t="n"/>
+      <c r="J30" s="55" t="n"/>
+      <c r="K30" s="39" t="n"/>
+      <c r="L30" s="51" t="n"/>
+    </row>
+    <row r="31" ht="15" customFormat="1" customHeight="1" s="33">
+      <c r="A31" s="76" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" s="43" t="inlineStr">
+        <is>
+          <t>ccr_switch_chk</t>
+        </is>
+      </c>
+      <c r="C31" s="43" t="inlineStr">
+        <is>
+          <t>Check and show switch config</t>
+        </is>
+      </c>
+      <c r="D31" s="40" t="inlineStr">
+        <is>
+          <t>Pass - return 0; Fail - return 1</t>
+        </is>
+      </c>
+      <c r="E31" s="40" t="inlineStr">
+        <is>
+          <t>only applies to the master blade</t>
+        </is>
+      </c>
+      <c r="F31" s="75" t="n"/>
+      <c r="G31" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="H31" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="I31" s="55" t="n"/>
+      <c r="J31" s="55" t="n"/>
+      <c r="K31" s="39" t="n"/>
+      <c r="L31" s="51" t="n"/>
+    </row>
+    <row r="32" ht="15" customFormat="1" customHeight="1" s="33">
+      <c r="A32" s="76" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" s="43" t="inlineStr">
+        <is>
+          <t>set_ssd_spf_mode</t>
+        </is>
+      </c>
+      <c r="C32" s="43" t="n"/>
+      <c r="D32" s="40" t="n"/>
+      <c r="E32" s="40" t="n"/>
       <c r="F32" s="75" t="n"/>
       <c r="G32" s="55" t="b">
         <v>0</v>
@@ -7556,28 +7515,28 @@
       <c r="K32" s="39" t="n"/>
       <c r="L32" s="51" t="n"/>
     </row>
-    <row r="33" ht="40.5" customFormat="1" customHeight="1" s="33">
+    <row r="33" ht="27" customFormat="1" customHeight="1" s="33">
       <c r="A33" s="76" t="n">
         <v>31</v>
       </c>
       <c r="B33" s="43" t="inlineStr">
         <is>
-          <t>uut_ac_cycle</t>
+          <t>bmc_sel_clear</t>
         </is>
       </c>
       <c r="C33" s="43" t="inlineStr">
         <is>
-          <t>AC power-cycle using an OEM raw IPMI command (rather than a standard power-control command)</t>
+          <t>Clear BMC System Event Log (SEL) and verify it is cleared correctly.</t>
         </is>
       </c>
       <c r="D33" s="40" t="inlineStr">
         <is>
-          <t>PASS if the AC power-cycle execute successfully.</t>
+          <t>SEL clear command executes successfully and log ID changes after clear.</t>
         </is>
       </c>
       <c r="E33" s="40" t="inlineStr">
         <is>
-          <t>If a FW update is performed and an AC power cycle is required for the update to take effect, this test item will be triggered. Otherwise, this test item will be skipped.</t>
+          <t>Logs SEL before clearing for traceability; verifies clear status by comparing log ID.</t>
         </is>
       </c>
       <c r="F33" s="75" t="n"/>
@@ -7592,54 +7551,72 @@
       <c r="K33" s="39" t="n"/>
       <c r="L33" s="51" t="n"/>
     </row>
-    <row r="34" ht="15" customFormat="1" customHeight="1" s="33">
-      <c r="A34" s="76" t="n">
+    <row r="34" customFormat="1" s="33">
+      <c r="A34" s="81" t="n">
         <v>32</v>
       </c>
-      <c r="B34" s="43" t="inlineStr">
-        <is>
-          <t>ccr_switch_chk</t>
-        </is>
-      </c>
-      <c r="C34" s="43" t="inlineStr">
-        <is>
-          <t>Check and show switch config</t>
-        </is>
-      </c>
-      <c r="D34" s="40" t="inlineStr">
-        <is>
-          <t>Pass - return 0; Fail - return 1</t>
-        </is>
-      </c>
-      <c r="E34" s="40" t="inlineStr">
-        <is>
-          <t>only applies to the master blade</t>
-        </is>
-      </c>
-      <c r="F34" s="75" t="n"/>
-      <c r="G34" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="H34" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="I34" s="55" t="n"/>
-      <c r="J34" s="55" t="n"/>
-      <c r="K34" s="39" t="n"/>
-      <c r="L34" s="51" t="n"/>
-    </row>
-    <row r="35" ht="15" customFormat="1" customHeight="1" s="33">
+      <c r="B34" s="82" t="inlineStr">
+        <is>
+          <t>bmc_boot_sel_check</t>
+        </is>
+      </c>
+      <c r="C34" s="82" t="inlineStr">
+        <is>
+          <t>Verify BMC SEL after UUT boot (System Event Log) events during testing to ensure no unexpected events have occurred.</t>
+        </is>
+      </c>
+      <c r="D34" s="83" t="inlineStr">
+        <is>
+          <t>SEL event counts should not exceed the defined thresholds based on testing duration.</t>
+        </is>
+      </c>
+      <c r="E34" s="83" t="inlineStr">
+        <is>
+          <t>Fail log will be saved in project folder if abnormal events are detected.</t>
+        </is>
+      </c>
+      <c r="F34" s="84" t="inlineStr">
+        <is>
+          <t>[Get BMC SEL Log]
+CMD: ipmitool sel elist -v &gt; sel.log
+Parse the sel.log and compare with allowed list</t>
+        </is>
+      </c>
+      <c r="G34" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="H34" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="I34" s="84" t="n"/>
+      <c r="J34" s="84" t="n"/>
+      <c r="K34" s="85" t="n"/>
+      <c r="L34" s="86" t="n"/>
+    </row>
+    <row r="35" ht="27" customFormat="1" customHeight="1" s="33">
       <c r="A35" s="76" t="n">
         <v>33</v>
       </c>
       <c r="B35" s="43" t="inlineStr">
         <is>
-          <t>set_ssd_spf_mode</t>
-        </is>
-      </c>
-      <c r="C35" s="43" t="n"/>
-      <c r="D35" s="40" t="n"/>
-      <c r="E35" s="40" t="n"/>
+          <t>bmc_sdr_chk</t>
+        </is>
+      </c>
+      <c r="C35" s="43" t="inlineStr">
+        <is>
+          <t>Verify BMC Sensor Data Records (SDR) by checking sensor list output and filtering unexpected entries.</t>
+        </is>
+      </c>
+      <c r="D35" s="40" t="inlineStr">
+        <is>
+          <t>No unexpected or unmasked SDR entries found in BMCSDR.log.</t>
+        </is>
+      </c>
+      <c r="E35" s="40" t="inlineStr">
+        <is>
+          <t>Test fails if filtered output is not empty.</t>
+        </is>
+      </c>
       <c r="F35" s="75" t="n"/>
       <c r="G35" s="55" t="b">
         <v>0</v>
@@ -7658,22 +7635,22 @@
       </c>
       <c r="B36" s="43" t="inlineStr">
         <is>
-          <t>bmc_sel_clear</t>
+          <t>uut_dmesg_chk</t>
         </is>
       </c>
       <c r="C36" s="43" t="inlineStr">
         <is>
-          <t>Clear BMC System Event Log (SEL) and verify it is cleared correctly.</t>
+          <t>Check UUT dmesg log for unexpected error messages and record PCI device status.</t>
         </is>
       </c>
       <c r="D36" s="40" t="inlineStr">
         <is>
-          <t>SEL clear command executes successfully and log ID changes after clear.</t>
+          <t>No unmasked error messages found in dmesg and all expected messages are properly filtered.</t>
         </is>
       </c>
       <c r="E36" s="40" t="inlineStr">
         <is>
-          <t>Logs SEL before clearing for traceability; verifies clear status by comparing log ID.</t>
+          <t>Filter list (filter_list.csv) and error map (err_map.ini) are required for filtering and mapping errors.</t>
         </is>
       </c>
       <c r="F36" s="75" t="n"/>
@@ -7688,70 +7665,60 @@
       <c r="K36" s="39" t="n"/>
       <c r="L36" s="51" t="n"/>
     </row>
-    <row r="37" customFormat="1" s="33">
-      <c r="A37" s="81" t="n">
+    <row r="37" ht="27" customFormat="1" customHeight="1" s="33">
+      <c r="A37" s="76" t="n">
         <v>35</v>
       </c>
-      <c r="B37" s="82" t="inlineStr">
-        <is>
-          <t>bmc_boot_sel_check</t>
-        </is>
-      </c>
-      <c r="C37" s="82" t="inlineStr">
-        <is>
-          <t>Verify BMC SEL after UUT boot (System Event Log) events during testing to ensure no unexpected events have occurred.</t>
-        </is>
-      </c>
-      <c r="D37" s="83" t="inlineStr">
-        <is>
-          <t>SEL event counts should not exceed the defined thresholds based on testing duration.</t>
-        </is>
-      </c>
-      <c r="E37" s="83" t="inlineStr">
-        <is>
-          <t>Fail log will be saved in project folder if abnormal events are detected.</t>
-        </is>
-      </c>
-      <c r="F37" s="84" t="inlineStr">
-        <is>
-          <t>[Get BMC SEL Log]
-CMD: ipmitool sel elist -v &gt; sel.log
-Parse the sel.log and compare with allowed list</t>
-        </is>
-      </c>
-      <c r="G37" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="H37" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="I37" s="84" t="n"/>
-      <c r="J37" s="84" t="n"/>
-      <c r="K37" s="85" t="n"/>
-      <c r="L37" s="86" t="n"/>
-    </row>
-    <row r="38" ht="27" customFormat="1" customHeight="1" s="33">
+      <c r="B37" s="43" t="inlineStr">
+        <is>
+          <t>uut_syslog_chk</t>
+        </is>
+      </c>
+      <c r="C37" s="43" t="inlineStr">
+        <is>
+          <t>Check and record UUT system log (syslog/messages) to ensure no unexpected errors.</t>
+        </is>
+      </c>
+      <c r="D37" s="40" t="inlineStr">
+        <is>
+          <t>UUT syslog must not contain unmasked error patterns, excluding skip patterns. Log file must exist and contain no unfiltered critical errors.</t>
+        </is>
+      </c>
+      <c r="E37" s="40" t="n"/>
+      <c r="F37" s="75" t="n"/>
+      <c r="G37" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="H37" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="I37" s="55" t="n"/>
+      <c r="J37" s="55" t="n"/>
+      <c r="K37" s="39" t="n"/>
+      <c r="L37" s="51" t="n"/>
+    </row>
+    <row r="38" ht="40.5" customFormat="1" customHeight="1" s="33">
       <c r="A38" s="76" t="n">
         <v>36</v>
       </c>
       <c r="B38" s="43" t="inlineStr">
         <is>
-          <t>bmc_sdr_chk</t>
+          <t>rm_fru_chk</t>
         </is>
       </c>
       <c r="C38" s="43" t="inlineStr">
         <is>
-          <t>Verify BMC Sensor Data Records (SDR) by checking sensor list output and filtering unexpected entries.</t>
+          <t>Check RM FRU information</t>
         </is>
       </c>
       <c r="D38" s="40" t="inlineStr">
         <is>
-          <t>No unexpected or unmasked SDR entries found in BMCSDR.log.</t>
+          <t>Pass Successfully retrieves the FRU data and the Product Serial Number matches the expected value from config. Fail Unable to retrieve FRU data or serial number does not match.</t>
         </is>
       </c>
       <c r="E38" s="40" t="inlineStr">
         <is>
-          <t>Test fails if filtered output is not empty.</t>
+          <t>only applies to the master blade</t>
         </is>
       </c>
       <c r="F38" s="75" t="n"/>
@@ -7766,28 +7733,20 @@
       <c r="K38" s="39" t="n"/>
       <c r="L38" s="51" t="n"/>
     </row>
-    <row r="39" ht="27" customFormat="1" customHeight="1" s="33">
+    <row r="39" ht="15" customFormat="1" customHeight="1" s="33">
       <c r="A39" s="76" t="n">
         <v>37</v>
       </c>
       <c r="B39" s="43" t="inlineStr">
         <is>
-          <t>uut_dmesg_chk</t>
-        </is>
-      </c>
-      <c r="C39" s="43" t="inlineStr">
-        <is>
-          <t>Check UUT dmesg log for unexpected error messages and record PCI device status.</t>
-        </is>
-      </c>
-      <c r="D39" s="40" t="inlineStr">
-        <is>
-          <t>No unmasked error messages found in dmesg and all expected messages are properly filtered.</t>
-        </is>
-      </c>
+          <t>rm_pmdu_fru_chk</t>
+        </is>
+      </c>
+      <c r="C39" s="43" t="n"/>
+      <c r="D39" s="40" t="n"/>
       <c r="E39" s="40" t="inlineStr">
         <is>
-          <t>Filter list (filter_list.csv) and error map (err_map.ini) are required for filtering and mapping errors.</t>
+          <t>only applies to the master blade</t>
         </is>
       </c>
       <c r="F39" s="75" t="n"/>
@@ -7802,26 +7761,22 @@
       <c r="K39" s="39" t="n"/>
       <c r="L39" s="51" t="n"/>
     </row>
-    <row r="40" ht="27" customFormat="1" customHeight="1" s="33">
+    <row r="40" ht="15" customFormat="1" customHeight="1" s="33">
       <c r="A40" s="76" t="n">
         <v>38</v>
       </c>
       <c r="B40" s="43" t="inlineStr">
         <is>
-          <t>uut_syslog_chk</t>
-        </is>
-      </c>
-      <c r="C40" s="43" t="inlineStr">
-        <is>
-          <t>Check and record UUT system log (syslog/messages) to ensure no unexpected errors.</t>
-        </is>
-      </c>
-      <c r="D40" s="40" t="inlineStr">
-        <is>
-          <t>UUT syslog must not contain unmasked error patterns, excluding skip patterns. Log file must exist and contain no unfiltered critical errors.</t>
-        </is>
-      </c>
-      <c r="E40" s="40" t="n"/>
+          <t>rm_acdc_fru_chk</t>
+        </is>
+      </c>
+      <c r="C40" s="43" t="n"/>
+      <c r="D40" s="40" t="n"/>
+      <c r="E40" s="40" t="inlineStr">
+        <is>
+          <t>only applies to the master blade</t>
+        </is>
+      </c>
       <c r="F40" s="75" t="n"/>
       <c r="G40" s="55" t="b">
         <v>0</v>
@@ -7834,30 +7789,26 @@
       <c r="K40" s="39" t="n"/>
       <c r="L40" s="51" t="n"/>
     </row>
-    <row r="41" ht="40.5" customFormat="1" customHeight="1" s="33">
+    <row r="41" ht="15" customFormat="1" customHeight="1" s="33">
       <c r="A41" s="76" t="n">
         <v>39</v>
       </c>
       <c r="B41" s="43" t="inlineStr">
         <is>
-          <t>rm_fru_chk</t>
+          <t>rm_sys_fru_chk</t>
         </is>
       </c>
       <c r="C41" s="43" t="inlineStr">
         <is>
-          <t>Check RM FRU information</t>
+          <t>Check System FRU via RM</t>
         </is>
       </c>
       <c r="D41" s="40" t="inlineStr">
         <is>
-          <t>Pass Successfully retrieves the FRU data and the Product Serial Number matches the expected value from config. Fail Unable to retrieve FRU data or serial number does not match.</t>
-        </is>
-      </c>
-      <c r="E41" s="40" t="inlineStr">
-        <is>
-          <t>only applies to the master blade</t>
-        </is>
-      </c>
+          <t>Pass - return 0; Fail - return 1</t>
+        </is>
+      </c>
+      <c r="E41" s="40" t="n"/>
       <c r="F41" s="75" t="n"/>
       <c r="G41" s="55" t="b">
         <v>0</v>
@@ -7876,14 +7827,22 @@
       </c>
       <c r="B42" s="43" t="inlineStr">
         <is>
-          <t>rm_pmdu_fru_chk</t>
-        </is>
-      </c>
-      <c r="C42" s="43" t="n"/>
-      <c r="D42" s="40" t="n"/>
+          <t>rm_scm_fru_chk</t>
+        </is>
+      </c>
+      <c r="C42" s="43" t="inlineStr">
+        <is>
+          <t>Check DC-SCM(M1120) FRU via RM</t>
+        </is>
+      </c>
+      <c r="D42" s="40" t="inlineStr">
+        <is>
+          <t>Pass - return 0; Fail - return 1</t>
+        </is>
+      </c>
       <c r="E42" s="40" t="inlineStr">
         <is>
-          <t>only applies to the master blade</t>
+          <t>Check b oard s erial n umber</t>
         </is>
       </c>
       <c r="F42" s="75" t="n"/>
@@ -7904,14 +7863,22 @@
       </c>
       <c r="B43" s="43" t="inlineStr">
         <is>
-          <t>rm_acdc_fru_chk</t>
-        </is>
-      </c>
-      <c r="C43" s="43" t="n"/>
-      <c r="D43" s="40" t="n"/>
+          <t>rm_gp_fru_chk</t>
+        </is>
+      </c>
+      <c r="C43" s="43" t="inlineStr">
+        <is>
+          <t>Check GlacierPeak FRU via RM</t>
+        </is>
+      </c>
+      <c r="D43" s="40" t="inlineStr">
+        <is>
+          <t>Pass - return 0; Fail - return 1</t>
+        </is>
+      </c>
       <c r="E43" s="40" t="inlineStr">
         <is>
-          <t>only applies to the master blade</t>
+          <t>Check b oard s erial n umber</t>
         </is>
       </c>
       <c r="F43" s="75" t="n"/>
@@ -7926,26 +7893,29 @@
       <c r="K43" s="39" t="n"/>
       <c r="L43" s="51" t="n"/>
     </row>
-    <row r="44" ht="15" customFormat="1" customHeight="1" s="33">
+    <row r="44" ht="53.25" customFormat="1" customHeight="1" s="33">
       <c r="A44" s="76" t="n">
         <v>42</v>
       </c>
       <c r="B44" s="43" t="inlineStr">
         <is>
-          <t>rm_sys_fru_chk</t>
+          <t>rm_relay_port_chk</t>
         </is>
       </c>
       <c r="C44" s="43" t="inlineStr">
         <is>
-          <t>Check System FRU via RM</t>
-        </is>
-      </c>
-      <c r="D44" s="40" t="inlineStr">
-        <is>
-          <t>Pass - return 0; Fail - return 1</t>
-        </is>
-      </c>
-      <c r="E44" s="40" t="n"/>
+          <t>need to verify the status of the Relay Port Status - ON. Take CAUTION with turning ON state– delay for 20 second – then OFF state of the RELAY and OFF state – 20 seconds delay – ON state.</t>
+        </is>
+      </c>
+      <c r="D44" s="40" t="n"/>
+      <c r="E44" s="40" t="inlineStr">
+        <is>
+          <t>only applies to the master blade
+Feed1powerstatus = healthy
+Feed2powerstatus = healthy
+powerdrawninwatt &lt; maxpowerinwatts</t>
+        </is>
+      </c>
       <c r="F44" s="75" t="n"/>
       <c r="G44" s="55" t="b">
         <v>0</v>
@@ -7964,22 +7934,14 @@
       </c>
       <c r="B45" s="43" t="inlineStr">
         <is>
-          <t>rm_scm_fru_chk</t>
-        </is>
-      </c>
-      <c r="C45" s="43" t="inlineStr">
-        <is>
-          <t>Check DC-SCM(M1120) FRU via RM</t>
-        </is>
-      </c>
-      <c r="D45" s="40" t="inlineStr">
-        <is>
-          <t>Pass - return 0; Fail - return 1</t>
-        </is>
-      </c>
+          <t>rm_power_reading_chk</t>
+        </is>
+      </c>
+      <c r="C45" s="43" t="n"/>
+      <c r="D45" s="40" t="n"/>
       <c r="E45" s="40" t="inlineStr">
         <is>
-          <t>Check b oard s erial n umber</t>
+          <t>only applies to the master blade</t>
         </is>
       </c>
       <c r="F45" s="75" t="n"/>
@@ -7994,28 +7956,28 @@
       <c r="K45" s="39" t="n"/>
       <c r="L45" s="51" t="n"/>
     </row>
-    <row r="46" ht="15" customFormat="1" customHeight="1" s="33">
+    <row r="46" ht="67.5" customFormat="1" customHeight="1" s="33">
       <c r="A46" s="76" t="n">
         <v>44</v>
       </c>
       <c r="B46" s="43" t="inlineStr">
         <is>
-          <t>rm_gp_fru_chk</t>
+          <t>rm_power_capping_check</t>
         </is>
       </c>
       <c r="C46" s="43" t="inlineStr">
         <is>
-          <t>Check GlacierPeak FRU via RM</t>
+          <t>Validates RM rack-level power capping behavior, including: - DCMI-based static power limit control - PSU alert-triggered throttling (SM_ALERT)</t>
         </is>
       </c>
       <c r="D46" s="40" t="inlineStr">
         <is>
-          <t>Pass - return 0; Fail - return 1</t>
+          <t>- PASS when ALL are true: - Power limit successfully applied &amp; activated - System load is capped within expected power window (± tolerance) - After removing the cap → system power rebounds above limit - PSU alert scenario triggers throttling and later fully recovers (no SM_ALERT still active) - BMC SEL log contains no unexpected errors</t>
         </is>
       </c>
       <c r="E46" s="40" t="inlineStr">
         <is>
-          <t>Check b oard s erial n umber</t>
+          <t>- Feature introduces POWER_CAPPING lock file to ensure only 1 DUT tests at a time - Test requires mprime stress load installed &amp; runnable - Test may cycle through high load &amp; recovery, ensure environment power is stable - SEL whitelist temporarily extended and restored afterward</t>
         </is>
       </c>
       <c r="F46" s="75" t="n"/>
@@ -8030,29 +7992,26 @@
       <c r="K46" s="39" t="n"/>
       <c r="L46" s="51" t="n"/>
     </row>
-    <row r="47" ht="53.25" customFormat="1" customHeight="1" s="33">
+    <row r="47" ht="40.5" customFormat="1" customHeight="1" s="33">
       <c r="A47" s="76" t="n">
         <v>45</v>
       </c>
       <c r="B47" s="43" t="inlineStr">
         <is>
-          <t>rm_relay_port_chk</t>
+          <t>bios_dmidecode_fru_chk</t>
         </is>
       </c>
       <c r="C47" s="43" t="inlineStr">
         <is>
-          <t>need to verify the status of the Relay Port Status - ON. Take CAUTION with turning ON state– delay for 20 second – then OFF state of the RELAY and OFF state – 20 seconds delay – ON state.</t>
-        </is>
-      </c>
-      <c r="D47" s="40" t="n"/>
-      <c r="E47" s="40" t="inlineStr">
-        <is>
-          <t>only applies to the master blade
-Feed1powerstatus = healthy
-Feed2powerstatus = healthy
-powerdrawninwatt &lt; maxpowerinwatts</t>
-        </is>
-      </c>
+          <t>Cross-checks dmidecode SMBIOS Type 1 (Product/System), Type 2 (Board), and Type 3 (Chassis) fields against the motherboard FRU (ipmitool fru print 0), using field-name mappings from bios_dmidecode_t1/t2/t3 config.</t>
+        </is>
+      </c>
+      <c r="D47" s="40" t="inlineStr">
+        <is>
+          <t>PASS only if every mapped field in all three checked SMBIOS types matches the corresponding FRU field exactly.</t>
+        </is>
+      </c>
+      <c r="E47" s="40" t="n"/>
       <c r="F47" s="75" t="n"/>
       <c r="G47" s="55" t="b">
         <v>0</v>
@@ -8071,16 +8030,20 @@
       </c>
       <c r="B48" s="43" t="inlineStr">
         <is>
-          <t>rm_power_reading_chk</t>
-        </is>
-      </c>
-      <c r="C48" s="43" t="n"/>
-      <c r="D48" s="40" t="n"/>
-      <c r="E48" s="40" t="inlineStr">
-        <is>
-          <t>only applies to the master blade</t>
-        </is>
-      </c>
+          <t>bmc_mac_chk</t>
+        </is>
+      </c>
+      <c r="C48" s="43" t="inlineStr">
+        <is>
+          <t>Checks the BMC's dedicated management NIC MAC address against SF.</t>
+        </is>
+      </c>
+      <c r="D48" s="40" t="inlineStr">
+        <is>
+          <t>PASS if ipmitool lan print 1 MAC equals SF.</t>
+        </is>
+      </c>
+      <c r="E48" s="40" t="n"/>
       <c r="F48" s="75" t="n"/>
       <c r="G48" s="55" t="b">
         <v>0</v>
@@ -8093,28 +8056,28 @@
       <c r="K48" s="39" t="n"/>
       <c r="L48" s="51" t="n"/>
     </row>
-    <row r="49" ht="67.5" customFormat="1" customHeight="1" s="33">
+    <row r="49" ht="27" customFormat="1" customHeight="1" s="33">
       <c r="A49" s="76" t="n">
         <v>47</v>
       </c>
       <c r="B49" s="43" t="inlineStr">
         <is>
-          <t>rm_power_capping_check</t>
+          <t>bmc_guid_chk</t>
         </is>
       </c>
       <c r="C49" s="43" t="inlineStr">
         <is>
-          <t>Validates RM rack-level power capping behavior, including: - DCMI-based static power limit control - PSU alert-triggered throttling (SM_ALERT)</t>
+          <t>Checks both the BMC "system GUID" (ipmitool mc guid) and "device GUID" (ipmitool raw 0x6 0x8) are not the all-ff placeholder value,.</t>
         </is>
       </c>
       <c r="D49" s="40" t="inlineStr">
         <is>
-          <t>- PASS when ALL are true: - Power limit successfully applied &amp; activated - System load is capped within expected power window (± tolerance) - After removing the cap → system power rebounds above limit - PSU alert scenario triggers throttling and later fully recovers (no SM_ALERT still active) - BMC SEL log contains no unexpected errors</t>
+          <t>PASS if neither GUID contains ffffffffffff.</t>
         </is>
       </c>
       <c r="E49" s="40" t="inlineStr">
         <is>
-          <t>- Feature introduces POWER_CAPPING lock file to ensure only 1 DUT tests at a time - Test requires mprime stress load installed &amp; runnable - Test may cycle through high load &amp; recovery, ensure environment power is stable - SEL whitelist temporarily extended and restored afterward</t>
+          <t>If GUID is invalid, automatically trigger GUID re-write.</t>
         </is>
       </c>
       <c r="F49" s="75" t="n"/>
@@ -8129,23 +8092,23 @@
       <c r="K49" s="39" t="n"/>
       <c r="L49" s="51" t="n"/>
     </row>
-    <row r="50" ht="40.5" customFormat="1" customHeight="1" s="33">
+    <row r="50" ht="27" customFormat="1" customHeight="1" s="33">
       <c r="A50" s="76" t="n">
         <v>48</v>
       </c>
       <c r="B50" s="43" t="inlineStr">
         <is>
-          <t>bios_dmidecode_fru_chk</t>
+          <t>bmc_scm_boardid_chk</t>
         </is>
       </c>
       <c r="C50" s="43" t="inlineStr">
         <is>
-          <t>Cross-checks dmidecode SMBIOS Type 1 (Product/System), Type 2 (Board), and Type 3 (Chassis) fields against the motherboard FRU (ipmitool fru print 0), using field-name mappings from bios_dmidecode_t1/t2/t3 config.</t>
+          <t>Reads the SCM board-revision ID via IPMI raw command and decodes specific bits to determine the board's build stage.</t>
         </is>
       </c>
       <c r="D50" s="40" t="inlineStr">
         <is>
-          <t>PASS only if every mapped field in all three checked SMBIOS types matches the corresponding FRU field exactly.</t>
+          <t>PASS if the decoded 3-bit board ID matches the code for the configured.</t>
         </is>
       </c>
       <c r="E50" s="40" t="n"/>
@@ -8161,37 +8124,42 @@
       <c r="K50" s="39" t="n"/>
       <c r="L50" s="51" t="n"/>
     </row>
-    <row r="51" ht="15" customFormat="1" customHeight="1" s="33">
-      <c r="A51" s="76" t="n">
+    <row r="51" customFormat="1" s="33">
+      <c r="A51" s="81" t="n">
         <v>49</v>
       </c>
-      <c r="B51" s="43" t="inlineStr">
-        <is>
-          <t>bmc_mac_chk</t>
-        </is>
-      </c>
-      <c r="C51" s="43" t="inlineStr">
-        <is>
-          <t>Checks the BMC's dedicated management NIC MAC address against SF.</t>
-        </is>
-      </c>
-      <c r="D51" s="40" t="inlineStr">
-        <is>
-          <t>PASS if ipmitool lan print 1 MAC equals SF.</t>
-        </is>
-      </c>
-      <c r="E51" s="40" t="n"/>
-      <c r="F51" s="75" t="n"/>
-      <c r="G51" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="H51" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="I51" s="55" t="n"/>
-      <c r="J51" s="55" t="n"/>
-      <c r="K51" s="39" t="n"/>
-      <c r="L51" s="51" t="n"/>
+      <c r="B51" s="82" t="inlineStr">
+        <is>
+          <t>bios_boardid_chk</t>
+        </is>
+      </c>
+      <c r="C51" s="82" t="inlineStr">
+        <is>
+          <t>Test mb board id reversion</t>
+        </is>
+      </c>
+      <c r="D51" s="83" t="inlineStr">
+        <is>
+          <t>The parsed current Board ID must match the expected ID for the given project and stage.</t>
+        </is>
+      </c>
+      <c r="E51" s="83" t="n"/>
+      <c r="F51" s="84" t="inlineStr">
+        <is>
+          <t>EVT CMD: ipmitool raw 0x36 0xf3 0x12 0xa6 0x02 0x00 0x18
+DVT CMD: ipmitool raw 0x36 0xf3 0x12 0xa6 0x02 0x00 0x12</t>
+        </is>
+      </c>
+      <c r="G51" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="H51" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="I51" s="84" t="n"/>
+      <c r="J51" s="84" t="n"/>
+      <c r="K51" s="85" t="n"/>
+      <c r="L51" s="86" t="n"/>
     </row>
     <row r="52" ht="27" customFormat="1" customHeight="1" s="33">
       <c r="A52" s="76" t="n">
@@ -8199,24 +8167,20 @@
       </c>
       <c r="B52" s="43" t="inlineStr">
         <is>
-          <t>bmc_guid_chk</t>
+          <t>bmc_hpm_boardid_chk</t>
         </is>
       </c>
       <c r="C52" s="43" t="inlineStr">
         <is>
-          <t>Checks both the BMC "system GUID" (ipmitool mc guid) and "device GUID" (ipmitool raw 0x6 0x8) are not the all-ff placeholder value,.</t>
+          <t>Reads the HPM board-revision ID via IPMI raw command and decodes specific bits to determine the board's build stage.</t>
         </is>
       </c>
       <c r="D52" s="40" t="inlineStr">
         <is>
-          <t>PASS if neither GUID contains ffffffffffff.</t>
-        </is>
-      </c>
-      <c r="E52" s="40" t="inlineStr">
-        <is>
-          <t>If GUID is invalid, automatically trigger GUID re-write.</t>
-        </is>
-      </c>
+          <t>PASS if the decoded 3-bit board ID matches the code for the configured.</t>
+        </is>
+      </c>
+      <c r="E52" s="40" t="n"/>
       <c r="F52" s="75" t="n"/>
       <c r="G52" s="55" t="b">
         <v>0</v>
@@ -8229,133 +8193,32 @@
       <c r="K52" s="39" t="n"/>
       <c r="L52" s="51" t="n"/>
     </row>
-    <row r="53" ht="27" customFormat="1" customHeight="1" s="33">
-      <c r="A53" s="76" t="n">
+    <row r="53" customFormat="1" s="33">
+      <c r="A53" s="81" t="n">
         <v>51</v>
       </c>
-      <c r="B53" s="43" t="inlineStr">
-        <is>
-          <t>bmc_scm_boardid_chk</t>
-        </is>
-      </c>
-      <c r="C53" s="43" t="inlineStr">
-        <is>
-          <t>Reads the SCM board-revision ID via IPMI raw command and decodes specific bits to determine the board's build stage.</t>
-        </is>
-      </c>
-      <c r="D53" s="40" t="inlineStr">
-        <is>
-          <t>PASS if the decoded 3-bit board ID matches the code for the configured.</t>
-        </is>
-      </c>
-      <c r="E53" s="40" t="n"/>
-      <c r="F53" s="75" t="n"/>
-      <c r="G53" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="H53" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="I53" s="55" t="n"/>
-      <c r="J53" s="55" t="n"/>
-      <c r="K53" s="39" t="n"/>
-      <c r="L53" s="51" t="n"/>
-    </row>
-    <row r="54" customFormat="1" s="33">
-      <c r="A54" s="81" t="n">
-        <v>52</v>
-      </c>
-      <c r="B54" s="82" t="inlineStr">
-        <is>
-          <t>bios_boardid_chk</t>
-        </is>
-      </c>
-      <c r="C54" s="82" t="inlineStr">
-        <is>
-          <t>Test mb board id reversion</t>
-        </is>
-      </c>
-      <c r="D54" s="83" t="inlineStr">
-        <is>
-          <t>The parsed current Board ID must match the expected ID for the given project and stage.</t>
-        </is>
-      </c>
-      <c r="E54" s="83" t="n"/>
-      <c r="F54" s="84" t="inlineStr">
-        <is>
-          <t>EVT CMD: ipmitool raw 0x36 0xf3 0x12 0xa6 0x02 0x00 0x18
-DVT CMD: ipmitool raw 0x36 0xf3 0x12 0xa6 0x02 0x00 0x12</t>
-        </is>
-      </c>
-      <c r="G54" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="H54" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="I54" s="84" t="n"/>
-      <c r="J54" s="84" t="n"/>
-      <c r="K54" s="85" t="n"/>
-      <c r="L54" s="86" t="n"/>
-    </row>
-    <row r="55" ht="27" customFormat="1" customHeight="1" s="33">
-      <c r="A55" s="76" t="n">
-        <v>53</v>
-      </c>
-      <c r="B55" s="43" t="inlineStr">
-        <is>
-          <t>bmc_hpm_boardid_chk</t>
-        </is>
-      </c>
-      <c r="C55" s="43" t="inlineStr">
-        <is>
-          <t>Reads the HPM board-revision ID via IPMI raw command and decodes specific bits to determine the board's build stage.</t>
-        </is>
-      </c>
-      <c r="D55" s="40" t="inlineStr">
-        <is>
-          <t>PASS if the decoded 3-bit board ID matches the code for the configured.</t>
-        </is>
-      </c>
-      <c r="E55" s="40" t="n"/>
-      <c r="F55" s="75" t="n"/>
-      <c r="G55" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="H55" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="I55" s="55" t="n"/>
-      <c r="J55" s="55" t="n"/>
-      <c r="K55" s="39" t="n"/>
-      <c r="L55" s="51" t="n"/>
-    </row>
-    <row r="56" customFormat="1" s="33">
-      <c r="A56" s="81" t="n">
-        <v>54</v>
-      </c>
-      <c r="B56" s="82" t="inlineStr">
+      <c r="B53" s="82" t="inlineStr">
         <is>
           <t>bmc_vr_chk</t>
         </is>
       </c>
-      <c r="C56" s="82" t="inlineStr">
+      <c r="C53" s="82" t="inlineStr">
         <is>
           <t>Verify BMC MB Voltage Regulator (VR) checksums.</t>
         </is>
       </c>
-      <c r="D56" s="83" t="inlineStr">
+      <c r="D53" s="83" t="inlineStr">
         <is>
           <t>All VR checksums match expected values from config file.</t>
         </is>
       </c>
-      <c r="E56" s="83" t="inlineStr">
+      <c r="E53" s="83" t="inlineStr">
         <is>
           <t>- Supports 1 or 2 expected VR checksum sets and auto-selects correct group.
 - Fails if config values or commands are missing.</t>
         </is>
       </c>
-      <c r="F56" s="84" t="inlineStr">
+      <c r="F53" s="84" t="inlineStr">
         <is>
           <t>[Get VR version]
 Executing: ipmitool raw 0x36 0xf3 0x14 0xc0 0x00 0xfd 0x04 0x00 0x00 0x00 0x00&amp;&amp;ipmitool raw 0x36 0xf3 0x14 0xc0 0x00 0xfe 0x2d&amp;&amp;ipmitool raw 0x36 0xf3 0x14 0xc0 0x05 0xfd
@@ -8366,37 +8229,37 @@
 Executing: ipmitool raw 0x36 0xf3 0x16 0xd2 0x00 0xfd 0x04 0x00 0x00 0x00 0x00&amp;&amp;ipmitool raw 0x36 0xf3 0x16 0xd2 0x00 0xfe 0x2d&amp;&amp;ipmitool raw 0x36 0xf3 0x16 0xd2 0x05 0xfd</t>
         </is>
       </c>
-      <c r="G56" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="H56" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="I56" s="84" t="n"/>
-      <c r="J56" s="84" t="n"/>
-      <c r="K56" s="85" t="n"/>
-      <c r="L56" s="86" t="n"/>
-    </row>
-    <row r="57" customFormat="1" s="33">
-      <c r="A57" s="81" t="n">
-        <v>55</v>
-      </c>
-      <c r="B57" s="82" t="inlineStr">
+      <c r="G53" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="H53" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="I53" s="84" t="n"/>
+      <c r="J53" s="84" t="n"/>
+      <c r="K53" s="85" t="n"/>
+      <c r="L53" s="86" t="n"/>
+    </row>
+    <row r="54" customFormat="1" s="33">
+      <c r="A54" s="81" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" s="82" t="inlineStr">
         <is>
           <t>bmc_pdb_vr_chk</t>
         </is>
       </c>
-      <c r="C57" s="82" t="inlineStr">
+      <c r="C54" s="82" t="inlineStr">
         <is>
           <t>Verify BMC PDB Voltage Regulator (VR) checksums.</t>
         </is>
       </c>
-      <c r="D57" s="83" t="inlineStr">
+      <c r="D54" s="83" t="inlineStr">
         <is>
           <t>All VR checksums match expected values from config file.</t>
         </is>
       </c>
-      <c r="E57" s="83" t="inlineStr">
+      <c r="E54" s="83" t="inlineStr">
         <is>
           <t>- Supports 1 or 2 expected VR checksum sets and auto-selects correct group.
 - Fails if config values or commands are missing.
@@ -8405,7 +8268,7 @@
 &gt;&gt;&gt;PDB 2nd source has VR checksum. Wait for commodity and command to support this function. &gt;&gt;&gt;BMC RD updated the checksum.</t>
         </is>
       </c>
-      <c r="F57" s="84" t="inlineStr">
+      <c r="F54" s="84" t="inlineStr">
         <is>
           <t>[Get VR version]
 1. Check the PDB is main source or second soure.
@@ -8417,174 +8280,174 @@
 ./xdp711_crc.sh -b 31 -s 0x10</t>
         </is>
       </c>
-      <c r="G57" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="H57" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="I57" s="84" t="n"/>
-      <c r="J57" s="84" t="n"/>
-      <c r="K57" s="85" t="n"/>
-      <c r="L57" s="86" t="n"/>
-    </row>
-    <row r="58" ht="27" customFormat="1" customHeight="1" s="33">
-      <c r="A58" s="76" t="n">
+      <c r="G54" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="H54" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="I54" s="84" t="n"/>
+      <c r="J54" s="84" t="n"/>
+      <c r="K54" s="85" t="n"/>
+      <c r="L54" s="86" t="n"/>
+    </row>
+    <row r="55" ht="27" customFormat="1" customHeight="1" s="33">
+      <c r="A55" s="76" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" s="43" t="inlineStr">
+        <is>
+          <t>bmc_selftest_chk</t>
+        </is>
+      </c>
+      <c r="C55" s="43" t="inlineStr">
+        <is>
+          <t>Checks the BMC's own IPMI self-test result code against the expected "all subsystems healthy" value.</t>
+        </is>
+      </c>
+      <c r="D55" s="40" t="inlineStr">
+        <is>
+          <t>PASS if ipmitool raw 0x06 0x04 (whitespace-stripped) equals getConfigValue('bmc_selftest_rest').</t>
+        </is>
+      </c>
+      <c r="E55" s="40" t="inlineStr">
+        <is>
+          <t>A self-test failure is a hard FAIL with no retry/upgrade path.</t>
+        </is>
+      </c>
+      <c r="F55" s="75" t="n"/>
+      <c r="G55" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="H55" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="I55" s="55" t="n"/>
+      <c r="J55" s="55" t="n"/>
+      <c r="K55" s="39" t="n"/>
+      <c r="L55" s="51" t="n"/>
+    </row>
+    <row r="56" ht="27" customFormat="1" customHeight="1" s="33">
+      <c r="A56" s="76" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" s="43" t="inlineStr">
+        <is>
+          <t>bmc_func_test</t>
+        </is>
+      </c>
+      <c r="C56" s="43" t="inlineStr">
+        <is>
+          <t>Perform BMC functional test including Device ID, BMC version, self-test, chassis status, watchdog timer, and SDR check.</t>
+        </is>
+      </c>
+      <c r="D56" s="40" t="inlineStr">
+        <is>
+          <t>PASS if function test returns 0. On failure, greps LogFile.log for Failed entries and logs them alongside the detailed log.</t>
+        </is>
+      </c>
+      <c r="E56" s="40" t="n"/>
+      <c r="F56" s="75" t="n"/>
+      <c r="G56" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="H56" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="I56" s="55" t="n"/>
+      <c r="J56" s="55" t="n"/>
+      <c r="K56" s="39" t="n"/>
+      <c r="L56" s="51" t="n"/>
+    </row>
+    <row r="57" ht="27" customFormat="1" customHeight="1" s="33">
+      <c r="A57" s="76" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" s="43" t="inlineStr">
+        <is>
+          <t>bmc_i2c_test</t>
+        </is>
+      </c>
+      <c r="C57" s="43" t="inlineStr">
+        <is>
+          <t>Runs an on-BMC I2C stress-test script against MB/PDB/FAN buses, uploaded and executed live over SSH, with a BMC-SEL check both before and after.</t>
+        </is>
+      </c>
+      <c r="D57" s="40" t="inlineStr">
+        <is>
+          <t>PASS if the uploaded script's log reports "Test successful" (no "Test Failed" / "No such file or directory" lines) AND the post-test BMC SEL check is clean.</t>
+        </is>
+      </c>
+      <c r="E57" s="40" t="inlineStr">
+        <is>
+          <t>SEL is explicitly cleared right before the I2C run so the post-run SEL check only reflects entries from this test.</t>
+        </is>
+      </c>
+      <c r="F57" s="75" t="n"/>
+      <c r="G57" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="H57" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="I57" s="55" t="n"/>
+      <c r="J57" s="55" t="n"/>
+      <c r="K57" s="39" t="n"/>
+      <c r="L57" s="51" t="n"/>
+    </row>
+    <row r="58" customFormat="1" s="33">
+      <c r="A58" s="81" t="n">
         <v>56</v>
       </c>
-      <c r="B58" s="43" t="inlineStr">
-        <is>
-          <t>bmc_selftest_chk</t>
-        </is>
-      </c>
-      <c r="C58" s="43" t="inlineStr">
-        <is>
-          <t>Checks the BMC's own IPMI self-test result code against the expected "all subsystems healthy" value.</t>
-        </is>
-      </c>
-      <c r="D58" s="40" t="inlineStr">
-        <is>
-          <t>PASS if ipmitool raw 0x06 0x04 (whitespace-stripped) equals getConfigValue('bmc_selftest_rest').</t>
-        </is>
-      </c>
-      <c r="E58" s="40" t="inlineStr">
-        <is>
-          <t>A self-test failure is a hard FAIL with no retry/upgrade path.</t>
-        </is>
-      </c>
-      <c r="F58" s="75" t="n"/>
-      <c r="G58" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="H58" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="I58" s="55" t="n"/>
-      <c r="J58" s="55" t="n"/>
-      <c r="K58" s="39" t="n"/>
-      <c r="L58" s="51" t="n"/>
-    </row>
-    <row r="59" ht="27" customFormat="1" customHeight="1" s="33">
-      <c r="A59" s="76" t="n">
-        <v>57</v>
-      </c>
-      <c r="B59" s="43" t="inlineStr">
-        <is>
-          <t>bmc_func_test</t>
-        </is>
-      </c>
-      <c r="C59" s="43" t="inlineStr">
-        <is>
-          <t>Perform BMC functional test including Device ID, BMC version, self-test, chassis status, watchdog timer, and SDR check.</t>
-        </is>
-      </c>
-      <c r="D59" s="40" t="inlineStr">
-        <is>
-          <t>PASS if function test returns 0. On failure, greps LogFile.log for Failed entries and logs them alongside the detailed log.</t>
-        </is>
-      </c>
-      <c r="E59" s="40" t="n"/>
-      <c r="F59" s="75" t="n"/>
-      <c r="G59" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="H59" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="I59" s="55" t="n"/>
-      <c r="J59" s="55" t="n"/>
-      <c r="K59" s="39" t="n"/>
-      <c r="L59" s="51" t="n"/>
-    </row>
-    <row r="60" ht="27" customFormat="1" customHeight="1" s="33">
-      <c r="A60" s="76" t="n">
-        <v>58</v>
-      </c>
-      <c r="B60" s="43" t="inlineStr">
-        <is>
-          <t>bmc_i2c_test</t>
-        </is>
-      </c>
-      <c r="C60" s="43" t="inlineStr">
-        <is>
-          <t>Runs an on-BMC I2C stress-test script against MB/PDB/FAN buses, uploaded and executed live over SSH, with a BMC-SEL check both before and after.</t>
-        </is>
-      </c>
-      <c r="D60" s="40" t="inlineStr">
-        <is>
-          <t>PASS if the uploaded script's log reports "Test successful" (no "Test Failed" / "No such file or directory" lines) AND the post-test BMC SEL check is clean.</t>
-        </is>
-      </c>
-      <c r="E60" s="40" t="inlineStr">
-        <is>
-          <t>SEL is explicitly cleared right before the I2C run so the post-run SEL check only reflects entries from this test.</t>
-        </is>
-      </c>
-      <c r="F60" s="75" t="n"/>
-      <c r="G60" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="H60" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="I60" s="55" t="n"/>
-      <c r="J60" s="55" t="n"/>
-      <c r="K60" s="39" t="n"/>
-      <c r="L60" s="51" t="n"/>
-    </row>
-    <row r="61" customFormat="1" s="33">
-      <c r="A61" s="81" t="n">
-        <v>59</v>
-      </c>
-      <c r="B61" s="82" t="inlineStr">
+      <c r="B58" s="82" t="inlineStr">
         <is>
           <t>bmc_i3c_test</t>
         </is>
       </c>
-      <c r="C61" s="82" t="inlineStr">
+      <c r="C58" s="82" t="inlineStr">
         <is>
           <t>Check bmc i3c test and sel log check only for Castle Peak</t>
         </is>
       </c>
-      <c r="D61" s="83" t="inlineStr">
+      <c r="D58" s="83" t="inlineStr">
         <is>
           <t>Pass - return 0; Fail - return 1
 Pass - return 0; Fail - return 1</t>
         </is>
       </c>
-      <c r="E61" s="83" t="inlineStr">
+      <c r="E58" s="83" t="inlineStr">
         <is>
           <t>&gt;&gt;&gt; Will be implemented in DVT.</t>
         </is>
       </c>
-      <c r="F61" s="84" t="inlineStr">
+      <c r="F58" s="84" t="inlineStr">
         <is>
           <t>apml_tool 1 --showtsiregister
 apml_tool 2 --showtsiregister
 ===&gt; tu7_dvt_i2c_i3c_stress.sh 1 i3c</t>
         </is>
       </c>
-      <c r="G61" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="H61" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="I61" s="84" t="n"/>
-      <c r="J61" s="84" t="n"/>
-      <c r="K61" s="85" t="n"/>
-      <c r="L61" s="86" t="n"/>
-    </row>
-    <row r="62" customFormat="1" s="33">
-      <c r="A62" s="81" t="n">
-        <v>60</v>
-      </c>
-      <c r="B62" s="82" t="inlineStr">
+      <c r="G58" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="H58" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="I58" s="84" t="n"/>
+      <c r="J58" s="84" t="n"/>
+      <c r="K58" s="85" t="n"/>
+      <c r="L58" s="86" t="n"/>
+    </row>
+    <row r="59" customFormat="1" s="33">
+      <c r="A59" s="81" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" s="82" t="inlineStr">
         <is>
           <t>bmc_cpld_security_chk</t>
         </is>
       </c>
-      <c r="C62" s="82" t="inlineStr">
+      <c r="C59" s="82" t="inlineStr">
         <is>
           <t>Check all SCM/HPM CPLD information status via bmc jtag raw command
 SCM CPLD Criteria:
@@ -8620,8 +8483,8 @@
 HPM CPLD CENTRAL LOCK check</t>
         </is>
       </c>
-      <c r="D62" s="83" t="n"/>
-      <c r="E62" s="83" t="inlineStr">
+      <c r="D59" s="83" t="n"/>
+      <c r="E59" s="83" t="inlineStr">
         <is>
           <t>- Follow C44AD to combine bmc_cpld_security_chk and bmc_hpm_cpld_security_chk.
 &gt;&gt;&gt;bmc_cpld_security_chk will be implemented in DVT Canary.
@@ -8629,7 +8492,7 @@
 &gt;&gt;&gt; Waiver for ship the Canary demand with CPLD Ping-pong mode. WAIVER 3622374</t>
         </is>
       </c>
-      <c r="F62" s="84">
+      <c r="F59" s="84">
         <f>======= [ SCM CPLD ] ========
 [Get SCM Pull JTAG_BMC_OE_N Low]
 ipmitool raw 0x30 0xe0 0 8 1 0
@@ -8706,52 +8569,161 @@
 jtag-rbpi -if /var/wcs/home/Read_Lock_Sector.stp -m fwupdate -t HPM -j /usr/share/cpld-config/configurations/cpld-config.json -o /xyz/openbmc_project/software/HPM_CPLD -debug</f>
         <v/>
       </c>
-      <c r="G62" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="H62" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="I62" s="84" t="n"/>
-      <c r="J62" s="84" t="n"/>
-      <c r="K62" s="85" t="n"/>
-      <c r="L62" s="86" t="n"/>
-    </row>
-    <row r="63" customFormat="1" s="33">
-      <c r="A63" s="81" t="n">
+      <c r="G59" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="H59" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="I59" s="84" t="n"/>
+      <c r="J59" s="84" t="n"/>
+      <c r="K59" s="85" t="n"/>
+      <c r="L59" s="86" t="n"/>
+    </row>
+    <row r="60" customFormat="1" s="33">
+      <c r="A60" s="81" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" s="82" t="inlineStr">
+        <is>
+          <t>bmc_scm_cpu_uart_check</t>
+        </is>
+      </c>
+      <c r="C60" s="82" t="inlineStr">
+        <is>
+          <t>Check the UART0 path from SCM to CPU0 by validating SSH reachability through the chain: Host → BMC → Host. This ensures the SCM UART bus is working correctly by confirming that the BMC can relay communication back to the host system.</t>
+        </is>
+      </c>
+      <c r="D60" s="83" t="n"/>
+      <c r="E60" s="83" t="inlineStr">
+        <is>
+          <t>&gt;&gt;&gt; Will be implemented in DVT.</t>
+        </is>
+      </c>
+      <c r="F60" s="84" t="inlineStr">
+        <is>
+          <t>[Get BMC IP]</t>
+        </is>
+      </c>
+      <c r="G60" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="H60" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="I60" s="84" t="n"/>
+      <c r="J60" s="84" t="n"/>
+      <c r="K60" s="85" t="n"/>
+      <c r="L60" s="86" t="n"/>
+    </row>
+    <row r="61" ht="27" customFormat="1" customHeight="1" s="33">
+      <c r="A61" s="76" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" s="43" t="inlineStr">
+        <is>
+          <t>bmc_dedicate_chk</t>
+        </is>
+      </c>
+      <c r="C61" s="43" t="inlineStr">
+        <is>
+          <t>Verifies the BMC's dedicated management NIC is physically connected and DHCP-reachable by pinging it.</t>
+        </is>
+      </c>
+      <c r="D61" s="40" t="inlineStr">
+        <is>
+          <t>PASS if 5/5 pings succeed (or the RM-routed SSH connect succeeds).</t>
+        </is>
+      </c>
+      <c r="E61" s="40" t="inlineStr">
+        <is>
+          <t>M1/M3: via a direct ICMP ping
+M5: ping via an SSH-through-RM reachability check</t>
+        </is>
+      </c>
+      <c r="F61" s="75" t="n"/>
+      <c r="G61" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="H61" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="I61" s="55" t="n"/>
+      <c r="J61" s="55" t="n"/>
+      <c r="K61" s="39" t="n"/>
+      <c r="L61" s="51" t="n"/>
+    </row>
+    <row r="62" ht="27" customFormat="1" customHeight="1" s="33">
+      <c r="A62" s="76" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" s="43" t="inlineStr">
+        <is>
+          <t>cpu_qty_check</t>
+        </is>
+      </c>
+      <c r="C62" s="43" t="inlineStr">
+        <is>
+          <t>Checks the number of populated CPU sockets against SF-expected count.</t>
+        </is>
+      </c>
+      <c r="D62" s="40" t="inlineStr">
+        <is>
+          <t>PASS if grep 'physical id' /proc/cpuinfo | sort | uniq | wc -l equals getConfigValue('cpu_qty').</t>
+        </is>
+      </c>
+      <c r="E62" s="40" t="inlineStr">
+        <is>
+          <t>Straightforward count check, no upgrade/self-heal path (CPU quantity isn't something firmware can fix).</t>
+        </is>
+      </c>
+      <c r="F62" s="75" t="n"/>
+      <c r="G62" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="H62" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="I62" s="55" t="n"/>
+      <c r="J62" s="55" t="n"/>
+      <c r="K62" s="39" t="n"/>
+      <c r="L62" s="51" t="n"/>
+    </row>
+    <row r="63" ht="27" customFormat="1" customHeight="1" s="33">
+      <c r="A63" s="76" t="n">
         <v>61</v>
       </c>
-      <c r="B63" s="82" t="inlineStr">
-        <is>
-          <t>bmc_scm_cpu_uart_check</t>
-        </is>
-      </c>
-      <c r="C63" s="82" t="inlineStr">
-        <is>
-          <t>Check the UART0 path from SCM to CPU0 by validating SSH reachability through the chain: Host → BMC → Host. This ensures the SCM UART bus is working correctly by confirming that the BMC can relay communication back to the host system.</t>
-        </is>
-      </c>
-      <c r="D63" s="83" t="n"/>
-      <c r="E63" s="83" t="inlineStr">
-        <is>
-          <t>&gt;&gt;&gt; Will be implemented in DVT.</t>
-        </is>
-      </c>
-      <c r="F63" s="84" t="inlineStr">
-        <is>
-          <t>[Get BMC IP]</t>
-        </is>
-      </c>
-      <c r="G63" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="H63" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="I63" s="84" t="n"/>
-      <c r="J63" s="84" t="n"/>
-      <c r="K63" s="85" t="n"/>
-      <c r="L63" s="86" t="n"/>
+      <c r="B63" s="43" t="inlineStr">
+        <is>
+          <t>cpu_info_chk</t>
+        </is>
+      </c>
+      <c r="C63" s="43" t="inlineStr">
+        <is>
+          <t>Validate CPU information using dmidecode (type 4), comparing it with expected config values.</t>
+        </is>
+      </c>
+      <c r="D63" s="40" t="inlineStr">
+        <is>
+          <t>PASS if, per CPU, the Manufacturer/Version/Speed combo, Signature, and Core Count all measure equal to expected.</t>
+        </is>
+      </c>
+      <c r="E63" s="40" t="inlineStr">
+        <is>
+          <t>In L6 prj_level, all checks are informational-only.</t>
+        </is>
+      </c>
+      <c r="F63" s="75" t="n"/>
+      <c r="G63" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="H63" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="I63" s="55" t="n"/>
+      <c r="J63" s="55" t="n"/>
+      <c r="K63" s="39" t="n"/>
+      <c r="L63" s="51" t="n"/>
     </row>
     <row r="64" ht="27" customFormat="1" customHeight="1" s="33">
       <c r="A64" s="76" t="n">
@@ -8759,23 +8731,22 @@
       </c>
       <c r="B64" s="43" t="inlineStr">
         <is>
-          <t>bmc_dedicate_chk</t>
+          <t>cpu_func_test</t>
         </is>
       </c>
       <c r="C64" s="43" t="inlineStr">
         <is>
-          <t>Verifies the BMC's dedicated management NIC is physically connected and DHCP-reachable by pinging it.</t>
+          <t>Runs a sequence of CPU feature functional tests (Cache, FPU, MMX, SSE, SSE2, SSE3, x64Cap, SMP, SMP-cache-coherency, AES, SSE4).</t>
         </is>
       </c>
       <c r="D64" s="40" t="inlineStr">
         <is>
-          <t>PASS if 5/5 pings succeed (or the RM-routed SSH connect succeeds).</t>
+          <t>PASS only if every sub-test in the sequence returns exit code 0; the function returns 1 immediately on the first sub-test failure.</t>
         </is>
       </c>
       <c r="E64" s="40" t="inlineStr">
         <is>
-          <t>M1/M3: via a direct ICMP ping
-M5: ping via an SSH-through-RM reachability check</t>
+          <t>Fail-fast means a Cache-test failure prevents FPU/MMX/etc.</t>
         </is>
       </c>
       <c r="F64" s="75" t="n"/>
@@ -8790,129 +8761,21 @@
       <c r="K64" s="39" t="n"/>
       <c r="L64" s="51" t="n"/>
     </row>
-    <row r="65" ht="27" customFormat="1" customHeight="1" s="33">
-      <c r="A65" s="76" t="n">
+    <row r="65" customFormat="1" s="33">
+      <c r="A65" s="81" t="n">
         <v>63</v>
       </c>
-      <c r="B65" s="43" t="inlineStr">
-        <is>
-          <t>cpu_qty_check</t>
-        </is>
-      </c>
-      <c r="C65" s="43" t="inlineStr">
-        <is>
-          <t>Checks the number of populated CPU sockets against SF-expected count.</t>
-        </is>
-      </c>
-      <c r="D65" s="40" t="inlineStr">
-        <is>
-          <t>PASS if grep 'physical id' /proc/cpuinfo | sort | uniq | wc -l equals getConfigValue('cpu_qty').</t>
-        </is>
-      </c>
-      <c r="E65" s="40" t="inlineStr">
-        <is>
-          <t>Straightforward count check, no upgrade/self-heal path (CPU quantity isn't something firmware can fix).</t>
-        </is>
-      </c>
-      <c r="F65" s="75" t="n"/>
-      <c r="G65" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="H65" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="I65" s="55" t="n"/>
-      <c r="J65" s="55" t="n"/>
-      <c r="K65" s="39" t="n"/>
-      <c r="L65" s="51" t="n"/>
-    </row>
-    <row r="66" ht="27" customFormat="1" customHeight="1" s="33">
-      <c r="A66" s="76" t="n">
-        <v>64</v>
-      </c>
-      <c r="B66" s="43" t="inlineStr">
-        <is>
-          <t>cpu_info_chk</t>
-        </is>
-      </c>
-      <c r="C66" s="43" t="inlineStr">
-        <is>
-          <t>Validate CPU information using dmidecode (type 4), comparing it with expected config values.</t>
-        </is>
-      </c>
-      <c r="D66" s="40" t="inlineStr">
-        <is>
-          <t>PASS if, per CPU, the Manufacturer/Version/Speed combo, Signature, and Core Count all measure equal to expected.</t>
-        </is>
-      </c>
-      <c r="E66" s="40" t="inlineStr">
-        <is>
-          <t>In L6 prj_level, all checks are informational-only.</t>
-        </is>
-      </c>
-      <c r="F66" s="75" t="n"/>
-      <c r="G66" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="H66" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="I66" s="55" t="n"/>
-      <c r="J66" s="55" t="n"/>
-      <c r="K66" s="39" t="n"/>
-      <c r="L66" s="51" t="n"/>
-    </row>
-    <row r="67" ht="27" customFormat="1" customHeight="1" s="33">
-      <c r="A67" s="76" t="n">
-        <v>65</v>
-      </c>
-      <c r="B67" s="43" t="inlineStr">
-        <is>
-          <t>cpu_func_test</t>
-        </is>
-      </c>
-      <c r="C67" s="43" t="inlineStr">
-        <is>
-          <t>Runs a sequence of CPU feature functional tests (Cache, FPU, MMX, SSE, SSE2, SSE3, x64Cap, SMP, SMP-cache-coherency, AES, SSE4).</t>
-        </is>
-      </c>
-      <c r="D67" s="40" t="inlineStr">
-        <is>
-          <t>PASS only if every sub-test in the sequence returns exit code 0; the function returns 1 immediately on the first sub-test failure.</t>
-        </is>
-      </c>
-      <c r="E67" s="40" t="inlineStr">
-        <is>
-          <t>Fail-fast means a Cache-test failure prevents FPU/MMX/etc.</t>
-        </is>
-      </c>
-      <c r="F67" s="75" t="n"/>
-      <c r="G67" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="H67" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="I67" s="55" t="n"/>
-      <c r="J67" s="55" t="n"/>
-      <c r="K67" s="39" t="n"/>
-      <c r="L67" s="51" t="n"/>
-    </row>
-    <row r="68" customFormat="1" s="33">
-      <c r="A68" s="81" t="n">
-        <v>66</v>
-      </c>
-      <c r="B68" s="82" t="inlineStr">
+      <c r="B65" s="82" t="inlineStr">
         <is>
           <t>cpu_xgmi</t>
         </is>
       </c>
-      <c r="C68" s="82" t="inlineStr">
+      <c r="C65" s="82" t="inlineStr">
         <is>
           <t>This test verifies the status and configuration of AMD's XGMI (inter-socket high-speed link) functionality between CPUs.</t>
         </is>
       </c>
-      <c r="D68" s="83" t="inlineStr">
+      <c r="D65" s="83" t="inlineStr">
         <is>
           <t>The XGMI links between CPUs must be:
 - Detected successfully by the system
@@ -8920,39 +8783,39 @@
 - All links must pass without errors or degradation</t>
         </is>
       </c>
-      <c r="E68" s="83" t="inlineStr">
+      <c r="E65" s="83" t="inlineStr">
         <is>
           <t>&gt;&gt;&gt;Secured CPU has Bug#3771751, which plan to be resolved in 1A21.</t>
         </is>
       </c>
-      <c r="F68" s="84" t="inlineStr">
+      <c r="F65" s="84" t="inlineStr">
         <is>
           <t>./AMDXIO -i=0:,1:,2:,3: -xgmi -linkstatus ===&gt; dpkg -i …amdxio_nda.deb</t>
         </is>
       </c>
-      <c r="G68" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="H68" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="I68" s="84" t="n"/>
-      <c r="J68" s="84" t="n"/>
-      <c r="K68" s="85" t="n"/>
-      <c r="L68" s="86" t="n"/>
-    </row>
-    <row r="69" customFormat="1" s="33">
-      <c r="A69" s="81" t="n">
-        <v>67</v>
-      </c>
-      <c r="B69" s="82" t="inlineStr">
+      <c r="G65" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="H65" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="I65" s="84" t="n"/>
+      <c r="J65" s="84" t="n"/>
+      <c r="K65" s="85" t="n"/>
+      <c r="L65" s="86" t="n"/>
+    </row>
+    <row r="66" customFormat="1" s="33">
+      <c r="A66" s="81" t="n">
+        <v>64</v>
+      </c>
+      <c r="B66" s="82" t="inlineStr">
         <is>
           <t>cpu_xgmi_bw</t>
         </is>
       </c>
-      <c r="C69" s="82" t="n"/>
-      <c r="D69" s="83" t="n"/>
-      <c r="E69" s="83" t="inlineStr">
+      <c r="C66" s="82" t="n"/>
+      <c r="D66" s="83" t="n"/>
+      <c r="E66" s="83" t="inlineStr">
         <is>
           <t>"cpu_xgmi" test failed with secured PC CPU.
 The Alternative method (MLC+APML tool) to to verify xGMI bandwidth/xGMI connection (1 cable-connected, 2 on-board trace)
@@ -8962,30 +8825,30 @@
 &gt;&gt;&gt;This test item can be removed when AMD provides a workable xgmi tool.</t>
         </is>
       </c>
-      <c r="F69" s="84" t="n"/>
-      <c r="G69" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="H69" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="I69" s="84" t="n"/>
-      <c r="J69" s="84" t="n"/>
-      <c r="K69" s="85" t="n"/>
-      <c r="L69" s="86" t="n"/>
-    </row>
-    <row r="70" s="80">
-      <c r="A70" s="81" t="n">
-        <v>68</v>
-      </c>
-      <c r="B70" s="82" t="inlineStr">
+      <c r="F66" s="84" t="n"/>
+      <c r="G66" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="H66" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="I66" s="84" t="n"/>
+      <c r="J66" s="84" t="n"/>
+      <c r="K66" s="85" t="n"/>
+      <c r="L66" s="86" t="n"/>
+    </row>
+    <row r="67" customFormat="1" s="33">
+      <c r="A67" s="81" t="n">
+        <v>65</v>
+      </c>
+      <c r="B67" s="82" t="inlineStr">
         <is>
           <t>cpu_esmi_xgmi_link_speed</t>
         </is>
       </c>
-      <c r="C70" s="82" t="n"/>
-      <c r="D70" s="83" t="n"/>
-      <c r="E70" s="83" t="inlineStr">
+      <c r="C67" s="82" t="n"/>
+      <c r="D67" s="83" t="n"/>
+      <c r="E67" s="83" t="inlineStr">
         <is>
           <t>to verify the configured xGMI link speed
 &gt;&gt;&gt;Move cpu_esmi_xgmi_link_speed from L10 FAT to L11 Pretest since E-SMI work with L11 Canary CRD BIOS 1A20.
@@ -8994,38 +8857,128 @@
 &gt;&gt;&gt;This test item can be removed when AMD provides a workable xgmi tool.</t>
         </is>
       </c>
-      <c r="F70" s="84" t="n"/>
-      <c r="G70" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="H70" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="I70" s="84" t="n"/>
-      <c r="J70" s="84" t="n"/>
-      <c r="K70" s="85" t="n"/>
-      <c r="L70" s="86" t="n"/>
+      <c r="F67" s="84" t="n"/>
+      <c r="G67" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="H67" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="I67" s="84" t="n"/>
+      <c r="J67" s="84" t="n"/>
+      <c r="K67" s="85" t="n"/>
+      <c r="L67" s="86" t="n"/>
+    </row>
+    <row r="68" ht="27" customFormat="1" customHeight="1" s="33">
+      <c r="A68" s="76" t="n">
+        <v>66</v>
+      </c>
+      <c r="B68" s="43" t="inlineStr">
+        <is>
+          <t>mem_info_chk</t>
+        </is>
+      </c>
+      <c r="C68" s="43" t="inlineStr">
+        <is>
+          <t>Checks each populated DIMM slot's Size/Speed/Manufacturer/Part-Number against SF-expected mem list, parsed from a filtered dmidecode -t 17 dump.</t>
+        </is>
+      </c>
+      <c r="D68" s="40" t="inlineStr">
+        <is>
+          <t>PASS if every slot's manf,size,speed,PN string matches the corresponding SF entry exactly.</t>
+        </is>
+      </c>
+      <c r="E68" s="40" t="n"/>
+      <c r="F68" s="75" t="n"/>
+      <c r="G68" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="H68" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="I68" s="55" t="n"/>
+      <c r="J68" s="55" t="n"/>
+      <c r="K68" s="39" t="n"/>
+      <c r="L68" s="51" t="n"/>
+    </row>
+    <row r="69" ht="15" customFormat="1" customHeight="1" s="33">
+      <c r="A69" s="76" t="n"/>
+      <c r="B69" s="43" t="inlineStr">
+        <is>
+          <t>rm_mem_size_chk</t>
+        </is>
+      </c>
+      <c r="C69" s="43" t="n"/>
+      <c r="D69" s="40" t="n"/>
+      <c r="E69" s="40" t="n"/>
+      <c r="F69" s="75" t="n"/>
+      <c r="G69" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="H69" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="I69" s="55" t="n"/>
+      <c r="J69" s="55" t="n"/>
+      <c r="K69" s="39" t="n"/>
+      <c r="L69" s="51" t="n"/>
+    </row>
+    <row r="70" ht="27" customHeight="1" s="80">
+      <c r="A70" s="76" t="n">
+        <v>67</v>
+      </c>
+      <c r="B70" s="43" t="inlineStr">
+        <is>
+          <t>mem_size_chk</t>
+        </is>
+      </c>
+      <c r="C70" s="43" t="inlineStr">
+        <is>
+          <t>Cross-checks total populated-DIMM count and per-DIMM size (in the detected unit, MB or GB) against SF's mem_num/mem_size.</t>
+        </is>
+      </c>
+      <c r="D70" s="40" t="inlineStr">
+        <is>
+          <t>PASS if the count of DIMMs reporting the dominant size equals mem_num AND that size (converted to the detected unit) equals mem_size.</t>
+        </is>
+      </c>
+      <c r="E70" s="40" t="n"/>
+      <c r="F70" s="75" t="n"/>
+      <c r="G70" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="H70" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="I70" s="55" t="n"/>
+      <c r="J70" s="55" t="n"/>
+      <c r="K70" s="39" t="n"/>
+      <c r="L70" s="51" t="n"/>
     </row>
     <row r="71" ht="27" customHeight="1" s="80">
       <c r="A71" s="76" t="n">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="B71" s="43" t="inlineStr">
         <is>
-          <t>mem_info_chk</t>
+          <t>mem_func_test</t>
         </is>
       </c>
       <c r="C71" s="43" t="inlineStr">
         <is>
-          <t>Checks each populated DIMM slot's Size/Speed/Manufacturer/Part-Number against SF-expected mem list, parsed from a filtered dmidecode -t 17 dump.</t>
+          <t>Runs a memory read/write functional stress test with swap disabled during the run.</t>
         </is>
       </c>
       <c r="D71" s="40" t="inlineStr">
         <is>
-          <t>PASS if every slot's manf,size,speed,PN string matches the corresponding SF entry exactly.</t>
-        </is>
-      </c>
-      <c r="E71" s="40" t="n"/>
+          <t>PASS if the test command's exit code is 0.</t>
+        </is>
+      </c>
+      <c r="E71" s="40" t="inlineStr">
+        <is>
+          <t>Maps specific nonzero return codes to human-readable error names in the failure log message.</t>
+        </is>
+      </c>
       <c r="F71" s="75" t="n"/>
       <c r="G71" s="55" t="b">
         <v>0</v>
@@ -9038,16 +8991,30 @@
       <c r="K71" s="39" t="n"/>
       <c r="L71" s="51" t="n"/>
     </row>
-    <row r="72" ht="15" customHeight="1" s="80">
-      <c r="A72" s="76" t="n"/>
+    <row r="72" ht="67.5" customHeight="1" s="80">
+      <c r="A72" s="76" t="n">
+        <v>69</v>
+      </c>
       <c r="B72" s="43" t="inlineStr">
         <is>
-          <t>rm_mem_size_chk</t>
-        </is>
-      </c>
-      <c r="C72" s="43" t="n"/>
-      <c r="D72" s="40" t="n"/>
-      <c r="E72" s="40" t="n"/>
+          <t>pcie_manticore_log_chk</t>
+        </is>
+      </c>
+      <c r="C72" s="43" t="inlineStr">
+        <is>
+          <t>Reads the Manticore chip's debug log (cerberus_utility debuglogread), verifies the FW version recorded in the log matches expected, checks CS0/CS1 flash device consistency, scans for uncleared error codes since the last boot, and scans for unfiltered Warning/Error lines against a configurable skip-pattern list — clearing the log only after a full PASS.</t>
+        </is>
+      </c>
+      <c r="D72" s="40" t="inlineStr">
+        <is>
+          <t>PASS only if: (1) FW version found in log matches pcie_manticore_ver, (2) Port 1 CS0/CS1 vendor+device+capacity match each other, (3) no known bad error codes (0x7f001e0c/0d/0e, 0x7f001d05, 0x7f001d10) appear after the last-boot marker, (4) no unfiltered Warning/Error lines appear after the last-boot marker.</t>
+        </is>
+      </c>
+      <c r="E72" s="40" t="inlineStr">
+        <is>
+          <t>If the log is completely empty of a FW-version line, it triggers an AC power cycle as a recovery action and still FAILs the current pass (log message: "please AC the server"). pcie_manticore_debuglog_skip config defines patterns to exclude from the Warning/Error scan</t>
+        </is>
+      </c>
       <c r="F72" s="75" t="n"/>
       <c r="G72" s="55" t="b">
         <v>0</v>
@@ -9060,26 +9027,30 @@
       <c r="K72" s="39" t="n"/>
       <c r="L72" s="51" t="n"/>
     </row>
-    <row r="73" ht="27" customHeight="1" s="80">
+    <row r="73" ht="67.5" customHeight="1" s="80">
       <c r="A73" s="76" t="n">
         <v>70</v>
       </c>
       <c r="B73" s="43" t="inlineStr">
         <is>
-          <t>mem_size_chk</t>
+          <t>pcie_tip_log_chk</t>
         </is>
       </c>
       <c r="C73" s="43" t="inlineStr">
         <is>
-          <t>Cross-checks total populated-DIMM count and per-DIMM size (in the detected unit, MB or GB) against SF's mem_num/mem_size.</t>
+          <t>Reads the Hydra/TIP chip's debug log (cerberus_utility debuglogread), verifies the FW version recorded in the log matches expected, checks CS0/CS1 flash device consistency, scans for uncleared error codes since the last boot, and scans for unfiltered Warning/Error lines against a configurable skip-pattern list — clearing the log only after a full PASS.</t>
         </is>
       </c>
       <c r="D73" s="40" t="inlineStr">
         <is>
-          <t>PASS if the count of DIMMs reporting the dominant size equals mem_num AND that size (converted to the detected unit) equals mem_size.</t>
-        </is>
-      </c>
-      <c r="E73" s="40" t="n"/>
+          <t>PASS if: (1) the log contains a "Cerberus main flash" entry at all (else AC-cycle + FAIL), (2) main/recovery flash vendor+device+capacity match, (3) no unfiltered Warning/Error tagged lines appear after the last-boot marker.</t>
+        </is>
+      </c>
+      <c r="E73" s="40" t="inlineStr">
+        <is>
+          <t>The Warning/Error scan here additionally requires the tag field (3rd |-delimited column) itself contain "Warning" or "Error", not just the whole line.</t>
+        </is>
+      </c>
       <c r="F73" s="75" t="n"/>
       <c r="G73" s="55" t="b">
         <v>0</v>
@@ -9098,24 +9069,20 @@
       </c>
       <c r="B74" s="43" t="inlineStr">
         <is>
-          <t>mem_func_test</t>
+          <t>fpga_gp_mac_chk</t>
         </is>
       </c>
       <c r="C74" s="43" t="inlineStr">
         <is>
-          <t>Runs a memory read/write functional stress test with swap disabled during the run.</t>
+          <t>Checks the GlacierPeak's own network interface MAC address (read via ifconfig enm0 over SSH to the GP SoC) against mac[0].</t>
         </is>
       </c>
       <c r="D74" s="40" t="inlineStr">
         <is>
-          <t>PASS if the test command's exit code is 0.</t>
-        </is>
-      </c>
-      <c r="E74" s="40" t="inlineStr">
-        <is>
-          <t>Maps specific nonzero return codes to human-readable error names in the failure log message.</t>
-        </is>
-      </c>
+          <t>PASS if the parsed ether MAC equals getConfigValue('mac')[0] (uppercased, colon-stripped).</t>
+        </is>
+      </c>
+      <c r="E74" s="40" t="n"/>
       <c r="F74" s="75" t="n"/>
       <c r="G74" s="55" t="b">
         <v>0</v>
@@ -9128,28 +9095,28 @@
       <c r="K74" s="39" t="n"/>
       <c r="L74" s="51" t="n"/>
     </row>
-    <row r="75" ht="67.5" customHeight="1" s="80">
+    <row r="75" ht="135" customHeight="1" s="80">
       <c r="A75" s="76" t="n">
         <v>72</v>
       </c>
       <c r="B75" s="43" t="inlineStr">
         <is>
-          <t>pcie_manticore_log_chk</t>
+          <t>fpga_gp_status_chk</t>
         </is>
       </c>
       <c r="C75" s="43" t="inlineStr">
         <is>
-          <t>Reads the Manticore chip's debug log (cerberus_utility debuglogread), verifies the FW version recorded in the log matches expected, checks CS0/CS1 flash device consistency, scans for uncleared error codes since the last boot, and scans for unfiltered Warning/Error lines against a configurable skip-pattern list — clearing the log only after a full PASS.</t>
+          <t>Runs fpgadiagnostics -dumpHealth (via a stage-appropriate SSH route: direct M3, RM-jumper M3, or RM-serial-proxy M5) and parses per-subsystem [FPGA-XXX] health lines, with specific waivers for known FPGA-NETWORK and FPGA-CONFIG warnings, and a one-time auto-reboot self-heal if the PCIe link status reads "WARNING" while in App mode.</t>
         </is>
       </c>
       <c r="D75" s="40" t="inlineStr">
         <is>
-          <t>PASS only if: (1) FW version found in log matches pcie_manticore_ver, (2) Port 1 CS0/CS1 vendor+device+capacity match each other, (3) no known bad error codes (0x7f001e0c/0d/0e, 0x7f001d05, 0x7f001d10) appear after the last-boot marker, (4) no unfiltered Warning/Error lines appear after the last-boot marker.</t>
+          <t>PASS if no un-waived [FPGA-XXX] line fails its ] OK [ check.</t>
         </is>
       </c>
       <c r="E75" s="40" t="inlineStr">
         <is>
-          <t>If the log is completely empty of a FW-version line, it triggers an AC power cycle as a recovery action and still FAILs the current pass (log message: "please AC the server"). pcie_manticore_debuglog_skip config defines patterns to exclude from the Warning/Error scan</t>
+          <t>Likely bug: in the FPGA-NETWORK-on-M5 branch, the failure path does isfail += 1 — but the function only ever initializes a variable named fail = 0, never isfail. If that exact branch is hit (M5 stage, FPGA-NETWORK reports non-OK, and the message isn't the specific waived "one or more network links down" string), this will raise NameError: name 'isfail' is not defined instead of cleanly failing the test. Also implements a reboot self-heal: if PCIe status is "WARNING" while FPGA is in App mode (config_status == "0") and no .reboot marker file exists yet for this unit, it touches the marker and issues reboot immediately rather than failing — the next run after reboot either clears (marker removed, PASS) or fails hard if the WARNING persists (marker already present).</t>
         </is>
       </c>
       <c r="F75" s="75" t="n"/>
@@ -9164,167 +9131,63 @@
       <c r="K75" s="39" t="n"/>
       <c r="L75" s="51" t="n"/>
     </row>
-    <row r="76" ht="67.5" customHeight="1" s="80">
-      <c r="A76" s="76" t="n">
+    <row r="76" s="80">
+      <c r="A76" s="81" t="n">
         <v>73</v>
       </c>
-      <c r="B76" s="43" t="inlineStr">
-        <is>
-          <t>pcie_tip_log_chk</t>
-        </is>
-      </c>
-      <c r="C76" s="43" t="inlineStr">
-        <is>
-          <t>Reads the Hydra/TIP chip's debug log (cerberus_utility debuglogread), verifies the FW version recorded in the log matches expected, checks CS0/CS1 flash device consistency, scans for uncleared error codes since the last boot, and scans for unfiltered Warning/Error lines against a configurable skip-pattern list — clearing the log only after a full PASS.</t>
-        </is>
-      </c>
-      <c r="D76" s="40" t="inlineStr">
-        <is>
-          <t>PASS if: (1) the log contains a "Cerberus main flash" entry at all (else AC-cycle + FAIL), (2) main/recovery flash vendor+device+capacity match, (3) no unfiltered Warning/Error tagged lines appear after the last-boot marker.</t>
-        </is>
-      </c>
-      <c r="E76" s="40" t="inlineStr">
-        <is>
-          <t>The Warning/Error scan here additionally requires the tag field (3rd |-delimited column) itself contain "Warning" or "Error", not just the whole line.</t>
-        </is>
-      </c>
-      <c r="F76" s="75" t="n"/>
-      <c r="G76" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="H76" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="I76" s="55" t="n"/>
-      <c r="J76" s="55" t="n"/>
-      <c r="K76" s="39" t="n"/>
-      <c r="L76" s="51" t="n"/>
-    </row>
-    <row r="77" ht="27" customHeight="1" s="80">
-      <c r="A77" s="76" t="n">
-        <v>74</v>
-      </c>
-      <c r="B77" s="43" t="inlineStr">
-        <is>
-          <t>fpga_gp_mac_chk</t>
-        </is>
-      </c>
-      <c r="C77" s="43" t="inlineStr">
-        <is>
-          <t>Checks the GlacierPeak's own network interface MAC address (read via ifconfig enm0 over SSH to the GP SoC) against mac[0].</t>
-        </is>
-      </c>
-      <c r="D77" s="40" t="inlineStr">
-        <is>
-          <t>PASS if the parsed ether MAC equals getConfigValue('mac')[0] (uppercased, colon-stripped).</t>
-        </is>
-      </c>
-      <c r="E77" s="40" t="n"/>
-      <c r="F77" s="75" t="n"/>
-      <c r="G77" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="H77" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="I77" s="55" t="n"/>
-      <c r="J77" s="55" t="n"/>
-      <c r="K77" s="39" t="n"/>
-      <c r="L77" s="51" t="n"/>
-    </row>
-    <row r="78" ht="135" customHeight="1" s="80">
-      <c r="A78" s="76" t="n">
-        <v>75</v>
-      </c>
-      <c r="B78" s="43" t="inlineStr">
-        <is>
-          <t>fpga_gp_status_chk</t>
-        </is>
-      </c>
-      <c r="C78" s="43" t="inlineStr">
-        <is>
-          <t>Runs fpgadiagnostics -dumpHealth (via a stage-appropriate SSH route: direct M3, RM-jumper M3, or RM-serial-proxy M5) and parses per-subsystem [FPGA-XXX] health lines, with specific waivers for known FPGA-NETWORK and FPGA-CONFIG warnings, and a one-time auto-reboot self-heal if the PCIe link status reads "WARNING" while in App mode.</t>
-        </is>
-      </c>
-      <c r="D78" s="40" t="inlineStr">
-        <is>
-          <t>PASS if no un-waived [FPGA-XXX] line fails its ] OK [ check.</t>
-        </is>
-      </c>
-      <c r="E78" s="40" t="inlineStr">
-        <is>
-          <t>Likely bug: in the FPGA-NETWORK-on-M5 branch, the failure path does isfail += 1 — but the function only ever initializes a variable named fail = 0, never isfail. If that exact branch is hit (M5 stage, FPGA-NETWORK reports non-OK, and the message isn't the specific waived "one or more network links down" string), this will raise NameError: name 'isfail' is not defined instead of cleanly failing the test. Also implements a reboot self-heal: if PCIe status is "WARNING" while FPGA is in App mode (config_status == "0") and no .reboot marker file exists yet for this unit, it touches the marker and issues reboot immediately rather than failing — the next run after reboot either clears (marker removed, PASS) or fails hard if the WARNING persists (marker already present).</t>
-        </is>
-      </c>
-      <c r="F78" s="75" t="n"/>
-      <c r="G78" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="H78" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="I78" s="55" t="n"/>
-      <c r="J78" s="55" t="n"/>
-      <c r="K78" s="39" t="n"/>
-      <c r="L78" s="51" t="n"/>
-    </row>
-    <row r="79" customFormat="1" s="55">
-      <c r="A79" s="81" t="n">
-        <v>76</v>
-      </c>
-      <c r="B79" s="82" t="inlineStr">
+      <c r="B76" s="82" t="inlineStr">
         <is>
           <t>pcie_cap_uart_chk</t>
         </is>
       </c>
-      <c r="C79" s="82" t="inlineStr">
+      <c r="C76" s="82" t="inlineStr">
         <is>
           <t>This test verifies the UART communication link between the BMC and the Castle Peak (CaP) card. It ensures that the BMC can successfully establish a UART session with the CaP device.</t>
         </is>
       </c>
-      <c r="D79" s="83" t="inlineStr">
+      <c r="D76" s="83" t="inlineStr">
         <is>
           <t>- BMC must be able to initiate and maintain a stable UART connection to the CaP card
 - The terminal must respond with expected outputs or prompt</t>
         </is>
       </c>
-      <c r="E79" s="83" t="n"/>
-      <c r="F79" s="84" t="inlineStr">
+      <c r="E76" s="83" t="n"/>
+      <c r="F76" s="84" t="inlineStr">
         <is>
           <t>[CMD] Send ssh command</t>
         </is>
       </c>
-      <c r="G79" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="H79" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="I79" s="84" t="n"/>
-      <c r="J79" s="84" t="n"/>
-      <c r="K79" s="85" t="n"/>
-      <c r="L79" s="86" t="n"/>
-    </row>
-    <row r="80" s="80">
-      <c r="A80" s="81" t="n">
-        <v>77</v>
-      </c>
-      <c r="B80" s="82" t="inlineStr">
+      <c r="G76" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="H76" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="I76" s="84" t="n"/>
+      <c r="J76" s="84" t="n"/>
+      <c r="K76" s="85" t="n"/>
+      <c r="L76" s="86" t="n"/>
+    </row>
+    <row r="77" s="80">
+      <c r="A77" s="81" t="n">
+        <v>74</v>
+      </c>
+      <c r="B77" s="82" t="inlineStr">
         <is>
           <t>pcie_cap_ppk_security_chk</t>
         </is>
       </c>
-      <c r="C80" s="82" t="inlineStr">
+      <c r="C77" s="82" t="inlineStr">
         <is>
           <t>Execute PPK test to check CaP card secure status.</t>
         </is>
       </c>
-      <c r="D80" s="83" t="inlineStr">
+      <c r="D77" s="83" t="inlineStr">
         <is>
           <t>Pass - return 0; Fail - return 1</t>
         </is>
       </c>
-      <c r="E80" s="83" t="inlineStr">
+      <c r="E77" s="83" t="inlineStr">
         <is>
           <t>- CMC (Tahoe)
 - OMC (Overlake Mgmt. Controller)
@@ -9336,45 +9199,153 @@
 &gt;&gt;&gt; Will be implemented in DVT.</t>
         </is>
       </c>
-      <c r="F80" s="84" t="inlineStr">
+      <c r="F77" s="84" t="inlineStr">
         <is>
           <t>"cerberus_utility fwversion
 cat obmc-console-OVL.log"</t>
         </is>
       </c>
-      <c r="G80" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="H80" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="I80" s="84" t="n"/>
-      <c r="J80" s="84" t="n"/>
-      <c r="K80" s="85" t="n"/>
-      <c r="L80" s="86" t="n"/>
-    </row>
-    <row r="81" ht="27" customHeight="1" s="80">
+      <c r="G77" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="H77" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="I77" s="84" t="n"/>
+      <c r="J77" s="84" t="n"/>
+      <c r="K77" s="85" t="n"/>
+      <c r="L77" s="86" t="n"/>
+    </row>
+    <row r="78" ht="27" customHeight="1" s="80">
+      <c r="A78" s="76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B78" s="43" t="inlineStr">
+        <is>
+          <t>bmc_fan_qty_chk</t>
+        </is>
+      </c>
+      <c r="C78" s="43" t="inlineStr">
+        <is>
+          <t>Checks the number of fans reporting an "OK" SDR state against SF's bmc_fan_qty.</t>
+        </is>
+      </c>
+      <c r="D78" s="40" t="inlineStr">
+        <is>
+          <t>PASS if ipmitool sdr elist | grep -E "^Fan" | grep -ic ok equals getConfigValue('bmc_fan_qty').</t>
+        </is>
+      </c>
+      <c r="E78" s="40" t="inlineStr">
+        <is>
+          <t>Simple count check; no self-heal (a missing/failed fan is a physical issue, not a firmware one).</t>
+        </is>
+      </c>
+      <c r="F78" s="75" t="n"/>
+      <c r="G78" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="H78" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="I78" s="55" t="n"/>
+      <c r="J78" s="55" t="n"/>
+      <c r="K78" s="39" t="n"/>
+      <c r="L78" s="51" t="n"/>
+    </row>
+    <row r="79" ht="40.5" customFormat="1" customHeight="1" s="55">
+      <c r="A79" s="76" t="n">
+        <v>76</v>
+      </c>
+      <c r="B79" s="43" t="inlineStr">
+        <is>
+          <t>bmc_fan_speed_chk</t>
+        </is>
+      </c>
+      <c r="C79" s="43" t="inlineStr">
+        <is>
+          <t>Sweeps fan duty cycle through 100%/50%/30% (100% skipped at M1 stage per an old thermal-noise waiver) and checks each fan's measured RPM against inlet/outlet min/max bounds for the detected fan vendor.</t>
+        </is>
+      </c>
+      <c r="D79" s="40" t="inlineStr">
+        <is>
+          <t>PASS if every fan's RPM at every tested duty point falls within its vendor-specific inlet/outlet min/max range.</t>
+        </is>
+      </c>
+      <c r="E79" s="40" t="inlineStr">
+        <is>
+          <t>After the sweep, fan mode is forced back to auto unconditionally, and at M1 stage specifically it's additionally set to a fixed 50% manual.</t>
+        </is>
+      </c>
+      <c r="F79" s="75" t="n"/>
+      <c r="G79" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="H79" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="I79" s="55" t="n"/>
+      <c r="J79" s="55" t="n"/>
+      <c r="K79" s="39" t="n"/>
+      <c r="L79" s="51" t="n"/>
+    </row>
+    <row r="80" ht="53.25" customHeight="1" s="80">
+      <c r="A80" s="76" t="n">
+        <v>77</v>
+      </c>
+      <c r="B80" s="43" t="inlineStr">
+        <is>
+          <t>storage_nvme_quantity_chk</t>
+        </is>
+      </c>
+      <c r="C80" s="43" t="inlineStr">
+        <is>
+          <t>Checks the number of enumerated NVMe devices against stge_nvme_cnt, with a self-heal attempt if more drives are found than expected</t>
+        </is>
+      </c>
+      <c r="D80" s="40" t="inlineStr">
+        <is>
+          <t>PASS if NVMe count equals stge_nvme_cnt (or the M1-stage E1.S-specific count variants).</t>
+        </is>
+      </c>
+      <c r="E80" s="40" t="inlineStr">
+        <is>
+          <t>Task 40165: "E1.S may arrive in MPF/TCG-locked state (e.g. swapped E1.S_2 with half-finished TCG)" — the recovery workaround is only attempted when the count is higher than expected, not lower; a lower-than-expected count goes straight to FAIL with no remediation.</t>
+        </is>
+      </c>
+      <c r="F80" s="75" t="n"/>
+      <c r="G80" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="H80" s="55" t="b">
+        <v>0</v>
+      </c>
+      <c r="I80" s="55" t="n"/>
+      <c r="J80" s="55" t="n"/>
+      <c r="K80" s="39" t="n"/>
+      <c r="L80" s="51" t="n"/>
+    </row>
+    <row r="81" ht="40.5" customHeight="1" s="80">
       <c r="A81" s="76" t="n">
         <v>78</v>
       </c>
       <c r="B81" s="43" t="inlineStr">
         <is>
-          <t>bmc_fan_qty_chk</t>
+          <t>storage_hdd_func_test</t>
         </is>
       </c>
       <c r="C81" s="43" t="inlineStr">
         <is>
-          <t>Checks the number of fans reporting an "OK" SDR state against SF's bmc_fan_qty.</t>
+          <t>Runs a random-access read/write functional test (tools/HDDtest --random) against every enumerated SATA and NVMe device.</t>
         </is>
       </c>
       <c r="D81" s="40" t="inlineStr">
         <is>
-          <t>PASS if ipmitool sdr elist | grep -E "^Fan" | grep -ic ok equals getConfigValue('bmc_fan_qty').</t>
+          <t>PASS only if every device's HDDtest --random run returns 0; fails fast on the first bad device.</t>
         </is>
       </c>
       <c r="E81" s="40" t="inlineStr">
         <is>
-          <t>Simple count check; no self-heal (a missing/failed fan is a physical issue, not a firmware one).</t>
+          <t>No retry/self-heal — a single device failure stops the loop and fails the whole test item immediately, so devices later in the enumeration order are never tested in that pass.</t>
         </is>
       </c>
       <c r="F81" s="75" t="n"/>
@@ -9395,22 +9366,22 @@
       </c>
       <c r="B82" s="43" t="inlineStr">
         <is>
-          <t>bmc_fan_speed_chk</t>
+          <t>storage_nvme_smart_chk</t>
         </is>
       </c>
       <c r="C82" s="43" t="inlineStr">
         <is>
-          <t>Sweeps fan duty cycle through 100%/50%/30% (100% skipped at M1 stage per an old thermal-noise waiver) and checks each fan's measured RPM against inlet/outlet min/max bounds for the detected fan vendor.</t>
+          <t>Reads nvme smart-log for every enumerated NVMe device and checks Critical Warning, Percentage Used, Available Spare, Media Errors, and (Intel-only) CRC Error Count against thresholds.</t>
         </is>
       </c>
       <c r="D82" s="40" t="inlineStr">
         <is>
-          <t>PASS if every fan's RPM at every tested duty point falls within its vendor-specific inlet/outlet min/max range.</t>
+          <t>PASS if, per device: critical_warning == 0 (hex), percentage_used under threshold, available_spare &gt;= 99%, media_errors == 0, and (Intel drives only) CRC error count hasn't increased since the last recorded check.</t>
         </is>
       </c>
       <c r="E82" s="40" t="inlineStr">
         <is>
-          <t>After the sweep, fan mode is forced back to auto unconditionally, and at M1 stage specifically it's additionally set to a fixed 50% manual.</t>
+          <t>Percentage-Used check has a two-stage threshold — primary 5%; if exceeded, re-checked against stge_scale_pu_threshold config and only fails if it also exceeds that secondary threshold..</t>
         </is>
       </c>
       <c r="F82" s="75" t="n"/>
@@ -9431,22 +9402,22 @@
       </c>
       <c r="B83" s="43" t="inlineStr">
         <is>
-          <t>storage_nvme_quantity_chk</t>
+          <t>pcie_device_chk</t>
         </is>
       </c>
       <c r="C83" s="43" t="inlineStr">
         <is>
-          <t>Checks the number of enumerated NVMe devices against stge_nvme_cnt, with a self-heal attempt if more drives are found than expected</t>
+          <t>Checks each configured PCIe device's link speed, width, and (optionally) vendor:device ID against a hardcoded expected list, plus verifies all E1.S slots use a consistent vendor (no mixed Samsung/Hynix).</t>
         </is>
       </c>
       <c r="D83" s="40" t="inlineStr">
         <is>
-          <t>PASS if NVMe count equals stge_nvme_cnt (or the M1-stage E1.S-specific count variants).</t>
+          <t>PASS if, for every entry in the resolved pcie device list, the lspci -D -nn -vvv reported speed/width (and vendor:device ID, if the config line includes it) match, AND all E1.S bus entries report the same vendor ID. FAIL on any mismatch or malformed config-line entry.</t>
         </is>
       </c>
       <c r="E83" s="40" t="inlineStr">
         <is>
-          <t>Task 40165: "E1.S may arrive in MPF/TCG-locked state (e.g. swapped E1.S_2 with half-finished TCG)" — the recovery workaround is only attempted when the count is higher than expected, not lower; a lower-than-expected count goes straight to FAIL with no remediation.</t>
+          <t>VID:PID checking can be disabled via an args={"viddid": False} option.</t>
         </is>
       </c>
       <c r="F83" s="75" t="n"/>
@@ -9461,28 +9432,28 @@
       <c r="K83" s="39" t="n"/>
       <c r="L83" s="51" t="n"/>
     </row>
-    <row r="84" ht="40.5" customHeight="1" s="80">
+    <row r="84" ht="27" customHeight="1" s="80">
       <c r="A84" s="76" t="n">
         <v>81</v>
       </c>
       <c r="B84" s="43" t="inlineStr">
         <is>
-          <t>storage_hdd_func_test</t>
+          <t>pcie_cmp_chk</t>
         </is>
       </c>
       <c r="C84" s="43" t="inlineStr">
         <is>
-          <t>Runs a random-access read/write functional test (tools/HDDtest --random) against every enumerated SATA and NVMe device.</t>
+          <t>Compares the full enumerated PCIe device topology (PCIe_py -c) against a golden reference file specific to this model/PN/M.2-vendor/E1.S-vendor.</t>
         </is>
       </c>
       <c r="D84" s="40" t="inlineStr">
         <is>
-          <t>PASS only if every device's HDDtest --random run returns 0; fails fast on the first bad device.</t>
+          <t>PASS if PCIe_py -c {goldenfile} returns 0.</t>
         </is>
       </c>
       <c r="E84" s="40" t="inlineStr">
         <is>
-          <t>No retry/self-heal — a single device failure stops the loop and fails the whole test item immediately, so devices later in the enumeration order are never tested in that pass.</t>
+          <t>Auto-generating the golden file on first run for a given combination.</t>
         </is>
       </c>
       <c r="F84" s="75" t="n"/>
@@ -9497,28 +9468,28 @@
       <c r="K84" s="39" t="n"/>
       <c r="L84" s="51" t="n"/>
     </row>
-    <row r="85" ht="40.5" customHeight="1" s="80">
+    <row r="85" ht="27" customHeight="1" s="80">
       <c r="A85" s="76" t="n">
         <v>82</v>
       </c>
       <c r="B85" s="43" t="inlineStr">
         <is>
-          <t>storage_nvme_smart_chk</t>
+          <t>bmc_batvolt_chk</t>
         </is>
       </c>
       <c r="C85" s="43" t="inlineStr">
         <is>
-          <t>Reads nvme smart-log for every enumerated NVMe device and checks Critical Warning, Percentage Used, Available Spare, Media Errors, and (Intel-only) CRC Error Count against thresholds.</t>
+          <t>Checks the RTC/CMOS battery voltage sensor reading against a configured lower bound.</t>
         </is>
       </c>
       <c r="D85" s="40" t="inlineStr">
         <is>
-          <t>PASS if, per device: critical_warning == 0 (hex), percentage_used under threshold, available_spare &gt;= 99%, media_errors == 0, and (Intel drives only) CRC error count hasn't increased since the last recorded check.</t>
+          <t>PASS if ipmitool sdr elist | grep 'BAT' | awk '{print $9}' (as float) is &gt;= bmc_batvolt_lower_bound.</t>
         </is>
       </c>
       <c r="E85" s="40" t="inlineStr">
         <is>
-          <t>Percentage-Used check has a two-stage threshold — primary 5%; if exceeded, re-checked against stge_scale_pu_threshold config and only fails if it also exceeds that secondary threshold..</t>
+          <t>FAILs explicitly if ipmitool can't detect the battery voltage sensor at all — distinguished from a low-but-present reading.</t>
         </is>
       </c>
       <c r="F85" s="75" t="n"/>
@@ -9533,30 +9504,26 @@
       <c r="K85" s="39" t="n"/>
       <c r="L85" s="51" t="n"/>
     </row>
-    <row r="86" ht="53.25" customHeight="1" s="80">
+    <row r="86" ht="27" customHeight="1" s="80">
       <c r="A86" s="76" t="n">
         <v>83</v>
       </c>
       <c r="B86" s="43" t="inlineStr">
         <is>
-          <t>pcie_device_chk</t>
+          <t>tpm_qty_chk</t>
         </is>
       </c>
       <c r="C86" s="43" t="inlineStr">
         <is>
-          <t>Checks each configured PCIe device's link speed, width, and (optionally) vendor:device ID against a hardcoded expected list, plus verifies all E1.S slots use a consistent vendor (no mixed Samsung/Hynix).</t>
+          <t>Checks the number of detected TPM 2.0 devices against an internal expected count (self._tpm_num, a class attribute rather than an SF config value).</t>
         </is>
       </c>
       <c r="D86" s="40" t="inlineStr">
         <is>
-          <t>PASS if, for every entry in the resolved pcie device list, the lspci -D -nn -vvv reported speed/width (and vendor:device ID, if the config line includes it) match, AND all E1.S bus entries report the same vendor ID. FAIL on any mismatch or malformed config-line entry.</t>
-        </is>
-      </c>
-      <c r="E86" s="40" t="inlineStr">
-        <is>
-          <t>VID:PID checking can be disabled via an args={"viddid": False} option.</t>
-        </is>
-      </c>
+          <t>PASS if ls /dev/tpm* | grep -v tpmrm | wc -l equals self._tpm_num.</t>
+        </is>
+      </c>
+      <c r="E86" s="40" t="n"/>
       <c r="F86" s="75" t="n"/>
       <c r="G86" s="55" t="b">
         <v>0</v>
@@ -9575,142 +9542,38 @@
       </c>
       <c r="B87" s="43" t="inlineStr">
         <is>
-          <t>pcie_cmp_chk</t>
+          <t>tpm_func_test</t>
         </is>
       </c>
       <c r="C87" s="43" t="inlineStr">
         <is>
-          <t>Compares the full enumerated PCIe device topology (PCIe_py -c) against a golden reference file specific to this model/PN/M.2-vendor/E1.S-vendor.</t>
+          <t>Runs the TPM 2.0 full and not-full self-tests (eltt2 -t full / eltt2 -t not_full) and a "get value" sanity read (eltt2 -g).</t>
         </is>
       </c>
       <c r="D87" s="40" t="inlineStr">
         <is>
-          <t>PASS if PCIe_py -c {goldenfile} returns 0.</t>
-        </is>
-      </c>
-      <c r="E87" s="40" t="inlineStr">
-        <is>
-          <t>Auto-generating the golden file on first run for a given combination.</t>
-        </is>
-      </c>
-      <c r="F87" s="75" t="n"/>
-      <c r="G87" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="H87" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="I87" s="55" t="n"/>
-      <c r="J87" s="55" t="n"/>
-      <c r="K87" s="39" t="n"/>
-      <c r="L87" s="51" t="n"/>
-    </row>
-    <row r="88" ht="27" customHeight="1" s="80">
-      <c r="A88" s="76" t="n">
-        <v>85</v>
-      </c>
-      <c r="B88" s="43" t="inlineStr">
-        <is>
-          <t>bmc_batvolt_chk</t>
-        </is>
-      </c>
-      <c r="C88" s="43" t="inlineStr">
-        <is>
-          <t>Checks the RTC/CMOS battery voltage sensor reading against a configured lower bound.</t>
-        </is>
-      </c>
-      <c r="D88" s="40" t="inlineStr">
-        <is>
-          <t>PASS if ipmitool sdr elist | grep 'BAT' | awk '{print $9}' (as float) is &gt;= bmc_batvolt_lower_bound.</t>
-        </is>
-      </c>
-      <c r="E88" s="40" t="inlineStr">
-        <is>
-          <t>FAILs explicitly if ipmitool can't detect the battery voltage sensor at all — distinguished from a low-but-present reading.</t>
-        </is>
-      </c>
-      <c r="F88" s="75" t="n"/>
-      <c r="G88" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="H88" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="I88" s="55" t="n"/>
-      <c r="J88" s="55" t="n"/>
-      <c r="K88" s="39" t="n"/>
-      <c r="L88" s="51" t="n"/>
-    </row>
-    <row r="89" ht="27" customHeight="1" s="80">
-      <c r="A89" s="76" t="n">
-        <v>86</v>
-      </c>
-      <c r="B89" s="43" t="inlineStr">
-        <is>
-          <t>tpm_qty_chk</t>
-        </is>
-      </c>
-      <c r="C89" s="43" t="inlineStr">
-        <is>
-          <t>Checks the number of detected TPM 2.0 devices against an internal expected count (self._tpm_num, a class attribute rather than an SF config value).</t>
-        </is>
-      </c>
-      <c r="D89" s="40" t="inlineStr">
-        <is>
-          <t>PASS if ls /dev/tpm* | grep -v tpmrm | wc -l equals self._tpm_num.</t>
-        </is>
-      </c>
-      <c r="E89" s="40" t="n"/>
-      <c r="F89" s="75" t="n"/>
-      <c r="G89" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="H89" s="55" t="b">
-        <v>0</v>
-      </c>
-      <c r="I89" s="55" t="n"/>
-      <c r="J89" s="55" t="n"/>
-      <c r="K89" s="39" t="n"/>
-      <c r="L89" s="51" t="n"/>
-    </row>
-    <row r="90" ht="27" customHeight="1" s="80">
-      <c r="A90" s="76" t="n">
-        <v>87</v>
-      </c>
-      <c r="B90" s="43" t="inlineStr">
-        <is>
-          <t>tpm_func_test</t>
-        </is>
-      </c>
-      <c r="C90" s="43" t="inlineStr">
-        <is>
-          <t>Runs the TPM 2.0 full and not-full self-tests (eltt2 -t full / eltt2 -t not_full) and a "get value" sanity read (eltt2 -g).</t>
-        </is>
-      </c>
-      <c r="D90" s="40" t="inlineStr">
-        <is>
           <t>PASS only if all three sub-commands (full selftest, not-full selftest, get-value) return exit code 0.</t>
         </is>
       </c>
-      <c r="E90" s="40" t="n"/>
-      <c r="F90" s="43" t="inlineStr">
+      <c r="E87" s="40" t="n"/>
+      <c r="F87" s="43" t="inlineStr">
         <is>
           <t>[ Check powershelf firmware version ] show powershelf psu info -s {INDEX} Capability IC Device ID Manufacturer ID Manufacturer Model Manufacturer Revision Manufacturer Serial Completion Code - - - - - If mismatch - - - - - [ Upgrade Rack SCM firmware version ] C heck fw package exists in RM show manager tftp list Upload fw to Rack-SCM set manager tftp get -s {IP} -f {FILE} Fw Upgrade set manager cerberus cmd -c pcdupdate /usr/srvroot/shared/{FILE}</t>
         </is>
       </c>
-      <c r="G90" s="47" t="n"/>
-      <c r="H90" s="47" t="b">
+      <c r="G87" s="47" t="n"/>
+      <c r="H87" s="47" t="b">
         <v>1</v>
       </c>
-      <c r="I90" s="41" t="inlineStr">
+      <c r="I87" s="41" t="inlineStr">
         <is>
           <t xml:space="preserve">PSU SN (traceability only, not a pass/fail criterion): ['P831061850674041', 'P831061851642041', 'P831061851637041', 'P831061850968041', 'P831061824386041', 'P831061851683041']
 [PASS] Check PSU location PASS
 </t>
         </is>
       </c>
-      <c r="J90" s="41" t="n"/>
-      <c r="K90" s="42" t="inlineStr">
+      <c r="J87" s="41" t="n"/>
+      <c r="K87" s="42" t="inlineStr">
         <is>
           <t>Rack SCM Powershelf PSU 1 Version Check PASS. EXP: 000F0F00 GET: 000F0F00
 Rack SCM Powershelf PSU 2 Version Check PASS. EXP: 000F0F00 GET: 000F0F00
@@ -9722,7 +9585,207 @@
 [PASS] Rack Power Shelf(PSU) FW CHECK PASS</t>
         </is>
       </c>
-      <c r="L90" s="31" t="n"/>
+      <c r="L87" s="31" t="n"/>
+      <c r="M87" s="18" t="n"/>
+      <c r="N87" s="37" t="n"/>
+      <c r="O87" s="18" t="n"/>
+      <c r="P87" s="19" t="n"/>
+      <c r="Q87" s="17" t="n"/>
+      <c r="R87" s="17" t="n"/>
+      <c r="S87" s="17" t="n"/>
+      <c r="T87" s="17" t="n"/>
+      <c r="U87" s="17" t="n"/>
+      <c r="V87" s="17" t="n"/>
+      <c r="W87" s="17" t="n"/>
+      <c r="X87" s="17" t="n"/>
+      <c r="Y87" s="17" t="n"/>
+    </row>
+    <row r="88" s="80">
+      <c r="A88" s="81" t="n">
+        <v>85</v>
+      </c>
+      <c r="B88" s="82" t="inlineStr">
+        <is>
+          <t>ccr_test</t>
+        </is>
+      </c>
+      <c r="C88" s="82" t="inlineStr">
+        <is>
+          <t>Check switch cable mapping</t>
+        </is>
+      </c>
+      <c r="D88" s="83" t="inlineStr">
+        <is>
+          <t>Pass - return 0; Fail - return 1</t>
+        </is>
+      </c>
+      <c r="E88" s="83" t="inlineStr">
+        <is>
+          <t>- Only the master node initiates mapping and updates `mac_table.txt`.
+- Slave nodes wait for the file and perform comparison based on it.
+- Retry mechanism included to ensure MAC addresses are discovered after traffic generation.
+&gt;&gt;&gt;For EVT only.
+&gt;&gt;&gt;For DV NV rack only.</t>
+        </is>
+      </c>
+      <c r="F88" s="84" t="n"/>
+      <c r="G88" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="H88" s="84" t="b">
+        <v>0</v>
+      </c>
+      <c r="I88" s="84" t="n"/>
+      <c r="J88" s="84" t="n"/>
+      <c r="K88" s="85" t="n"/>
+      <c r="L88" s="86" t="n"/>
+    </row>
+    <row r="89" s="80">
+      <c r="A89" s="76" t="n">
+        <v>86</v>
+      </c>
+      <c r="B89" s="43" t="inlineStr">
+        <is>
+          <t>uut_pic_test</t>
+        </is>
+      </c>
+      <c r="C89" s="43" t="inlineStr">
+        <is>
+          <t>Runs a PIC (Programmable Interrupt Controller) functional test command.</t>
+        </is>
+      </c>
+      <c r="D89" s="40" t="inlineStr">
+        <is>
+          <t>PASS if self.cmd_lst['uut_test_pic'] returns exit code 0.</t>
+        </is>
+      </c>
+      <c r="E89" s="40" t="inlineStr">
+        <is>
+          <t>Minimal wrapper, no special edge cases.</t>
+        </is>
+      </c>
+      <c r="F89" s="43" t="inlineStr">
+        <is>
+          <t>[Check RM Cerberus Version] show manager cerberus version - - - - - If mismatch - - - - - [Upgrade RM Cerberus] set manager cerberus update -f {FILE} [Check RM Cerberus PCD ID] set manager cerberus cmd -c pcdid - - - - - If mismatch - - - - - [Upgrade RM Cerberus PCD ID] set manager cerberus cmd -c pcdupdate /usr/srvroot/shared/{FILE} [Check RM Cerberus PFM ID] show manager cerberus pfm id -p 1 -r 0 - - - - - If mismatch - - - - - [Upgrade RM Cerberus PFM ID] set manager cerberus pfm update -f {FILE} -p 1 [Get RM information FAIL] show manager version - - - - - If mismatch - - - - - [Upgrade RM information] set manager fwupdate -f {FILE} [Check RM CPLD version] show manager cpld version - - - - - If mismatch - - - - - [Upgrade RM CPLD version] set manager cpld update -f {FILE}</t>
+        </is>
+      </c>
+      <c r="G89" s="47" t="n"/>
+      <c r="H89" s="47" t="b">
+        <v>1</v>
+      </c>
+      <c r="I89" s="41" t="inlineStr">
+        <is>
+          <t>Rack SCM Powershelf PSU 1 Version Check PASS. EXP: 000F0F00 GET: 000F0F00
+...
+Rack SCM Powershelf PSU 12 Version Check PASS. EXP: 000F0F00 GET: 000F0F00
+POWERSHELF PSU INFO AND VERSION CHECK PASS.
+[PASS] Rack Power Shelf(PSU) FW CHECK PASS</t>
+        </is>
+      </c>
+      <c r="J89" s="41" t="n"/>
+      <c r="K89" s="42" t="inlineStr">
+        <is>
+          <t>Check RM Cerberus Version PASS. Exp:1.5.7.5 Get:1.5.7.5
+Check RM PCD Version ID PASS. SF:0x1 Get:0x1
+Check RM PCD Platform ID PASS. SF:M4011 Get:M4011
+Check RM PFM ID Version PASS. Exp:0x3DA Get:0x3da
+Check RM information PASS. Exp:1.31.6, get_rootfs:1.31.6, get_kernel:1.31.6, get_package:1.31.6, get_device_tree:1.31.6
+Check RM CPLD Version PASS. Exp:V3.5 Get:V3.5
+Get RM Manager Type PASS. GET : 3OU_POWER_SHELF; EXP : 3OU_POWER_SHELF
+Get RM Host Name PASS. GET : rm-hs-sr2-m4010; EXP : rm-hs-sr2-m4010
+Get RM Uboot Version PASS. GET : 2021.01; EXP : 2021.01
+Get RM NTP Server PASS. GET : 172.52.0.1; EXP : 172.52.0.1
+Check All RM Version PASS.</t>
+        </is>
+      </c>
+      <c r="L89" s="31" t="inlineStr">
+        <is>
+          <t>Matches CRD: Cerberus 1.5.7.5, PFMID 0x3DA, PCD M4011/0x1, RM 1.31.6, CPLD V3.5.</t>
+        </is>
+      </c>
+      <c r="M89" s="18" t="n"/>
+      <c r="N89" s="37" t="n"/>
+      <c r="O89" s="18" t="n"/>
+      <c r="P89" s="19" t="n"/>
+      <c r="Q89" s="17" t="n"/>
+      <c r="R89" s="17" t="n"/>
+      <c r="S89" s="17" t="n"/>
+      <c r="T89" s="17" t="n"/>
+      <c r="U89" s="17" t="n"/>
+      <c r="V89" s="17" t="n"/>
+      <c r="W89" s="17" t="n"/>
+      <c r="X89" s="17" t="n"/>
+      <c r="Y89" s="17" t="n"/>
+    </row>
+    <row r="90" s="80">
+      <c r="A90" s="76" t="n">
+        <v>87</v>
+      </c>
+      <c r="B90" s="43" t="inlineStr">
+        <is>
+          <t>uut_hpet_test</t>
+        </is>
+      </c>
+      <c r="C90" s="43" t="inlineStr">
+        <is>
+          <t>Runs an HPET (High Precision Event Timer) functional test command.</t>
+        </is>
+      </c>
+      <c r="D90" s="40" t="inlineStr">
+        <is>
+          <t>PASS if self.cmd_lst['uut_test_hpet'] returns exit code 0.</t>
+        </is>
+      </c>
+      <c r="E90" s="40" t="inlineStr">
+        <is>
+          <t>Minimal wrapper, structurally identical to uut_pic_test.</t>
+        </is>
+      </c>
+      <c r="F90" s="43" t="inlineStr">
+        <is>
+          <t>[ Get system info via RM ] show system info -i { RM_PORT } Mac Address SerialNumber BiosVersion BMCVersion CpldVersion DCSCMCpldVersion Count TotalSystemMemoryGib - - - - - If mismatch - - - - - [ Upgrade system firmware version ] set system file put -i {PORT} -f {FILE} set system bios update -i {PORT} -f {FILE} set system bmc update -i {PORT} -f {FILE}</t>
+        </is>
+      </c>
+      <c r="G90" s="47" t="b">
+        <v>1</v>
+      </c>
+      <c r="H90" s="47" t="b">
+        <v>1</v>
+      </c>
+      <c r="I90" s="41" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Mac Address              check PASS. Get:             0427283DD689, Exp:             0427283DD689
+SerialNumber             check PASS. Get:         P54376354001203A, Exp:         P54376354001203A
+BiosVersion              check PASS. Get:     C44AD.0.BS.1C11.GN.1, Exp:     C44AD.0.BS.1C11.GN.1
+BMCVersion               check PASS. Get:                  26.4.24, Exp:                  26.4.24
+ CpldVersion             check PASS. Get:                 02.06.00, Exp:                 02.06.00
+DCSCMCpldVersion         check PASS. Get:                 03.06.00, Exp:                 03.06.00
+Count                    check PASS. Get:                        2, Exp:                        2
+TotalSystemMemoryGib     check PASS. Get:                      512, Exp:                      512
+[PASS] Check system info via RM PASS
+</t>
+        </is>
+      </c>
+      <c r="J90" s="41" t="n"/>
+      <c r="K90" s="42" t="inlineStr">
+        <is>
+          <t>Mac Address              check PASS. Get:             0427283DD689, Exp:             0427283DD689
+SerialNumber             check PASS. Get:         P54376354001203A, Exp:         P54376354001203A
+BiosVersion              check PASS. Get:     C44AD.0.BS.1C11.GN.1, Exp:     C44AD.0.BS.1C11.GN.1
+BMCVersion               check PASS. Get:                  26.4.24, Exp:                  26.4.24
+CpldVersion             check PASS. Get:                 02.06.00, Exp:                 02.06.00
+DCSCMCpldVersion         check PASS. Get:                 03.06.00, Exp:                 03.06.00
+Count                    check PASS. Get:                        2, Exp:                        2
+TotalSystemMemoryGib     check PASS. Get:                      512, Exp:                      512
+[PASS] Check system info via RM PASS"</t>
+        </is>
+      </c>
+      <c r="L90" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Matches CRD: BIOS C44AD.0.BS.1C11.GN.1, BMC 26.04.24, MB CPLD 02.06.00, DC-SCM CPLD 03.06.00, 512 GiB, 2 CPU.
+</t>
+        </is>
+      </c>
       <c r="M90" s="18" t="n"/>
       <c r="N90" s="37" t="n"/>
       <c r="O90" s="18" t="n"/>
@@ -9743,12 +9806,12 @@
       </c>
       <c r="B91" s="82" t="inlineStr">
         <is>
-          <t>ccr_test</t>
+          <t>bios_cmos_test</t>
         </is>
       </c>
       <c r="C91" s="82" t="inlineStr">
         <is>
-          <t>Check switch cable mapping</t>
+          <t>Test the BIOS CMOS functionality by verifying the read/write capability of CMOS registers and checking battery and CMOS operation status.</t>
         </is>
       </c>
       <c r="D91" s="83" t="inlineStr">
@@ -9758,14 +9821,15 @@
       </c>
       <c r="E91" s="83" t="inlineStr">
         <is>
-          <t>- Only the master node initiates mapping and updates `mac_table.txt`.
-- Slave nodes wait for the file and perform comparison based on it.
-- Retry mechanism included to ensure MAC addresses are discovered after traffic generation.
-&gt;&gt;&gt;For EVT only.
-&gt;&gt;&gt;For DV NV rack only.</t>
-        </is>
-      </c>
-      <c r="F91" s="84" t="n"/>
+          <t>&gt;&gt;&gt;MTE agreed to waive in EVT. ADO#2909063</t>
+        </is>
+      </c>
+      <c r="F91" s="84" t="inlineStr">
+        <is>
+          <t>[Execute CMOS test]
+CMOStest -d</t>
+        </is>
+      </c>
       <c r="G91" s="84" t="b">
         <v>0</v>
       </c>
@@ -9777,69 +9841,40 @@
       <c r="K91" s="85" t="n"/>
       <c r="L91" s="86" t="n"/>
     </row>
-    <row r="92" s="80">
+    <row r="92" ht="27" customHeight="1" s="80">
       <c r="A92" s="76" t="n">
         <v>89</v>
       </c>
       <c r="B92" s="43" t="inlineStr">
         <is>
-          <t>uut_pic_test</t>
+          <t>bmc_sel_chk</t>
         </is>
       </c>
       <c r="C92" s="43" t="inlineStr">
         <is>
-          <t>Runs a PIC (Programmable Interrupt Controller) functional test command.</t>
+          <t>A plain BMC SEL check, run late in the flow after all functional tests have completed, right before the final SDR/dmesg/syslog snapshot and SEL clear.</t>
         </is>
       </c>
       <c r="D92" s="40" t="inlineStr">
         <is>
-          <t>PASS if self.cmd_lst['uut_test_pic'] returns exit code 0.</t>
+          <t>PASS if returns truthy (no un-whitelisted SEL entries found). FAIL otherwise.</t>
         </is>
       </c>
       <c r="E92" s="40" t="inlineStr">
         <is>
-          <t>Minimal wrapper, no special edge cases.</t>
-        </is>
-      </c>
-      <c r="F92" s="43" t="inlineStr">
-        <is>
-          <t>[Check RM Cerberus Version] show manager cerberus version - - - - - If mismatch - - - - - [Upgrade RM Cerberus] set manager cerberus update -f {FILE} [Check RM Cerberus PCD ID] set manager cerberus cmd -c pcdid - - - - - If mismatch - - - - - [Upgrade RM Cerberus PCD ID] set manager cerberus cmd -c pcdupdate /usr/srvroot/shared/{FILE} [Check RM Cerberus PFM ID] show manager cerberus pfm id -p 1 -r 0 - - - - - If mismatch - - - - - [Upgrade RM Cerberus PFM ID] set manager cerberus pfm update -f {FILE} -p 1 [Get RM information FAIL] show manager version - - - - - If mismatch - - - - - [Upgrade RM information] set manager fwupdate -f {FILE} [Check RM CPLD version] show manager cpld version - - - - - If mismatch - - - - - [Upgrade RM CPLD version] set manager cpld update -f {FILE}</t>
-        </is>
-      </c>
-      <c r="G92" s="47" t="n"/>
-      <c r="H92" s="47" t="b">
-        <v>1</v>
-      </c>
-      <c r="I92" s="41" t="inlineStr">
-        <is>
-          <t>Rack SCM Powershelf PSU 1 Version Check PASS. EXP: 000F0F00 GET: 000F0F00
-...
-Rack SCM Powershelf PSU 12 Version Check PASS. EXP: 000F0F00 GET: 000F0F00
-POWERSHELF PSU INFO AND VERSION CHECK PASS.
-[PASS] Rack Power Shelf(PSU) FW CHECK PASS</t>
-        </is>
-      </c>
-      <c r="J92" s="41" t="n"/>
-      <c r="K92" s="42" t="inlineStr">
-        <is>
-          <t>Check RM Cerberus Version PASS. Exp:1.5.7.5 Get:1.5.7.5
-Check RM PCD Version ID PASS. SF:0x1 Get:0x1
-Check RM PCD Platform ID PASS. SF:M4011 Get:M4011
-Check RM PFM ID Version PASS. Exp:0x3DA Get:0x3da
-Check RM information PASS. Exp:1.31.6, get_rootfs:1.31.6, get_kernel:1.31.6, get_package:1.31.6, get_device_tree:1.31.6
-Check RM CPLD Version PASS. Exp:V3.5 Get:V3.5
-Get RM Manager Type PASS. GET : 3OU_POWER_SHELF; EXP : 3OU_POWER_SHELF
-Get RM Host Name PASS. GET : rm-hs-sr2-m4010; EXP : rm-hs-sr2-m4010
-Get RM Uboot Version PASS. GET : 2021.01; EXP : 2021.01
-Get RM NTP Server PASS. GET : 172.52.0.1; EXP : 172.52.0.1
-Check All RM Version PASS.</t>
-        </is>
-      </c>
-      <c r="L92" s="31" t="inlineStr">
-        <is>
-          <t>Matches CRD: Cerberus 1.5.7.5, PFMID 0x3DA, PCD M4011/0x1, RM 1.31.6, CPLD V3.5.</t>
-        </is>
-      </c>
+          <t>Different call site/intent (post-functional-test SEL sweep vs. pre-test boot-time SEL sweep), same underlying logic.</t>
+        </is>
+      </c>
+      <c r="F92" s="75" t="n"/>
+      <c r="G92" s="78" t="b">
+        <v>0</v>
+      </c>
+      <c r="H92" s="78" t="b">
+        <v>0</v>
+      </c>
+      <c r="I92" s="55" t="n"/>
+      <c r="J92" s="55" t="n"/>
+      <c r="L92" s="31" t="n"/>
       <c r="M92" s="18" t="n"/>
       <c r="N92" s="37" t="n"/>
       <c r="O92" s="18" t="n"/>
@@ -9854,75 +9889,36 @@
       <c r="X92" s="17" t="n"/>
       <c r="Y92" s="17" t="n"/>
     </row>
-    <row r="93" s="80">
+    <row r="93" ht="27" customHeight="1" s="80">
       <c r="A93" s="76" t="n">
         <v>90</v>
       </c>
       <c r="B93" s="43" t="inlineStr">
         <is>
-          <t>uut_hpet_test</t>
+          <t>bmc_sdr_chk</t>
         </is>
       </c>
       <c r="C93" s="43" t="inlineStr">
         <is>
-          <t>Runs an HPET (High Precision Event Timer) functional test command.</t>
+          <t>Validates BMC Sensor Data Record contents (all sensor readings within expected bounds).</t>
         </is>
       </c>
       <c r="D93" s="40" t="inlineStr">
         <is>
-          <t>PASS if self.cmd_lst['uut_test_hpet'] returns exit code 0.</t>
-        </is>
-      </c>
-      <c r="E93" s="40" t="inlineStr">
-        <is>
-          <t>Minimal wrapper, structurally identical to uut_pic_test.</t>
-        </is>
-      </c>
-      <c r="F93" s="43" t="inlineStr">
-        <is>
-          <t>[ Get system info via RM ] show system info -i { RM_PORT } Mac Address SerialNumber BiosVersion BMCVersion CpldVersion DCSCMCpldVersion Count TotalSystemMemoryGib - - - - - If mismatch - - - - - [ Upgrade system firmware version ] set system file put -i {PORT} -f {FILE} set system bios update -i {PORT} -f {FILE} set system bmc update -i {PORT} -f {FILE}</t>
-        </is>
-      </c>
-      <c r="G93" s="47" t="b">
-        <v>1</v>
-      </c>
-      <c r="H93" s="47" t="b">
-        <v>1</v>
-      </c>
-      <c r="I93" s="41" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Mac Address              check PASS. Get:             0427283DD689, Exp:             0427283DD689
-SerialNumber             check PASS. Get:         P54376354001203A, Exp:         P54376354001203A
-BiosVersion              check PASS. Get:     C44AD.0.BS.1C11.GN.1, Exp:     C44AD.0.BS.1C11.GN.1
-BMCVersion               check PASS. Get:                  26.4.24, Exp:                  26.4.24
- CpldVersion             check PASS. Get:                 02.06.00, Exp:                 02.06.00
-DCSCMCpldVersion         check PASS. Get:                 03.06.00, Exp:                 03.06.00
-Count                    check PASS. Get:                        2, Exp:                        2
-TotalSystemMemoryGib     check PASS. Get:                      512, Exp:                      512
-[PASS] Check system info via RM PASS
-</t>
-        </is>
-      </c>
-      <c r="J93" s="41" t="n"/>
-      <c r="K93" s="42" t="inlineStr">
-        <is>
-          <t>Mac Address              check PASS. Get:             0427283DD689, Exp:             0427283DD689
-SerialNumber             check PASS. Get:         P54376354001203A, Exp:         P54376354001203A
-BiosVersion              check PASS. Get:     C44AD.0.BS.1C11.GN.1, Exp:     C44AD.0.BS.1C11.GN.1
-BMCVersion               check PASS. Get:                  26.4.24, Exp:                  26.4.24
-CpldVersion             check PASS. Get:                 02.06.00, Exp:                 02.06.00
-DCSCMCpldVersion         check PASS. Get:                 03.06.00, Exp:                 03.06.00
-Count                    check PASS. Get:                        2, Exp:                        2
-TotalSystemMemoryGib     check PASS. Get:                      512, Exp:                      512
-[PASS] Check system info via RM PASS"</t>
-        </is>
-      </c>
-      <c r="L93" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Matches CRD: BIOS C44AD.0.BS.1C11.GN.1, BMC 26.04.24, MB CPLD 02.06.00, DC-SCM CPLD 03.06.00, 512 GiB, 2 CPU.
-</t>
-        </is>
-      </c>
+          <t>PASS if ipmitool sdr elist succeeds. FAIL otherwise.</t>
+        </is>
+      </c>
+      <c r="E93" s="40" t="n"/>
+      <c r="F93" s="75" t="n"/>
+      <c r="G93" s="78" t="b">
+        <v>0</v>
+      </c>
+      <c r="H93" s="78" t="b">
+        <v>0</v>
+      </c>
+      <c r="I93" s="55" t="n"/>
+      <c r="J93" s="55" t="n"/>
+      <c r="L93" s="31" t="n"/>
       <c r="M93" s="18" t="n"/>
       <c r="N93" s="37" t="n"/>
       <c r="O93" s="18" t="n"/>
@@ -9937,46 +9933,49 @@
       <c r="X93" s="17" t="n"/>
       <c r="Y93" s="17" t="n"/>
     </row>
-    <row r="94" s="80">
-      <c r="A94" s="81" t="n">
+    <row r="94" ht="27" customHeight="1" s="80">
+      <c r="A94" s="76" t="n">
         <v>91</v>
       </c>
-      <c r="B94" s="82" t="inlineStr">
-        <is>
-          <t>bios_cmos_test</t>
-        </is>
-      </c>
-      <c r="C94" s="82" t="inlineStr">
-        <is>
-          <t>Test the BIOS CMOS functionality by verifying the read/write capability of CMOS registers and checking battery and CMOS operation status.</t>
-        </is>
-      </c>
-      <c r="D94" s="83" t="inlineStr">
-        <is>
-          <t>Pass - return 0; Fail - return 1</t>
-        </is>
-      </c>
-      <c r="E94" s="83" t="inlineStr">
-        <is>
-          <t>&gt;&gt;&gt;MTE agreed to waive in EVT. ADO#2909063</t>
-        </is>
-      </c>
-      <c r="F94" s="84" t="inlineStr">
-        <is>
-          <t>[Execute CMOS test]
-CMOStest -d</t>
-        </is>
-      </c>
-      <c r="G94" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="H94" s="84" t="b">
-        <v>0</v>
-      </c>
-      <c r="I94" s="84" t="n"/>
-      <c r="J94" s="84" t="n"/>
-      <c r="K94" s="85" t="n"/>
-      <c r="L94" s="86" t="n"/>
+      <c r="B94" s="43" t="inlineStr">
+        <is>
+          <t>uut_dmesg_chk</t>
+        </is>
+      </c>
+      <c r="C94" s="43" t="inlineStr">
+        <is>
+          <t>Captures dmesg, lspci -vvv, and ras-mc-ctl --errors, then filters against an allow-list and a CSV-driven bypass filter list to detect real kernel errors.</t>
+        </is>
+      </c>
+      <c r="D94" s="40" t="inlineStr">
+        <is>
+          <t>PASS if, after filtering, no un-bypassed error lines remain in dmesg. FAIL if any survive filtering, or if the filter list file is missing/fails.</t>
+        </is>
+      </c>
+      <c r="E94" s="40" t="n"/>
+      <c r="F94" s="75" t="n"/>
+      <c r="G94" s="78" t="b">
+        <v>0</v>
+      </c>
+      <c r="H94" s="78" t="b">
+        <v>0</v>
+      </c>
+      <c r="I94" s="55" t="n"/>
+      <c r="J94" s="55" t="n"/>
+      <c r="L94" s="31" t="n"/>
+      <c r="M94" s="18" t="n"/>
+      <c r="N94" s="37" t="n"/>
+      <c r="O94" s="18" t="n"/>
+      <c r="P94" s="19" t="n"/>
+      <c r="Q94" s="17" t="n"/>
+      <c r="R94" s="17" t="n"/>
+      <c r="S94" s="17" t="n"/>
+      <c r="T94" s="17" t="n"/>
+      <c r="U94" s="17" t="n"/>
+      <c r="V94" s="17" t="n"/>
+      <c r="W94" s="17" t="n"/>
+      <c r="X94" s="17" t="n"/>
+      <c r="Y94" s="17" t="n"/>
     </row>
     <row r="95" ht="27" customHeight="1" s="80">
       <c r="A95" s="76" t="n">
@@ -9984,24 +9983,20 @@
       </c>
       <c r="B95" s="43" t="inlineStr">
         <is>
-          <t>bmc_sel_chk</t>
+          <t>uut_syslog_chk</t>
         </is>
       </c>
       <c r="C95" s="43" t="inlineStr">
         <is>
-          <t>A plain BMC SEL check, run late in the flow after all functional tests have completed, right before the final SDR/dmesg/syslog snapshot and SEL clear.</t>
+          <t>Detects OS kernel, regenerates /var/log/syslog via journalctl -b --no-pager, and filters for errors using an allow-list + CSV bypass.</t>
         </is>
       </c>
       <c r="D95" s="40" t="inlineStr">
         <is>
-          <t>PASS if returns truthy (no un-whitelisted SEL entries found). FAIL otherwise.</t>
-        </is>
-      </c>
-      <c r="E95" s="40" t="inlineStr">
-        <is>
-          <t>Different call site/intent (post-functional-test SEL sweep vs. pre-test boot-time SEL sweep), same underlying logic.</t>
-        </is>
-      </c>
+          <t>PASS if, after filtering, no un-bypassed error lines remain in dmesg. FAIL if any survive filtering, or if the filter list file is missing/fails.</t>
+        </is>
+      </c>
+      <c r="E95" s="40" t="n"/>
       <c r="F95" s="75" t="n"/>
       <c r="G95" s="78" t="b">
         <v>0</v>
@@ -10032,17 +10027,17 @@
       </c>
       <c r="B96" s="43" t="inlineStr">
         <is>
-          <t>bmc_sdr_chk</t>
+          <t>bmc_sel_clear</t>
         </is>
       </c>
       <c r="C96" s="43" t="inlineStr">
         <is>
-          <t>Validates BMC Sensor Data Record contents (all sensor readings within expected bounds).</t>
+          <t>Records the current BMC SEL to a log file, then clears the SEL (System Event Log).</t>
         </is>
       </c>
       <c r="D96" s="40" t="inlineStr">
         <is>
-          <t>PASS if ipmitool sdr elist succeeds. FAIL otherwise.</t>
+          <t>PASS if ipmitool sel clear succeeds. FAIL otherwise.</t>
         </is>
       </c>
       <c r="E96" s="40" t="n"/>
@@ -10076,34 +10071,59 @@
       </c>
       <c r="B97" s="43" t="inlineStr">
         <is>
-          <t>uut_dmesg_chk</t>
+          <t>uut_boot_change</t>
         </is>
       </c>
       <c r="C97" s="43" t="inlineStr">
         <is>
-          <t>Captures dmesg, lspci -vvv, and ras-mc-ctl --errors, then filters against an allow-list and a CSV-driven bypass filter list to detect real kernel errors.</t>
-        </is>
-      </c>
-      <c r="D97" s="40" t="inlineStr">
-        <is>
-          <t>PASS if, after filtering, no un-bypassed error lines remain in dmesg. FAIL if any survive filtering, or if the filter list file is missing/fails.</t>
-        </is>
-      </c>
+          <t>change boot option to windows env. for window testing.
+AC cycle so the UUT boots into Windows</t>
+        </is>
+      </c>
+      <c r="D97" s="40" t="n"/>
       <c r="E97" s="40" t="n"/>
-      <c r="F97" s="75" t="n"/>
-      <c r="G97" s="78" t="b">
-        <v>0</v>
-      </c>
-      <c r="H97" s="78" t="b">
-        <v>0</v>
-      </c>
-      <c r="I97" s="55" t="n"/>
-      <c r="J97" s="55" t="n"/>
-      <c r="L97" s="31" t="n"/>
-      <c r="M97" s="18" t="n"/>
-      <c r="N97" s="37" t="n"/>
-      <c r="O97" s="18" t="n"/>
-      <c r="P97" s="19" t="n"/>
+      <c r="F97" s="43" t="inlineStr">
+        <is>
+          <t>[ Get version of below items ] Inventory ipmitool raw 0x36 0xd2 1 0x01 PowerCapping ipmitool raw 0x36 0xd2 3 0x01 FanTable ipmitool raw 0x36 0xd2 4 0x01 SDRGenerator ipmitool raw 0x36 0xd2 6 0x01</t>
+        </is>
+      </c>
+      <c r="G97" s="47" t="b">
+        <v>1</v>
+      </c>
+      <c r="H97" s="47" t="b">
+        <v>1</v>
+      </c>
+      <c r="I97" s="41" t="inlineStr">
+        <is>
+          <t>Measuring Get Inventory Version:1.9.2, equal to 1.9.2
+Measuring Get PowerCapping Version:3.9.1, equal to 3.9.1
+Measuring Get FanTable Version:4.9.2, equal to 4.9.2
+Measuring Get SDRGenerator Version:6.9.2, equal to 6.9.2
+[BMC_SKU_INFO] JSON File Version Check PASS.
+[PASS] BMC SKU Info Check PASS.</t>
+        </is>
+      </c>
+      <c r="J97" s="41" t="n"/>
+      <c r="K97" s="42" t="inlineStr">
+        <is>
+          <t>Measuring Get Inventory Version:1.9.2, equal to 1.9.2
+Measuring Get PowerCapping Version:3.9.1, equal to 3.9.1
+Measuring Get FanTable Version:4.9.2, equal to 4.9.2
+Measuring Get SDRGenerator Version:6.9.2, equal to 6.9.2
+[BMC_SKU_INFO] JSON File Version Check PASS.
+[PASS] BMC SKU Info Check PASS.</t>
+        </is>
+      </c>
+      <c r="L97" s="31" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Matches CRD (FanTable 4.9.2, Inventory 1.9.2, PowerCapping 3.9.1, SDRGenerator 6.9.2). CRD PCBA table still lists SDRGenerator 6.9.1 (System table says 6.9.2).
+</t>
+        </is>
+      </c>
+      <c r="M97" s="20" t="n"/>
+      <c r="N97" s="20" t="n"/>
+      <c r="O97" s="20" t="n"/>
+      <c r="P97" s="20" t="n"/>
       <c r="Q97" s="17" t="n"/>
       <c r="R97" s="17" t="n"/>
       <c r="S97" s="17" t="n"/>
@@ -10114,49 +10134,50 @@
       <c r="X97" s="17" t="n"/>
       <c r="Y97" s="17" t="n"/>
     </row>
-    <row r="98" ht="27" customHeight="1" s="80">
+    <row r="98" ht="53.25" customHeight="1" s="80">
       <c r="A98" s="76" t="n">
         <v>95</v>
       </c>
       <c r="B98" s="43" t="inlineStr">
         <is>
-          <t>uut_syslog_chk</t>
+          <t>tcg_spf_mode_chk</t>
         </is>
       </c>
       <c r="C98" s="43" t="inlineStr">
         <is>
-          <t>Detects OS kernel, regenerates /var/log/syslog via journalctl -b --no-pager, and filters for errors using an allow-list + CSV bypass.</t>
+          <t>Prepare TCG testing in Linux. WinPE ipxe menu override set.
+Switch target system to WinPE by updating PXE boot configuration and collecting Windows logs/config.</t>
         </is>
       </c>
       <c r="D98" s="40" t="inlineStr">
         <is>
-          <t>PASS if, after filtering, no un-bypassed error lines remain in dmesg. FAIL if any survive filtering, or if the filter list file is missing/fails.</t>
-        </is>
-      </c>
-      <c r="E98" s="40" t="n"/>
-      <c r="F98" s="75" t="n"/>
-      <c r="G98" s="78" t="b">
-        <v>0</v>
-      </c>
-      <c r="H98" s="78" t="b">
-        <v>0</v>
-      </c>
-      <c r="I98" s="55" t="n"/>
-      <c r="J98" s="55" t="n"/>
-      <c r="L98" s="31" t="n"/>
-      <c r="M98" s="18" t="n"/>
-      <c r="N98" s="37" t="n"/>
-      <c r="O98" s="18" t="n"/>
-      <c r="P98" s="19" t="n"/>
-      <c r="Q98" s="17" t="n"/>
-      <c r="R98" s="17" t="n"/>
-      <c r="S98" s="17" t="n"/>
-      <c r="T98" s="17" t="n"/>
-      <c r="U98" s="17" t="n"/>
-      <c r="V98" s="17" t="n"/>
-      <c r="W98" s="17" t="n"/>
-      <c r="X98" s="17" t="n"/>
-      <c r="Y98" s="17" t="n"/>
+          <t>Windows config and log directories must be created. Log files must be collected and stored correctly. PXE boot script must exist and execute without error.</t>
+        </is>
+      </c>
+      <c r="E98" s="40" t="inlineStr">
+        <is>
+          <t>This function prepares and stores Windows logs to specific locations under /testlog/&lt;project&gt;/windows/ PXE boot config is changed by uploading specific iPXE script based on MAC address. If the shell script is missing or fails, the system will exit or log failure to SF.</t>
+        </is>
+      </c>
+      <c r="F98" s="43" t="inlineStr">
+        <is>
+          <t>[ Get Boot MAC ] ifconfig -a | egrep "eth" | egrep "ether" | awk '{print $2}' - - - - - If b oot method is ipxe - - - - - Replace set menu-default with winpe - - - - - If b oot method is not ipxe - - - - - [ Set Boot Device to disk ] ipmitool chassis bootdev disk [ Format nvme devices ] nvme format /dev/nvme0n1 Install a Windows ISO to /dev/nvme0n1 [ Execute AC Cycle ] ipmitool raw 0x30 0xe0 116 1 1</t>
+        </is>
+      </c>
+      <c r="G98" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="H98" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="I98" s="45" t="n"/>
+      <c r="J98" s="45" t="n"/>
+      <c r="K98" s="42" t="inlineStr">
+        <is>
+          <t>[PASS] WinPE ipxe menu override set.</t>
+        </is>
+      </c>
+      <c r="L98" s="52" t="n"/>
     </row>
     <row r="99" ht="27" customHeight="1" s="80">
       <c r="A99" s="76" t="n">
@@ -10164,204 +10185,46 @@
       </c>
       <c r="B99" s="43" t="inlineStr">
         <is>
-          <t>bmc_sel_clear</t>
+          <t>bios_boot_option_set_default</t>
         </is>
       </c>
       <c r="C99" s="43" t="inlineStr">
-        <is>
-          <t>Records the current BMC SEL to a log file, then clears the SEL (System Event Log).</t>
-        </is>
-      </c>
-      <c r="D99" s="40" t="inlineStr">
-        <is>
-          <t>PASS if ipmitool sel clear succeeds. FAIL otherwise.</t>
-        </is>
-      </c>
-      <c r="E99" s="40" t="n"/>
-      <c r="F99" s="75" t="n"/>
-      <c r="G99" s="78" t="b">
-        <v>0</v>
-      </c>
-      <c r="H99" s="78" t="b">
-        <v>0</v>
-      </c>
-      <c r="I99" s="55" t="n"/>
-      <c r="J99" s="55" t="n"/>
-      <c r="L99" s="31" t="n"/>
-      <c r="M99" s="18" t="n"/>
-      <c r="N99" s="37" t="n"/>
-      <c r="O99" s="18" t="n"/>
-      <c r="P99" s="19" t="n"/>
-      <c r="Q99" s="17" t="n"/>
-      <c r="R99" s="17" t="n"/>
-      <c r="S99" s="17" t="n"/>
-      <c r="T99" s="17" t="n"/>
-      <c r="U99" s="17" t="n"/>
-      <c r="V99" s="17" t="n"/>
-      <c r="W99" s="17" t="n"/>
-      <c r="X99" s="17" t="n"/>
-      <c r="Y99" s="17" t="n"/>
-    </row>
-    <row r="100" ht="27" customHeight="1" s="80">
-      <c r="A100" s="76" t="n">
-        <v>97</v>
-      </c>
-      <c r="B100" s="43" t="inlineStr">
-        <is>
-          <t>uut_boot_change</t>
-        </is>
-      </c>
-      <c r="C100" s="43" t="inlineStr">
-        <is>
-          <t>change boot option to windows env. for window testing.
-AC cycle so the UUT boots into Windows</t>
-        </is>
-      </c>
-      <c r="D100" s="40" t="n"/>
-      <c r="E100" s="40" t="n"/>
-      <c r="F100" s="43" t="inlineStr">
-        <is>
-          <t>[ Get version of below items ] Inventory ipmitool raw 0x36 0xd2 1 0x01 PowerCapping ipmitool raw 0x36 0xd2 3 0x01 FanTable ipmitool raw 0x36 0xd2 4 0x01 SDRGenerator ipmitool raw 0x36 0xd2 6 0x01</t>
-        </is>
-      </c>
-      <c r="G100" s="47" t="b">
-        <v>1</v>
-      </c>
-      <c r="H100" s="47" t="b">
-        <v>1</v>
-      </c>
-      <c r="I100" s="41" t="inlineStr">
-        <is>
-          <t>Measuring Get Inventory Version:1.9.2, equal to 1.9.2
-Measuring Get PowerCapping Version:3.9.1, equal to 3.9.1
-Measuring Get FanTable Version:4.9.2, equal to 4.9.2
-Measuring Get SDRGenerator Version:6.9.2, equal to 6.9.2
-[BMC_SKU_INFO] JSON File Version Check PASS.
-[PASS] BMC SKU Info Check PASS.</t>
-        </is>
-      </c>
-      <c r="J100" s="41" t="n"/>
-      <c r="K100" s="42" t="inlineStr">
-        <is>
-          <t>Measuring Get Inventory Version:1.9.2, equal to 1.9.2
-Measuring Get PowerCapping Version:3.9.1, equal to 3.9.1
-Measuring Get FanTable Version:4.9.2, equal to 4.9.2
-Measuring Get SDRGenerator Version:6.9.2, equal to 6.9.2
-[BMC_SKU_INFO] JSON File Version Check PASS.
-[PASS] BMC SKU Info Check PASS.</t>
-        </is>
-      </c>
-      <c r="L100" s="31" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Matches CRD (FanTable 4.9.2, Inventory 1.9.2, PowerCapping 3.9.1, SDRGenerator 6.9.2). CRD PCBA table still lists SDRGenerator 6.9.1 (System table says 6.9.2).
-</t>
-        </is>
-      </c>
-      <c r="M100" s="20" t="n"/>
-      <c r="N100" s="20" t="n"/>
-      <c r="O100" s="20" t="n"/>
-      <c r="P100" s="20" t="n"/>
-      <c r="Q100" s="17" t="n"/>
-      <c r="R100" s="17" t="n"/>
-      <c r="S100" s="17" t="n"/>
-      <c r="T100" s="17" t="n"/>
-      <c r="U100" s="17" t="n"/>
-      <c r="V100" s="17" t="n"/>
-      <c r="W100" s="17" t="n"/>
-      <c r="X100" s="17" t="n"/>
-      <c r="Y100" s="17" t="n"/>
-    </row>
-    <row r="101" ht="53.25" customHeight="1" s="80">
-      <c r="A101" s="76" t="n">
-        <v>98</v>
-      </c>
-      <c r="B101" s="43" t="inlineStr">
-        <is>
-          <t>tcg_spf_mode_chk</t>
-        </is>
-      </c>
-      <c r="C101" s="43" t="inlineStr">
-        <is>
-          <t>Prepare TCG testing in Linux. WinPE ipxe menu override set.
-Switch target system to WinPE by updating PXE boot configuration and collecting Windows logs/config.</t>
-        </is>
-      </c>
-      <c r="D101" s="40" t="inlineStr">
-        <is>
-          <t>Windows config and log directories must be created. Log files must be collected and stored correctly. PXE boot script must exist and execute without error.</t>
-        </is>
-      </c>
-      <c r="E101" s="40" t="inlineStr">
-        <is>
-          <t>This function prepares and stores Windows logs to specific locations under /testlog/&lt;project&gt;/windows/ PXE boot config is changed by uploading specific iPXE script based on MAC address. If the shell script is missing or fails, the system will exit or log failure to SF.</t>
-        </is>
-      </c>
-      <c r="F101" s="43" t="inlineStr">
-        <is>
-          <t>[ Get Boot MAC ] ifconfig -a | egrep "eth" | egrep "ether" | awk '{print $2}' - - - - - If b oot method is ipxe - - - - - Replace set menu-default with winpe - - - - - If b oot method is not ipxe - - - - - [ Set Boot Device to disk ] ipmitool chassis bootdev disk [ Format nvme devices ] nvme format /dev/nvme0n1 Install a Windows ISO to /dev/nvme0n1 [ Execute AC Cycle ] ipmitool raw 0x30 0xe0 116 1 1</t>
-        </is>
-      </c>
-      <c r="G101" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="H101" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="I101" s="45" t="n"/>
-      <c r="J101" s="45" t="n"/>
-      <c r="K101" s="42" t="inlineStr">
-        <is>
-          <t>[PASS] WinPE ipxe menu override set.</t>
-        </is>
-      </c>
-      <c r="L101" s="52" t="n"/>
-    </row>
-    <row r="102" ht="27" customHeight="1" s="80">
-      <c r="A102" s="76" t="n">
-        <v>99</v>
-      </c>
-      <c r="B102" s="43" t="inlineStr">
-        <is>
-          <t>bios_boot_option_set_default</t>
-        </is>
-      </c>
-      <c r="C102" s="43" t="inlineStr">
         <is>
           <t>change boot option to linux env. for next station Linux testing.
 AC cycle so the UUT boots into Linux</t>
         </is>
       </c>
-      <c r="D102" s="40" t="n"/>
-      <c r="E102" s="40" t="n"/>
-      <c r="F102" s="43" t="inlineStr">
+      <c r="D99" s="40" t="n"/>
+      <c r="E99" s="40" t="n"/>
+      <c r="F99" s="43" t="inlineStr">
         <is>
           <t>ipmitool chassis bootdev disk options=persistent
 AC cycle so the UUT boots into Windows</t>
         </is>
       </c>
-      <c r="G102" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="H102" s="47" t="b">
+      <c r="G99" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="H99" s="47" t="b">
         <v>1</v>
       </c>
-      <c r="K102" s="39" t="inlineStr">
+      <c r="K99" s="39" t="inlineStr">
         <is>
           <t>[PASS] Already AC-cycled into disk-Windows, continue to next item</t>
         </is>
       </c>
-      <c r="L102" s="52" t="n"/>
-      <c r="M102" s="55" t="n"/>
-      <c r="N102" s="55" t="n"/>
-      <c r="O102" s="55" t="n"/>
-      <c r="P102" s="55" t="n"/>
-    </row>
-    <row r="103" s="80"/>
-    <row r="104" s="80">
-      <c r="G104" s="49" t="n">
+      <c r="L99" s="52" t="n"/>
+      <c r="M99" s="55" t="n"/>
+      <c r="N99" s="55" t="n"/>
+      <c r="O99" s="55" t="n"/>
+      <c r="P99" s="55" t="n"/>
+    </row>
+    <row r="100" s="80"/>
+    <row r="101" s="80">
+      <c r="G101" s="49" t="n">
         <v>6</v>
       </c>
-      <c r="H104" s="49" t="inlineStr">
+      <c r="H101" s="49" t="inlineStr">
         <is>
           <t>Hours</t>
         </is>
@@ -11765,7 +11628,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L90"/>
+  <dimension ref="A1:L87"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="9.140625" defaultRowHeight="12.75"/>
   <cols>
     <col width="5.7109375" customWidth="1" style="20" min="1" max="1"/>
@@ -12290,171 +12153,44 @@
         </is>
       </c>
     </row>
-    <row r="13" s="80">
-      <c r="A13" s="81" t="n">
+    <row r="13" ht="67.5" customHeight="1" s="80">
+      <c r="A13" s="76" t="n">
         <v>11</v>
       </c>
-      <c r="B13" s="82" t="inlineStr">
-        <is>
-          <t>rm_powershelf_fw_chk</t>
-        </is>
-      </c>
-      <c r="C13" s="82" t="inlineStr">
-        <is>
-          <t>Check the PSU firmware version on the power shelf via RM for the current UUT. This function only performs the check on master nodes.</t>
-        </is>
-      </c>
-      <c r="D13" s="82" t="inlineStr">
-        <is>
-          <t>- Pass:
-- UUT is a master node.
-- All PSU serial numbers, manufacturers, and firmware versions match expected values.
-- Fail
-- Unable to get RM IP.
-- PSU information cannot be retrieved or parsed.
-- PSU not found in the expected list.
-- Firmware version mismatch and auto-upgrade fails.</t>
-        </is>
-      </c>
-      <c r="E13" s="82" t="inlineStr">
-        <is>
-          <t>- Only master nodes will perform the check.
-- Only master nodes in pretest station will perform the upgrade if mismatch
-- Location format: {RM_location}-{RM_port}-{UUT_location}-{BMC} (e.g., U26-6-U9-BMC0)</t>
-        </is>
-      </c>
-      <c r="F13" s="82" t="inlineStr">
-        <is>
-          <t>[Check powershelf firmware version]
-show powershelf psu info -s {INDEX}
-Capability
--        IC Device ID
--        Manufacturer ID
--        Manufacturer Model
--        Manufacturer Revision
--        Manufacturer Serial
--        Completion Code</t>
-        </is>
-      </c>
-      <c r="G13" s="87" t="b">
-        <v>0</v>
-      </c>
-      <c r="H13" s="87" t="b">
-        <v>0</v>
-      </c>
-      <c r="I13" s="88" t="n"/>
-      <c r="J13" s="88" t="n"/>
-      <c r="K13" s="89" t="n"/>
-      <c r="L13" s="90" t="n"/>
-    </row>
-    <row r="14" s="80">
-      <c r="A14" s="81" t="n">
-        <v>12</v>
-      </c>
-      <c r="B14" s="82" t="inlineStr">
-        <is>
-          <t>rm_health_check</t>
-        </is>
-      </c>
-      <c r="C14" s="82" t="inlineStr">
-        <is>
-          <t>Check RM Health Status</t>
-        </is>
-      </c>
-      <c r="D14" s="82" t="inlineStr">
-        <is>
-          <t>PSU state should be “Healthy”.
-(Master Only)</t>
-        </is>
-      </c>
-      <c r="E14" s="82" t="n"/>
-      <c r="F14" s="82" t="inlineStr">
-        <is>
-          <t>Command: show powershelf psu state</t>
-        </is>
-      </c>
-      <c r="G14" s="87" t="b">
-        <v>0</v>
-      </c>
-      <c r="H14" s="87" t="b">
-        <v>0</v>
-      </c>
-      <c r="I14" s="88" t="n"/>
-      <c r="J14" s="88" t="n"/>
-      <c r="K14" s="89" t="n"/>
-      <c r="L14" s="90" t="n"/>
-    </row>
-    <row r="15" s="80">
-      <c r="A15" s="81" t="n">
-        <v>13</v>
-      </c>
-      <c r="B15" s="82" t="inlineStr">
-        <is>
-          <t>rm_manager_type_check</t>
-        </is>
-      </c>
-      <c r="C15" s="82" t="inlineStr">
-        <is>
-          <t>Check POWERSHELF Product Name
-Check RM Manager Type</t>
-        </is>
-      </c>
-      <c r="D15" s="82" t="n"/>
-      <c r="E15" s="82" t="n"/>
-      <c r="F15" s="82" t="inlineStr">
-        <is>
-          <t>show manager type</t>
-        </is>
-      </c>
-      <c r="G15" s="87" t="b">
-        <v>0</v>
-      </c>
-      <c r="H15" s="87" t="b">
-        <v>0</v>
-      </c>
-      <c r="I15" s="88" t="n"/>
-      <c r="J15" s="88" t="n"/>
-      <c r="K15" s="89" t="n"/>
-      <c r="L15" s="90" t="n"/>
-    </row>
-    <row r="16" ht="67.5" customHeight="1" s="80">
-      <c r="A16" s="76" t="n">
-        <v>14</v>
-      </c>
-      <c r="B16" s="43" t="inlineStr">
+      <c r="B13" s="43" t="inlineStr">
         <is>
           <t>rm_uut_info_chk</t>
         </is>
       </c>
-      <c r="C16" s="43" t="inlineStr">
+      <c r="C13" s="43" t="inlineStr">
         <is>
           <t>C hecks UUT system information via the RM interface and compares it with the expected configuration values .</t>
         </is>
       </c>
-      <c r="D16" s="43" t="inlineStr">
+      <c r="D13" s="43" t="inlineStr">
         <is>
           <t>Pass All fields (MAC, SN, BIOS version, BMC version, CPLD versions, CPU count, and memory size) match expected values. Or mismatched fields are successfully auto-updated (if allowed). Fail Unable to retrieve system info from RM. Mismatched field(s) and auto-upgrade is either disabled or unsuccessful.</t>
         </is>
       </c>
-      <c r="E16" s="43" t="inlineStr">
+      <c r="E13" s="43" t="inlineStr">
         <is>
           <t>This check is only performed on master blades. The upgrade is onl y performed in Pretest station if mismatch. BMC version comparison trims prefix/suffix for accurate matching. Some version formats (e.g., CPLD) are normalized before comparison (e.g., removing dots). A uto-update will be attempted for mismatched items in Pretest station .</t>
         </is>
       </c>
-      <c r="F16" s="43" t="inlineStr">
+      <c r="F13" s="43" t="inlineStr">
         <is>
           <t>[ Get system info via RM ] show system info -i { RM_PORT } Mac Address SerialNumber BiosVersion BMCVersion CpldVersion DCSCMCpldVersion Count TotalSystemMemoryGib - - - - - If mismatch - - - - - [ Upgrade system firmware version ] set system file put -i {PORT} -f {FILE} set system bios update -i {PORT} -f {FILE} set system bmc update -i {PORT} -f {FILE}</t>
         </is>
       </c>
-      <c r="G16" s="47" t="b">
+      <c r="G13" s="47" t="b">
         <v>1</v>
       </c>
-      <c r="H16" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="I16" s="48" t="n"/>
-      <c r="J16" s="48" t="n"/>
-      <c r="K16" s="42" t="inlineStr">
+      <c r="H13" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="I13" s="48" t="n"/>
+      <c r="J13" s="48" t="n"/>
+      <c r="K13" s="42" t="inlineStr">
         <is>
           <t>Mac Address              check PASS. Get:             0427283DD689, Exp:             0427283DD689
 SerialNumber             check PASS. Get:         P54376354001203A, Exp:         P54376354001203A
@@ -12467,37 +12203,122 @@
 [PASS] Check system info via RM PASS"</t>
         </is>
       </c>
-      <c r="L16" s="31" t="inlineStr">
+      <c r="L13" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">Matches CRD: BIOS C44AD.0.BS.1C11.GN.1, BMC 26.04.24, MB CPLD 02.06.00, DC-SCM CPLD 03.06.00, 512 GiB, 2 CPU.
 </t>
         </is>
       </c>
     </row>
-    <row r="17" ht="40.5" customHeight="1" s="80">
+    <row r="14" ht="40.5" customHeight="1" s="80">
+      <c r="A14" s="76" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="43" t="inlineStr">
+        <is>
+          <t>rm_fru_chk</t>
+        </is>
+      </c>
+      <c r="C14" s="43" t="inlineStr">
+        <is>
+          <t>Check RM FRU information</t>
+        </is>
+      </c>
+      <c r="D14" s="43" t="inlineStr">
+        <is>
+          <t>Pass Successfully retrieves the FRU data and the Product Serial Number matches the expected value from config. Fail Unable to retrieve FRU data or serial number does not match.</t>
+        </is>
+      </c>
+      <c r="E14" s="43" t="inlineStr">
+        <is>
+          <t>only applies to the master blade</t>
+        </is>
+      </c>
+      <c r="F14" s="43" t="n"/>
+      <c r="G14" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="H14" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="I14" s="48" t="n"/>
+      <c r="J14" s="48" t="n"/>
+      <c r="L14" s="31" t="n"/>
+    </row>
+    <row r="15" ht="13.5" customHeight="1" s="80">
+      <c r="A15" s="76" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="43" t="inlineStr">
+        <is>
+          <t>rm_pmdu_fru_chk</t>
+        </is>
+      </c>
+      <c r="C15" s="43" t="n"/>
+      <c r="D15" s="43" t="n"/>
+      <c r="E15" s="43" t="inlineStr">
+        <is>
+          <t>only applies to the master blade</t>
+        </is>
+      </c>
+      <c r="F15" s="43" t="n"/>
+      <c r="G15" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="H15" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="I15" s="48" t="n"/>
+      <c r="J15" s="48" t="n"/>
+      <c r="L15" s="31" t="n"/>
+    </row>
+    <row r="16" ht="13.5" customHeight="1" s="80">
+      <c r="A16" s="76" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="43" t="inlineStr">
+        <is>
+          <t>rm_acdc_fru_chk</t>
+        </is>
+      </c>
+      <c r="C16" s="43" t="n"/>
+      <c r="D16" s="43" t="n"/>
+      <c r="E16" s="43" t="inlineStr">
+        <is>
+          <t>only applies to the master blade</t>
+        </is>
+      </c>
+      <c r="F16" s="43" t="n"/>
+      <c r="G16" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="H16" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="I16" s="48" t="n"/>
+      <c r="J16" s="48" t="n"/>
+      <c r="L16" s="31" t="n"/>
+    </row>
+    <row r="17" ht="13.5" customHeight="1" s="80">
       <c r="A17" s="76" t="n">
         <v>15</v>
       </c>
       <c r="B17" s="43" t="inlineStr">
         <is>
-          <t>rm_fru_chk</t>
+          <t>rm_sys_fru_chk</t>
         </is>
       </c>
       <c r="C17" s="43" t="inlineStr">
         <is>
-          <t>Check RM FRU information</t>
+          <t>Check System FRU via RM</t>
         </is>
       </c>
       <c r="D17" s="43" t="inlineStr">
         <is>
-          <t>Pass Successfully retrieves the FRU data and the Product Serial Number matches the expected value from config. Fail Unable to retrieve FRU data or serial number does not match.</t>
-        </is>
-      </c>
-      <c r="E17" s="43" t="inlineStr">
-        <is>
-          <t>only applies to the master blade</t>
-        </is>
-      </c>
+          <t>Pass - return 0; Fail - return 1</t>
+        </is>
+      </c>
+      <c r="E17" s="43" t="n"/>
       <c r="F17" s="43" t="n"/>
       <c r="G17" s="47" t="b">
         <v>0</v>
@@ -12515,14 +12336,22 @@
       </c>
       <c r="B18" s="43" t="inlineStr">
         <is>
-          <t>rm_pmdu_fru_chk</t>
-        </is>
-      </c>
-      <c r="C18" s="43" t="n"/>
-      <c r="D18" s="43" t="n"/>
+          <t>rm_scm_fru_chk</t>
+        </is>
+      </c>
+      <c r="C18" s="43" t="inlineStr">
+        <is>
+          <t>Check DC-SCM(M1120) FRU via RM</t>
+        </is>
+      </c>
+      <c r="D18" s="43" t="inlineStr">
+        <is>
+          <t>Pass - return 0; Fail - return 1</t>
+        </is>
+      </c>
       <c r="E18" s="43" t="inlineStr">
         <is>
-          <t>only applies to the master blade</t>
+          <t>Check b oard s erial n umber</t>
         </is>
       </c>
       <c r="F18" s="43" t="n"/>
@@ -12542,14 +12371,22 @@
       </c>
       <c r="B19" s="43" t="inlineStr">
         <is>
-          <t>rm_acdc_fru_chk</t>
-        </is>
-      </c>
-      <c r="C19" s="43" t="n"/>
-      <c r="D19" s="43" t="n"/>
+          <t>rm_gp_fru_chk</t>
+        </is>
+      </c>
+      <c r="C19" s="43" t="inlineStr">
+        <is>
+          <t>Check GlacierPeak FRU via RM</t>
+        </is>
+      </c>
+      <c r="D19" s="43" t="inlineStr">
+        <is>
+          <t>Pass - return 0; Fail - return 1</t>
+        </is>
+      </c>
       <c r="E19" s="43" t="inlineStr">
         <is>
-          <t>only applies to the master blade</t>
+          <t>Check b oard s erial n umber</t>
         </is>
       </c>
       <c r="F19" s="43" t="n"/>
@@ -12563,123 +12400,22 @@
       <c r="J19" s="48" t="n"/>
       <c r="L19" s="31" t="n"/>
     </row>
-    <row r="20" ht="13.5" customHeight="1" s="80">
+    <row r="20" ht="53.25" customHeight="1" s="80">
       <c r="A20" s="76" t="n">
         <v>18</v>
       </c>
       <c r="B20" s="43" t="inlineStr">
         <is>
-          <t>rm_sys_fru_chk</t>
+          <t>rm_relay_port_chk</t>
         </is>
       </c>
       <c r="C20" s="43" t="inlineStr">
         <is>
-          <t>Check System FRU via RM</t>
-        </is>
-      </c>
-      <c r="D20" s="43" t="inlineStr">
-        <is>
-          <t>Pass - return 0; Fail - return 1</t>
-        </is>
-      </c>
-      <c r="E20" s="43" t="n"/>
-      <c r="F20" s="43" t="n"/>
-      <c r="G20" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="H20" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="I20" s="48" t="n"/>
-      <c r="J20" s="48" t="n"/>
-      <c r="L20" s="31" t="n"/>
-    </row>
-    <row r="21" ht="13.5" customHeight="1" s="80">
-      <c r="A21" s="76" t="n">
-        <v>19</v>
-      </c>
-      <c r="B21" s="43" t="inlineStr">
-        <is>
-          <t>rm_scm_fru_chk</t>
-        </is>
-      </c>
-      <c r="C21" s="43" t="inlineStr">
-        <is>
-          <t>Check DC-SCM(M1120) FRU via RM</t>
-        </is>
-      </c>
-      <c r="D21" s="43" t="inlineStr">
-        <is>
-          <t>Pass - return 0; Fail - return 1</t>
-        </is>
-      </c>
-      <c r="E21" s="43" t="inlineStr">
-        <is>
-          <t>Check b oard s erial n umber</t>
-        </is>
-      </c>
-      <c r="F21" s="43" t="n"/>
-      <c r="G21" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="H21" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="I21" s="48" t="n"/>
-      <c r="J21" s="48" t="n"/>
-      <c r="L21" s="31" t="n"/>
-    </row>
-    <row r="22" ht="13.5" customHeight="1" s="80">
-      <c r="A22" s="76" t="n">
-        <v>20</v>
-      </c>
-      <c r="B22" s="43" t="inlineStr">
-        <is>
-          <t>rm_gp_fru_chk</t>
-        </is>
-      </c>
-      <c r="C22" s="43" t="inlineStr">
-        <is>
-          <t>Check GlacierPeak FRU via RM</t>
-        </is>
-      </c>
-      <c r="D22" s="43" t="inlineStr">
-        <is>
-          <t>Pass - return 0; Fail - return 1</t>
-        </is>
-      </c>
-      <c r="E22" s="43" t="inlineStr">
-        <is>
-          <t>Check b oard s erial n umber</t>
-        </is>
-      </c>
-      <c r="F22" s="43" t="n"/>
-      <c r="G22" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="H22" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="I22" s="48" t="n"/>
-      <c r="J22" s="48" t="n"/>
-      <c r="L22" s="31" t="n"/>
-    </row>
-    <row r="23" ht="53.25" customHeight="1" s="80">
-      <c r="A23" s="76" t="n">
-        <v>21</v>
-      </c>
-      <c r="B23" s="43" t="inlineStr">
-        <is>
-          <t>rm_relay_port_chk</t>
-        </is>
-      </c>
-      <c r="C23" s="43" t="inlineStr">
-        <is>
           <t>need to verify the status of the Relay Port Status - ON. Take CAUTION with turning ON state– delay for 20 second – then OFF state of the RELAY and OFF state – 20 seconds delay – ON state.</t>
         </is>
       </c>
-      <c r="D23" s="43" t="n"/>
-      <c r="E23" s="43" t="inlineStr">
+      <c r="D20" s="43" t="n"/>
+      <c r="E20" s="43" t="inlineStr">
         <is>
           <t>only applies to the master blade
 Feed1powerstatus = healthy
@@ -12687,113 +12423,113 @@
 powerdrawninwatt &lt; maxpowerinwatts</t>
         </is>
       </c>
-      <c r="F23" s="43" t="n"/>
+      <c r="F20" s="43" t="n"/>
+      <c r="G20" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="H20" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="I20" s="48" t="n"/>
+      <c r="J20" s="48" t="n"/>
+      <c r="L20" s="31" t="n"/>
+    </row>
+    <row r="21" ht="13.5" customHeight="1" s="80">
+      <c r="A21" s="76" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="43" t="inlineStr">
+        <is>
+          <t>rm_power_reading_chk</t>
+        </is>
+      </c>
+      <c r="C21" s="43" t="n"/>
+      <c r="D21" s="43" t="n"/>
+      <c r="E21" s="43" t="inlineStr">
+        <is>
+          <t>only applies to the master blade</t>
+        </is>
+      </c>
+      <c r="F21" s="43" t="n"/>
+      <c r="G21" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="H21" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="I21" s="48" t="n"/>
+      <c r="J21" s="48" t="n"/>
+      <c r="L21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="40.5" customHeight="1" s="80">
+      <c r="A22" s="76" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" s="43" t="inlineStr">
+        <is>
+          <t>bios_dmidecode_fru_chk</t>
+        </is>
+      </c>
+      <c r="C22" s="43" t="inlineStr">
+        <is>
+          <t>Cross-checks dmidecode SMBIOS Type 1 (Product/System), Type 2 (Board), and Type 3 (Chassis) fields against the motherboard FRU (ipmitool fru print 0), using field-name mappings from bios_dmidecode_t1/t2/t3 config.</t>
+        </is>
+      </c>
+      <c r="D22" s="43" t="inlineStr">
+        <is>
+          <t>PASS only if every mapped field in all three checked SMBIOS types matches the corresponding FRU field exactly.</t>
+        </is>
+      </c>
+      <c r="E22" s="43" t="n"/>
+      <c r="F22" s="43" t="n"/>
+      <c r="G22" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="H22" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="I22" s="48" t="n"/>
+      <c r="J22" s="48" t="n"/>
+      <c r="L22" s="31" t="n"/>
+    </row>
+    <row r="23" ht="40.5" customHeight="1" s="80">
+      <c r="A23" s="76" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" s="43" t="inlineStr">
+        <is>
+          <t>bmc_sku_info_chk</t>
+        </is>
+      </c>
+      <c r="C23" s="43" t="inlineStr">
+        <is>
+          <t>Check BMC SKU JSON information to ensure correct versioning and system functionality. If a mismatch is detected, an automatic upgrade will be performed.</t>
+        </is>
+      </c>
+      <c r="D23" s="43" t="inlineStr">
+        <is>
+          <t>Pass - match; Fail - mismatch</t>
+        </is>
+      </c>
+      <c r="E23" s="43" t="inlineStr">
+        <is>
+          <t>Version check M1 - Check only M3/M5 Check and upgrade at Pretest. Check only at the other stations</t>
+        </is>
+      </c>
+      <c r="F23" s="43" t="inlineStr">
+        <is>
+          <t>[ Get version of below items ] Inventory ipmitool raw 0x36 0xd2 1 0x01 PowerCapping ipmitool raw 0x36 0xd2 3 0x01 FanTable ipmitool raw 0x36 0xd2 4 0x01 SDRGenerator ipmitool raw 0x36 0xd2 6 0x01</t>
+        </is>
+      </c>
       <c r="G23" s="47" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H23" s="47" t="b">
         <v>0</v>
       </c>
       <c r="I23" s="48" t="n"/>
       <c r="J23" s="48" t="n"/>
-      <c r="L23" s="31" t="n"/>
-    </row>
-    <row r="24" ht="13.5" customHeight="1" s="80">
-      <c r="A24" s="76" t="n">
-        <v>22</v>
-      </c>
-      <c r="B24" s="43" t="inlineStr">
-        <is>
-          <t>rm_power_reading_chk</t>
-        </is>
-      </c>
-      <c r="C24" s="43" t="n"/>
-      <c r="D24" s="43" t="n"/>
-      <c r="E24" s="43" t="inlineStr">
-        <is>
-          <t>only applies to the master blade</t>
-        </is>
-      </c>
-      <c r="F24" s="43" t="n"/>
-      <c r="G24" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="H24" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="I24" s="48" t="n"/>
-      <c r="J24" s="48" t="n"/>
-      <c r="L24" s="31" t="n"/>
-    </row>
-    <row r="25" ht="40.5" customHeight="1" s="80">
-      <c r="A25" s="76" t="n">
-        <v>23</v>
-      </c>
-      <c r="B25" s="43" t="inlineStr">
-        <is>
-          <t>bios_dmidecode_fru_chk</t>
-        </is>
-      </c>
-      <c r="C25" s="43" t="inlineStr">
-        <is>
-          <t>Cross-checks dmidecode SMBIOS Type 1 (Product/System), Type 2 (Board), and Type 3 (Chassis) fields against the motherboard FRU (ipmitool fru print 0), using field-name mappings from bios_dmidecode_t1/t2/t3 config.</t>
-        </is>
-      </c>
-      <c r="D25" s="43" t="inlineStr">
-        <is>
-          <t>PASS only if every mapped field in all three checked SMBIOS types matches the corresponding FRU field exactly.</t>
-        </is>
-      </c>
-      <c r="E25" s="43" t="n"/>
-      <c r="F25" s="43" t="n"/>
-      <c r="G25" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="H25" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="I25" s="48" t="n"/>
-      <c r="J25" s="48" t="n"/>
-      <c r="L25" s="31" t="n"/>
-    </row>
-    <row r="26" ht="40.5" customHeight="1" s="80">
-      <c r="A26" s="76" t="n">
-        <v>24</v>
-      </c>
-      <c r="B26" s="43" t="inlineStr">
-        <is>
-          <t>bmc_sku_info_chk</t>
-        </is>
-      </c>
-      <c r="C26" s="43" t="inlineStr">
-        <is>
-          <t>Check BMC SKU JSON information to ensure correct versioning and system functionality. If a mismatch is detected, an automatic upgrade will be performed.</t>
-        </is>
-      </c>
-      <c r="D26" s="43" t="inlineStr">
-        <is>
-          <t>Pass - match; Fail - mismatch</t>
-        </is>
-      </c>
-      <c r="E26" s="43" t="inlineStr">
-        <is>
-          <t>Version check M1 - Check only M3/M5 Check and upgrade at Pretest. Check only at the other stations</t>
-        </is>
-      </c>
-      <c r="F26" s="43" t="inlineStr">
-        <is>
-          <t>[ Get version of below items ] Inventory ipmitool raw 0x36 0xd2 1 0x01 PowerCapping ipmitool raw 0x36 0xd2 3 0x01 FanTable ipmitool raw 0x36 0xd2 4 0x01 SDRGenerator ipmitool raw 0x36 0xd2 6 0x01</t>
-        </is>
-      </c>
-      <c r="G26" s="47" t="b">
-        <v>1</v>
-      </c>
-      <c r="H26" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="I26" s="48" t="n"/>
-      <c r="J26" s="48" t="n"/>
-      <c r="K26" s="42" t="inlineStr">
+      <c r="K23" s="42" t="inlineStr">
         <is>
           <t>Measuring Get Inventory Version:1.9.2, equal to 1.9.2
 Measuring Get PowerCapping Version:3.9.1, equal to 3.9.1
@@ -12803,33 +12539,130 @@
 [PASS] BMC SKU Info Check PASS.</t>
         </is>
       </c>
-      <c r="L26" s="31" t="inlineStr">
+      <c r="L23" s="31" t="inlineStr">
         <is>
           <t xml:space="preserve">Matches CRD (FanTable 4.9.2, Inventory 1.9.2, PowerCapping 3.9.1, SDRGenerator 6.9.2). CRD PCBA table still lists SDRGenerator 6.9.1 (System table says 6.9.2).
 </t>
         </is>
       </c>
     </row>
-    <row r="27" ht="16.5" customHeight="1" s="80">
+    <row r="24" ht="16.5" customHeight="1" s="80">
+      <c r="A24" s="76" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" s="43" t="inlineStr">
+        <is>
+          <t>bmc_retimer_fw_chk</t>
+        </is>
+      </c>
+      <c r="C24" s="43" t="inlineStr">
+        <is>
+          <t>Check the HPM retimer version</t>
+        </is>
+      </c>
+      <c r="D24" s="43" t="inlineStr">
+        <is>
+          <t>PASS if decoded version matches exactly.</t>
+        </is>
+      </c>
+      <c r="E24" s="43" t="n"/>
+      <c r="F24" s="43" t="n"/>
+      <c r="G24" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="H24" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="I24" s="48" t="n"/>
+      <c r="J24" s="48" t="n"/>
+      <c r="L24" s="31" t="n"/>
+    </row>
+    <row r="25" ht="27" customHeight="1" s="80">
+      <c r="A25" s="76" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" s="43" t="inlineStr">
+        <is>
+          <t>bmc_psu_fw_chk</t>
+        </is>
+      </c>
+      <c r="C25" s="43" t="inlineStr">
+        <is>
+          <t>Check the PSU version</t>
+        </is>
+      </c>
+      <c r="D25" s="43" t="inlineStr">
+        <is>
+          <t>PASS if current version equals expected. On mismatch, if upgrade is allowed, attempts psu upgrade.</t>
+        </is>
+      </c>
+      <c r="E25" s="43" t="n"/>
+      <c r="F25" s="43" t="n"/>
+      <c r="G25" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="H25" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="I25" s="48" t="n"/>
+      <c r="J25" s="48" t="n"/>
+      <c r="L25" s="31" t="n"/>
+    </row>
+    <row r="26" ht="13.5" customHeight="1" s="80">
+      <c r="A26" s="76" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" s="43" t="inlineStr">
+        <is>
+          <t>bmc_mac_chk</t>
+        </is>
+      </c>
+      <c r="C26" s="43" t="inlineStr">
+        <is>
+          <t>Checks the BMC's dedicated management NIC MAC address against SF.</t>
+        </is>
+      </c>
+      <c r="D26" s="43" t="inlineStr">
+        <is>
+          <t>PASS if ipmitool lan print 1 MAC equals SF.</t>
+        </is>
+      </c>
+      <c r="E26" s="43" t="n"/>
+      <c r="F26" s="43" t="n"/>
+      <c r="G26" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="H26" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="I26" s="48" t="n"/>
+      <c r="J26" s="48" t="n"/>
+      <c r="L26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="27" customHeight="1" s="80">
       <c r="A27" s="76" t="n">
         <v>25</v>
       </c>
       <c r="B27" s="43" t="inlineStr">
         <is>
-          <t>bmc_retimer_fw_chk</t>
+          <t>bmc_guid_chk</t>
         </is>
       </c>
       <c r="C27" s="43" t="inlineStr">
         <is>
-          <t>Check the HPM retimer version</t>
+          <t>Checks both the BMC "system GUID" (ipmitool mc guid) and "device GUID" (ipmitool raw 0x6 0x8) are not the all-ff placeholder value,.</t>
         </is>
       </c>
       <c r="D27" s="43" t="inlineStr">
         <is>
-          <t>PASS if decoded version matches exactly.</t>
-        </is>
-      </c>
-      <c r="E27" s="43" t="n"/>
+          <t>PASS if neither GUID contains ffffffffffff.</t>
+        </is>
+      </c>
+      <c r="E27" s="43" t="inlineStr">
+        <is>
+          <t>If GUID is invalid, automatically trigger GUID re-write.</t>
+        </is>
+      </c>
       <c r="F27" s="43" t="n"/>
       <c r="G27" s="47" t="b">
         <v>0</v>
@@ -12847,17 +12680,17 @@
       </c>
       <c r="B28" s="43" t="inlineStr">
         <is>
-          <t>bmc_psu_fw_chk</t>
+          <t>bmc_scm_boardid_chk</t>
         </is>
       </c>
       <c r="C28" s="43" t="inlineStr">
         <is>
-          <t>Check the PSU version</t>
+          <t>Reads the SCM board-revision ID via IPMI raw command and decodes specific bits to determine the board's build stage.</t>
         </is>
       </c>
       <c r="D28" s="43" t="inlineStr">
         <is>
-          <t>PASS if current version equals expected. On mismatch, if upgrade is allowed, attempts psu upgrade.</t>
+          <t>PASS if the decoded 3-bit board ID matches the code for the configured.</t>
         </is>
       </c>
       <c r="E28" s="43" t="n"/>
@@ -12872,36 +12705,46 @@
       <c r="J28" s="48" t="n"/>
       <c r="L28" s="31" t="n"/>
     </row>
-    <row r="29" ht="13.5" customHeight="1" s="80">
-      <c r="A29" s="76" t="n">
+    <row r="29" s="80">
+      <c r="A29" s="81" t="n">
         <v>27</v>
       </c>
-      <c r="B29" s="43" t="inlineStr">
-        <is>
-          <t>bmc_mac_chk</t>
-        </is>
-      </c>
-      <c r="C29" s="43" t="inlineStr">
-        <is>
-          <t>Checks the BMC's dedicated management NIC MAC address against SF.</t>
-        </is>
-      </c>
-      <c r="D29" s="43" t="inlineStr">
-        <is>
-          <t>PASS if ipmitool lan print 1 MAC equals SF.</t>
-        </is>
-      </c>
-      <c r="E29" s="43" t="n"/>
-      <c r="F29" s="43" t="n"/>
-      <c r="G29" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="H29" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="I29" s="48" t="n"/>
-      <c r="J29" s="48" t="n"/>
-      <c r="L29" s="31" t="n"/>
+      <c r="B29" s="82" t="inlineStr">
+        <is>
+          <t>bios_boardid_chk</t>
+        </is>
+      </c>
+      <c r="C29" s="82" t="inlineStr">
+        <is>
+          <t>Test BIOS board id reversion</t>
+        </is>
+      </c>
+      <c r="D29" s="82" t="inlineStr">
+        <is>
+          <t>The parsed current Board ID must match the expected ID for the given project and BIOS stage.</t>
+        </is>
+      </c>
+      <c r="E29" s="82" t="inlineStr">
+        <is>
+          <t>Revision ID in BoardID EEPROM has been defined in ADO#3462688 (EV: 01 00 | DV: 02 00 | PV: 03 00)</t>
+        </is>
+      </c>
+      <c r="F29" s="82" t="inlineStr">
+        <is>
+          <t>EVT CMD: ipmitool raw 0x36 0xf3 0x12 0xa6 0x02 0x00 0x18
+DVT CMD: ipmitool raw 0x36 0xf3 0x12 0xa6 0x02 0x00 0x12</t>
+        </is>
+      </c>
+      <c r="G29" s="87" t="b">
+        <v>0</v>
+      </c>
+      <c r="H29" s="87" t="b">
+        <v>0</v>
+      </c>
+      <c r="I29" s="88" t="n"/>
+      <c r="J29" s="88" t="n"/>
+      <c r="K29" s="89" t="n"/>
+      <c r="L29" s="90" t="n"/>
     </row>
     <row r="30" ht="27" customHeight="1" s="80">
       <c r="A30" s="76" t="n">
@@ -12909,24 +12752,20 @@
       </c>
       <c r="B30" s="43" t="inlineStr">
         <is>
-          <t>bmc_guid_chk</t>
+          <t>bmc_hpm_boardid_chk</t>
         </is>
       </c>
       <c r="C30" s="43" t="inlineStr">
         <is>
-          <t>Checks both the BMC "system GUID" (ipmitool mc guid) and "device GUID" (ipmitool raw 0x6 0x8) are not the all-ff placeholder value,.</t>
+          <t>Reads the HPM board-revision ID via IPMI raw command and decodes specific bits to determine the board's build stage.</t>
         </is>
       </c>
       <c r="D30" s="43" t="inlineStr">
         <is>
-          <t>PASS if neither GUID contains ffffffffffff.</t>
-        </is>
-      </c>
-      <c r="E30" s="43" t="inlineStr">
-        <is>
-          <t>If GUID is invalid, automatically trigger GUID re-write.</t>
-        </is>
-      </c>
+          <t>PASS if the decoded 3-bit board ID matches the code for the configured.</t>
+        </is>
+      </c>
+      <c r="E30" s="43" t="n"/>
       <c r="F30" s="43" t="n"/>
       <c r="G30" s="47" t="b">
         <v>0</v>
@@ -12938,36 +12777,46 @@
       <c r="J30" s="48" t="n"/>
       <c r="L30" s="31" t="n"/>
     </row>
-    <row r="31" ht="27" customHeight="1" s="80">
-      <c r="A31" s="76" t="n">
+    <row r="31" s="80">
+      <c r="A31" s="81" t="n">
         <v>29</v>
       </c>
-      <c r="B31" s="43" t="inlineStr">
-        <is>
-          <t>bmc_scm_boardid_chk</t>
-        </is>
-      </c>
-      <c r="C31" s="43" t="inlineStr">
-        <is>
-          <t>Reads the SCM board-revision ID via IPMI raw command and decodes specific bits to determine the board's build stage.</t>
-        </is>
-      </c>
-      <c r="D31" s="43" t="inlineStr">
-        <is>
-          <t>PASS if the decoded 3-bit board ID matches the code for the configured.</t>
-        </is>
-      </c>
-      <c r="E31" s="43" t="n"/>
-      <c r="F31" s="43" t="n"/>
-      <c r="G31" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="H31" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="I31" s="48" t="n"/>
-      <c r="J31" s="48" t="n"/>
-      <c r="L31" s="31" t="n"/>
+      <c r="B31" s="82" t="inlineStr">
+        <is>
+          <t>bmc_vr_chk</t>
+        </is>
+      </c>
+      <c r="C31" s="82" t="inlineStr">
+        <is>
+          <t>Verify BMC MB Voltage Regulator (VR) checksums.</t>
+        </is>
+      </c>
+      <c r="D31" s="82" t="inlineStr">
+        <is>
+          <t>All VR checksums match expected values from config file.</t>
+        </is>
+      </c>
+      <c r="E31" s="82" t="inlineStr">
+        <is>
+          <t>- Supports 1 or 2 expected VR checksum sets and auto-selects correct group.
+- Fails if config values or commands are missing.</t>
+        </is>
+      </c>
+      <c r="F31" s="82" t="inlineStr">
+        <is>
+          <t>[Get VR version]</t>
+        </is>
+      </c>
+      <c r="G31" s="87" t="b">
+        <v>0</v>
+      </c>
+      <c r="H31" s="87" t="b">
+        <v>0</v>
+      </c>
+      <c r="I31" s="88" t="n"/>
+      <c r="J31" s="88" t="n"/>
+      <c r="K31" s="89" t="n"/>
+      <c r="L31" s="90" t="n"/>
     </row>
     <row r="32" s="80">
       <c r="A32" s="81" t="n">
@@ -12975,133 +12824,20 @@
       </c>
       <c r="B32" s="82" t="inlineStr">
         <is>
-          <t>bios_boardid_chk</t>
+          <t>bmc_pdb_vr_chk</t>
         </is>
       </c>
       <c r="C32" s="82" t="inlineStr">
         <is>
-          <t>Test BIOS board id reversion</t>
+          <t>Verify BMC PDB Voltage Regulator (VR) checksums.</t>
         </is>
       </c>
       <c r="D32" s="82" t="inlineStr">
         <is>
-          <t>The parsed current Board ID must match the expected ID for the given project and BIOS stage.</t>
+          <t>All VR checksums match expected values from config file.</t>
         </is>
       </c>
       <c r="E32" s="82" t="inlineStr">
-        <is>
-          <t>Revision ID in BoardID EEPROM has been defined in ADO#3462688 (EV: 01 00 | DV: 02 00 | PV: 03 00)</t>
-        </is>
-      </c>
-      <c r="F32" s="82" t="inlineStr">
-        <is>
-          <t>EVT CMD: ipmitool raw 0x36 0xf3 0x12 0xa6 0x02 0x00 0x18
-DVT CMD: ipmitool raw 0x36 0xf3 0x12 0xa6 0x02 0x00 0x12</t>
-        </is>
-      </c>
-      <c r="G32" s="87" t="b">
-        <v>0</v>
-      </c>
-      <c r="H32" s="87" t="b">
-        <v>0</v>
-      </c>
-      <c r="I32" s="88" t="n"/>
-      <c r="J32" s="88" t="n"/>
-      <c r="K32" s="89" t="n"/>
-      <c r="L32" s="90" t="n"/>
-    </row>
-    <row r="33" ht="27" customHeight="1" s="80">
-      <c r="A33" s="76" t="n">
-        <v>31</v>
-      </c>
-      <c r="B33" s="43" t="inlineStr">
-        <is>
-          <t>bmc_hpm_boardid_chk</t>
-        </is>
-      </c>
-      <c r="C33" s="43" t="inlineStr">
-        <is>
-          <t>Reads the HPM board-revision ID via IPMI raw command and decodes specific bits to determine the board's build stage.</t>
-        </is>
-      </c>
-      <c r="D33" s="43" t="inlineStr">
-        <is>
-          <t>PASS if the decoded 3-bit board ID matches the code for the configured.</t>
-        </is>
-      </c>
-      <c r="E33" s="43" t="n"/>
-      <c r="F33" s="43" t="n"/>
-      <c r="G33" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="H33" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="I33" s="48" t="n"/>
-      <c r="J33" s="48" t="n"/>
-      <c r="L33" s="31" t="n"/>
-    </row>
-    <row r="34" s="80">
-      <c r="A34" s="81" t="n">
-        <v>32</v>
-      </c>
-      <c r="B34" s="82" t="inlineStr">
-        <is>
-          <t>bmc_vr_chk</t>
-        </is>
-      </c>
-      <c r="C34" s="82" t="inlineStr">
-        <is>
-          <t>Verify BMC MB Voltage Regulator (VR) checksums.</t>
-        </is>
-      </c>
-      <c r="D34" s="82" t="inlineStr">
-        <is>
-          <t>All VR checksums match expected values from config file.</t>
-        </is>
-      </c>
-      <c r="E34" s="82" t="inlineStr">
-        <is>
-          <t>- Supports 1 or 2 expected VR checksum sets and auto-selects correct group.
-- Fails if config values or commands are missing.</t>
-        </is>
-      </c>
-      <c r="F34" s="82" t="inlineStr">
-        <is>
-          <t>[Get VR version]</t>
-        </is>
-      </c>
-      <c r="G34" s="87" t="b">
-        <v>0</v>
-      </c>
-      <c r="H34" s="87" t="b">
-        <v>0</v>
-      </c>
-      <c r="I34" s="88" t="n"/>
-      <c r="J34" s="88" t="n"/>
-      <c r="K34" s="89" t="n"/>
-      <c r="L34" s="90" t="n"/>
-    </row>
-    <row r="35" s="80">
-      <c r="A35" s="81" t="n">
-        <v>33</v>
-      </c>
-      <c r="B35" s="82" t="inlineStr">
-        <is>
-          <t>bmc_pdb_vr_chk</t>
-        </is>
-      </c>
-      <c r="C35" s="82" t="inlineStr">
-        <is>
-          <t>Verify BMC PDB Voltage Regulator (VR) checksums.</t>
-        </is>
-      </c>
-      <c r="D35" s="82" t="inlineStr">
-        <is>
-          <t>All VR checksums match expected values from config file.</t>
-        </is>
-      </c>
-      <c r="E35" s="82" t="inlineStr">
         <is>
           <t>- Supports 1 or 2 expected VR checksum sets and auto-selects correct group.
 - Fails if config values or commands are missing.
@@ -13110,7 +12846,7 @@
 &gt;&gt;&gt;PDB 2nd source has VR checksum. Wait for commodity and command to support this function.&gt;&gt;&gt;BMC RD updated the checksum.</t>
         </is>
       </c>
-      <c r="F35" s="82" t="inlineStr">
+      <c r="F32" s="82" t="inlineStr">
         <is>
           <t>[Get VR version]
 1. Check the PDB is main source or second soure.
@@ -13122,185 +12858,185 @@
 ./xdp711_crc.sh -b 31 -s 0x10</t>
         </is>
       </c>
-      <c r="G35" s="87" t="b">
-        <v>0</v>
-      </c>
-      <c r="H35" s="87" t="b">
-        <v>0</v>
-      </c>
-      <c r="I35" s="88" t="n"/>
-      <c r="J35" s="88" t="n"/>
-      <c r="K35" s="89" t="n"/>
-      <c r="L35" s="90" t="n"/>
-    </row>
-    <row r="36" ht="27" customHeight="1" s="80">
-      <c r="A36" s="76" t="n">
+      <c r="G32" s="87" t="b">
+        <v>0</v>
+      </c>
+      <c r="H32" s="87" t="b">
+        <v>0</v>
+      </c>
+      <c r="I32" s="88" t="n"/>
+      <c r="J32" s="88" t="n"/>
+      <c r="K32" s="89" t="n"/>
+      <c r="L32" s="90" t="n"/>
+    </row>
+    <row r="33" ht="27" customHeight="1" s="80">
+      <c r="A33" s="76" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" s="43" t="inlineStr">
+        <is>
+          <t>bmc_selftest_chk</t>
+        </is>
+      </c>
+      <c r="C33" s="43" t="inlineStr">
+        <is>
+          <t>Checks the BMC's own IPMI self-test result code against the expected "all subsystems healthy" value.</t>
+        </is>
+      </c>
+      <c r="D33" s="43" t="inlineStr">
+        <is>
+          <t>PASS if ipmitool raw 0x06 0x04 (whitespace-stripped) equals getConfigValue('bmc_selftest_rest').</t>
+        </is>
+      </c>
+      <c r="E33" s="43" t="inlineStr">
+        <is>
+          <t>A self-test failure is a hard FAIL with no retry/upgrade path.</t>
+        </is>
+      </c>
+      <c r="F33" s="43" t="n"/>
+      <c r="G33" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="H33" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="I33" s="48" t="n"/>
+      <c r="J33" s="48" t="n"/>
+      <c r="L33" s="31" t="n"/>
+    </row>
+    <row r="34" ht="27" customHeight="1" s="80">
+      <c r="A34" s="76" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" s="43" t="inlineStr">
+        <is>
+          <t>bmc_func_test</t>
+        </is>
+      </c>
+      <c r="C34" s="43" t="inlineStr">
+        <is>
+          <t>Perform BMC functional test including Device ID, BMC version, self-test, chassis status, watchdog timer, and SDR check.</t>
+        </is>
+      </c>
+      <c r="D34" s="43" t="inlineStr">
+        <is>
+          <t>PASS if function test returns 0. On failure, greps LogFile.log for Failed entries and logs them alongside the detailed log.</t>
+        </is>
+      </c>
+      <c r="E34" s="43" t="n"/>
+      <c r="F34" s="43" t="n"/>
+      <c r="G34" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="H34" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="I34" s="48" t="n"/>
+      <c r="J34" s="48" t="n"/>
+      <c r="L34" s="31" t="n"/>
+    </row>
+    <row r="35" ht="27" customHeight="1" s="80">
+      <c r="A35" s="76" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" s="43" t="inlineStr">
+        <is>
+          <t>bmc_i2c_test</t>
+        </is>
+      </c>
+      <c r="C35" s="43" t="inlineStr">
+        <is>
+          <t>Runs an on-BMC I2C stress-test script against MB/PDB/FAN buses, uploaded and executed live over SSH, with a BMC-SEL check both before and after.</t>
+        </is>
+      </c>
+      <c r="D35" s="43" t="inlineStr">
+        <is>
+          <t>PASS if the uploaded script's log reports "Test successful" (no "Test Failed" / "No such file or directory" lines) AND the post-test BMC SEL check is clean.</t>
+        </is>
+      </c>
+      <c r="E35" s="43" t="inlineStr">
+        <is>
+          <t>SEL is explicitly cleared right before the I2C run so the post-run SEL check only reflects entries from this test.</t>
+        </is>
+      </c>
+      <c r="F35" s="43" t="n"/>
+      <c r="G35" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="H35" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="I35" s="48" t="n"/>
+      <c r="J35" s="48" t="n"/>
+      <c r="L35" s="31" t="n"/>
+    </row>
+    <row r="36" s="80">
+      <c r="A36" s="81" t="n">
         <v>34</v>
       </c>
-      <c r="B36" s="43" t="inlineStr">
-        <is>
-          <t>bmc_selftest_chk</t>
-        </is>
-      </c>
-      <c r="C36" s="43" t="inlineStr">
-        <is>
-          <t>Checks the BMC's own IPMI self-test result code against the expected "all subsystems healthy" value.</t>
-        </is>
-      </c>
-      <c r="D36" s="43" t="inlineStr">
-        <is>
-          <t>PASS if ipmitool raw 0x06 0x04 (whitespace-stripped) equals getConfigValue('bmc_selftest_rest').</t>
-        </is>
-      </c>
-      <c r="E36" s="43" t="inlineStr">
-        <is>
-          <t>A self-test failure is a hard FAIL with no retry/upgrade path.</t>
-        </is>
-      </c>
-      <c r="F36" s="43" t="n"/>
-      <c r="G36" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="H36" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="I36" s="48" t="n"/>
-      <c r="J36" s="48" t="n"/>
-      <c r="L36" s="31" t="n"/>
-    </row>
-    <row r="37" ht="27" customHeight="1" s="80">
-      <c r="A37" s="76" t="n">
-        <v>35</v>
-      </c>
-      <c r="B37" s="43" t="inlineStr">
-        <is>
-          <t>bmc_func_test</t>
-        </is>
-      </c>
-      <c r="C37" s="43" t="inlineStr">
-        <is>
-          <t>Perform BMC functional test including Device ID, BMC version, self-test, chassis status, watchdog timer, and SDR check.</t>
-        </is>
-      </c>
-      <c r="D37" s="43" t="inlineStr">
-        <is>
-          <t>PASS if function test returns 0. On failure, greps LogFile.log for Failed entries and logs them alongside the detailed log.</t>
-        </is>
-      </c>
-      <c r="E37" s="43" t="n"/>
-      <c r="F37" s="43" t="n"/>
-      <c r="G37" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="H37" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="I37" s="48" t="n"/>
-      <c r="J37" s="48" t="n"/>
-      <c r="L37" s="31" t="n"/>
-    </row>
-    <row r="38" ht="27" customHeight="1" s="80">
-      <c r="A38" s="76" t="n">
-        <v>36</v>
-      </c>
-      <c r="B38" s="43" t="inlineStr">
-        <is>
-          <t>bmc_i2c_test</t>
-        </is>
-      </c>
-      <c r="C38" s="43" t="inlineStr">
-        <is>
-          <t>Runs an on-BMC I2C stress-test script against MB/PDB/FAN buses, uploaded and executed live over SSH, with a BMC-SEL check both before and after.</t>
-        </is>
-      </c>
-      <c r="D38" s="43" t="inlineStr">
-        <is>
-          <t>PASS if the uploaded script's log reports "Test successful" (no "Test Failed" / "No such file or directory" lines) AND the post-test BMC SEL check is clean.</t>
-        </is>
-      </c>
-      <c r="E38" s="43" t="inlineStr">
-        <is>
-          <t>SEL is explicitly cleared right before the I2C run so the post-run SEL check only reflects entries from this test.</t>
-        </is>
-      </c>
-      <c r="F38" s="43" t="n"/>
-      <c r="G38" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="H38" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="I38" s="48" t="n"/>
-      <c r="J38" s="48" t="n"/>
-      <c r="L38" s="31" t="n"/>
-    </row>
-    <row r="39" s="80">
-      <c r="A39" s="81" t="n">
-        <v>37</v>
-      </c>
-      <c r="B39" s="82" t="inlineStr">
+      <c r="B36" s="82" t="inlineStr">
         <is>
           <t>bmc_i3c_test</t>
         </is>
       </c>
-      <c r="C39" s="82" t="inlineStr">
+      <c r="C36" s="82" t="inlineStr">
         <is>
           <t>Check bmc i3c test and sel log check only for Castle Peak</t>
         </is>
       </c>
-      <c r="D39" s="82" t="inlineStr">
+      <c r="D36" s="82" t="inlineStr">
         <is>
           <t>Pass - return 0; Fail - return 1
 Pass - return 0; Fail - return 1</t>
         </is>
       </c>
-      <c r="E39" s="82" t="inlineStr">
+      <c r="E36" s="82" t="inlineStr">
         <is>
           <t>&gt;&gt;&gt; Will be implemented in DVT.</t>
         </is>
       </c>
-      <c r="F39" s="82" t="inlineStr">
+      <c r="F36" s="82" t="inlineStr">
         <is>
           <t>apml_tool 1 --showtsiregister
 apml_tool 2 --showtsiregister</t>
         </is>
       </c>
-      <c r="G39" s="87" t="b">
-        <v>0</v>
-      </c>
-      <c r="H39" s="87" t="b">
-        <v>0</v>
-      </c>
-      <c r="I39" s="88" t="n"/>
-      <c r="J39" s="88" t="n"/>
-      <c r="K39" s="89" t="n"/>
-      <c r="L39" s="90" t="n"/>
-    </row>
-    <row r="40" s="80">
-      <c r="A40" s="81" t="n">
-        <v>38</v>
-      </c>
-      <c r="B40" s="82" t="inlineStr">
+      <c r="G36" s="87" t="b">
+        <v>0</v>
+      </c>
+      <c r="H36" s="87" t="b">
+        <v>0</v>
+      </c>
+      <c r="I36" s="88" t="n"/>
+      <c r="J36" s="88" t="n"/>
+      <c r="K36" s="89" t="n"/>
+      <c r="L36" s="90" t="n"/>
+    </row>
+    <row r="37" s="80">
+      <c r="A37" s="81" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" s="82" t="inlineStr">
         <is>
           <t>bmc_scm_cpu_uart_check</t>
         </is>
       </c>
-      <c r="C40" s="82" t="inlineStr">
+      <c r="C37" s="82" t="inlineStr">
         <is>
           <t>Check the UART0 path from SCM to CPU0 by validating SSH reachability through the chain: Host → BMC → Host. This ensures the SCM UART bus is working correctly by confirming that the BMC can relay communication back to the host system.</t>
         </is>
       </c>
-      <c r="D40" s="82" t="inlineStr">
+      <c r="D37" s="82" t="inlineStr">
         <is>
           <t>Pass : return 0 ; Fail : return 1</t>
         </is>
       </c>
-      <c r="E40" s="82" t="inlineStr">
+      <c r="E37" s="82" t="inlineStr">
         <is>
           <t>&gt;&gt;&gt; Will be implemented in DVT.</t>
         </is>
       </c>
-      <c r="F40" s="82" t="inlineStr">
+      <c r="F37" s="82" t="inlineStr">
         <is>
           <t>[Get BMC IP]
 ipmitool lan print | grep 'IP Address' | grep -v 'Source' | awk '{{print $4}}'
@@ -13308,27 +13044,27 @@
 nc {bmc_ip} {"22"} &lt; /dev/null &gt;/dev/null 2&gt;&amp;1 &amp;&amp; echo 0 || echo 1</t>
         </is>
       </c>
-      <c r="G40" s="87" t="b">
-        <v>0</v>
-      </c>
-      <c r="H40" s="87" t="b">
-        <v>0</v>
-      </c>
-      <c r="I40" s="88" t="n"/>
-      <c r="J40" s="88" t="n"/>
-      <c r="K40" s="89" t="n"/>
-      <c r="L40" s="90" t="n"/>
-    </row>
-    <row r="41" s="80">
-      <c r="A41" s="81" t="n">
-        <v>39</v>
-      </c>
-      <c r="B41" s="82" t="inlineStr">
+      <c r="G37" s="87" t="b">
+        <v>0</v>
+      </c>
+      <c r="H37" s="87" t="b">
+        <v>0</v>
+      </c>
+      <c r="I37" s="88" t="n"/>
+      <c r="J37" s="88" t="n"/>
+      <c r="K37" s="89" t="n"/>
+      <c r="L37" s="90" t="n"/>
+    </row>
+    <row r="38" s="80">
+      <c r="A38" s="81" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" s="82" t="inlineStr">
         <is>
           <t>bmc_cpld_security_chk</t>
         </is>
       </c>
-      <c r="C41" s="82" t="inlineStr">
+      <c r="C38" s="82" t="inlineStr">
         <is>
           <t>Check all SCM/HPM CPLD information status via bmc jtag raw command
 SCM CPLD Criteria:
@@ -13364,8 +13100,8 @@
 HPM CPLD CENTRAL LOCK check</t>
         </is>
       </c>
-      <c r="D41" s="82" t="n"/>
-      <c r="E41" s="82" t="inlineStr">
+      <c r="D38" s="82" t="n"/>
+      <c r="E38" s="82" t="inlineStr">
         <is>
           <t>- Follow C44AD to combine bmc_cpld_security_chk and bmc_hpm_cpld_security_chk.
 &gt;&gt;&gt;bmc_cpld_security_chk will be implemented in DVT Canary.
@@ -13373,7 +13109,7 @@
 &gt;&gt;&gt; Waiver for ship the Canary demand with CPLD Ping-pong mode. WAIVER 3622374</t>
         </is>
       </c>
-      <c r="F41" s="82">
+      <c r="F38" s="82">
         <f>======= [ SCM CPLD ] ========
 [Get SCM Pull JTAG_BMC_OE_N Low]
 ipmitool raw 0x30 0xe0 0 8 1 0
@@ -13450,16 +13186,122 @@
 jtag-rbpi -if /var/wcs/home/Read_Lock_Sector.stp -m fwupdate -t HPM -j /usr/share/cpld-config/configurations/cpld-config.json -o /xyz/openbmc_project/software/HPM_CPLD -debug</f>
         <v/>
       </c>
-      <c r="G41" s="87" t="b">
-        <v>0</v>
-      </c>
-      <c r="H41" s="87" t="b">
-        <v>0</v>
-      </c>
-      <c r="I41" s="88" t="n"/>
-      <c r="J41" s="88" t="n"/>
-      <c r="K41" s="89" t="n"/>
-      <c r="L41" s="90" t="n"/>
+      <c r="G38" s="87" t="b">
+        <v>0</v>
+      </c>
+      <c r="H38" s="87" t="b">
+        <v>0</v>
+      </c>
+      <c r="I38" s="88" t="n"/>
+      <c r="J38" s="88" t="n"/>
+      <c r="K38" s="89" t="n"/>
+      <c r="L38" s="90" t="n"/>
+    </row>
+    <row r="39" ht="27" customHeight="1" s="80">
+      <c r="A39" s="76" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" s="43" t="inlineStr">
+        <is>
+          <t>bmc_dedicate_chk</t>
+        </is>
+      </c>
+      <c r="C39" s="43" t="inlineStr">
+        <is>
+          <t>Verifies the BMC's dedicated management NIC is physically connected and DHCP-reachable by pinging it.</t>
+        </is>
+      </c>
+      <c r="D39" s="43" t="inlineStr">
+        <is>
+          <t>PASS if 5/5 pings succeed (or the RM-routed SSH connect succeeds).</t>
+        </is>
+      </c>
+      <c r="E39" s="43" t="inlineStr">
+        <is>
+          <t>M1/M3: via a direct ICMP ping
+M5: ping via an SSH-through-RM reachability check</t>
+        </is>
+      </c>
+      <c r="F39" s="43" t="n"/>
+      <c r="G39" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="H39" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="I39" s="48" t="n"/>
+      <c r="J39" s="48" t="n"/>
+      <c r="L39" s="31" t="n"/>
+    </row>
+    <row r="40" ht="27" customHeight="1" s="80">
+      <c r="A40" s="76" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" s="43" t="inlineStr">
+        <is>
+          <t>cpu_qty_check</t>
+        </is>
+      </c>
+      <c r="C40" s="43" t="inlineStr">
+        <is>
+          <t>Checks the number of populated CPU sockets against SF-expected count.</t>
+        </is>
+      </c>
+      <c r="D40" s="43" t="inlineStr">
+        <is>
+          <t>PASS if grep 'physical id' /proc/cpuinfo | sort | uniq | wc -l equals getConfigValue('cpu_qty').</t>
+        </is>
+      </c>
+      <c r="E40" s="43" t="inlineStr">
+        <is>
+          <t>Straightforward count check, no upgrade/self-heal path (CPU quantity isn't something firmware can fix).</t>
+        </is>
+      </c>
+      <c r="F40" s="43" t="n"/>
+      <c r="G40" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="H40" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="I40" s="48" t="n"/>
+      <c r="J40" s="48" t="n"/>
+      <c r="L40" s="31" t="n"/>
+    </row>
+    <row r="41" ht="27" customHeight="1" s="80">
+      <c r="A41" s="76" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" s="43" t="inlineStr">
+        <is>
+          <t>cpu_info_chk</t>
+        </is>
+      </c>
+      <c r="C41" s="43" t="inlineStr">
+        <is>
+          <t>Validate CPU information using dmidecode (type 4), comparing it with expected config values.</t>
+        </is>
+      </c>
+      <c r="D41" s="43" t="inlineStr">
+        <is>
+          <t>PASS if, per CPU, the Manufacturer/Version/Speed combo, Signature, and Core Count all measure equal to expected.</t>
+        </is>
+      </c>
+      <c r="E41" s="43" t="inlineStr">
+        <is>
+          <t>In L6 prj_level, all checks are informational-only.</t>
+        </is>
+      </c>
+      <c r="F41" s="43" t="n"/>
+      <c r="G41" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="H41" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="I41" s="48" t="n"/>
+      <c r="J41" s="48" t="n"/>
+      <c r="L41" s="31" t="n"/>
     </row>
     <row r="42" ht="27" customHeight="1" s="80">
       <c r="A42" s="76" t="n">
@@ -13467,23 +13309,22 @@
       </c>
       <c r="B42" s="43" t="inlineStr">
         <is>
-          <t>bmc_dedicate_chk</t>
+          <t>cpu_func_test</t>
         </is>
       </c>
       <c r="C42" s="43" t="inlineStr">
         <is>
-          <t>Verifies the BMC's dedicated management NIC is physically connected and DHCP-reachable by pinging it.</t>
+          <t>Runs a sequence of CPU feature functional tests (Cache, FPU, MMX, SSE, SSE2, SSE3, x64Cap, SMP, SMP-cache-coherency, AES, SSE4).</t>
         </is>
       </c>
       <c r="D42" s="43" t="inlineStr">
         <is>
-          <t>PASS if 5/5 pings succeed (or the RM-routed SSH connect succeeds).</t>
+          <t>PASS only if every sub-test in the sequence returns exit code 0; the function returns 1 immediately on the first sub-test failure.</t>
         </is>
       </c>
       <c r="E42" s="43" t="inlineStr">
         <is>
-          <t>M1/M3: via a direct ICMP ping
-M5: ping via an SSH-through-RM reachability check</t>
+          <t>Fail-fast means a Cache-test failure prevents FPU/MMX/etc.</t>
         </is>
       </c>
       <c r="F42" s="43" t="n"/>
@@ -13497,126 +13338,21 @@
       <c r="J42" s="48" t="n"/>
       <c r="L42" s="31" t="n"/>
     </row>
-    <row r="43" ht="27" customHeight="1" s="80">
-      <c r="A43" s="76" t="n">
+    <row r="43" s="80">
+      <c r="A43" s="81" t="n">
         <v>41</v>
       </c>
-      <c r="B43" s="43" t="inlineStr">
-        <is>
-          <t>cpu_qty_check</t>
-        </is>
-      </c>
-      <c r="C43" s="43" t="inlineStr">
-        <is>
-          <t>Checks the number of populated CPU sockets against SF-expected count.</t>
-        </is>
-      </c>
-      <c r="D43" s="43" t="inlineStr">
-        <is>
-          <t>PASS if grep 'physical id' /proc/cpuinfo | sort | uniq | wc -l equals getConfigValue('cpu_qty').</t>
-        </is>
-      </c>
-      <c r="E43" s="43" t="inlineStr">
-        <is>
-          <t>Straightforward count check, no upgrade/self-heal path (CPU quantity isn't something firmware can fix).</t>
-        </is>
-      </c>
-      <c r="F43" s="43" t="n"/>
-      <c r="G43" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="H43" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="I43" s="48" t="n"/>
-      <c r="J43" s="48" t="n"/>
-      <c r="L43" s="31" t="n"/>
-    </row>
-    <row r="44" ht="27" customHeight="1" s="80">
-      <c r="A44" s="76" t="n">
-        <v>42</v>
-      </c>
-      <c r="B44" s="43" t="inlineStr">
-        <is>
-          <t>cpu_info_chk</t>
-        </is>
-      </c>
-      <c r="C44" s="43" t="inlineStr">
-        <is>
-          <t>Validate CPU information using dmidecode (type 4), comparing it with expected config values.</t>
-        </is>
-      </c>
-      <c r="D44" s="43" t="inlineStr">
-        <is>
-          <t>PASS if, per CPU, the Manufacturer/Version/Speed combo, Signature, and Core Count all measure equal to expected.</t>
-        </is>
-      </c>
-      <c r="E44" s="43" t="inlineStr">
-        <is>
-          <t>In L6 prj_level, all checks are informational-only.</t>
-        </is>
-      </c>
-      <c r="F44" s="43" t="n"/>
-      <c r="G44" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="H44" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="I44" s="48" t="n"/>
-      <c r="J44" s="48" t="n"/>
-      <c r="L44" s="31" t="n"/>
-    </row>
-    <row r="45" ht="27" customHeight="1" s="80">
-      <c r="A45" s="76" t="n">
-        <v>43</v>
-      </c>
-      <c r="B45" s="43" t="inlineStr">
-        <is>
-          <t>cpu_func_test</t>
-        </is>
-      </c>
-      <c r="C45" s="43" t="inlineStr">
-        <is>
-          <t>Runs a sequence of CPU feature functional tests (Cache, FPU, MMX, SSE, SSE2, SSE3, x64Cap, SMP, SMP-cache-coherency, AES, SSE4).</t>
-        </is>
-      </c>
-      <c r="D45" s="43" t="inlineStr">
-        <is>
-          <t>PASS only if every sub-test in the sequence returns exit code 0; the function returns 1 immediately on the first sub-test failure.</t>
-        </is>
-      </c>
-      <c r="E45" s="43" t="inlineStr">
-        <is>
-          <t>Fail-fast means a Cache-test failure prevents FPU/MMX/etc.</t>
-        </is>
-      </c>
-      <c r="F45" s="43" t="n"/>
-      <c r="G45" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="H45" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="I45" s="48" t="n"/>
-      <c r="J45" s="48" t="n"/>
-      <c r="L45" s="31" t="n"/>
-    </row>
-    <row r="46" s="80">
-      <c r="A46" s="81" t="n">
-        <v>44</v>
-      </c>
-      <c r="B46" s="82" t="inlineStr">
+      <c r="B43" s="82" t="inlineStr">
         <is>
           <t>cpu_xgmi</t>
         </is>
       </c>
-      <c r="C46" s="82" t="inlineStr">
+      <c r="C43" s="82" t="inlineStr">
         <is>
           <t>This test verifies the status and configuration of AMD's XGMI (inter-socket high-speed link) functionality between CPUs.</t>
         </is>
       </c>
-      <c r="D46" s="82" t="inlineStr">
+      <c r="D43" s="82" t="inlineStr">
         <is>
           <t>The XGMI links between CPUs must be:
 - Detected successfully by the system
@@ -13624,39 +13360,39 @@
 - All links must pass without errors or degradation</t>
         </is>
       </c>
-      <c r="E46" s="82" t="inlineStr">
+      <c r="E43" s="82" t="inlineStr">
         <is>
           <t>&gt;&gt;&gt;Secured CPU has Bug#3771751, which plan to be resolved in 1A21.</t>
         </is>
       </c>
-      <c r="F46" s="82" t="inlineStr">
+      <c r="F43" s="82" t="inlineStr">
         <is>
           <t>./AMDXIO -i=0:,1:,2:,3: -xgmi -linkstatus</t>
         </is>
       </c>
-      <c r="G46" s="87" t="b">
-        <v>0</v>
-      </c>
-      <c r="H46" s="87" t="b">
-        <v>0</v>
-      </c>
-      <c r="I46" s="88" t="n"/>
-      <c r="J46" s="88" t="n"/>
-      <c r="K46" s="89" t="n"/>
-      <c r="L46" s="90" t="n"/>
-    </row>
-    <row r="47" s="80">
-      <c r="A47" s="81" t="n">
-        <v>45</v>
-      </c>
-      <c r="B47" s="82" t="inlineStr">
+      <c r="G43" s="87" t="b">
+        <v>0</v>
+      </c>
+      <c r="H43" s="87" t="b">
+        <v>0</v>
+      </c>
+      <c r="I43" s="88" t="n"/>
+      <c r="J43" s="88" t="n"/>
+      <c r="K43" s="89" t="n"/>
+      <c r="L43" s="90" t="n"/>
+    </row>
+    <row r="44" s="80">
+      <c r="A44" s="81" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" s="82" t="inlineStr">
         <is>
           <t>cpu_xgmi_bw</t>
         </is>
       </c>
-      <c r="C47" s="82" t="n"/>
-      <c r="D47" s="82" t="n"/>
-      <c r="E47" s="82" t="inlineStr">
+      <c r="C44" s="82" t="n"/>
+      <c r="D44" s="82" t="n"/>
+      <c r="E44" s="82" t="inlineStr">
         <is>
           <t>"cpu_xgmi" test failed with secured PC CPU.
 The Alternative method (MLC+APML tool) to to verify xGMI bandwidth/xGMI connection (1 cable-connected, 2 on-board trace)
@@ -13665,30 +13401,30 @@
 &gt;&gt;&gt;This test item can be removed when AMD provides a workable xgmi tool.</t>
         </is>
       </c>
-      <c r="F47" s="82" t="n"/>
-      <c r="G47" s="87" t="b">
-        <v>0</v>
-      </c>
-      <c r="H47" s="87" t="b">
-        <v>0</v>
-      </c>
-      <c r="I47" s="88" t="n"/>
-      <c r="J47" s="88" t="n"/>
-      <c r="K47" s="89" t="n"/>
-      <c r="L47" s="90" t="n"/>
-    </row>
-    <row r="48" s="80">
-      <c r="A48" s="81" t="n">
-        <v>46</v>
-      </c>
-      <c r="B48" s="82" t="inlineStr">
+      <c r="F44" s="82" t="n"/>
+      <c r="G44" s="87" t="b">
+        <v>0</v>
+      </c>
+      <c r="H44" s="87" t="b">
+        <v>0</v>
+      </c>
+      <c r="I44" s="88" t="n"/>
+      <c r="J44" s="88" t="n"/>
+      <c r="K44" s="89" t="n"/>
+      <c r="L44" s="90" t="n"/>
+    </row>
+    <row r="45" s="80">
+      <c r="A45" s="81" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" s="82" t="inlineStr">
         <is>
           <t>cpu_esmi_xgmi_link_speed</t>
         </is>
       </c>
-      <c r="C48" s="82" t="n"/>
-      <c r="D48" s="82" t="n"/>
-      <c r="E48" s="82" t="inlineStr">
+      <c r="C45" s="82" t="n"/>
+      <c r="D45" s="82" t="n"/>
+      <c r="E45" s="82" t="inlineStr">
         <is>
           <t>to verify the configured xGMI link speed
 &gt;&gt;&gt;Move cpu_esmi_xgmi_link_speed from L10 FAT to L11 Pretest since E-SMI work with L11 Canary CRD BIOS 1A20.
@@ -13697,17 +13433,102 @@
 &gt;&gt;&gt;This test item can be removed when AMD provides a workable xgmi tool.</t>
         </is>
       </c>
-      <c r="F48" s="82" t="n"/>
-      <c r="G48" s="87" t="b">
-        <v>0</v>
-      </c>
-      <c r="H48" s="87" t="b">
-        <v>0</v>
-      </c>
-      <c r="I48" s="88" t="n"/>
-      <c r="J48" s="88" t="n"/>
-      <c r="K48" s="89" t="n"/>
-      <c r="L48" s="90" t="n"/>
+      <c r="F45" s="82" t="n"/>
+      <c r="G45" s="87" t="b">
+        <v>0</v>
+      </c>
+      <c r="H45" s="87" t="b">
+        <v>0</v>
+      </c>
+      <c r="I45" s="88" t="n"/>
+      <c r="J45" s="88" t="n"/>
+      <c r="K45" s="89" t="n"/>
+      <c r="L45" s="90" t="n"/>
+    </row>
+    <row r="46" ht="27" customHeight="1" s="80">
+      <c r="A46" s="76" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" s="43" t="inlineStr">
+        <is>
+          <t>mem_info_chk</t>
+        </is>
+      </c>
+      <c r="C46" s="43" t="inlineStr">
+        <is>
+          <t>Checks each populated DIMM slot's Size/Speed/Manufacturer/Part-Number against SF-expected mem list, parsed from a filtered dmidecode -t 17 dump.</t>
+        </is>
+      </c>
+      <c r="D46" s="43" t="inlineStr">
+        <is>
+          <t>PASS if every slot's manf,size,speed,PN string matches the corresponding SF entry exactly.</t>
+        </is>
+      </c>
+      <c r="E46" s="43" t="n"/>
+      <c r="F46" s="43" t="n"/>
+      <c r="G46" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="H46" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="I46" s="48" t="n"/>
+      <c r="J46" s="48" t="n"/>
+      <c r="L46" s="31" t="n"/>
+    </row>
+    <row r="47" ht="13.5" customHeight="1" s="80">
+      <c r="A47" s="76" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" s="43" t="inlineStr">
+        <is>
+          <t>rm_mem_size_chk</t>
+        </is>
+      </c>
+      <c r="C47" s="43" t="n"/>
+      <c r="D47" s="43" t="n"/>
+      <c r="E47" s="43" t="n"/>
+      <c r="F47" s="43" t="n"/>
+      <c r="G47" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="H47" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="I47" s="48" t="n"/>
+      <c r="J47" s="48" t="n"/>
+      <c r="L47" s="31" t="n"/>
+    </row>
+    <row r="48" ht="27" customHeight="1" s="80">
+      <c r="A48" s="76" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" s="43" t="inlineStr">
+        <is>
+          <t>mem_size_chk</t>
+        </is>
+      </c>
+      <c r="C48" s="43" t="inlineStr">
+        <is>
+          <t>Cross-checks total populated-DIMM count and per-DIMM size (in the detected unit, MB or GB) against SF's mem_num/mem_size.</t>
+        </is>
+      </c>
+      <c r="D48" s="43" t="inlineStr">
+        <is>
+          <t>PASS if the count of DIMMs reporting the dominant size equals mem_num AND that size (converted to the detected unit) equals mem_size.</t>
+        </is>
+      </c>
+      <c r="E48" s="43" t="n"/>
+      <c r="F48" s="43" t="n"/>
+      <c r="G48" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="H48" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="I48" s="48" t="n"/>
+      <c r="J48" s="48" t="n"/>
+      <c r="L48" s="31" t="n"/>
     </row>
     <row r="49" ht="27" customHeight="1" s="80">
       <c r="A49" s="76" t="n">
@@ -13715,20 +13536,24 @@
       </c>
       <c r="B49" s="43" t="inlineStr">
         <is>
-          <t>mem_info_chk</t>
+          <t>mem_func_test</t>
         </is>
       </c>
       <c r="C49" s="43" t="inlineStr">
         <is>
-          <t>Checks each populated DIMM slot's Size/Speed/Manufacturer/Part-Number against SF-expected mem list, parsed from a filtered dmidecode -t 17 dump.</t>
+          <t>Runs a memory read/write functional stress test with swap disabled during the run.</t>
         </is>
       </c>
       <c r="D49" s="43" t="inlineStr">
         <is>
-          <t>PASS if every slot's manf,size,speed,PN string matches the corresponding SF entry exactly.</t>
-        </is>
-      </c>
-      <c r="E49" s="43" t="n"/>
+          <t>PASS if the test command's exit code is 0.</t>
+        </is>
+      </c>
+      <c r="E49" s="43" t="inlineStr">
+        <is>
+          <t>Maps specific nonzero return codes to human-readable error names in the failure log message.</t>
+        </is>
+      </c>
       <c r="F49" s="43" t="n"/>
       <c r="G49" s="47" t="b">
         <v>0</v>
@@ -13740,18 +13565,30 @@
       <c r="J49" s="48" t="n"/>
       <c r="L49" s="31" t="n"/>
     </row>
-    <row r="50" ht="13.5" customHeight="1" s="80">
+    <row r="50" ht="40.5" customHeight="1" s="80">
       <c r="A50" s="76" t="n">
         <v>48</v>
       </c>
       <c r="B50" s="43" t="inlineStr">
         <is>
-          <t>rm_mem_size_chk</t>
-        </is>
-      </c>
-      <c r="C50" s="43" t="n"/>
-      <c r="D50" s="43" t="n"/>
-      <c r="E50" s="43" t="n"/>
+          <t>pcie_manticore_chk</t>
+        </is>
+      </c>
+      <c r="C50" s="43" t="inlineStr">
+        <is>
+          <t>Check DC-SCM Manticore firmware version. If a mismatch is detected, an automatic upgrade will be performed.</t>
+        </is>
+      </c>
+      <c r="D50" s="43" t="inlineStr">
+        <is>
+          <t>Pass - match; Fail - mismatch</t>
+        </is>
+      </c>
+      <c r="E50" s="43" t="inlineStr">
+        <is>
+          <t>Automatically upgrade Manticore FW if version mismatch and upgrade flag is set. M1 - Check only M3/M5 - Check and upgrade at Pretest. Check only at the other stations</t>
+        </is>
+      </c>
       <c r="F50" s="43" t="n"/>
       <c r="G50" s="47" t="b">
         <v>0</v>
@@ -13763,26 +13600,32 @@
       <c r="J50" s="48" t="n"/>
       <c r="L50" s="31" t="n"/>
     </row>
-    <row r="51" ht="27" customHeight="1" s="80">
+    <row r="51" ht="135" customHeight="1" s="80">
       <c r="A51" s="76" t="n">
         <v>49</v>
       </c>
       <c r="B51" s="43" t="inlineStr">
         <is>
-          <t>mem_size_chk</t>
+          <t>pcie_manticore_provision_chk</t>
         </is>
       </c>
       <c r="C51" s="43" t="inlineStr">
         <is>
-          <t>Cross-checks total populated-DIMM count and per-DIMM size (in the detected unit, MB or GB) against SF's mem_num/mem_size.</t>
+          <t>One-time factory provisioning of the DC-SCM Manticore (Cerberus v2) security chip's certificate chain — Device ID, Root CA, and Intermediate CA certificates are fused into the chip via cerberus_utility importsignedcert.</t>
         </is>
       </c>
       <c r="D51" s="43" t="inlineStr">
         <is>
-          <t>PASS if the count of DIMMs reporting the dominant size equals mem_num AND that size (converted to the detected unit) equals mem_size.</t>
-        </is>
-      </c>
-      <c r="E51" s="43" t="n"/>
+          <t>PASS if the chip already shows a complete signed certificate chain, or if all three cerberus_fuse() calls succeed and a post-fuse is_provision check confirms completion.</t>
+        </is>
+      </c>
+      <c r="E51" s="43" t="inlineStr">
+        <is>
+          <t>- Security/identity-relevant, one-time step. Uses is_provision("Manticore") to skip entirely if already provisioned (idempotent). If the public key harvested from the chip (CSR) doesn't match what SF (the factory server / key-management system) has on file, it is treated as a "re-harvest" condition.
+- Certificate fusing order is Device ID (HWKey1, cert index 0/file index 1) → Root CA (HWKey3, cert index 1/file index 3) → Intermediate CA (HWKey2, cert index 2/file index 2). 
+- cerberus_fuse() treats IPMI return code 74 ("Certificate provisioning locked") as a soft-success, not a failure, since re-fusing an already-locked slot is expected on retries.</t>
+        </is>
+      </c>
       <c r="F51" s="43" t="n"/>
       <c r="G51" s="47" t="b">
         <v>0</v>
@@ -13794,28 +13637,28 @@
       <c r="J51" s="48" t="n"/>
       <c r="L51" s="31" t="n"/>
     </row>
-    <row r="52" ht="27" customHeight="1" s="80">
+    <row r="52" ht="67.5" customHeight="1" s="80">
       <c r="A52" s="76" t="n">
         <v>50</v>
       </c>
       <c r="B52" s="43" t="inlineStr">
         <is>
-          <t>mem_func_test</t>
+          <t>pcie_manticore_log_chk</t>
         </is>
       </c>
       <c r="C52" s="43" t="inlineStr">
         <is>
-          <t>Runs a memory read/write functional stress test with swap disabled during the run.</t>
+          <t>Reads the Manticore chip's debug log (cerberus_utility debuglogread), verifies the FW version recorded in the log matches expected, checks CS0/CS1 flash device consistency, scans for uncleared error codes since the last boot, and scans for unfiltered Warning/Error lines against a configurable skip-pattern list — clearing the log only after a full PASS.</t>
         </is>
       </c>
       <c r="D52" s="43" t="inlineStr">
         <is>
-          <t>PASS if the test command's exit code is 0.</t>
+          <t>PASS only if: (1) FW version found in log matches pcie_manticore_ver, (2) Port 1 CS0/CS1 vendor+device+capacity match each other, (3) no known bad error codes (0x7f001e0c/0d/0e, 0x7f001d05, 0x7f001d10) appear after the last-boot marker, (4) no unfiltered Warning/Error lines appear after the last-boot marker.</t>
         </is>
       </c>
       <c r="E52" s="43" t="inlineStr">
         <is>
-          <t>Maps specific nonzero return codes to human-readable error names in the failure log message.</t>
+          <t>If the log is completely empty of a FW-version line, it triggers an AC power cycle as a recovery action and still FAILs the current pass (log message: "please AC the server"). pcie_manticore_debuglog_skip config defines patterns to exclude from the Warning/Error scan</t>
         </is>
       </c>
       <c r="F52" s="43" t="n"/>
@@ -13835,17 +13678,17 @@
       </c>
       <c r="B53" s="43" t="inlineStr">
         <is>
-          <t>pcie_manticore_chk</t>
+          <t>pcie_tip_chk</t>
         </is>
       </c>
       <c r="C53" s="43" t="inlineStr">
         <is>
-          <t>Check DC-SCM Manticore firmware version. If a mismatch is detected, an automatic upgrade will be performed.</t>
+          <t>Check DC-SCM Hydra TIP firmware version. If a mismatch is detected, an automatic upgrade will be performed.</t>
         </is>
       </c>
       <c r="D53" s="43" t="inlineStr">
         <is>
-          <t>Pass - match; Fail - mismatch</t>
+          <t>Pass - match; Fail – mismatch</t>
         </is>
       </c>
       <c r="E53" s="43" t="inlineStr">
@@ -13864,30 +13707,28 @@
       <c r="J53" s="48" t="n"/>
       <c r="L53" s="31" t="n"/>
     </row>
-    <row r="54" ht="135" customHeight="1" s="80">
+    <row r="54" ht="40.5" customHeight="1" s="80">
       <c r="A54" s="76" t="n">
         <v>52</v>
       </c>
       <c r="B54" s="43" t="inlineStr">
         <is>
-          <t>pcie_manticore_provision_chk</t>
+          <t>pcie_tip_provision_chk</t>
         </is>
       </c>
       <c r="C54" s="43" t="inlineStr">
         <is>
-          <t>One-time factory provisioning of the DC-SCM Manticore (Cerberus v2) security chip's certificate chain — Device ID, Root CA, and Intermediate CA certificates are fused into the chip via cerberus_utility importsignedcert.</t>
+          <t>Same one-time provisioning flow as pcie_manticore_provision, but for the DC-SCM Hydra/TIP security chip (BMC-side security control introduced with M1120).</t>
         </is>
       </c>
       <c r="D54" s="43" t="inlineStr">
         <is>
-          <t>PASS if the chip already shows a complete signed certificate chain, or if all three cerberus_fuse() calls succeed and a post-fuse is_provision check confirms completion.</t>
+          <t>Identical logic/criteria to pcie_manticore_provision, keyed on component name "Hydra".</t>
         </is>
       </c>
       <c r="E54" s="43" t="inlineStr">
         <is>
-          <t>- Security/identity-relevant, one-time step. Uses is_provision("Manticore") to skip entirely if already provisioned (idempotent). If the public key harvested from the chip (CSR) doesn't match what SF (the factory server / key-management system) has on file, it is treated as a "re-harvest" condition.
-- Certificate fusing order is Device ID (HWKey1, cert index 0/file index 1) → Root CA (HWKey3, cert index 1/file index 3) → Intermediate CA (HWKey2, cert index 2/file index 2). 
-- cerberus_fuse() treats IPMI return code 74 ("Certificate provisioning locked") as a soft-success, not a failure, since re-fusing an already-locked slot is expected on retries.</t>
+          <t>Security/identity-relevant, one-time step. Structurally identical to Manticore provisioning, same 3-cert fuse order Device ID → Root CA → Intermediate CA).</t>
         </is>
       </c>
       <c r="F54" s="43" t="n"/>
@@ -13907,22 +13748,22 @@
       </c>
       <c r="B55" s="43" t="inlineStr">
         <is>
-          <t>pcie_manticore_log_chk</t>
+          <t>pcie_tip_log_chk</t>
         </is>
       </c>
       <c r="C55" s="43" t="inlineStr">
         <is>
-          <t>Reads the Manticore chip's debug log (cerberus_utility debuglogread), verifies the FW version recorded in the log matches expected, checks CS0/CS1 flash device consistency, scans for uncleared error codes since the last boot, and scans for unfiltered Warning/Error lines against a configurable skip-pattern list — clearing the log only after a full PASS.</t>
+          <t>Reads the Hydra/TIP chip's debug log (cerberus_utility debuglogread), verifies the FW version recorded in the log matches expected, checks CS0/CS1 flash device consistency, scans for uncleared error codes since the last boot, and scans for unfiltered Warning/Error lines against a configurable skip-pattern list — clearing the log only after a full PASS.</t>
         </is>
       </c>
       <c r="D55" s="43" t="inlineStr">
         <is>
-          <t>PASS only if: (1) FW version found in log matches pcie_manticore_ver, (2) Port 1 CS0/CS1 vendor+device+capacity match each other, (3) no known bad error codes (0x7f001e0c/0d/0e, 0x7f001d05, 0x7f001d10) appear after the last-boot marker, (4) no unfiltered Warning/Error lines appear after the last-boot marker.</t>
+          <t>PASS if: (1) the log contains a "Cerberus main flash" entry at all (else AC-cycle + FAIL), (2) main/recovery flash vendor+device+capacity match, (3) no unfiltered Warning/Error tagged lines appear after the last-boot marker.</t>
         </is>
       </c>
       <c r="E55" s="43" t="inlineStr">
         <is>
-          <t>If the log is completely empty of a FW-version line, it triggers an AC power cycle as a recovery action and still FAILs the current pass (log message: "please AC the server"). pcie_manticore_debuglog_skip config defines patterns to exclude from the Warning/Error scan</t>
+          <t>The Warning/Error scan here additionally requires the tag field (3rd |-delimited column) itself contain "Warning" or "Error", not just the whole line.</t>
         </is>
       </c>
       <c r="F55" s="43" t="n"/>
@@ -13936,30 +13777,26 @@
       <c r="J55" s="48" t="n"/>
       <c r="L55" s="31" t="n"/>
     </row>
-    <row r="56" ht="40.5" customHeight="1" s="80">
+    <row r="56" ht="27" customHeight="1" s="80">
       <c r="A56" s="76" t="n">
         <v>54</v>
       </c>
       <c r="B56" s="43" t="inlineStr">
         <is>
-          <t>pcie_tip_chk</t>
+          <t>fpga_gp_mac_chk</t>
         </is>
       </c>
       <c r="C56" s="43" t="inlineStr">
         <is>
-          <t>Check DC-SCM Hydra TIP firmware version. If a mismatch is detected, an automatic upgrade will be performed.</t>
+          <t>Checks the GlacierPeak's own network interface MAC address (read via ifconfig enm0 over SSH to the GP SoC) against mac[0].</t>
         </is>
       </c>
       <c r="D56" s="43" t="inlineStr">
         <is>
-          <t>Pass - match; Fail – mismatch</t>
-        </is>
-      </c>
-      <c r="E56" s="43" t="inlineStr">
-        <is>
-          <t>Automatically upgrade Manticore FW if version mismatch and upgrade flag is set. M1 - Check only M3/M5 - Check and upgrade at Pretest. Check only at the other stations</t>
-        </is>
-      </c>
+          <t>PASS if the parsed ether MAC equals getConfigValue('mac')[0] (uppercased, colon-stripped).</t>
+        </is>
+      </c>
+      <c r="E56" s="43" t="n"/>
       <c r="F56" s="43" t="n"/>
       <c r="G56" s="47" t="b">
         <v>0</v>
@@ -13971,28 +13808,28 @@
       <c r="J56" s="48" t="n"/>
       <c r="L56" s="31" t="n"/>
     </row>
-    <row r="57" ht="40.5" customHeight="1" s="80">
+    <row r="57" ht="135" customHeight="1" s="80">
       <c r="A57" s="76" t="n">
         <v>55</v>
       </c>
       <c r="B57" s="43" t="inlineStr">
         <is>
-          <t>pcie_tip_provision_chk</t>
+          <t>fpga_gp_status_chk</t>
         </is>
       </c>
       <c r="C57" s="43" t="inlineStr">
         <is>
-          <t>Same one-time provisioning flow as pcie_manticore_provision, but for the DC-SCM Hydra/TIP security chip (BMC-side security control introduced with M1120).</t>
+          <t>Runs fpgadiagnostics -dumpHealth (via a stage-appropriate SSH route: direct M3, RM-jumper M3, or RM-serial-proxy M5) and parses per-subsystem [FPGA-XXX] health lines, with specific waivers for known FPGA-NETWORK and FPGA-CONFIG warnings, and a one-time auto-reboot self-heal if the PCIe link status reads "WARNING" while in App mode.</t>
         </is>
       </c>
       <c r="D57" s="43" t="inlineStr">
         <is>
-          <t>Identical logic/criteria to pcie_manticore_provision, keyed on component name "Hydra".</t>
+          <t>PASS if no un-waived [FPGA-XXX] line fails its ] OK [ check.</t>
         </is>
       </c>
       <c r="E57" s="43" t="inlineStr">
         <is>
-          <t>Security/identity-relevant, one-time step. Structurally identical to Manticore provisioning, same 3-cert fuse order Device ID → Root CA → Intermediate CA).</t>
+          <t>Likely bug: in the FPGA-NETWORK-on-M5 branch, the failure path does isfail += 1 — but the function only ever initializes a variable named fail = 0, never isfail. If that exact branch is hit (M5 stage, FPGA-NETWORK reports non-OK, and the message isn't the specific waived "one or more network links down" string), this will raise NameError: name 'isfail' is not defined instead of cleanly failing the test. Also implements a reboot self-heal: if PCIe status is "WARNING" while FPGA is in App mode (config_status == "0") and no .reboot marker file exists yet for this unit, it touches the marker and issues reboot immediately rather than failing — the next run after reboot either clears (marker removed, PASS) or fails hard if the WARNING persists (marker already present).</t>
         </is>
       </c>
       <c r="F57" s="43" t="n"/>
@@ -14006,28 +13843,28 @@
       <c r="J57" s="48" t="n"/>
       <c r="L57" s="31" t="n"/>
     </row>
-    <row r="58" ht="67.5" customHeight="1" s="80">
+    <row r="58" ht="108" customHeight="1" s="80">
       <c r="A58" s="76" t="n">
         <v>56</v>
       </c>
       <c r="B58" s="43" t="inlineStr">
         <is>
-          <t>pcie_tip_log_chk</t>
+          <t>fpga_gp_fw_chk</t>
         </is>
       </c>
       <c r="C58" s="43" t="inlineStr">
         <is>
-          <t>Reads the Hydra/TIP chip's debug log (cerberus_utility debuglogread), verifies the FW version recorded in the log matches expected, checks CS0/CS1 flash device consistency, scans for uncleared error codes since the last boot, and scans for unfiltered Warning/Error lines against a configurable skip-pattern list — clearing the log only after a full PASS.</t>
+          <t>The most comprehensive FPGA firmware check in this station — validates Cerberus FW, Cyclone V PFM Device/Platform ID + image version, SoC PFM Device/Platform ID, SoC FIP firmware, SoC OS version, Linux kernel version, and FPGA diagnostic tools version, all read from a single batched SSH session to the GlacierPeak SoC console — with a coordinated multi-component upgrade sequence (in a specific vendor-mandated order) if any check fails and upgrades are allowed.</t>
         </is>
       </c>
       <c r="D58" s="43" t="inlineStr">
         <is>
-          <t>PASS if: (1) the log contains a "Cerberus main flash" entry at all (else AC-cycle + FAIL), (2) main/recovery flash vendor+device+capacity match, (3) no unfiltered Warning/Error tagged lines appear after the last-boot marker.</t>
+          <t>PASS only if every one of the 11 checked version/ID pairs matches (SoC OS version additionally requires the SoC's boot mode to be 0/PXE — a match while in a non-PXE bootmode is treated as needing a re-image and still counts as a failure needing upgrade).</t>
         </is>
       </c>
       <c r="E58" s="43" t="inlineStr">
         <is>
-          <t>The Warning/Error scan here additionally requires the tag field (3rd |-delimited column) itself contain "Warning" or "Error", not just the whole line.</t>
+          <t>Upgrade ordering follows a documented vendor spec (comment cites "M1195579 RevD A2051 GLACIER PEAK INTEGRATION REQUIREMENTS"): Cerberus FW → SoC PFM ID → Cyclone V PFM ID → SoC FIP → SoC OS Image → Cyclone V FPGA Image → Agilex FPGA APP/SoftNIC Image. SoC Linux Kernel version and SoC FPGA Tools version are explicitly flagged as non-upgradable — a mismatch there just fails, with no remediation path. A successful PFM/FIP/OS-image/App-image upgrade sets an is_reset flag that triggers gp_reset() (an AC-cycle-equivalent reset+power-cycle-and-wait) at the very end.</t>
         </is>
       </c>
       <c r="F58" s="43" t="n"/>
@@ -14041,26 +13878,30 @@
       <c r="J58" s="48" t="n"/>
       <c r="L58" s="31" t="n"/>
     </row>
-    <row r="59" ht="27" customHeight="1" s="80">
+    <row r="59" ht="148.5" customHeight="1" s="80">
       <c r="A59" s="76" t="n">
         <v>57</v>
       </c>
       <c r="B59" s="43" t="inlineStr">
         <is>
-          <t>fpga_gp_mac_chk</t>
+          <t>fpga_gp_softnic_ver_chk</t>
         </is>
       </c>
       <c r="C59" s="43" t="inlineStr">
         <is>
-          <t>Checks the GlacierPeak's own network interface MAC address (read via ifconfig enm0 over SSH to the GP SoC) against mac[0].</t>
+          <t>Checks the GlacierPeak Agilex FPGA SoftNIC image version by putting the GP into "golden mode" (boot mode 0) and reading recorded register values (role 65/101) from a status log left on the BMC filesystem.</t>
         </is>
       </c>
       <c r="D59" s="43" t="inlineStr">
         <is>
-          <t>PASS if the parsed ether MAC equals getConfigValue('mac')[0] (uppercased, colon-stripped).</t>
-        </is>
-      </c>
-      <c r="E59" s="43" t="n"/>
+          <t>PASS when the recorded role_id role_ver equals fpga_gp_softnic_ver. FAIL on SSH/SFTP failure, on failure to reach golden boot mode, or on version mismatch when upgrade is disabled/fails.</t>
+        </is>
+      </c>
+      <c r="E59" s="43" t="inlineStr">
+        <is>
+          <t>Multi-stage, stateful check keyed on the presence of /vol/data/persistent/tests/golden_status.txt on the BMC. If the log doesn't exist yet, the function uploads SoCFPGAGoldenTestSvc.service and fpga_golden_check.py to the BMC, switches GP into golden boot mode (cerberus_utility fpgasetbootmode 0), forces an AC cycle (RM rm_system_ac on M5, gs_pdb_ac_cycle otherwise) to make the mode take effect, and then returns 1 — meaning the first pass of this item after an image/config change always intentionally fails and needs a subsequent PRETEST re-run to actually validate the version. On version mismatch with fpga_gp_fw_upgrade TRUE, it calls _gp_fpga_softnic_upgrade() and then re-generates the golden log (also returning 1) rather than re-checking in the same pass.</t>
+        </is>
+      </c>
       <c r="F59" s="43" t="n"/>
       <c r="G59" s="47" t="b">
         <v>0</v>
@@ -14078,22 +13919,24 @@
       </c>
       <c r="B60" s="43" t="inlineStr">
         <is>
-          <t>fpga_gp_status_chk</t>
+          <t>fpga_gp_cerberus_provision_chk</t>
         </is>
       </c>
       <c r="C60" s="43" t="inlineStr">
         <is>
-          <t>Runs fpgadiagnostics -dumpHealth (via a stage-appropriate SSH route: direct M3, RM-jumper M3, or RM-serial-proxy M5) and parses per-subsystem [FPGA-XXX] health lines, with specific waivers for known FPGA-NETWORK and FPGA-CONFIG warnings, and a one-time auto-reboot self-heal if the PCIe link status reads "WARNING" while in App mode.</t>
+          <t>One-time provisioning of the GlacierPeak's own Cerberus security chip (distinct from Agilex slots above) — fuses Device ID/Root CA/Intermediate CA certs via a UART/SSH session directly into the GlacierPeak SoC console.</t>
         </is>
       </c>
       <c r="D60" s="43" t="inlineStr">
         <is>
-          <t>PASS if no un-waived [FPGA-XXX] line fails its ] OK [ check.</t>
+          <t>PASS if pcie_tool.is_provision("Cerberus") already shows complete, or if all three certs are fused successfully and a post-check confirms completion.</t>
         </is>
       </c>
       <c r="E60" s="43" t="inlineStr">
         <is>
-          <t>Likely bug: in the FPGA-NETWORK-on-M5 branch, the failure path does isfail += 1 — but the function only ever initializes a variable named fail = 0, never isfail. If that exact branch is hit (M5 stage, FPGA-NETWORK reports non-OK, and the message isn't the specific waived "one or more network links down" string), this will raise NameError: name 'isfail' is not defined instead of cleanly failing the test. Also implements a reboot self-heal: if PCIe status is "WARNING" while FPGA is in App mode (config_status == "0") and no .reboot marker file exists yet for this unit, it touches the marker and issues reboot immediately rather than failing — the next run after reboot either clears (marker removed, PASS) or fails hard if the WARNING persists (marker already present).</t>
+          <t>Two very different code paths: 
+- for prj_stage == "M5" it SFTP-uploads the three HWKEY .bin files to the BMC, then uses a shell command list over usb0 (10.235.100.0/31 point-to-point link) with scp -P 2200 to pull each key onto the GlacierPeak SoC and run cerberus_utility importsignedcert locally there — all three fuse commands (root CA idx 1, intermediate idx 2, device ID idx 0) run under a single rm_lock.
+- For other stages it uses a raw pxssh session direct to the GlacierPeak SoC on port 8295 (user admin/admin), with up to 2 retries and a 90s backoff between attempts if the SoC is "busy". HWKey files are deleted from the BMC after fusing in both paths.</t>
         </is>
       </c>
       <c r="F60" s="43" t="n"/>
@@ -14107,133 +13950,26 @@
       <c r="J60" s="48" t="n"/>
       <c r="L60" s="31" t="n"/>
     </row>
-    <row r="61" ht="108" customHeight="1" s="80">
+    <row r="61" ht="121.5" customHeight="1" s="80">
       <c r="A61" s="76" t="n">
         <v>59</v>
       </c>
       <c r="B61" s="43" t="inlineStr">
         <is>
-          <t>fpga_gp_fw_chk</t>
+          <t>fpga_gp_agilex_provision</t>
         </is>
       </c>
       <c r="C61" s="43" t="inlineStr">
         <is>
-          <t>The most comprehensive FPGA firmware check in this station — validates Cerberus FW, Cyclone V PFM Device/Platform ID + image version, SoC PFM Device/Platform ID, SoC FIP firmware, SoC OS version, Linux kernel version, and FPGA diagnostic tools version, all read from a single batched SSH session to the GlacierPeak SoC console — with a coordinated multi-component upgrade sequence (in a specific vendor-mandated order) if any check fails and upgrades are allowed.</t>
+          <t>One-time provisioning of the GlacierPeak Agilex FPGA's two certificate slots via the fpgasec tool — slot 0 for "Intel IPCS" (Agilex_mfg) and slot 1 for "Microsoft" (Agilex_msft), each independently skippable if already provisioned.</t>
         </is>
       </c>
       <c r="D61" s="43" t="inlineStr">
         <is>
-          <t>PASS only if every one of the 11 checked version/ID pairs matches (SoC OS version additionally requires the SoC's boot mode to be 0/PXE — a match while in a non-PXE bootmode is treated as needing a re-image and still counts as a failure needing upgrade).</t>
+          <t>PASS if both slot0 and slot1 report provisioned after the flow (checked via _is_gp_agilex_provision). FAIL if the fpgasec_{ver} tool is missing, cert files can't be obtained/uploaded, -setCertificate fails, or the final status check still shows either slot unprovisioned.</t>
         </is>
       </c>
       <c r="E61" s="43" t="inlineStr">
-        <is>
-          <t>Upgrade ordering follows a documented vendor spec (comment cites "M1195579 RevD A2051 GLACIER PEAK INTEGRATION REQUIREMENTS"): Cerberus FW → SoC PFM ID → Cyclone V PFM ID → SoC FIP → SoC OS Image → Cyclone V FPGA Image → Agilex FPGA APP/SoftNIC Image. SoC Linux Kernel version and SoC FPGA Tools version are explicitly flagged as non-upgradable — a mismatch there just fails, with no remediation path. A successful PFM/FIP/OS-image/App-image upgrade sets an is_reset flag that triggers gp_reset() (an AC-cycle-equivalent reset+power-cycle-and-wait) at the very end.</t>
-        </is>
-      </c>
-      <c r="F61" s="43" t="n"/>
-      <c r="G61" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="H61" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="I61" s="48" t="n"/>
-      <c r="J61" s="48" t="n"/>
-      <c r="L61" s="31" t="n"/>
-    </row>
-    <row r="62" ht="148.5" customHeight="1" s="80">
-      <c r="A62" s="76" t="n">
-        <v>60</v>
-      </c>
-      <c r="B62" s="43" t="inlineStr">
-        <is>
-          <t>fpga_gp_softnic_ver_chk</t>
-        </is>
-      </c>
-      <c r="C62" s="43" t="inlineStr">
-        <is>
-          <t>Checks the GlacierPeak Agilex FPGA SoftNIC image version by putting the GP into "golden mode" (boot mode 0) and reading recorded register values (role 65/101) from a status log left on the BMC filesystem.</t>
-        </is>
-      </c>
-      <c r="D62" s="43" t="inlineStr">
-        <is>
-          <t>PASS when the recorded role_id role_ver equals fpga_gp_softnic_ver. FAIL on SSH/SFTP failure, on failure to reach golden boot mode, or on version mismatch when upgrade is disabled/fails.</t>
-        </is>
-      </c>
-      <c r="E62" s="43" t="inlineStr">
-        <is>
-          <t>Multi-stage, stateful check keyed on the presence of /vol/data/persistent/tests/golden_status.txt on the BMC. If the log doesn't exist yet, the function uploads SoCFPGAGoldenTestSvc.service and fpga_golden_check.py to the BMC, switches GP into golden boot mode (cerberus_utility fpgasetbootmode 0), forces an AC cycle (RM rm_system_ac on M5, gs_pdb_ac_cycle otherwise) to make the mode take effect, and then returns 1 — meaning the first pass of this item after an image/config change always intentionally fails and needs a subsequent PRETEST re-run to actually validate the version. On version mismatch with fpga_gp_fw_upgrade TRUE, it calls _gp_fpga_softnic_upgrade() and then re-generates the golden log (also returning 1) rather than re-checking in the same pass.</t>
-        </is>
-      </c>
-      <c r="F62" s="43" t="n"/>
-      <c r="G62" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="H62" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="I62" s="48" t="n"/>
-      <c r="J62" s="48" t="n"/>
-      <c r="L62" s="31" t="n"/>
-    </row>
-    <row r="63" ht="135" customHeight="1" s="80">
-      <c r="A63" s="76" t="n">
-        <v>61</v>
-      </c>
-      <c r="B63" s="43" t="inlineStr">
-        <is>
-          <t>fpga_gp_cerberus_provision_chk</t>
-        </is>
-      </c>
-      <c r="C63" s="43" t="inlineStr">
-        <is>
-          <t>One-time provisioning of the GlacierPeak's own Cerberus security chip (distinct from Agilex slots above) — fuses Device ID/Root CA/Intermediate CA certs via a UART/SSH session directly into the GlacierPeak SoC console.</t>
-        </is>
-      </c>
-      <c r="D63" s="43" t="inlineStr">
-        <is>
-          <t>PASS if pcie_tool.is_provision("Cerberus") already shows complete, or if all three certs are fused successfully and a post-check confirms completion.</t>
-        </is>
-      </c>
-      <c r="E63" s="43" t="inlineStr">
-        <is>
-          <t>Two very different code paths: 
-- for prj_stage == "M5" it SFTP-uploads the three HWKEY .bin files to the BMC, then uses a shell command list over usb0 (10.235.100.0/31 point-to-point link) with scp -P 2200 to pull each key onto the GlacierPeak SoC and run cerberus_utility importsignedcert locally there — all three fuse commands (root CA idx 1, intermediate idx 2, device ID idx 0) run under a single rm_lock.
-- For other stages it uses a raw pxssh session direct to the GlacierPeak SoC on port 8295 (user admin/admin), with up to 2 retries and a 90s backoff between attempts if the SoC is "busy". HWKey files are deleted from the BMC after fusing in both paths.</t>
-        </is>
-      </c>
-      <c r="F63" s="43" t="n"/>
-      <c r="G63" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="H63" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="I63" s="48" t="n"/>
-      <c r="J63" s="48" t="n"/>
-      <c r="L63" s="31" t="n"/>
-    </row>
-    <row r="64" ht="121.5" customHeight="1" s="80">
-      <c r="A64" s="76" t="n">
-        <v>62</v>
-      </c>
-      <c r="B64" s="43" t="inlineStr">
-        <is>
-          <t>fpga_gp_agilex_provision</t>
-        </is>
-      </c>
-      <c r="C64" s="43" t="inlineStr">
-        <is>
-          <t>One-time provisioning of the GlacierPeak Agilex FPGA's two certificate slots via the fpgasec tool — slot 0 for "Intel IPCS" (Agilex_mfg) and slot 1 for "Microsoft" (Agilex_msft), each independently skippable if already provisioned.</t>
-        </is>
-      </c>
-      <c r="D64" s="43" t="inlineStr">
-        <is>
-          <t>PASS if both slot0 and slot1 report provisioned after the flow (checked via _is_gp_agilex_provision). FAIL if the fpgasec_{ver} tool is missing, cert files can't be obtained/uploaded, -setCertificate fails, or the final status check still shows either slot unprovisioned.</t>
-        </is>
-      </c>
-      <c r="E64" s="43" t="inlineStr">
         <is>
           <t>- Security/identity-relevant, one-time step, M3-only. 
 - Unlike the Manticore/TIP flow this checks each slot independently — a partially-provisioned board (e.g. slot0 done, slot1 not) only provisions the missing slot. 
@@ -14242,6 +13978,111 @@
 - After both slots are set, it resets the FPGA and sleeps 300s before the final confirmation check.</t>
         </is>
       </c>
+      <c r="F61" s="43" t="n"/>
+      <c r="G61" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="H61" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="I61" s="48" t="n"/>
+      <c r="J61" s="48" t="n"/>
+      <c r="L61" s="31" t="n"/>
+    </row>
+    <row r="62" ht="27" customHeight="1" s="80">
+      <c r="A62" s="76" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" s="43" t="inlineStr">
+        <is>
+          <t>bmc_fan_qty_chk</t>
+        </is>
+      </c>
+      <c r="C62" s="43" t="inlineStr">
+        <is>
+          <t>Checks the number of fans reporting an "OK" SDR state against SF's bmc_fan_qty.</t>
+        </is>
+      </c>
+      <c r="D62" s="43" t="inlineStr">
+        <is>
+          <t>PASS if ipmitool sdr elist | grep -E "^Fan" | grep -ic ok equals getConfigValue('bmc_fan_qty').</t>
+        </is>
+      </c>
+      <c r="E62" s="43" t="inlineStr">
+        <is>
+          <t>Simple count check; no self-heal (a missing/failed fan is a physical issue, not a firmware one).</t>
+        </is>
+      </c>
+      <c r="F62" s="43" t="n"/>
+      <c r="G62" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="H62" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="I62" s="48" t="n"/>
+      <c r="J62" s="48" t="n"/>
+      <c r="L62" s="31" t="n"/>
+    </row>
+    <row r="63" ht="40.5" customHeight="1" s="80">
+      <c r="A63" s="76" t="n">
+        <v>61</v>
+      </c>
+      <c r="B63" s="43" t="inlineStr">
+        <is>
+          <t>bmc_fan_speed_chk</t>
+        </is>
+      </c>
+      <c r="C63" s="43" t="inlineStr">
+        <is>
+          <t>Sweeps fan duty cycle through 100%/50%/30% (100% skipped at M1 stage per an old thermal-noise waiver) and checks each fan's measured RPM against inlet/outlet min/max bounds for the detected fan vendor.</t>
+        </is>
+      </c>
+      <c r="D63" s="43" t="inlineStr">
+        <is>
+          <t>PASS if every fan's RPM at every tested duty point falls within its vendor-specific inlet/outlet min/max range.</t>
+        </is>
+      </c>
+      <c r="E63" s="43" t="inlineStr">
+        <is>
+          <t>After the sweep, fan mode is forced back to auto unconditionally, and at M1 stage specifically it's additionally set to a fixed 50% manual.</t>
+        </is>
+      </c>
+      <c r="F63" s="43" t="n"/>
+      <c r="G63" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="H63" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="I63" s="48" t="n"/>
+      <c r="J63" s="48" t="n"/>
+      <c r="L63" s="31" t="n"/>
+    </row>
+    <row r="64" ht="27" customHeight="1" s="80">
+      <c r="A64" s="76" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" s="43" t="inlineStr">
+        <is>
+          <t>storage_hdd_info_chk</t>
+        </is>
+      </c>
+      <c r="C64" s="43" t="inlineStr">
+        <is>
+          <t>Check SATA/NVMe disk info (model, size, firmware) consistency between DUT and config file.</t>
+        </is>
+      </c>
+      <c r="D64" s="43" t="inlineStr">
+        <is>
+          <t>Disk count matches config. Each disk's model, size, and firmware match expected values.</t>
+        </is>
+      </c>
+      <c r="E64" s="43" t="inlineStr">
+        <is>
+          <t>EMPTY slots in config are skipped. M3/M5 Check and upgrade at Pretest. Check only at the other stations .</t>
+        </is>
+      </c>
       <c r="F64" s="43" t="n"/>
       <c r="G64" s="47" t="b">
         <v>0</v>
@@ -14259,22 +14100,22 @@
       </c>
       <c r="B65" s="43" t="inlineStr">
         <is>
-          <t>bmc_fan_qty_chk</t>
+          <t>storage_nvme_quantity_chk</t>
         </is>
       </c>
       <c r="C65" s="43" t="inlineStr">
         <is>
-          <t>Checks the number of fans reporting an "OK" SDR state against SF's bmc_fan_qty.</t>
+          <t>Verify the total number of detected NVM E drives matches the expected quantity.</t>
         </is>
       </c>
       <c r="D65" s="43" t="inlineStr">
         <is>
-          <t>PASS if ipmitool sdr elist | grep -E "^Fan" | grep -ic ok equals getConfigValue('bmc_fan_qty').</t>
+          <t>Pass - return 0; Fail - return 1</t>
         </is>
       </c>
       <c r="E65" s="43" t="inlineStr">
         <is>
-          <t>Simple count check; no self-heal (a missing/failed fan is a physical issue, not a firmware one).</t>
+          <t>M1 : expected count is determined by E1S2 or E1S4.</t>
         </is>
       </c>
       <c r="F65" s="43" t="n"/>
@@ -14288,30 +14129,26 @@
       <c r="J65" s="48" t="n"/>
       <c r="L65" s="31" t="n"/>
     </row>
-    <row r="66" ht="40.5" customHeight="1" s="80">
+    <row r="66" ht="13.5" customHeight="1" s="80">
       <c r="A66" s="76" t="n">
         <v>64</v>
       </c>
       <c r="B66" s="43" t="inlineStr">
         <is>
-          <t>bmc_fan_speed_chk</t>
+          <t>storage_hdd_func_test</t>
         </is>
       </c>
       <c r="C66" s="43" t="inlineStr">
         <is>
-          <t>Sweeps fan duty cycle through 100%/50%/30% (100% skipped at M1 stage per an old thermal-noise waiver) and checks each fan's measured RPM against inlet/outlet min/max bounds for the detected fan vendor.</t>
+          <t>Perform random read/write test on all HDDs and NVMEs.</t>
         </is>
       </c>
       <c r="D66" s="43" t="inlineStr">
         <is>
-          <t>PASS if every fan's RPM at every tested duty point falls within its vendor-specific inlet/outlet min/max range.</t>
-        </is>
-      </c>
-      <c r="E66" s="43" t="inlineStr">
-        <is>
-          <t>After the sweep, fan mode is forced back to auto unconditionally, and at M1 stage specifically it's additionally set to a fixed 50% manual.</t>
-        </is>
-      </c>
+          <t>Pass - return 0; Fail - return 1</t>
+        </is>
+      </c>
+      <c r="E66" s="43" t="n"/>
       <c r="F66" s="43" t="n"/>
       <c r="G66" s="47" t="b">
         <v>0</v>
@@ -14323,30 +14160,26 @@
       <c r="J66" s="48" t="n"/>
       <c r="L66" s="31" t="n"/>
     </row>
-    <row r="67" ht="27" customHeight="1" s="80">
+    <row r="67" ht="40.5" customHeight="1" s="80">
       <c r="A67" s="76" t="n">
         <v>65</v>
       </c>
       <c r="B67" s="43" t="inlineStr">
         <is>
-          <t>storage_hdd_info_chk</t>
+          <t>storage_nvme_smart_chk</t>
         </is>
       </c>
       <c r="C67" s="43" t="inlineStr">
         <is>
-          <t>Check SATA/NVMe disk info (model, size, firmware) consistency between DUT and config file.</t>
+          <t>Check NVMe SMART log parameters to ensure disk health is within acceptable thresholds.</t>
         </is>
       </c>
       <c r="D67" s="43" t="inlineStr">
         <is>
-          <t>Disk count matches config. Each disk's model, size, and firmware match expected values.</t>
-        </is>
-      </c>
-      <c r="E67" s="43" t="inlineStr">
-        <is>
-          <t>EMPTY slots in config are skipped. M3/M5 Check and upgrade at Pretest. Check only at the other stations .</t>
-        </is>
-      </c>
+          <t>All NVMe devices must meet: critical_warning == 0 temperature &lt; 70°C percentage_used &lt; 3% available_spare &gt;= 99% media_errors == 0 warning_temperature_time == 0</t>
+        </is>
+      </c>
+      <c r="E67" s="43" t="n"/>
       <c r="F67" s="43" t="n"/>
       <c r="G67" s="47" t="b">
         <v>0</v>
@@ -14364,22 +14197,22 @@
       </c>
       <c r="B68" s="43" t="inlineStr">
         <is>
-          <t>storage_nvme_quantity_chk</t>
+          <t>bmc_batvolt_chk</t>
         </is>
       </c>
       <c r="C68" s="43" t="inlineStr">
         <is>
-          <t>Verify the total number of detected NVM E drives matches the expected quantity.</t>
+          <t>Checks the RTC/CMOS battery voltage sensor reading against a configured lower bound.</t>
         </is>
       </c>
       <c r="D68" s="43" t="inlineStr">
         <is>
-          <t>Pass - return 0; Fail - return 1</t>
+          <t>PASS if ipmitool sdr elist | grep 'BAT' | awk '{print $9}' (as float) is &gt;= bmc_batvolt_lower_bound.</t>
         </is>
       </c>
       <c r="E68" s="43" t="inlineStr">
         <is>
-          <t>M1 : expected count is determined by E1S2 or E1S4.</t>
+          <t>FAILs explicitly if ipmitool can't detect the battery voltage sensor at all — distinguished from a low-but-present reading.</t>
         </is>
       </c>
       <c r="F68" s="43" t="n"/>
@@ -14393,26 +14226,30 @@
       <c r="J68" s="48" t="n"/>
       <c r="L68" s="31" t="n"/>
     </row>
-    <row r="69" ht="13.5" customHeight="1" s="80">
+    <row r="69" ht="27" customHeight="1" s="80">
       <c r="A69" s="76" t="n">
         <v>67</v>
       </c>
       <c r="B69" s="43" t="inlineStr">
         <is>
-          <t>storage_hdd_func_test</t>
+          <t>tpm_ver_chk</t>
         </is>
       </c>
       <c r="C69" s="43" t="inlineStr">
         <is>
-          <t>Perform random read/write test on all HDDs and NVMEs.</t>
+          <t>Checks the TPM's FIRMWARE_VERSION value against tpm_ver, upgrades and re-checks if mismatched and upgrade is allowed.</t>
         </is>
       </c>
       <c r="D69" s="43" t="inlineStr">
         <is>
-          <t>Pass - return 0; Fail - return 1</t>
-        </is>
-      </c>
-      <c r="E69" s="43" t="n"/>
+          <t>PASS if the parsed firmware version equals getConfigValue('tpm_ver').</t>
+        </is>
+      </c>
+      <c r="E69" s="43" t="inlineStr">
+        <is>
+          <t>On successful update, recursively re-check version.</t>
+        </is>
+      </c>
       <c r="F69" s="43" t="n"/>
       <c r="G69" s="47" t="b">
         <v>0</v>
@@ -14424,23 +14261,23 @@
       <c r="J69" s="48" t="n"/>
       <c r="L69" s="31" t="n"/>
     </row>
-    <row r="70" ht="40.5" customHeight="1" s="80">
+    <row r="70" ht="27" customHeight="1" s="80">
       <c r="A70" s="76" t="n">
         <v>68</v>
       </c>
       <c r="B70" s="43" t="inlineStr">
         <is>
-          <t>storage_nvme_smart_chk</t>
+          <t>tpm_qty_chk</t>
         </is>
       </c>
       <c r="C70" s="43" t="inlineStr">
         <is>
-          <t>Check NVMe SMART log parameters to ensure disk health is within acceptable thresholds.</t>
+          <t>Checks the number of detected TPM 2.0 devices against an internal expected count (self._tpm_num, a class attribute rather than an SF config value).</t>
         </is>
       </c>
       <c r="D70" s="43" t="inlineStr">
         <is>
-          <t>All NVMe devices must meet: critical_warning == 0 temperature &lt; 70°C percentage_used &lt; 3% available_spare &gt;= 99% media_errors == 0 warning_temperature_time == 0</t>
+          <t>PASS if ls /dev/tpm* | grep -v tpmrm | wc -l equals self._tpm_num.</t>
         </is>
       </c>
       <c r="E70" s="43" t="n"/>
@@ -14461,24 +14298,20 @@
       </c>
       <c r="B71" s="43" t="inlineStr">
         <is>
-          <t>bmc_batvolt_chk</t>
+          <t>tpm_func_test</t>
         </is>
       </c>
       <c r="C71" s="43" t="inlineStr">
         <is>
-          <t>Checks the RTC/CMOS battery voltage sensor reading against a configured lower bound.</t>
+          <t>Runs the TPM 2.0 full and not-full self-tests (eltt2 -t full / eltt2 -t not_full) and a "get value" sanity read (eltt2 -g).</t>
         </is>
       </c>
       <c r="D71" s="43" t="inlineStr">
         <is>
-          <t>PASS if ipmitool sdr elist | grep 'BAT' | awk '{print $9}' (as float) is &gt;= bmc_batvolt_lower_bound.</t>
-        </is>
-      </c>
-      <c r="E71" s="43" t="inlineStr">
-        <is>
-          <t>FAILs explicitly if ipmitool can't detect the battery voltage sensor at all — distinguished from a low-but-present reading.</t>
-        </is>
-      </c>
+          <t>PASS only if all three sub-commands (full selftest, not-full selftest, get-value) return exit code 0.</t>
+        </is>
+      </c>
+      <c r="E71" s="43" t="n"/>
       <c r="F71" s="43" t="n"/>
       <c r="G71" s="47" t="b">
         <v>0</v>
@@ -14490,28 +14323,28 @@
       <c r="J71" s="48" t="n"/>
       <c r="L71" s="31" t="n"/>
     </row>
-    <row r="72" ht="27" customHeight="1" s="80">
+    <row r="72" ht="13.5" customHeight="1" s="80">
       <c r="A72" s="76" t="n">
         <v>70</v>
       </c>
       <c r="B72" s="43" t="inlineStr">
         <is>
-          <t>tpm_ver_chk</t>
+          <t>uut_pic_test</t>
         </is>
       </c>
       <c r="C72" s="43" t="inlineStr">
         <is>
-          <t>Checks the TPM's FIRMWARE_VERSION value against tpm_ver, upgrades and re-checks if mismatched and upgrade is allowed.</t>
+          <t>Runs a PIC (Programmable Interrupt Controller) functional test command.</t>
         </is>
       </c>
       <c r="D72" s="43" t="inlineStr">
         <is>
-          <t>PASS if the parsed firmware version equals getConfigValue('tpm_ver').</t>
+          <t>PASS if self.cmd_lst['uut_test_pic'] returns exit code 0.</t>
         </is>
       </c>
       <c r="E72" s="43" t="inlineStr">
         <is>
-          <t>On successful update, recursively re-check version.</t>
+          <t>Minimal wrapper, no special edge cases.</t>
         </is>
       </c>
       <c r="F72" s="43" t="n"/>
@@ -14525,26 +14358,30 @@
       <c r="J72" s="48" t="n"/>
       <c r="L72" s="31" t="n"/>
     </row>
-    <row r="73" ht="27" customHeight="1" s="80">
+    <row r="73" ht="13.5" customHeight="1" s="80">
       <c r="A73" s="76" t="n">
         <v>71</v>
       </c>
       <c r="B73" s="43" t="inlineStr">
         <is>
-          <t>tpm_qty_chk</t>
+          <t>uut_hpet_test</t>
         </is>
       </c>
       <c r="C73" s="43" t="inlineStr">
         <is>
-          <t>Checks the number of detected TPM 2.0 devices against an internal expected count (self._tpm_num, a class attribute rather than an SF config value).</t>
+          <t>Runs an HPET (High Precision Event Timer) functional test command.</t>
         </is>
       </c>
       <c r="D73" s="43" t="inlineStr">
         <is>
-          <t>PASS if ls /dev/tpm* | grep -v tpmrm | wc -l equals self._tpm_num.</t>
-        </is>
-      </c>
-      <c r="E73" s="43" t="n"/>
+          <t>PASS if self.cmd_lst['uut_test_hpet'] returns exit code 0.</t>
+        </is>
+      </c>
+      <c r="E73" s="43" t="inlineStr">
+        <is>
+          <t>Minimal wrapper, structurally identical to uut_pic_test.</t>
+        </is>
+      </c>
       <c r="F73" s="43" t="n"/>
       <c r="G73" s="47" t="b">
         <v>0</v>
@@ -14556,169 +14393,68 @@
       <c r="J73" s="48" t="n"/>
       <c r="L73" s="31" t="n"/>
     </row>
-    <row r="74" ht="27" customHeight="1" s="80">
-      <c r="A74" s="76" t="n">
+    <row r="74" s="80">
+      <c r="A74" s="81" t="n">
         <v>72</v>
       </c>
-      <c r="B74" s="43" t="inlineStr">
-        <is>
-          <t>tpm_func_test</t>
-        </is>
-      </c>
-      <c r="C74" s="43" t="inlineStr">
-        <is>
-          <t>Runs the TPM 2.0 full and not-full self-tests (eltt2 -t full / eltt2 -t not_full) and a "get value" sanity read (eltt2 -g).</t>
-        </is>
-      </c>
-      <c r="D74" s="43" t="inlineStr">
-        <is>
-          <t>PASS only if all three sub-commands (full selftest, not-full selftest, get-value) return exit code 0.</t>
-        </is>
-      </c>
-      <c r="E74" s="43" t="n"/>
-      <c r="F74" s="43" t="n"/>
-      <c r="G74" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="H74" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="I74" s="48" t="n"/>
-      <c r="J74" s="48" t="n"/>
-      <c r="L74" s="31" t="n"/>
-    </row>
-    <row r="75" ht="13.5" customHeight="1" s="80">
-      <c r="A75" s="76" t="n">
-        <v>73</v>
-      </c>
-      <c r="B75" s="43" t="inlineStr">
-        <is>
-          <t>uut_pic_test</t>
-        </is>
-      </c>
-      <c r="C75" s="43" t="inlineStr">
-        <is>
-          <t>Runs a PIC (Programmable Interrupt Controller) functional test command.</t>
-        </is>
-      </c>
-      <c r="D75" s="43" t="inlineStr">
-        <is>
-          <t>PASS if self.cmd_lst['uut_test_pic'] returns exit code 0.</t>
-        </is>
-      </c>
-      <c r="E75" s="43" t="inlineStr">
-        <is>
-          <t>Minimal wrapper, no special edge cases.</t>
-        </is>
-      </c>
-      <c r="F75" s="43" t="n"/>
-      <c r="G75" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="H75" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="I75" s="48" t="n"/>
-      <c r="J75" s="48" t="n"/>
-      <c r="L75" s="31" t="n"/>
-    </row>
-    <row r="76" ht="13.5" customHeight="1" s="80">
-      <c r="A76" s="76" t="n">
-        <v>74</v>
-      </c>
-      <c r="B76" s="43" t="inlineStr">
-        <is>
-          <t>uut_hpet_test</t>
-        </is>
-      </c>
-      <c r="C76" s="43" t="inlineStr">
-        <is>
-          <t>Runs an HPET (High Precision Event Timer) functional test command.</t>
-        </is>
-      </c>
-      <c r="D76" s="43" t="inlineStr">
-        <is>
-          <t>PASS if self.cmd_lst['uut_test_hpet'] returns exit code 0.</t>
-        </is>
-      </c>
-      <c r="E76" s="43" t="inlineStr">
-        <is>
-          <t>Minimal wrapper, structurally identical to uut_pic_test.</t>
-        </is>
-      </c>
-      <c r="F76" s="43" t="n"/>
-      <c r="G76" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="H76" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="I76" s="48" t="n"/>
-      <c r="J76" s="48" t="n"/>
-      <c r="L76" s="31" t="n"/>
-    </row>
-    <row r="77" s="80">
-      <c r="A77" s="81" t="n">
-        <v>75</v>
-      </c>
-      <c r="B77" s="82" t="inlineStr">
+      <c r="B74" s="82" t="inlineStr">
         <is>
           <t>bios_cmos_test</t>
         </is>
       </c>
-      <c r="C77" s="82" t="inlineStr">
+      <c r="C74" s="82" t="inlineStr">
         <is>
           <t>Test the BIOS CMOS functionality by verifying the read/write capability of CMOS registers and checking battery and CMOS operation status.</t>
         </is>
       </c>
-      <c r="D77" s="82" t="inlineStr">
+      <c r="D74" s="82" t="inlineStr">
         <is>
           <t>Pass - return 0; Fail - return 1</t>
         </is>
       </c>
-      <c r="E77" s="82" t="inlineStr">
+      <c r="E74" s="82" t="inlineStr">
         <is>
           <t>&gt;&gt;&gt;MTE agreed to waive in EVT. ADO#2909063</t>
         </is>
       </c>
-      <c r="F77" s="82" t="inlineStr">
+      <c r="F74" s="82" t="inlineStr">
         <is>
           <t>[Execute CMOS test]
 CMOStest -d</t>
         </is>
       </c>
-      <c r="G77" s="87" t="b">
-        <v>0</v>
-      </c>
-      <c r="H77" s="87" t="b">
-        <v>0</v>
-      </c>
-      <c r="I77" s="88" t="n"/>
-      <c r="J77" s="88" t="n"/>
-      <c r="K77" s="89" t="n"/>
-      <c r="L77" s="90" t="n"/>
-    </row>
-    <row r="78" s="80">
-      <c r="A78" s="81" t="n">
-        <v>76</v>
-      </c>
-      <c r="B78" s="82" t="inlineStr">
+      <c r="G74" s="87" t="b">
+        <v>0</v>
+      </c>
+      <c r="H74" s="87" t="b">
+        <v>0</v>
+      </c>
+      <c r="I74" s="88" t="n"/>
+      <c r="J74" s="88" t="n"/>
+      <c r="K74" s="89" t="n"/>
+      <c r="L74" s="90" t="n"/>
+    </row>
+    <row r="75" s="80">
+      <c r="A75" s="81" t="n">
+        <v>73</v>
+      </c>
+      <c r="B75" s="82" t="inlineStr">
         <is>
           <t>ccr_switch_chk</t>
         </is>
       </c>
-      <c r="C78" s="82" t="inlineStr">
+      <c r="C75" s="82" t="inlineStr">
         <is>
           <t>Check and show switch config</t>
         </is>
       </c>
-      <c r="D78" s="82" t="inlineStr">
+      <c r="D75" s="82" t="inlineStr">
         <is>
           <t>Pass - return 0; Fail - return 1</t>
         </is>
       </c>
-      <c r="E78" s="82" t="n"/>
-      <c r="F78" s="82" t="inlineStr">
+      <c r="E75" s="82" t="n"/>
+      <c r="F75" s="82" t="inlineStr">
         <is>
           <t>[Get Switch Information]
 version_info: show version
@@ -14727,16 +14463,121 @@
 cable_status: show muxcable status</t>
         </is>
       </c>
-      <c r="G78" s="87" t="b">
-        <v>0</v>
-      </c>
-      <c r="H78" s="87" t="b">
-        <v>0</v>
-      </c>
-      <c r="I78" s="88" t="n"/>
-      <c r="J78" s="88" t="n"/>
-      <c r="K78" s="89" t="n"/>
-      <c r="L78" s="90" t="n"/>
+      <c r="G75" s="87" t="b">
+        <v>0</v>
+      </c>
+      <c r="H75" s="87" t="b">
+        <v>0</v>
+      </c>
+      <c r="I75" s="88" t="n"/>
+      <c r="J75" s="88" t="n"/>
+      <c r="K75" s="89" t="n"/>
+      <c r="L75" s="90" t="n"/>
+    </row>
+    <row r="76" ht="27" customHeight="1" s="80">
+      <c r="A76" s="76" t="n">
+        <v>74</v>
+      </c>
+      <c r="B76" s="43" t="inlineStr">
+        <is>
+          <t>bmc_sel_chk</t>
+        </is>
+      </c>
+      <c r="C76" s="43" t="inlineStr">
+        <is>
+          <t>V erif y BMC SEL (System Event Log) events during testing to ensure no unexpected events have occurred.</t>
+        </is>
+      </c>
+      <c r="D76" s="43" t="inlineStr">
+        <is>
+          <t>SEL event counts should not exceed the defined thresholds based on testing duration.</t>
+        </is>
+      </c>
+      <c r="E76" s="43" t="inlineStr">
+        <is>
+          <t>Fail log will be saved in project folder if abnormal events are detected.</t>
+        </is>
+      </c>
+      <c r="F76" s="43" t="n"/>
+      <c r="G76" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="H76" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="I76" s="48" t="n"/>
+      <c r="J76" s="48" t="n"/>
+      <c r="L76" s="31" t="n"/>
+    </row>
+    <row r="77" ht="27" customHeight="1" s="80">
+      <c r="A77" s="76" t="n">
+        <v>75</v>
+      </c>
+      <c r="B77" s="43" t="inlineStr">
+        <is>
+          <t>bmc_sdr_chk</t>
+        </is>
+      </c>
+      <c r="C77" s="43" t="inlineStr">
+        <is>
+          <t>Verify BMC Sensor Data Records (SDR) by checking sensor list output and filtering unexpected entries.</t>
+        </is>
+      </c>
+      <c r="D77" s="43" t="inlineStr">
+        <is>
+          <t>No unexpected or unmasked SDR entries found in BMCSDR.log.</t>
+        </is>
+      </c>
+      <c r="E77" s="43" t="inlineStr">
+        <is>
+          <t>Test fails if filtered output is not empty.</t>
+        </is>
+      </c>
+      <c r="F77" s="43" t="n"/>
+      <c r="G77" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="H77" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="I77" s="48" t="n"/>
+      <c r="J77" s="48" t="n"/>
+      <c r="L77" s="31" t="n"/>
+    </row>
+    <row r="78" ht="27" customHeight="1" s="80">
+      <c r="A78" s="76" t="n">
+        <v>76</v>
+      </c>
+      <c r="B78" s="43" t="inlineStr">
+        <is>
+          <t>uut_dmesg_chk</t>
+        </is>
+      </c>
+      <c r="C78" s="43" t="inlineStr">
+        <is>
+          <t>Check UUT dmesg log for unexpected error messages and record PCI device status.</t>
+        </is>
+      </c>
+      <c r="D78" s="43" t="inlineStr">
+        <is>
+          <t>No unmasked error messages found in dmesg and all expected messages are properly filtered.</t>
+        </is>
+      </c>
+      <c r="E78" s="43" t="inlineStr">
+        <is>
+          <t>Filter list (filter_list.csv) and error map (err_map.ini) are required for filtering and mapping errors.</t>
+        </is>
+      </c>
+      <c r="F78" s="43" t="n"/>
+      <c r="G78" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="H78" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="I78" s="48" t="n"/>
+      <c r="J78" s="48" t="n"/>
+      <c r="L78" s="31" t="n"/>
     </row>
     <row r="79" ht="27" customHeight="1" s="80">
       <c r="A79" s="76" t="n">
@@ -14744,24 +14585,20 @@
       </c>
       <c r="B79" s="43" t="inlineStr">
         <is>
-          <t>bmc_sel_chk</t>
+          <t>uut_syslog_chk</t>
         </is>
       </c>
       <c r="C79" s="43" t="inlineStr">
         <is>
-          <t>V erif y BMC SEL (System Event Log) events during testing to ensure no unexpected events have occurred.</t>
+          <t>Check and record UUT system log (syslog/messages) to ensure no unexpected errors.</t>
         </is>
       </c>
       <c r="D79" s="43" t="inlineStr">
         <is>
-          <t>SEL event counts should not exceed the defined thresholds based on testing duration.</t>
-        </is>
-      </c>
-      <c r="E79" s="43" t="inlineStr">
-        <is>
-          <t>Fail log will be saved in project folder if abnormal events are detected.</t>
-        </is>
-      </c>
+          <t>UUT syslog must not contain unmasked error patterns, excluding skip patterns. Log file must exist and contain no unfiltered critical errors.</t>
+        </is>
+      </c>
+      <c r="E79" s="43" t="n"/>
       <c r="F79" s="43" t="n"/>
       <c r="G79" s="47" t="b">
         <v>0</v>
@@ -14779,22 +14616,22 @@
       </c>
       <c r="B80" s="43" t="inlineStr">
         <is>
-          <t>bmc_sdr_chk</t>
+          <t>bmc_sel_clear</t>
         </is>
       </c>
       <c r="C80" s="43" t="inlineStr">
         <is>
-          <t>Verify BMC Sensor Data Records (SDR) by checking sensor list output and filtering unexpected entries.</t>
+          <t>Clear BMC System Event Log (SEL) and verify it is cleared correctly.</t>
         </is>
       </c>
       <c r="D80" s="43" t="inlineStr">
         <is>
-          <t>No unexpected or unmasked SDR entries found in BMCSDR.log.</t>
+          <t>SEL clear command executes successfully and log ID changes after clear.</t>
         </is>
       </c>
       <c r="E80" s="43" t="inlineStr">
         <is>
-          <t>Test fails if filtered output is not empty.</t>
+          <t>Logs SEL before clearing for traceability; verifies clear status by comparing log ID.</t>
         </is>
       </c>
       <c r="F80" s="43" t="n"/>
@@ -14808,134 +14645,33 @@
       <c r="J80" s="48" t="n"/>
       <c r="L80" s="31" t="n"/>
     </row>
-    <row r="81" ht="27" customHeight="1" s="80">
-      <c r="A81" s="76" t="n">
+    <row r="81" s="80">
+      <c r="A81" s="81" t="n">
         <v>79</v>
       </c>
-      <c r="B81" s="43" t="inlineStr">
-        <is>
-          <t>uut_dmesg_chk</t>
-        </is>
-      </c>
-      <c r="C81" s="43" t="inlineStr">
-        <is>
-          <t>Check UUT dmesg log for unexpected error messages and record PCI device status.</t>
-        </is>
-      </c>
-      <c r="D81" s="43" t="inlineStr">
-        <is>
-          <t>No unmasked error messages found in dmesg and all expected messages are properly filtered.</t>
-        </is>
-      </c>
-      <c r="E81" s="43" t="inlineStr">
-        <is>
-          <t>Filter list (filter_list.csv) and error map (err_map.ini) are required for filtering and mapping errors.</t>
-        </is>
-      </c>
-      <c r="F81" s="43" t="n"/>
-      <c r="G81" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="H81" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="I81" s="48" t="n"/>
-      <c r="J81" s="48" t="n"/>
-      <c r="L81" s="31" t="n"/>
-    </row>
-    <row r="82" ht="27" customHeight="1" s="80">
-      <c r="A82" s="76" t="n">
-        <v>80</v>
-      </c>
-      <c r="B82" s="43" t="inlineStr">
-        <is>
-          <t>uut_syslog_chk</t>
-        </is>
-      </c>
-      <c r="C82" s="43" t="inlineStr">
-        <is>
-          <t>Check and record UUT system log (syslog/messages) to ensure no unexpected errors.</t>
-        </is>
-      </c>
-      <c r="D82" s="43" t="inlineStr">
-        <is>
-          <t>UUT syslog must not contain unmasked error patterns, excluding skip patterns. Log file must exist and contain no unfiltered critical errors.</t>
-        </is>
-      </c>
-      <c r="E82" s="43" t="n"/>
-      <c r="F82" s="43" t="n"/>
-      <c r="G82" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="H82" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="I82" s="48" t="n"/>
-      <c r="J82" s="48" t="n"/>
-      <c r="L82" s="31" t="n"/>
-    </row>
-    <row r="83" ht="27" customHeight="1" s="80">
-      <c r="A83" s="76" t="n">
-        <v>81</v>
-      </c>
-      <c r="B83" s="43" t="inlineStr">
-        <is>
-          <t>bmc_sel_clear</t>
-        </is>
-      </c>
-      <c r="C83" s="43" t="inlineStr">
-        <is>
-          <t>Clear BMC System Event Log (SEL) and verify it is cleared correctly.</t>
-        </is>
-      </c>
-      <c r="D83" s="43" t="inlineStr">
-        <is>
-          <t>SEL clear command executes successfully and log ID changes after clear.</t>
-        </is>
-      </c>
-      <c r="E83" s="43" t="inlineStr">
-        <is>
-          <t>Logs SEL before clearing for traceability; verifies clear status by comparing log ID.</t>
-        </is>
-      </c>
-      <c r="F83" s="43" t="n"/>
-      <c r="G83" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="H83" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="I83" s="48" t="n"/>
-      <c r="J83" s="48" t="n"/>
-      <c r="L83" s="31" t="n"/>
-    </row>
-    <row r="84" s="80">
-      <c r="A84" s="81" t="n">
-        <v>82</v>
-      </c>
-      <c r="B84" s="82" t="inlineStr">
+      <c r="B81" s="82" t="inlineStr">
         <is>
           <t>pcie_manticore_reset_lock</t>
         </is>
       </c>
-      <c r="C84" s="82" t="inlineStr">
+      <c r="C81" s="82" t="inlineStr">
         <is>
           <t>Reset intrusion count and lock a Manticore PCIe device using Cerberus utility.</t>
         </is>
       </c>
-      <c r="D84" s="82" t="inlineStr">
+      <c r="D81" s="82" t="inlineStr">
         <is>
           <t>- Intrusion count and state reset successfully (validated by expected outputs).
 - Device locked successfully. Return 0 on success, 1 on failure.</t>
         </is>
       </c>
-      <c r="E84" s="82" t="inlineStr">
+      <c r="E81" s="82" t="inlineStr">
         <is>
           <t>- If device is already locked, manual TE intervention is required.
 - Device lock requires AC power cycle to take effect.</t>
         </is>
       </c>
-      <c r="F84" s="82" t="inlineStr">
+      <c r="F81" s="82" t="inlineStr">
         <is>
           <t>{CERBERUS_UTILITY} -e 40 msft getlockstatus
 {CERBERUS_UTILITY} -e 0x40 msft intrusiondetection
@@ -14945,43 +14681,43 @@
 {CERBERUS_UTILITY} -e 40 msft lockdevice</t>
         </is>
       </c>
-      <c r="G84" s="87" t="b">
-        <v>0</v>
-      </c>
-      <c r="H84" s="87" t="b">
-        <v>0</v>
-      </c>
-      <c r="I84" s="88" t="n"/>
-      <c r="J84" s="88" t="n"/>
-      <c r="K84" s="89" t="n"/>
-      <c r="L84" s="90" t="n"/>
-    </row>
-    <row r="85" s="80">
-      <c r="A85" s="81" t="n">
-        <v>83</v>
-      </c>
-      <c r="B85" s="82" t="inlineStr">
+      <c r="G81" s="87" t="b">
+        <v>0</v>
+      </c>
+      <c r="H81" s="87" t="b">
+        <v>0</v>
+      </c>
+      <c r="I81" s="88" t="n"/>
+      <c r="J81" s="88" t="n"/>
+      <c r="K81" s="89" t="n"/>
+      <c r="L81" s="90" t="n"/>
+    </row>
+    <row r="82" s="80">
+      <c r="A82" s="81" t="n">
+        <v>80</v>
+      </c>
+      <c r="B82" s="82" t="inlineStr">
         <is>
           <t>uut_poweroff_wakeup</t>
         </is>
       </c>
-      <c r="C85" s="82" t="inlineStr">
+      <c r="C82" s="82" t="inlineStr">
         <is>
           <t>Check poweroff log file</t>
         </is>
       </c>
-      <c r="D85" s="82" t="inlineStr">
+      <c r="D82" s="82" t="inlineStr">
         <is>
           <t>Pass - return 0 ; Fail - return 1</t>
         </is>
       </c>
-      <c r="E85" s="82" t="inlineStr">
+      <c r="E82" s="82" t="inlineStr">
         <is>
           <t>None
 &gt;&gt;&gt; This is AC cycle for above intrusion lock and below compstate/attestation test, which included in pcie_tip_pcd_chk and pcie_tip_cfm_chk.  All of the above test items will be skipped after the AC cycle to save testing time.</t>
         </is>
       </c>
-      <c r="F85" s="82" t="inlineStr">
+      <c r="F82" s="82" t="inlineStr">
         <is>
           <t>--- Check log POWEROFF_WAKEUP ---
 - Not present → set to POWEROFF_1
@@ -14996,37 +14732,140 @@
 - Return 0 (proceed to next test item)</t>
         </is>
       </c>
-      <c r="G85" s="87" t="b">
-        <v>0</v>
-      </c>
-      <c r="H85" s="87" t="b">
-        <v>0</v>
-      </c>
-      <c r="I85" s="88" t="n"/>
-      <c r="J85" s="88" t="n"/>
-      <c r="K85" s="89" t="n"/>
-      <c r="L85" s="90" t="n"/>
-    </row>
-    <row r="86" ht="27" customHeight="1" s="80">
+      <c r="G82" s="87" t="b">
+        <v>0</v>
+      </c>
+      <c r="H82" s="87" t="b">
+        <v>0</v>
+      </c>
+      <c r="I82" s="88" t="n"/>
+      <c r="J82" s="88" t="n"/>
+      <c r="K82" s="89" t="n"/>
+      <c r="L82" s="90" t="n"/>
+    </row>
+    <row r="83" ht="27" customHeight="1" s="80">
+      <c r="A83" s="76" t="n">
+        <v>81</v>
+      </c>
+      <c r="B83" s="43" t="inlineStr">
+        <is>
+          <t>bmc_synctime_upload</t>
+        </is>
+      </c>
+      <c r="C83" s="43" t="inlineStr">
+        <is>
+          <t>Upload NTP time sync config file (mtadams-ntp.conf) to BMC system to configure time synchronization.</t>
+        </is>
+      </c>
+      <c r="D83" s="43" t="inlineStr">
+        <is>
+          <t>PASS if the file upload (gs_tool_upload) succeeds.</t>
+        </is>
+      </c>
+      <c r="E83" s="43" t="n"/>
+      <c r="F83" s="43" t="n"/>
+      <c r="G83" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="H83" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="I83" s="48" t="n"/>
+      <c r="J83" s="48" t="n"/>
+      <c r="L83" s="31" t="n"/>
+    </row>
+    <row r="84" ht="27" customHeight="1" s="80">
+      <c r="A84" s="76" t="n">
+        <v>82</v>
+      </c>
+      <c r="B84" s="43" t="inlineStr">
+        <is>
+          <t>bios_load_default</t>
+        </is>
+      </c>
+      <c r="C84" s="43" t="inlineStr">
+        <is>
+          <t>The final item in the FFT flow — resets BIOS/CMOS settings to factory default via an IPMI OEM raw command to ensure a clean BIOS configuration.</t>
+        </is>
+      </c>
+      <c r="D84" s="43" t="inlineStr">
+        <is>
+          <t>PASS if ipmitool raw 0x00 0x08 0x05 0xa0 0x80 0x00 0x00 0x00 succeeds.</t>
+        </is>
+      </c>
+      <c r="E84" s="43" t="n"/>
+      <c r="F84" s="43" t="n"/>
+      <c r="G84" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="H84" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="I84" s="48" t="n"/>
+      <c r="J84" s="48" t="n"/>
+      <c r="L84" s="31" t="n"/>
+    </row>
+    <row r="85" ht="40.5" customHeight="1" s="80">
+      <c r="A85" s="76" t="n">
+        <v>83</v>
+      </c>
+      <c r="B85" s="64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pcie_tip_pcd_chk
+&gt;&gt;&gt;Has not been defined in CRD and disabled in DVT. </t>
+        </is>
+      </c>
+      <c r="C85" s="61" t="inlineStr">
+        <is>
+          <t>BMC TIP - PCD ID and platform check</t>
+        </is>
+      </c>
+      <c r="D85" s="61" t="inlineStr">
+        <is>
+          <t>Pass - return 0; Fail - return 1</t>
+        </is>
+      </c>
+      <c r="E85" s="61" t="inlineStr">
+        <is>
+          <t>- Only in FFT or FST stations will automatic TIP PCD update be triggered upon invalid PCD detection - After firmware update, the script will reset the BMC and retry fetching the PCD information</t>
+        </is>
+      </c>
+      <c r="F85" s="43" t="n"/>
+      <c r="G85" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="H85" s="47" t="b">
+        <v>0</v>
+      </c>
+      <c r="I85" s="48" t="n"/>
+      <c r="J85" s="48" t="n"/>
+      <c r="L85" s="31" t="n"/>
+    </row>
+    <row r="86" ht="81" customHeight="1" s="80">
       <c r="A86" s="76" t="n">
         <v>84</v>
       </c>
-      <c r="B86" s="43" t="inlineStr">
-        <is>
-          <t>bmc_synctime_upload</t>
-        </is>
-      </c>
-      <c r="C86" s="43" t="inlineStr">
-        <is>
-          <t>Upload NTP time sync config file (mtadams-ntp.conf) to BMC system to configure time synchronization.</t>
-        </is>
-      </c>
-      <c r="D86" s="43" t="inlineStr">
-        <is>
-          <t>PASS if the file upload (gs_tool_upload) succeeds.</t>
-        </is>
-      </c>
-      <c r="E86" s="43" t="n"/>
+      <c r="B86" s="64" t="inlineStr">
+        <is>
+          <t xml:space="preserve">pcie_tip_cfm_chk
+&gt;&gt;&gt;Has not been defined in CRD and disabled in DVT. </t>
+        </is>
+      </c>
+      <c r="C86" s="61" t="inlineStr">
+        <is>
+          <t>Get DC-SCM TIP Version ID and Platform ID</t>
+        </is>
+      </c>
+      <c r="D86" s="61" t="inlineStr">
+        <is>
+          <t>Pass - return 0; Fail - return 1</t>
+        </is>
+      </c>
+      <c r="E86" s="61" t="inlineStr">
+        <is>
+          <t>- PCD/CFM can only be updated when "No valid found". If DS-SCM is already active, need to clear PCD/CFM via HKMS first - CFM auto-update only triggers under FFT or FST station and when CFM is invalid - After firmware update, system will cold-reset BMC, wait for recovery, and do AC cycle to take effect - tip_cfm_components_chk(): If component attestation fails, will dump Cerberus debug log automatically</t>
+        </is>
+      </c>
       <c r="F86" s="43" t="n"/>
       <c r="G86" s="47" t="b">
         <v>0</v>
@@ -15038,115 +14877,12 @@
       <c r="J86" s="48" t="n"/>
       <c r="L86" s="31" t="n"/>
     </row>
-    <row r="87" ht="27" customHeight="1" s="80">
-      <c r="A87" s="76" t="n">
-        <v>85</v>
-      </c>
-      <c r="B87" s="43" t="inlineStr">
-        <is>
-          <t>bios_load_default</t>
-        </is>
-      </c>
-      <c r="C87" s="43" t="inlineStr">
-        <is>
-          <t>The final item in the FFT flow — resets BIOS/CMOS settings to factory default via an IPMI OEM raw command to ensure a clean BIOS configuration.</t>
-        </is>
-      </c>
-      <c r="D87" s="43" t="inlineStr">
-        <is>
-          <t>PASS if ipmitool raw 0x00 0x08 0x05 0xa0 0x80 0x00 0x00 0x00 succeeds.</t>
-        </is>
-      </c>
-      <c r="E87" s="43" t="n"/>
-      <c r="F87" s="43" t="n"/>
-      <c r="G87" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="H87" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="I87" s="48" t="n"/>
-      <c r="J87" s="48" t="n"/>
-      <c r="L87" s="31" t="n"/>
-    </row>
-    <row r="88" ht="40.5" customHeight="1" s="80">
-      <c r="A88" s="76" t="n">
-        <v>86</v>
-      </c>
-      <c r="B88" s="64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pcie_tip_pcd_chk
-&gt;&gt;&gt;Has not been defined in CRD and disabled in DVT. </t>
-        </is>
-      </c>
-      <c r="C88" s="61" t="inlineStr">
-        <is>
-          <t>BMC TIP - PCD ID and platform check</t>
-        </is>
-      </c>
-      <c r="D88" s="61" t="inlineStr">
-        <is>
-          <t>Pass - return 0; Fail - return 1</t>
-        </is>
-      </c>
-      <c r="E88" s="61" t="inlineStr">
-        <is>
-          <t>- Only in FFT or FST stations will automatic TIP PCD update be triggered upon invalid PCD detection - After firmware update, the script will reset the BMC and retry fetching the PCD information</t>
-        </is>
-      </c>
-      <c r="F88" s="43" t="n"/>
-      <c r="G88" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="H88" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="I88" s="48" t="n"/>
-      <c r="J88" s="48" t="n"/>
-      <c r="L88" s="31" t="n"/>
-    </row>
-    <row r="89" ht="81" customHeight="1" s="80">
-      <c r="A89" s="76" t="n">
-        <v>87</v>
-      </c>
-      <c r="B89" s="64" t="inlineStr">
-        <is>
-          <t xml:space="preserve">pcie_tip_cfm_chk
-&gt;&gt;&gt;Has not been defined in CRD and disabled in DVT. </t>
-        </is>
-      </c>
-      <c r="C89" s="61" t="inlineStr">
-        <is>
-          <t>Get DC-SCM TIP Version ID and Platform ID</t>
-        </is>
-      </c>
-      <c r="D89" s="61" t="inlineStr">
-        <is>
-          <t>Pass - return 0; Fail - return 1</t>
-        </is>
-      </c>
-      <c r="E89" s="61" t="inlineStr">
-        <is>
-          <t>- PCD/CFM can only be updated when "No valid found". If DS-SCM is already active, need to clear PCD/CFM via HKMS first - CFM auto-update only triggers under FFT or FST station and when CFM is invalid - After firmware update, system will cold-reset BMC, wait for recovery, and do AC cycle to take effect - tip_cfm_components_chk(): If component attestation fails, will dump Cerberus debug log automatically</t>
-        </is>
-      </c>
-      <c r="F89" s="43" t="n"/>
-      <c r="G89" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="H89" s="47" t="b">
-        <v>0</v>
-      </c>
-      <c r="I89" s="48" t="n"/>
-      <c r="J89" s="48" t="n"/>
-      <c r="L89" s="31" t="n"/>
-    </row>
-    <row r="90" ht="14.25" customHeight="1" s="80">
-      <c r="G90" s="30" t="n">
+    <row r="87" ht="14.25" customHeight="1" s="80">
+      <c r="G87" s="30" t="n">
         <v>1</v>
       </c>
-      <c r="H90" s="30" t="n"/>
-      <c r="I90" s="30" t="inlineStr">
+      <c r="H87" s="30" t="n"/>
+      <c r="I87" s="30" t="inlineStr">
         <is>
           <t>Hour1</t>
         </is>
